--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195C79ED-B489-45AE-AA1A-0FC1BBFEA41B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB79FCBB-32CB-4CF1-AA54-47A229A3C2F6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="847">
   <si>
     <t>UTK</t>
   </si>
@@ -258,21 +258,12 @@
     <t>248747147</t>
   </si>
   <si>
-    <t>260810-F00016277</t>
-  </si>
-  <si>
     <t>260812-F00009928</t>
   </si>
   <si>
-    <t>260814-W00008737</t>
-  </si>
-  <si>
     <t>260817-W00004129</t>
   </si>
   <si>
-    <t>260818-F00004888</t>
-  </si>
-  <si>
     <t>260818-W00008557</t>
   </si>
   <si>
@@ -294,15 +285,9 @@
     <t>260825-F00005152</t>
   </si>
   <si>
-    <t>260825-F00006332</t>
-  </si>
-  <si>
     <t>260825-F00012713-3</t>
   </si>
   <si>
-    <t>260826-F00011180</t>
-  </si>
-  <si>
     <t>260826-W00007114</t>
   </si>
   <si>
@@ -324,15 +309,9 @@
     <t>260829-F00003083</t>
   </si>
   <si>
-    <t>260829-F00004615</t>
-  </si>
-  <si>
     <t>260829-F00007105</t>
   </si>
   <si>
-    <t>260830-F00003867</t>
-  </si>
-  <si>
     <t>260830-W00002999</t>
   </si>
   <si>
@@ -573,9 +552,6 @@
     <t>260904-W00010076</t>
   </si>
   <si>
-    <t>260904-W00010492</t>
-  </si>
-  <si>
     <t>260904-W00010604</t>
   </si>
   <si>
@@ -627,9 +603,6 @@
     <t>260905-F00007879</t>
   </si>
   <si>
-    <t>260905-W00002193</t>
-  </si>
-  <si>
     <t>260905-W00003077</t>
   </si>
   <si>
@@ -666,9 +639,6 @@
     <t>260906-F00001225</t>
   </si>
   <si>
-    <t>260906-W00000312</t>
-  </si>
-  <si>
     <t>260906-W00004136</t>
   </si>
   <si>
@@ -726,9 +696,6 @@
     <t>260907-W00002701</t>
   </si>
   <si>
-    <t>260907-W00003138</t>
-  </si>
-  <si>
     <t>260907-W00003448</t>
   </si>
   <si>
@@ -1167,9 +1134,6 @@
     <t>NFD6-08-31-HS2G</t>
   </si>
   <si>
-    <t>NFD6-09-01-JNG3</t>
-  </si>
-  <si>
     <t>NFD6-09-01-MJSK</t>
   </si>
   <si>
@@ -1254,9 +1218,6 @@
     <t>NFD6-09-05-XHCT</t>
   </si>
   <si>
-    <t>NFD6-09-05-XWRZ</t>
-  </si>
-  <si>
     <t>NFD6-09-05-YDPZ</t>
   </si>
   <si>
@@ -1374,24 +1335,12 @@
     <t>248747147/1</t>
   </si>
   <si>
-    <t>6a9aa4b2c0fa1536b26fe0dc</t>
-  </si>
-  <si>
     <t>6a9acbbfc0fa1536b26fe740</t>
   </si>
   <si>
-    <t>6a9acb16c0fa1536b26fe70f</t>
-  </si>
-  <si>
-    <t>6a9acb16c0fa1536b26fe710</t>
-  </si>
-  <si>
     <t>6a9057bec0fa1536b26f388c</t>
   </si>
   <si>
-    <t>6a9abe63c0fa1536b26fe51b</t>
-  </si>
-  <si>
     <t>6a999dd4c0fa1536b26fd2c6</t>
   </si>
   <si>
@@ -1413,15 +1362,9 @@
     <t>6a9d893bc0fa1536b2700497</t>
   </si>
   <si>
-    <t>6a9a7939c0fa1536b26fd963</t>
-  </si>
-  <si>
     <t>6a998fe2c0fa1536b26fd17d</t>
   </si>
   <si>
-    <t>6a9aabbbc0fa1536b26fe213</t>
-  </si>
-  <si>
     <t>6a8ee6edc0fa1536b26f1afe</t>
   </si>
   <si>
@@ -1443,15 +1386,9 @@
     <t>6a9e7ae9c0fa1536b2700eb5</t>
   </si>
   <si>
-    <t>6a9aa580c0fa1536b26fe110</t>
-  </si>
-  <si>
     <t>6a9a8d3ac0fa1536b26fdd02</t>
   </si>
   <si>
-    <t>6a9980f0c0fa1536b26fcf21</t>
-  </si>
-  <si>
     <t>6a9a8d36c0fa1536b26fdcff</t>
   </si>
   <si>
@@ -1728,9 +1665,6 @@
     <t>6a9af0f5c0fa1536b26feadb</t>
   </si>
   <si>
-    <t>6a9af472c0fa1536b26feb18</t>
-  </si>
-  <si>
     <t>6a9af6cac0fa1536b26feb5c</t>
   </si>
   <si>
@@ -1800,12 +1734,6 @@
     <t>6a9c7ab3c0fa1536b26ffbbd</t>
   </si>
   <si>
-    <t>6a9bc88cc0fa1536b26fef1a</t>
-  </si>
-  <si>
-    <t>6a9bc88cc0fa1536b26fef1c</t>
-  </si>
-  <si>
     <t>6a9bd945c0fa1536b26ff1ba</t>
   </si>
   <si>
@@ -1845,12 +1773,6 @@
     <t>6a9d3062c0fa1536b26ffe77</t>
   </si>
   <si>
-    <t>6a9cc48cc0fa1536b26ffbdb</t>
-  </si>
-  <si>
-    <t>6a9cc48cc0fa1536b26ffbdc</t>
-  </si>
-  <si>
     <t>6a9d68b6c0fa1536b27002b2</t>
   </si>
   <si>
@@ -1923,9 +1845,6 @@
     <t>6a9e7ae9c0fa1536b2700ece</t>
   </si>
   <si>
-    <t>6a9e774ec0fa1536b2700d9b</t>
-  </si>
-  <si>
     <t>6a9e7bfcc0fa1536b2700eef</t>
   </si>
   <si>
@@ -2421,18 +2340,6 @@
     <t>202609042601856001</t>
   </si>
   <si>
-    <t>202609022601868301</t>
-  </si>
-  <si>
-    <t>202609022601868302</t>
-  </si>
-  <si>
-    <t>202609022601868303</t>
-  </si>
-  <si>
-    <t>202609022601868304</t>
-  </si>
-  <si>
     <t>202609072601864601</t>
   </si>
   <si>
@@ -2520,9 +2427,6 @@
     <t>202609072601887801</t>
   </si>
   <si>
-    <t>NFD6-09-05-XWRZ/1</t>
-  </si>
-  <si>
     <t>202609072601888401</t>
   </si>
   <si>
@@ -2662,6 +2566,9 @@
   </si>
   <si>
     <t>159995579543939398</t>
+  </si>
+  <si>
+    <t>K-915</t>
   </si>
 </sst>
 </file>
@@ -3015,7 +2922,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC11F24F-E222-443E-8401-2ECBA69A40D4}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:C445"/>
+  <dimension ref="A1:C426"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
@@ -3039,7 +2946,7 @@
         <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="C2" t="s">
         <v>67</v>
@@ -3050,7 +2957,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="C3" t="s">
         <v>47</v>
@@ -3061,7 +2968,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="C4" t="s">
         <v>47</v>
@@ -3072,7 +2979,7 @@
         <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
@@ -3083,10 +2990,10 @@
         <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -3094,10 +3001,10 @@
         <v>77</v>
       </c>
       <c r="B7" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -3105,128 +3012,128 @@
         <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>458</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>459</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>460</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="C19" t="s">
         <v>20</v>
@@ -3234,35 +3141,35 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>447</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>448</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -3270,51 +3177,51 @@
         <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="C27" t="s">
         <v>21</v>
@@ -3322,13 +3229,13 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -3336,10 +3243,10 @@
         <v>95</v>
       </c>
       <c r="B29" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="C29" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -3347,109 +3254,109 @@
         <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>470</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B32" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B33" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B35" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B36" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B37" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>464</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -3457,32 +3364,32 @@
         <v>104</v>
       </c>
       <c r="B40" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s">
-        <v>479</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -3490,10 +3397,10 @@
         <v>106</v>
       </c>
       <c r="B43" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="C43" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -3501,10 +3408,10 @@
         <v>107</v>
       </c>
       <c r="B44" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -3512,10 +3419,10 @@
         <v>108</v>
       </c>
       <c r="B45" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -3523,10 +3430,10 @@
         <v>109</v>
       </c>
       <c r="B46" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -3534,10 +3441,10 @@
         <v>110</v>
       </c>
       <c r="B47" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="C47" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -3545,98 +3452,98 @@
         <v>111</v>
       </c>
       <c r="B48" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>473</v>
       </c>
       <c r="C49" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="C50" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B51" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B52" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B53" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B54" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="C54" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="C56" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -3644,10 +3551,10 @@
         <v>119</v>
       </c>
       <c r="B57" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -3655,10 +3562,10 @@
         <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="C58" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -3666,10 +3573,10 @@
         <v>121</v>
       </c>
       <c r="B59" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="C59" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -3677,10 +3584,10 @@
         <v>122</v>
       </c>
       <c r="B60" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="C60" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -3688,10 +3595,10 @@
         <v>123</v>
       </c>
       <c r="B61" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="C61" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -3699,10 +3606,10 @@
         <v>124</v>
       </c>
       <c r="B62" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="C62" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -3710,10 +3617,10 @@
         <v>125</v>
       </c>
       <c r="B63" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="C63" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -3721,98 +3628,98 @@
         <v>126</v>
       </c>
       <c r="B64" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="C64" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B65" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B66" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="C66" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B67" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="C67" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B68" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="C68" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B69" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="C69" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B70" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="C70" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B71" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="C71" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B72" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="C72" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -3820,84 +3727,84 @@
         <v>134</v>
       </c>
       <c r="B73" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="C73" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B74" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="C74" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B75" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="C75" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B76" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="C76" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B77" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="C77" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B78" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="C78" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B79" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="C79" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B80" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="C80" t="s">
         <v>21</v>
@@ -3905,13 +3812,13 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B81" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -3919,65 +3826,65 @@
         <v>141</v>
       </c>
       <c r="B82" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B83" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="C83" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B84" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="C84" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B85" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="C85" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B86" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="C86" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B87" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -3985,7 +3892,7 @@
         <v>146</v>
       </c>
       <c r="B88" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="C88" t="s">
         <v>21</v>
@@ -3996,10 +3903,10 @@
         <v>147</v>
       </c>
       <c r="B89" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="C89" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -4007,54 +3914,54 @@
         <v>148</v>
       </c>
       <c r="B90" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="C90" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B91" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="C91" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B92" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="C92" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B93" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="C93" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B94" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="C94" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -4062,10 +3969,10 @@
         <v>152</v>
       </c>
       <c r="B95" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="C95" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -4073,10 +3980,10 @@
         <v>153</v>
       </c>
       <c r="B96" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -4084,29 +3991,29 @@
         <v>154</v>
       </c>
       <c r="B97" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="C97" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B98" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="C98" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B99" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="C99" t="s">
         <v>47</v>
@@ -4114,35 +4021,35 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B100" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="C100" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B101" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="C101" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B102" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="C102" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -4150,62 +4057,62 @@
         <v>159</v>
       </c>
       <c r="B103" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="C103" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B104" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="C104" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B105" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="C105" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B106" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="C106" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B107" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="C107" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B108" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="C108" t="s">
         <v>39</v>
@@ -4213,35 +4120,35 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B109" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="C109" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B110" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="C110" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B111" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="C111" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -4249,10 +4156,10 @@
         <v>166</v>
       </c>
       <c r="B112" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="C112" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -4260,18 +4167,18 @@
         <v>167</v>
       </c>
       <c r="B113" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="C113" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B114" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="C114" t="s">
         <v>24</v>
@@ -4279,13 +4186,13 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B115" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="C115" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -4293,10 +4200,10 @@
         <v>169</v>
       </c>
       <c r="B116" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="C116" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -4304,10 +4211,10 @@
         <v>170</v>
       </c>
       <c r="B117" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C117" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -4315,10 +4222,10 @@
         <v>171</v>
       </c>
       <c r="B118" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="C118" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -4326,10 +4233,10 @@
         <v>172</v>
       </c>
       <c r="B119" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="C119" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -4337,10 +4244,10 @@
         <v>173</v>
       </c>
       <c r="B120" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="C120" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -4348,10 +4255,10 @@
         <v>174</v>
       </c>
       <c r="B121" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="C121" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
@@ -4359,21 +4266,21 @@
         <v>175</v>
       </c>
       <c r="B122" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="C122" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B123" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="C123" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
@@ -4381,164 +4288,164 @@
         <v>176</v>
       </c>
       <c r="B124" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="C124" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B125" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="C125" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B126" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="C126" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B127" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="C127" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B128" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="C128" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B129" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="C129" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B130" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="C130" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B131" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="C131" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B132" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="C132" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B133" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="C133" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B134" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="C134" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B135" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="C135" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B136" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="C136" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B137" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="C137" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B138" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="C138" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -4546,32 +4453,32 @@
         <v>187</v>
       </c>
       <c r="B139" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="C139" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B140" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="C140" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B141" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="C141" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -4579,10 +4486,10 @@
         <v>189</v>
       </c>
       <c r="B142" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="C142" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
@@ -4590,10 +4497,10 @@
         <v>190</v>
       </c>
       <c r="B143" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="C143" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
@@ -4601,10 +4508,10 @@
         <v>191</v>
       </c>
       <c r="B144" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="C144" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -4612,10 +4519,10 @@
         <v>192</v>
       </c>
       <c r="B145" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="C145" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
@@ -4623,10 +4530,10 @@
         <v>193</v>
       </c>
       <c r="B146" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="C146" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
@@ -4634,10 +4541,10 @@
         <v>194</v>
       </c>
       <c r="B147" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="C147" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
@@ -4645,109 +4552,109 @@
         <v>195</v>
       </c>
       <c r="B148" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="C148" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B149" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="C149" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B150" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="C150" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B151" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="C151" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B152" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="C152" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B153" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="C153" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B154" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="C154" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B155" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="C155" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B156" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="C156" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B157" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="C157" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
@@ -4755,10 +4662,10 @@
         <v>203</v>
       </c>
       <c r="B158" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="C158" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
@@ -4766,62 +4673,62 @@
         <v>204</v>
       </c>
       <c r="B159" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="C159" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B160" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="C160" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B161" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="C161" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B162" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="C162" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B163" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="C163" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B164" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="C164" t="s">
         <v>4</v>
@@ -4829,24 +4736,24 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B165" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="C165" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B166" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="C166" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
@@ -4854,10 +4761,10 @@
         <v>211</v>
       </c>
       <c r="B167" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="C167" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
@@ -4865,21 +4772,21 @@
         <v>212</v>
       </c>
       <c r="B168" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="C168" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B169" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="C169" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -4887,51 +4794,51 @@
         <v>213</v>
       </c>
       <c r="B170" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="C170" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B171" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="C171" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B172" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="C172" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B173" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="C173" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B174" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="C174" t="s">
         <v>25</v>
@@ -4939,57 +4846,57 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B175" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="C175" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B176" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="C176" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B177" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="C177" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B178" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="C178" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B179" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="C179" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
@@ -4997,10 +4904,10 @@
         <v>221</v>
       </c>
       <c r="B180" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="C180" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -5008,10 +4915,10 @@
         <v>222</v>
       </c>
       <c r="B181" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="C181" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
@@ -5019,120 +4926,120 @@
         <v>223</v>
       </c>
       <c r="B182" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="C182" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B183" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="C183" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B184" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="C184" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B185" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="C185" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B186" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="C186" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B187" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="C187" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B188" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="C188" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B189" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="C189" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>229</v>
+        <v>55</v>
       </c>
       <c r="B190" t="s">
-        <v>627</v>
+        <v>62</v>
       </c>
       <c r="C190" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>230</v>
+        <v>55</v>
       </c>
       <c r="B191" t="s">
-        <v>628</v>
+        <v>63</v>
       </c>
       <c r="C191" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B192" t="s">
-        <v>629</v>
+        <v>614</v>
       </c>
       <c r="C192" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
@@ -5140,10 +5047,10 @@
         <v>231</v>
       </c>
       <c r="B193" t="s">
-        <v>630</v>
+        <v>615</v>
       </c>
       <c r="C193" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
@@ -5151,153 +5058,153 @@
         <v>232</v>
       </c>
       <c r="B194" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="C194" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>233</v>
+        <v>56</v>
       </c>
       <c r="B195" t="s">
-        <v>632</v>
+        <v>64</v>
       </c>
       <c r="C195" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>234</v>
+        <v>56</v>
       </c>
       <c r="B196" t="s">
-        <v>633</v>
+        <v>65</v>
       </c>
       <c r="C196" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B197" t="s">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="C197" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B198" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="C198" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B199" t="s">
-        <v>636</v>
+        <v>619</v>
       </c>
       <c r="C199" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B200" t="s">
-        <v>637</v>
+        <v>620</v>
       </c>
       <c r="C200" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B201" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="C201" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B202" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="C202" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B203" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="C203" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>55</v>
+        <v>240</v>
       </c>
       <c r="B204" t="s">
-        <v>62</v>
+        <v>624</v>
       </c>
       <c r="C204" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>55</v>
+        <v>241</v>
       </c>
       <c r="B205" t="s">
-        <v>63</v>
+        <v>625</v>
       </c>
       <c r="C205" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B206" t="s">
-        <v>641</v>
+        <v>626</v>
       </c>
       <c r="C206" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B207" t="s">
-        <v>642</v>
+        <v>627</v>
       </c>
       <c r="C207" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
@@ -5305,131 +5212,131 @@
         <v>243</v>
       </c>
       <c r="B208" t="s">
-        <v>643</v>
+        <v>628</v>
       </c>
       <c r="C208" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>56</v>
+        <v>243</v>
       </c>
       <c r="B209" t="s">
-        <v>64</v>
+        <v>629</v>
       </c>
       <c r="C209" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>56</v>
+        <v>244</v>
       </c>
       <c r="B210" t="s">
-        <v>65</v>
+        <v>630</v>
       </c>
       <c r="C210" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B211" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="C211" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B212" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="C212" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B213" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="C213" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B214" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="C214" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B215" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="C215" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B216" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="C216" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B217" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="C217" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B218" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="C218" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B219" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="C219" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
@@ -5437,21 +5344,21 @@
         <v>253</v>
       </c>
       <c r="B220" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="C220" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B221" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="C221" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
@@ -5459,43 +5366,43 @@
         <v>254</v>
       </c>
       <c r="B222" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="C222" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B223" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="C223" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B224" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="C224" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B225" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="C225" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
@@ -5503,10 +5410,10 @@
         <v>257</v>
       </c>
       <c r="B226" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="C226" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
@@ -5514,10 +5421,10 @@
         <v>258</v>
       </c>
       <c r="B227" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="C227" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
@@ -5525,10 +5432,10 @@
         <v>259</v>
       </c>
       <c r="B228" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="C228" t="s">
-        <v>6</v>
+        <v>72</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
@@ -5536,10 +5443,10 @@
         <v>260</v>
       </c>
       <c r="B229" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="C229" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
@@ -5547,10 +5454,10 @@
         <v>261</v>
       </c>
       <c r="B230" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="C230" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
@@ -5558,32 +5465,32 @@
         <v>262</v>
       </c>
       <c r="B231" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="C231" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B232" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="C232" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B233" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="C233" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
@@ -5591,260 +5498,260 @@
         <v>264</v>
       </c>
       <c r="B234" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="C234" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B235" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="C235" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B236" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="C236" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B237" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="C237" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B238" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="C238" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B239" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="C239" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B240" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="C240" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B241" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C241" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B242" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="C242" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B243" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="C243" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B244" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="C244" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B245" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="C245" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B246" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="C246" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B247" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="C247" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B248" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="C248" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B249" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="C249" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B250" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="C250" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B251" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="C251" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B252" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="C252" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B253" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="C253" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B254" t="s">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="C254" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B255" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="C255" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B256" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="C256" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B257" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="C257" t="s">
         <v>35</v>
@@ -5852,277 +5759,277 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B258" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="C258" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B259" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="C259" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B260" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="C260" t="s">
-        <v>72</v>
+        <v>4</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B261" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="C261" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B262" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="C262" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B263" t="s">
-        <v>696</v>
+        <v>683</v>
       </c>
       <c r="C263" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B264" t="s">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="C264" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B265" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="C265" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B266" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="C266" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B267" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="C267" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B268" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="C268" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B269" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="C269" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B270" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="C270" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B271" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="C271" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B272" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="C272" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B273" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="C273" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B274" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="C274" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B275" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="C275" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B276" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="C276" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B277" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="C277" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B278" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="C278" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B279" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="C279" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B280" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="C280" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B281" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="C281" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B282" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="C282" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
@@ -6130,10 +6037,10 @@
         <v>309</v>
       </c>
       <c r="B283" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="C283" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
@@ -6141,10 +6048,10 @@
         <v>310</v>
       </c>
       <c r="B284" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="C284" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
@@ -6152,10 +6059,10 @@
         <v>311</v>
       </c>
       <c r="B285" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="C285" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
@@ -6163,10 +6070,10 @@
         <v>312</v>
       </c>
       <c r="B286" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="C286" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
@@ -6174,10 +6081,10 @@
         <v>313</v>
       </c>
       <c r="B287" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="C287" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
@@ -6185,282 +6092,282 @@
         <v>314</v>
       </c>
       <c r="B288" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="C288" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B289" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="C289" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B290" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="C290" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B291" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="C291" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B292" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="C292" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B293" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="C293" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B294" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="C294" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B295" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="C295" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B296" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="C296" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B297" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="C297" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B298" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="C298" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B299" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="C299" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B300" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="C300" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B301" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="C301" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B302" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="C302" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B303" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="C303" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B304" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="C304" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B305" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="C305" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B306" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="C306" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B307" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="C307" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B308" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="C308" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B309" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="C309" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B310" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="C310" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B311" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="C311" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B312" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="C312" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B313" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="C313" t="s">
         <v>38</v>
@@ -6468,233 +6375,233 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B314" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="C314" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B315" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="C315" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B316" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="C316" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B317" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="C317" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B318" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="C318" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B319" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="C319" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B320" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="C320" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B321" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="C321" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B322" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="C322" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B323" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="C323" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B324" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="C324" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B325" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="C325" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B326" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="C326" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B327" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="C327" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B328" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="C328" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B329" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="C329" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B330" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="C330" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B331" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="C331" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B332" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="C332" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B333" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="C333" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B334" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="C334" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
@@ -6702,62 +6609,62 @@
         <v>356</v>
       </c>
       <c r="B335" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="C335" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B336" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="C336" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B337" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="C337" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B338" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
       <c r="C338" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B339" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="C339" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B340" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
       <c r="C340" t="s">
         <v>31</v>
@@ -6765,90 +6672,90 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B341" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="C341" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B342" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="C342" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B343" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="C343" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B344" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="C344" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B345" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
       <c r="C345" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B346" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
       <c r="C346" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B347" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="C347" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B348" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="C348" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
@@ -6856,32 +6763,32 @@
         <v>367</v>
       </c>
       <c r="B349" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="C349" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B350" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="C350" t="s">
-        <v>3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>368</v>
+        <v>57</v>
       </c>
       <c r="B351" t="s">
-        <v>784</v>
+        <v>66</v>
       </c>
       <c r="C351" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
@@ -6889,271 +6796,271 @@
         <v>369</v>
       </c>
       <c r="B352" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="C352" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B353" t="s">
-        <v>786</v>
+        <v>772</v>
       </c>
       <c r="C353" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B354" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="C354" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B355" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
       <c r="C355" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B356" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="C356" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B357" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="C357" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B358" t="s">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="C358" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B359" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="C359" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B360" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="C360" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B361" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="C361" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B362" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C362" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B363" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="C363" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B364" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
       <c r="C364" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B365" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="C365" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B366" t="s">
-        <v>799</v>
+        <v>785</v>
       </c>
       <c r="C366" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B367" t="s">
-        <v>800</v>
+        <v>786</v>
       </c>
       <c r="C367" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B368" t="s">
-        <v>801</v>
+        <v>787</v>
       </c>
       <c r="C368" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>57</v>
+        <v>386</v>
       </c>
       <c r="B369" t="s">
-        <v>66</v>
+        <v>788</v>
       </c>
       <c r="C369" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B370" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="C370" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B371" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="C371" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B372" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="C372" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B373" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
       <c r="C373" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B374" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="C374" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B375" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
       <c r="C375" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B376" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
       <c r="C376" t="s">
         <v>6</v>
@@ -7161,76 +7068,76 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B377" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
       <c r="C377" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B378" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="C378" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B379" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="C379" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B380" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="C380" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B381" t="s">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="C381" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B382" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="C382" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B383" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
       <c r="C383" t="s">
         <v>32</v>
@@ -7238,21 +7145,21 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B384" t="s">
-        <v>816</v>
+        <v>803</v>
       </c>
       <c r="C384" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B385" t="s">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="C385" t="s">
         <v>15</v>
@@ -7260,65 +7167,65 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B386" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="C386" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B387" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
       <c r="C387" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B388" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="C388" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B389" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
       <c r="C389" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B390" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="C390" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B391" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
       <c r="C391" t="s">
         <v>35</v>
@@ -7326,109 +7233,109 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B392" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="C392" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B393" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="C393" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B394" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="C394" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B395" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="C395" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B396" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="C396" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B397" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
       <c r="C397" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B398" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="C398" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B399" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="C399" t="s">
-        <v>7</v>
+        <v>846</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B400" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="C400" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B401" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="C401" t="s">
         <v>32</v>
@@ -7436,211 +7343,211 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B402" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="C402" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B403" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="C403" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B404" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="C404" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B405" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="C405" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B406" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="C406" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B407" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="C407" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B408" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="C408" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B409" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="C409" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B410" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="C410" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B411" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="C411" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B412" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
       <c r="C412" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B413" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="C413" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B414" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="C414" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B415" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="C415" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B416" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="C416" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B417" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="C417" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B418" t="s">
-        <v>850</v>
+        <v>837</v>
       </c>
       <c r="C418" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B419" t="s">
-        <v>851</v>
+        <v>838</v>
       </c>
       <c r="C419" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B420" t="s">
-        <v>852</v>
+        <v>839</v>
       </c>
       <c r="C420" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
@@ -7648,10 +7555,10 @@
         <v>427</v>
       </c>
       <c r="B421" t="s">
-        <v>853</v>
+        <v>840</v>
       </c>
       <c r="C421" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
@@ -7659,10 +7566,10 @@
         <v>428</v>
       </c>
       <c r="B422" t="s">
-        <v>854</v>
+        <v>841</v>
       </c>
       <c r="C422" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
@@ -7670,251 +7577,42 @@
         <v>429</v>
       </c>
       <c r="B423" t="s">
-        <v>855</v>
+        <v>842</v>
       </c>
       <c r="C423" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B424" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
       <c r="C424" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B425" t="s">
-        <v>857</v>
+        <v>844</v>
       </c>
       <c r="C425" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B426" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="C426" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A427" t="s">
-        <v>433</v>
-      </c>
-      <c r="B427" t="s">
-        <v>859</v>
-      </c>
-      <c r="C427" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A428" t="s">
-        <v>434</v>
-      </c>
-      <c r="B428" t="s">
-        <v>860</v>
-      </c>
-      <c r="C428" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A429" t="s">
-        <v>435</v>
-      </c>
-      <c r="B429" t="s">
-        <v>861</v>
-      </c>
-      <c r="C429" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A430" t="s">
-        <v>436</v>
-      </c>
-      <c r="B430" t="s">
-        <v>862</v>
-      </c>
-      <c r="C430" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A431" t="s">
-        <v>437</v>
-      </c>
-      <c r="B431" t="s">
-        <v>863</v>
-      </c>
-      <c r="C431" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A432" t="s">
-        <v>438</v>
-      </c>
-      <c r="B432" t="s">
-        <v>864</v>
-      </c>
-      <c r="C432" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A433" t="s">
-        <v>439</v>
-      </c>
-      <c r="B433" t="s">
-        <v>865</v>
-      </c>
-      <c r="C433" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A434" t="s">
-        <v>439</v>
-      </c>
-      <c r="B434" t="s">
-        <v>866</v>
-      </c>
-      <c r="C434" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A435" t="s">
-        <v>439</v>
-      </c>
-      <c r="B435" t="s">
-        <v>867</v>
-      </c>
-      <c r="C435" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A436" t="s">
-        <v>439</v>
-      </c>
-      <c r="B436" t="s">
-        <v>868</v>
-      </c>
-      <c r="C436" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A437" t="s">
-        <v>439</v>
-      </c>
-      <c r="B437" t="s">
-        <v>869</v>
-      </c>
-      <c r="C437" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A438" t="s">
-        <v>440</v>
-      </c>
-      <c r="B438" t="s">
-        <v>870</v>
-      </c>
-      <c r="C438" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A439" t="s">
-        <v>440</v>
-      </c>
-      <c r="B439" t="s">
-        <v>871</v>
-      </c>
-      <c r="C439" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A440" t="s">
-        <v>440</v>
-      </c>
-      <c r="B440" t="s">
-        <v>872</v>
-      </c>
-      <c r="C440" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A441" t="s">
-        <v>441</v>
-      </c>
-      <c r="B441" t="s">
-        <v>873</v>
-      </c>
-      <c r="C441" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A442" t="s">
-        <v>442</v>
-      </c>
-      <c r="B442" t="s">
-        <v>874</v>
-      </c>
-      <c r="C442" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A443" t="s">
-        <v>442</v>
-      </c>
-      <c r="B443" t="s">
-        <v>875</v>
-      </c>
-      <c r="C443" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A444" t="s">
-        <v>443</v>
-      </c>
-      <c r="B444" t="s">
-        <v>876</v>
-      </c>
-      <c r="C444" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A445" t="s">
-        <v>443</v>
-      </c>
-      <c r="B445" t="s">
-        <v>877</v>
-      </c>
-      <c r="C445" t="s">
         <v>28</v>
       </c>
     </row>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1734D15D-4D2E-49AA-BBA8-F1A4B700A277}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0323005F-70C4-44DE-B0FA-85F4E7845B8A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="358">
   <si>
     <t>UTK</t>
   </si>
@@ -42,9 +42,6 @@
     <t>327025825</t>
   </si>
   <si>
-    <t>SZ</t>
-  </si>
-  <si>
     <t>260829-F00004583</t>
   </si>
   <si>
@@ -400,6 +397,711 @@
   </si>
   <si>
     <t>327402613</t>
+  </si>
+  <si>
+    <t>260905-F00005625</t>
+  </si>
+  <si>
+    <t>267012879</t>
+  </si>
+  <si>
+    <t>267012883</t>
+  </si>
+  <si>
+    <t>267012901</t>
+  </si>
+  <si>
+    <t>267012906</t>
+  </si>
+  <si>
+    <t>267012908</t>
+  </si>
+  <si>
+    <t>267012963</t>
+  </si>
+  <si>
+    <t>26MPE0009526</t>
+  </si>
+  <si>
+    <t>840925658KR</t>
+  </si>
+  <si>
+    <t>ID5488_XD</t>
+  </si>
+  <si>
+    <t>ID5489_XD</t>
+  </si>
+  <si>
+    <t>NFD6-09-01-E93V</t>
+  </si>
+  <si>
+    <t>NFD6-09-04-LTGG</t>
+  </si>
+  <si>
+    <t>NFD6-09-05-686V</t>
+  </si>
+  <si>
+    <t>NFD6-09-07-3UZE</t>
+  </si>
+  <si>
+    <t>NFD6-09-07-6RH2</t>
+  </si>
+  <si>
+    <t>NFD6-09-07-CYCK</t>
+  </si>
+  <si>
+    <t>NFD6-09-07-G3B7</t>
+  </si>
+  <si>
+    <t>NFD6-09-07-GYCJ</t>
+  </si>
+  <si>
+    <t>NFD6-09-07-R958</t>
+  </si>
+  <si>
+    <t>NFD6-09-08-4MMX</t>
+  </si>
+  <si>
+    <t>NFD6-09-08-B8B6</t>
+  </si>
+  <si>
+    <t>NFD6-09-08-L9SY</t>
+  </si>
+  <si>
+    <t>NFD6-09-08-P48R</t>
+  </si>
+  <si>
+    <t>NFE6-09-04-5X39</t>
+  </si>
+  <si>
+    <t>NFE6-09-04-W5VT</t>
+  </si>
+  <si>
+    <t>NFE6-09-06-5TDD</t>
+  </si>
+  <si>
+    <t>NFE6-09-06-7BPF</t>
+  </si>
+  <si>
+    <t>NFE6-09-07-LF98</t>
+  </si>
+  <si>
+    <t>NFE6-09-08-25VN</t>
+  </si>
+  <si>
+    <t>NFE6-09-08-9RZP</t>
+  </si>
+  <si>
+    <t>NFE6-09-08-CZ7E</t>
+  </si>
+  <si>
+    <t>NFE6-09-08-E8XQ</t>
+  </si>
+  <si>
+    <t>NFE6-09-08-ENEJ</t>
+  </si>
+  <si>
+    <t>R435194</t>
+  </si>
+  <si>
+    <t>6a7e0059c0fa1536b26e2da1</t>
+  </si>
+  <si>
+    <t>6aa009292235a0231b9afc26</t>
+  </si>
+  <si>
+    <t>6aa009292235a0231b9afc27</t>
+  </si>
+  <si>
+    <t>6a9aa5ebc0fa1536b26fe113</t>
+  </si>
+  <si>
+    <t>6a9ea58dc0fa1536b27016eb</t>
+  </si>
+  <si>
+    <t>6a91565fc0fa1536b26f42d3</t>
+  </si>
+  <si>
+    <t>6a9fc1972235a0231b9aefd4</t>
+  </si>
+  <si>
+    <t>6a9fc1972235a0231b9aefd5</t>
+  </si>
+  <si>
+    <t>6a92b269c0fa1536b26f5856</t>
+  </si>
+  <si>
+    <t>6a9fd2b62235a0231b9af379</t>
+  </si>
+  <si>
+    <t>6a9fabdf2235a0231b9aec81</t>
+  </si>
+  <si>
+    <t>6a984b9cc0fa1536b26fb821</t>
+  </si>
+  <si>
+    <t>6aa12e582235a0231b9b0fd2</t>
+  </si>
+  <si>
+    <t>6a992f07c0fa1536b26fc132</t>
+  </si>
+  <si>
+    <t>6a9927e9c0fa1536b26fbfb1</t>
+  </si>
+  <si>
+    <t>6a9a89e0c0fa1536b26fdc83</t>
+  </si>
+  <si>
+    <t>6a9a96c6c0fa1536b26fded4</t>
+  </si>
+  <si>
+    <t>6a9acbb4c0fa1536b26fe731</t>
+  </si>
+  <si>
+    <t>6a9af5a3c0fa1536b26feb2a</t>
+  </si>
+  <si>
+    <t>6a9c1844c0fa1536b26ff790</t>
+  </si>
+  <si>
+    <t>6aa016e72235a0231b9afea0</t>
+  </si>
+  <si>
+    <t>6a9d15c1c0fa1536b26ffcb1</t>
+  </si>
+  <si>
+    <t>6a9d4c78c0fa1536b2700078</t>
+  </si>
+  <si>
+    <t>6a9d6e73c0fa1536b2700327</t>
+  </si>
+  <si>
+    <t>6a9d6e73c0fa1536b2700328</t>
+  </si>
+  <si>
+    <t>6a9d800ac0fa1536b2700419</t>
+  </si>
+  <si>
+    <t>6a9d951bc0fa1536b2700532</t>
+  </si>
+  <si>
+    <t>6a9e80acc0fa1536b2701014</t>
+  </si>
+  <si>
+    <t>6a9e9367c0fa1536b270136e</t>
+  </si>
+  <si>
+    <t>6a9eb91fc0fa1536b2701a9b</t>
+  </si>
+  <si>
+    <t>6a9ec122c0fa1536b2701c53</t>
+  </si>
+  <si>
+    <t>6a9ec37bc0fa1536b2701cad</t>
+  </si>
+  <si>
+    <t>6a9ec37bc0fa1536b2701cae</t>
+  </si>
+  <si>
+    <t>6a9fab7a2235a0231b9aec78</t>
+  </si>
+  <si>
+    <t>6a9ece2ac0fa1536b2701e61</t>
+  </si>
+  <si>
+    <t>6aa13d752235a0231b9b123c</t>
+  </si>
+  <si>
+    <t>6aa134ed2235a0231b9b10ce</t>
+  </si>
+  <si>
+    <t>6a9eea23c0fa1536b27021b7</t>
+  </si>
+  <si>
+    <t>6a9eea23c0fa1536b27021b8</t>
+  </si>
+  <si>
+    <t>6a9edc16c0fa1536b270203c</t>
+  </si>
+  <si>
+    <t>6a9ef380c0fa1536b2702279</t>
+  </si>
+  <si>
+    <t>6a9ef722c0fa1536b27022bf</t>
+  </si>
+  <si>
+    <t>6a9f3775c0fa1536b2702496</t>
+  </si>
+  <si>
+    <t>6a9fb0312235a0231b9aecd2</t>
+  </si>
+  <si>
+    <t>6a9fb4e02235a0231b9aed44</t>
+  </si>
+  <si>
+    <t>6a9fb4e02235a0231b9aed45</t>
+  </si>
+  <si>
+    <t>6a9fb4e02235a0231b9aed47</t>
+  </si>
+  <si>
+    <t>6a9fc2f82235a0231b9af012</t>
+  </si>
+  <si>
+    <t>6a9ffeba2235a0231b9afae8</t>
+  </si>
+  <si>
+    <t>6a9ffeba2235a0231b9afae9</t>
+  </si>
+  <si>
+    <t>6aa025642235a0231b9b0154</t>
+  </si>
+  <si>
+    <t>6aa03bcc2235a0231b9b03bf</t>
+  </si>
+  <si>
+    <t>6a9fb9902235a0231b9aee34</t>
+  </si>
+  <si>
+    <t>6a9fb9902235a0231b9aee36</t>
+  </si>
+  <si>
+    <t>6a9fc5662235a0231b9af097</t>
+  </si>
+  <si>
+    <t>6a9fc5662235a0231b9af09d</t>
+  </si>
+  <si>
+    <t>6a9ff1cf2235a0231b9af8e0</t>
+  </si>
+  <si>
+    <t>6aa0255e2235a0231b9b0140</t>
+  </si>
+  <si>
+    <t>6aa0255e2235a0231b9b0141</t>
+  </si>
+  <si>
+    <t>6aa0255f2235a0231b9b0148</t>
+  </si>
+  <si>
+    <t>6aa06bad2235a0231b9b065a</t>
+  </si>
+  <si>
+    <t>6aa109e02235a0231b9b092a</t>
+  </si>
+  <si>
+    <t>6aa12e3b2235a0231b9b0fb9</t>
+  </si>
+  <si>
+    <t>1449-578614</t>
+  </si>
+  <si>
+    <t>1449-990360</t>
+  </si>
+  <si>
+    <t>1449-406941</t>
+  </si>
+  <si>
+    <t>1449-705226</t>
+  </si>
+  <si>
+    <t>1449-310369</t>
+  </si>
+  <si>
+    <t>1449-685330</t>
+  </si>
+  <si>
+    <t>26MPE0009526/1</t>
+  </si>
+  <si>
+    <t>326268012/1</t>
+  </si>
+  <si>
+    <t>326325295/1</t>
+  </si>
+  <si>
+    <t>326457761/1</t>
+  </si>
+  <si>
+    <t>326515044/1</t>
+  </si>
+  <si>
+    <t>326515136/1</t>
+  </si>
+  <si>
+    <t>326515347/1</t>
+  </si>
+  <si>
+    <t>326572789/1</t>
+  </si>
+  <si>
+    <t>326572789/2</t>
+  </si>
+  <si>
+    <t>326622394/1</t>
+  </si>
+  <si>
+    <t>326667444/1</t>
+  </si>
+  <si>
+    <t>326667444/2</t>
+  </si>
+  <si>
+    <t>326667455/1</t>
+  </si>
+  <si>
+    <t>326761696/1</t>
+  </si>
+  <si>
+    <t>326761696/2</t>
+  </si>
+  <si>
+    <t>326813209/1</t>
+  </si>
+  <si>
+    <t>326813853/1</t>
+  </si>
+  <si>
+    <t>326813853/2</t>
+  </si>
+  <si>
+    <t>326859614/1</t>
+  </si>
+  <si>
+    <t>326859614/2</t>
+  </si>
+  <si>
+    <t>326859676/1</t>
+  </si>
+  <si>
+    <t>326859676/2</t>
+  </si>
+  <si>
+    <t>326859724/1</t>
+  </si>
+  <si>
+    <t>326860233/1</t>
+  </si>
+  <si>
+    <t>326860233/2</t>
+  </si>
+  <si>
+    <t>326913881/1</t>
+  </si>
+  <si>
+    <t>326913930/1</t>
+  </si>
+  <si>
+    <t>326914122/1</t>
+  </si>
+  <si>
+    <t>326914318/1</t>
+  </si>
+  <si>
+    <t>326967466/1</t>
+  </si>
+  <si>
+    <t>326967466/2</t>
+  </si>
+  <si>
+    <t>327025825/1</t>
+  </si>
+  <si>
+    <t>327025887/1</t>
+  </si>
+  <si>
+    <t>327025994/1</t>
+  </si>
+  <si>
+    <t>327026582/1</t>
+  </si>
+  <si>
+    <t>327070297/1</t>
+  </si>
+  <si>
+    <t>327070686/1</t>
+  </si>
+  <si>
+    <t>327070788/1</t>
+  </si>
+  <si>
+    <t>327110119/1</t>
+  </si>
+  <si>
+    <t>327110270/1</t>
+  </si>
+  <si>
+    <t>327110277/1</t>
+  </si>
+  <si>
+    <t>327110376/1</t>
+  </si>
+  <si>
+    <t>327110431/1</t>
+  </si>
+  <si>
+    <t>327110463/1</t>
+  </si>
+  <si>
+    <t>327110535/1</t>
+  </si>
+  <si>
+    <t>327110542/1</t>
+  </si>
+  <si>
+    <t>327110696/1</t>
+  </si>
+  <si>
+    <t>327153246/1</t>
+  </si>
+  <si>
+    <t>327153456/1</t>
+  </si>
+  <si>
+    <t>327153484/1</t>
+  </si>
+  <si>
+    <t>327153484/2</t>
+  </si>
+  <si>
+    <t>327153484/3</t>
+  </si>
+  <si>
+    <t>327153573/1</t>
+  </si>
+  <si>
+    <t>327153581/1</t>
+  </si>
+  <si>
+    <t>327153581/2</t>
+  </si>
+  <si>
+    <t>327153643/1</t>
+  </si>
+  <si>
+    <t>327153840/1</t>
+  </si>
+  <si>
+    <t>327198429/1</t>
+  </si>
+  <si>
+    <t>327198511/1</t>
+  </si>
+  <si>
+    <t>327198528/1</t>
+  </si>
+  <si>
+    <t>327198555/1</t>
+  </si>
+  <si>
+    <t>327198753/1</t>
+  </si>
+  <si>
+    <t>327198835/1</t>
+  </si>
+  <si>
+    <t>327198846/1</t>
+  </si>
+  <si>
+    <t>327198950/1</t>
+  </si>
+  <si>
+    <t>327199069/1</t>
+  </si>
+  <si>
+    <t>327199069/2</t>
+  </si>
+  <si>
+    <t>327199069/3</t>
+  </si>
+  <si>
+    <t>327199114/1</t>
+  </si>
+  <si>
+    <t>327199180/1</t>
+  </si>
+  <si>
+    <t>327199275/1</t>
+  </si>
+  <si>
+    <t>327199389/1</t>
+  </si>
+  <si>
+    <t>327253224/1</t>
+  </si>
+  <si>
+    <t>327253300/1</t>
+  </si>
+  <si>
+    <t>327253338/1</t>
+  </si>
+  <si>
+    <t>327253370/1</t>
+  </si>
+  <si>
+    <t>327253788/1</t>
+  </si>
+  <si>
+    <t>327310820/1</t>
+  </si>
+  <si>
+    <t>327310835/1</t>
+  </si>
+  <si>
+    <t>327310910/1</t>
+  </si>
+  <si>
+    <t>327310972/1</t>
+  </si>
+  <si>
+    <t>327402550/1</t>
+  </si>
+  <si>
+    <t>327402613/1</t>
+  </si>
+  <si>
+    <t>840925658KR/1</t>
+  </si>
+  <si>
+    <t>840925658KR/2</t>
+  </si>
+  <si>
+    <t>159995579543968374</t>
+  </si>
+  <si>
+    <t>159995579543968183</t>
+  </si>
+  <si>
+    <t>202609022601867201</t>
+  </si>
+  <si>
+    <t>202609072601882201</t>
+  </si>
+  <si>
+    <t>202609072601886601</t>
+  </si>
+  <si>
+    <t>202609082601904601</t>
+  </si>
+  <si>
+    <t>202609082601900501</t>
+  </si>
+  <si>
+    <t>202609082601905601</t>
+  </si>
+  <si>
+    <t>202609082601901901</t>
+  </si>
+  <si>
+    <t>202609082601905901</t>
+  </si>
+  <si>
+    <t>202609082601904301</t>
+  </si>
+  <si>
+    <t>202609092601909401</t>
+  </si>
+  <si>
+    <t>202609092601911901</t>
+  </si>
+  <si>
+    <t>202609092601911501</t>
+  </si>
+  <si>
+    <t>202609092601910901</t>
+  </si>
+  <si>
+    <t>202609072601883701</t>
+  </si>
+  <si>
+    <t>202609072601884901</t>
+  </si>
+  <si>
+    <t>202609072601897101</t>
+  </si>
+  <si>
+    <t>202609072601898601</t>
+  </si>
+  <si>
+    <t>202609082601899801</t>
+  </si>
+  <si>
+    <t>202609092601911701</t>
+  </si>
+  <si>
+    <t>202609092601908201</t>
+  </si>
+  <si>
+    <t>202609092601912701</t>
+  </si>
+  <si>
+    <t>202609092601911601</t>
+  </si>
+  <si>
+    <t>202609092601910001</t>
+  </si>
+  <si>
+    <t>159995579543877409</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-803</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
   </si>
 </sst>
 </file>
@@ -442,9 +1144,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -761,11 +1462,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC11F24F-E222-443E-8401-2ECBA69A40D4}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:C134"/>
+  <dimension ref="A1:C181"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -781,1003 +1482,1984 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B14" t="s">
+        <v>170</v>
+      </c>
+      <c r="C14" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B16" t="s">
+        <v>172</v>
+      </c>
+      <c r="C16" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B17" t="s">
+        <v>173</v>
+      </c>
+      <c r="C17" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B20" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="C18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B22" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="C19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B23" t="s">
+        <v>179</v>
+      </c>
+      <c r="C23" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="C20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B24" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="C21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B25" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>25</v>
       </c>
-      <c r="C22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>26</v>
       </c>
-      <c r="C23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>27</v>
       </c>
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B29" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>28</v>
       </c>
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="B30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>29</v>
       </c>
-      <c r="C26" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B31" t="s">
+        <v>187</v>
+      </c>
+      <c r="C31" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>30</v>
       </c>
-      <c r="C27" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C32" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>31</v>
       </c>
-      <c r="C28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B33" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>190</v>
+      </c>
+      <c r="C34" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>32</v>
       </c>
-      <c r="C29" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="B35" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>33</v>
       </c>
-      <c r="C30" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="B36" t="s">
+        <v>192</v>
+      </c>
+      <c r="C36" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>34</v>
       </c>
-      <c r="C31" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="B37" t="s">
+        <v>193</v>
+      </c>
+      <c r="C37" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>35</v>
       </c>
-      <c r="C32" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="B38" t="s">
+        <v>194</v>
+      </c>
+      <c r="C38" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>36</v>
       </c>
-      <c r="C33" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="B39" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" t="s">
+        <v>196</v>
+      </c>
+      <c r="C40" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>37</v>
       </c>
-      <c r="C34" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="B41" t="s">
+        <v>197</v>
+      </c>
+      <c r="C41" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>38</v>
       </c>
-      <c r="C35" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="B42" t="s">
+        <v>198</v>
+      </c>
+      <c r="C42" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>39</v>
       </c>
-      <c r="C36" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="B43" t="s">
+        <v>199</v>
+      </c>
+      <c r="C43" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>40</v>
       </c>
-      <c r="C37" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="B44" t="s">
+        <v>200</v>
+      </c>
+      <c r="C44" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>41</v>
       </c>
-      <c r="C38" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="B45" t="s">
+        <v>201</v>
+      </c>
+      <c r="C45" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>42</v>
       </c>
-      <c r="C39" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="B46" t="s">
+        <v>202</v>
+      </c>
+      <c r="C46" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" t="s">
+        <v>203</v>
+      </c>
+      <c r="C47" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>43</v>
       </c>
-      <c r="C40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="B49" t="s">
+        <v>205</v>
+      </c>
+      <c r="C49" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>44</v>
       </c>
-      <c r="C41" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="B50" t="s">
+        <v>206</v>
+      </c>
+      <c r="C50" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" t="s">
+        <v>207</v>
+      </c>
+      <c r="C51" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>45</v>
       </c>
-      <c r="C42" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="B52" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>46</v>
       </c>
-      <c r="C43" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="B53" t="s">
+        <v>209</v>
+      </c>
+      <c r="C53" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>47</v>
       </c>
-      <c r="C44" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="B54" t="s">
+        <v>210</v>
+      </c>
+      <c r="C54" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>47</v>
+      </c>
+      <c r="B55" t="s">
+        <v>211</v>
+      </c>
+      <c r="C55" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>48</v>
       </c>
-      <c r="C45" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="B56" t="s">
+        <v>212</v>
+      </c>
+      <c r="C56" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>48</v>
+      </c>
+      <c r="B57" t="s">
+        <v>213</v>
+      </c>
+      <c r="C57" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>49</v>
       </c>
-      <c r="C46" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="B58" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>50</v>
       </c>
-      <c r="C47" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="B59" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>50</v>
+      </c>
+      <c r="B60" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>51</v>
       </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="B61" t="s">
+        <v>217</v>
+      </c>
+      <c r="C61" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>52</v>
       </c>
-      <c r="C49" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="B62" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>53</v>
       </c>
-      <c r="C50" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="B63" t="s">
+        <v>219</v>
+      </c>
+      <c r="C63" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>54</v>
       </c>
-      <c r="C51" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="B64" t="s">
+        <v>220</v>
+      </c>
+      <c r="C64" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>124</v>
+      </c>
+      <c r="B65" t="s">
+        <v>221</v>
+      </c>
+      <c r="C65" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" t="s">
+        <v>222</v>
+      </c>
+      <c r="C66" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" t="s">
+        <v>223</v>
+      </c>
+      <c r="C67" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>127</v>
+      </c>
+      <c r="B68" t="s">
+        <v>224</v>
+      </c>
+      <c r="C68" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>128</v>
+      </c>
+      <c r="B69" t="s">
+        <v>225</v>
+      </c>
+      <c r="C69" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>129</v>
+      </c>
+      <c r="B70" t="s">
+        <v>226</v>
+      </c>
+      <c r="C70" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>130</v>
+      </c>
+      <c r="B71" t="s">
+        <v>227</v>
+      </c>
+      <c r="C71" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>55</v>
       </c>
-      <c r="C52" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="B72" t="s">
+        <v>228</v>
+      </c>
+      <c r="C72" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>56</v>
       </c>
-      <c r="C53" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="B73" t="s">
+        <v>229</v>
+      </c>
+      <c r="C73" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>57</v>
       </c>
-      <c r="C54" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="B74" t="s">
+        <v>230</v>
+      </c>
+      <c r="C74" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>58</v>
       </c>
-      <c r="C55" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="B75" t="s">
+        <v>231</v>
+      </c>
+      <c r="C75" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>59</v>
       </c>
-      <c r="C56" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="B76" t="s">
+        <v>232</v>
+      </c>
+      <c r="C76" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>60</v>
       </c>
-      <c r="C57" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+      <c r="B77" t="s">
+        <v>233</v>
+      </c>
+      <c r="C77" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>61</v>
       </c>
-      <c r="C58" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="B78" t="s">
+        <v>234</v>
+      </c>
+      <c r="C78" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>61</v>
+      </c>
+      <c r="B79" t="s">
+        <v>235</v>
+      </c>
+      <c r="C79" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>62</v>
       </c>
-      <c r="C59" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="B80" t="s">
+        <v>236</v>
+      </c>
+      <c r="C80" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>63</v>
       </c>
-      <c r="C60" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="B81" t="s">
+        <v>237</v>
+      </c>
+      <c r="C81" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>63</v>
+      </c>
+      <c r="B82" t="s">
+        <v>238</v>
+      </c>
+      <c r="C82" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>64</v>
       </c>
-      <c r="C61" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="B83" t="s">
+        <v>239</v>
+      </c>
+      <c r="C83" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>65</v>
       </c>
-      <c r="C62" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+      <c r="B84" t="s">
+        <v>240</v>
+      </c>
+      <c r="C84" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>65</v>
+      </c>
+      <c r="B85" t="s">
+        <v>241</v>
+      </c>
+      <c r="C85" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>66</v>
       </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="B86" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>67</v>
       </c>
-      <c r="C64" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="B87" t="s">
+        <v>243</v>
+      </c>
+      <c r="C87" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>67</v>
+      </c>
+      <c r="B88" t="s">
+        <v>244</v>
+      </c>
+      <c r="C88" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>68</v>
       </c>
-      <c r="C65" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="B89" t="s">
+        <v>245</v>
+      </c>
+      <c r="C89" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>68</v>
+      </c>
+      <c r="B90" t="s">
+        <v>246</v>
+      </c>
+      <c r="C90" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>69</v>
       </c>
-      <c r="C66" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="B91" t="s">
+        <v>247</v>
+      </c>
+      <c r="C91" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>69</v>
+      </c>
+      <c r="B92" t="s">
+        <v>248</v>
+      </c>
+      <c r="C92" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>70</v>
       </c>
-      <c r="C67" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="B93" t="s">
+        <v>249</v>
+      </c>
+      <c r="C93" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>71</v>
       </c>
-      <c r="C68" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+      <c r="B94" t="s">
+        <v>250</v>
+      </c>
+      <c r="C94" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>71</v>
+      </c>
+      <c r="B95" t="s">
+        <v>251</v>
+      </c>
+      <c r="C95" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>72</v>
       </c>
-      <c r="C69" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+      <c r="B96" t="s">
+        <v>252</v>
+      </c>
+      <c r="C96" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>73</v>
       </c>
-      <c r="C70" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="B97" t="s">
+        <v>253</v>
+      </c>
+      <c r="C97" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>74</v>
       </c>
-      <c r="C71" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="B98" t="s">
+        <v>254</v>
+      </c>
+      <c r="C98" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>75</v>
       </c>
-      <c r="C72" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+      <c r="B99" t="s">
+        <v>255</v>
+      </c>
+      <c r="C99" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>76</v>
       </c>
-      <c r="C73" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+      <c r="B100" t="s">
+        <v>256</v>
+      </c>
+      <c r="C100" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>76</v>
+      </c>
+      <c r="B101" t="s">
+        <v>257</v>
+      </c>
+      <c r="C101" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" t="s">
+        <v>258</v>
+      </c>
+      <c r="C102" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>77</v>
       </c>
-      <c r="C74" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C75" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="B103" t="s">
+        <v>259</v>
+      </c>
+      <c r="C103" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>78</v>
       </c>
-      <c r="C76" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+      <c r="B104" t="s">
+        <v>260</v>
+      </c>
+      <c r="C104" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>79</v>
       </c>
-      <c r="C77" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="B105" t="s">
+        <v>261</v>
+      </c>
+      <c r="C105" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>80</v>
       </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+      <c r="B106" t="s">
+        <v>262</v>
+      </c>
+      <c r="C106" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>81</v>
       </c>
-      <c r="C79" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+      <c r="B107" t="s">
+        <v>263</v>
+      </c>
+      <c r="C107" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>82</v>
       </c>
-      <c r="C80" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
+      <c r="B108" t="s">
+        <v>264</v>
+      </c>
+      <c r="C108" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>83</v>
       </c>
-      <c r="C81" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+      <c r="B109" t="s">
+        <v>265</v>
+      </c>
+      <c r="C109" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>84</v>
       </c>
-      <c r="C82" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
+      <c r="B110" t="s">
+        <v>266</v>
+      </c>
+      <c r="C110" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>85</v>
       </c>
-      <c r="C83" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
+      <c r="B111" t="s">
+        <v>267</v>
+      </c>
+      <c r="C111" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>86</v>
       </c>
-      <c r="C84" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+      <c r="B112" t="s">
+        <v>268</v>
+      </c>
+      <c r="C112" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>87</v>
       </c>
-      <c r="C85" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+      <c r="B113" t="s">
+        <v>269</v>
+      </c>
+      <c r="C113" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>88</v>
       </c>
-      <c r="C86" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+      <c r="B114" t="s">
+        <v>270</v>
+      </c>
+      <c r="C114" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>89</v>
       </c>
-      <c r="C87" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
+      <c r="B115" t="s">
+        <v>271</v>
+      </c>
+      <c r="C115" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>90</v>
       </c>
-      <c r="C88" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
+      <c r="B116" t="s">
+        <v>272</v>
+      </c>
+      <c r="C116" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>91</v>
       </c>
-      <c r="C89" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
+      <c r="B117" t="s">
+        <v>273</v>
+      </c>
+      <c r="C117" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>92</v>
       </c>
-      <c r="C90" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
+      <c r="B118" t="s">
+        <v>274</v>
+      </c>
+      <c r="C118" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>93</v>
       </c>
-      <c r="C91" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
+      <c r="B119" t="s">
+        <v>275</v>
+      </c>
+      <c r="C119" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>94</v>
       </c>
-      <c r="C92" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
+      <c r="B120" t="s">
+        <v>276</v>
+      </c>
+      <c r="C120" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>94</v>
+      </c>
+      <c r="B121" t="s">
+        <v>277</v>
+      </c>
+      <c r="C121" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>94</v>
+      </c>
+      <c r="B122" t="s">
+        <v>278</v>
+      </c>
+      <c r="C122" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>95</v>
       </c>
-      <c r="C93" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
+      <c r="B123" t="s">
+        <v>279</v>
+      </c>
+      <c r="C123" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
         <v>96</v>
       </c>
-      <c r="C94" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
+      <c r="B124" t="s">
+        <v>280</v>
+      </c>
+      <c r="C124" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>96</v>
+      </c>
+      <c r="B125" t="s">
+        <v>281</v>
+      </c>
+      <c r="C125" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>97</v>
       </c>
-      <c r="C95" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
+      <c r="B126" t="s">
+        <v>282</v>
+      </c>
+      <c r="C126" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>98</v>
       </c>
-      <c r="C96" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
+      <c r="B127" t="s">
+        <v>283</v>
+      </c>
+      <c r="C127" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>99</v>
       </c>
-      <c r="C97" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
+      <c r="B128" t="s">
+        <v>284</v>
+      </c>
+      <c r="C128" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>100</v>
       </c>
-      <c r="C98" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
+      <c r="B129" t="s">
+        <v>285</v>
+      </c>
+      <c r="C129" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>101</v>
       </c>
-      <c r="C99" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
+      <c r="B130" t="s">
+        <v>286</v>
+      </c>
+      <c r="C130" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>102</v>
       </c>
-      <c r="C100" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
+      <c r="B131" t="s">
+        <v>287</v>
+      </c>
+      <c r="C131" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
         <v>103</v>
       </c>
-      <c r="C101" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
+      <c r="B132" t="s">
+        <v>288</v>
+      </c>
+      <c r="C132" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>104</v>
       </c>
-      <c r="C102" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
+      <c r="B133" t="s">
+        <v>289</v>
+      </c>
+      <c r="C133" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>105</v>
       </c>
-      <c r="C103" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
+      <c r="B134" t="s">
+        <v>290</v>
+      </c>
+      <c r="C134" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>106</v>
       </c>
-      <c r="C104" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
+      <c r="B135" t="s">
+        <v>291</v>
+      </c>
+      <c r="C135" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>107</v>
       </c>
-      <c r="C105" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
+      <c r="B136" t="s">
+        <v>292</v>
+      </c>
+      <c r="C136" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>107</v>
+      </c>
+      <c r="B137" t="s">
+        <v>293</v>
+      </c>
+      <c r="C137" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>107</v>
+      </c>
+      <c r="B138" t="s">
+        <v>294</v>
+      </c>
+      <c r="C138" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
         <v>108</v>
       </c>
-      <c r="C106" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
+      <c r="B139" t="s">
+        <v>295</v>
+      </c>
+      <c r="C139" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
         <v>109</v>
       </c>
-      <c r="C107" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
+      <c r="B140" t="s">
+        <v>296</v>
+      </c>
+      <c r="C140" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
         <v>110</v>
       </c>
-      <c r="C108" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
+      <c r="B141" t="s">
+        <v>297</v>
+      </c>
+      <c r="C141" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>111</v>
       </c>
-      <c r="C109" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
+      <c r="B142" t="s">
+        <v>298</v>
+      </c>
+      <c r="C142" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>112</v>
       </c>
-      <c r="C110" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
+      <c r="B143" t="s">
+        <v>299</v>
+      </c>
+      <c r="C143" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>113</v>
       </c>
-      <c r="C111" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
+      <c r="B144" t="s">
+        <v>300</v>
+      </c>
+      <c r="C144" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>114</v>
       </c>
-      <c r="C112" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
+      <c r="B145" t="s">
+        <v>301</v>
+      </c>
+      <c r="C145" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
         <v>115</v>
       </c>
-      <c r="C113" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
+      <c r="B146" t="s">
+        <v>302</v>
+      </c>
+      <c r="C146" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>116</v>
       </c>
-      <c r="C114" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
+      <c r="B147" t="s">
+        <v>303</v>
+      </c>
+      <c r="C147" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>117</v>
       </c>
-      <c r="C115" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
+      <c r="B148" t="s">
+        <v>304</v>
+      </c>
+      <c r="C148" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>118</v>
       </c>
-      <c r="C116" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
+      <c r="B149" t="s">
+        <v>305</v>
+      </c>
+      <c r="C149" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
         <v>119</v>
       </c>
-      <c r="C117" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
+      <c r="B150" t="s">
+        <v>306</v>
+      </c>
+      <c r="C150" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
         <v>120</v>
       </c>
-      <c r="C118" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
+      <c r="B151" t="s">
+        <v>307</v>
+      </c>
+      <c r="C151" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
         <v>121</v>
       </c>
-      <c r="C119" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
+      <c r="B152" t="s">
+        <v>308</v>
+      </c>
+      <c r="C152" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
         <v>122</v>
       </c>
-      <c r="C120" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C121" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="1"/>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="1"/>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="1"/>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="1"/>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="1"/>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="1"/>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="1"/>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="1"/>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="1"/>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="1"/>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="1"/>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="1"/>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="1"/>
+      <c r="B153" t="s">
+        <v>309</v>
+      </c>
+      <c r="C153" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>131</v>
+      </c>
+      <c r="B154" t="s">
+        <v>310</v>
+      </c>
+      <c r="C154" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>131</v>
+      </c>
+      <c r="B155" t="s">
+        <v>311</v>
+      </c>
+      <c r="C155" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>132</v>
+      </c>
+      <c r="B156" t="s">
+        <v>312</v>
+      </c>
+      <c r="C156" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>133</v>
+      </c>
+      <c r="B157" t="s">
+        <v>313</v>
+      </c>
+      <c r="C157" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>134</v>
+      </c>
+      <c r="B158" t="s">
+        <v>314</v>
+      </c>
+      <c r="C158" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>135</v>
+      </c>
+      <c r="B159" t="s">
+        <v>315</v>
+      </c>
+      <c r="C159" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>136</v>
+      </c>
+      <c r="B160" t="s">
+        <v>316</v>
+      </c>
+      <c r="C160" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>137</v>
+      </c>
+      <c r="B161" t="s">
+        <v>317</v>
+      </c>
+      <c r="C161" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>138</v>
+      </c>
+      <c r="B162" t="s">
+        <v>318</v>
+      </c>
+      <c r="C162" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>139</v>
+      </c>
+      <c r="B163" t="s">
+        <v>319</v>
+      </c>
+      <c r="C163" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>140</v>
+      </c>
+      <c r="B164" t="s">
+        <v>320</v>
+      </c>
+      <c r="C164" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>141</v>
+      </c>
+      <c r="B165" t="s">
+        <v>321</v>
+      </c>
+      <c r="C165" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>142</v>
+      </c>
+      <c r="B166" t="s">
+        <v>322</v>
+      </c>
+      <c r="C166" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>143</v>
+      </c>
+      <c r="B167" t="s">
+        <v>323</v>
+      </c>
+      <c r="C167" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>144</v>
+      </c>
+      <c r="B168" t="s">
+        <v>324</v>
+      </c>
+      <c r="C168" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>145</v>
+      </c>
+      <c r="B169" t="s">
+        <v>325</v>
+      </c>
+      <c r="C169" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>146</v>
+      </c>
+      <c r="B170" t="s">
+        <v>326</v>
+      </c>
+      <c r="C170" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>147</v>
+      </c>
+      <c r="B171" t="s">
+        <v>327</v>
+      </c>
+      <c r="C171" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>148</v>
+      </c>
+      <c r="B172" t="s">
+        <v>328</v>
+      </c>
+      <c r="C172" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>149</v>
+      </c>
+      <c r="B173" t="s">
+        <v>329</v>
+      </c>
+      <c r="C173" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>150</v>
+      </c>
+      <c r="B174" t="s">
+        <v>330</v>
+      </c>
+      <c r="C174" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>151</v>
+      </c>
+      <c r="B175" t="s">
+        <v>331</v>
+      </c>
+      <c r="C175" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>152</v>
+      </c>
+      <c r="B176" t="s">
+        <v>332</v>
+      </c>
+      <c r="C176" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>153</v>
+      </c>
+      <c r="B177" t="s">
+        <v>333</v>
+      </c>
+      <c r="C177" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>154</v>
+      </c>
+      <c r="B178" t="s">
+        <v>334</v>
+      </c>
+      <c r="C178" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>155</v>
+      </c>
+      <c r="B179" t="s">
+        <v>335</v>
+      </c>
+      <c r="C179" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>156</v>
+      </c>
+      <c r="B180" t="s">
+        <v>336</v>
+      </c>
+      <c r="C180" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>157</v>
+      </c>
+      <c r="B181" t="s">
+        <v>337</v>
+      </c>
+      <c r="C181" t="s">
+        <v>343</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C496" xr:uid="{544EFAB1-8998-46EF-B9E5-D4918C9DF0DC}"/>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0323005F-70C4-44DE-B0FA-85F4E7845B8A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A259FE6E-A680-4290-AD20-A1CF6F8533EA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="978">
   <si>
     <t>UTK</t>
   </si>
@@ -1102,6 +1102,1866 @@
   </si>
   <si>
     <t>SZ-835</t>
+  </si>
+  <si>
+    <t>159995579543971534</t>
+  </si>
+  <si>
+    <t>159995579543971541</t>
+  </si>
+  <si>
+    <t>1040957306KR/1</t>
+  </si>
+  <si>
+    <t>1040957828KR/1</t>
+  </si>
+  <si>
+    <t>1040961529KR/1</t>
+  </si>
+  <si>
+    <t>1040961530KR/1</t>
+  </si>
+  <si>
+    <t>1340844601KR/1</t>
+  </si>
+  <si>
+    <t>6aa133492235a0231b9b10a4</t>
+  </si>
+  <si>
+    <t>6a9eac60c0fa1536b2701824</t>
+  </si>
+  <si>
+    <t>6a9aa4b2c0fa1536b26fe0dc</t>
+  </si>
+  <si>
+    <t>6a9acbbfc0fa1536b26fe740</t>
+  </si>
+  <si>
+    <t>6a9fc9972235a0231b9af16d</t>
+  </si>
+  <si>
+    <t>6a9fc9972235a0231b9af16f</t>
+  </si>
+  <si>
+    <t>6a8577e0c0fa1536b26e9b7a</t>
+  </si>
+  <si>
+    <t>6a97fc27c0fa1536b26faa91</t>
+  </si>
+  <si>
+    <t>6a9ee1bfc0fa1536b27020cf</t>
+  </si>
+  <si>
+    <t>6a9aabbbc0fa1536b26fe213</t>
+  </si>
+  <si>
+    <t>6a9ffc482235a0231b9afa86</t>
+  </si>
+  <si>
+    <t>6aa13c9f2235a0231b9b122a</t>
+  </si>
+  <si>
+    <t>6a9ebcffc0fa1536b2701b7c</t>
+  </si>
+  <si>
+    <t>6a9e744ec0fa1536b2700cf3</t>
+  </si>
+  <si>
+    <t>6a913a35c0fa1536b26f3db1</t>
+  </si>
+  <si>
+    <t>6aa01d802235a0231b9affd6</t>
+  </si>
+  <si>
+    <t>6a9ec09cc0fa1536b2701c31</t>
+  </si>
+  <si>
+    <t>6a9531afc0fa1536b26f6d41</t>
+  </si>
+  <si>
+    <t>6a9ed18ac0fa1536b2701ef5</t>
+  </si>
+  <si>
+    <t>6a9edf38c0fa1536b27020a3</t>
+  </si>
+  <si>
+    <t>6a9fd77f2235a0231b9af45c</t>
+  </si>
+  <si>
+    <t>6a9fd77f2235a0231b9af45d</t>
+  </si>
+  <si>
+    <t>6a95b7d0c0fa1536b26f83d1</t>
+  </si>
+  <si>
+    <t>6a95b7d0c0fa1536b26f83d4</t>
+  </si>
+  <si>
+    <t>6a9fbaed2235a0231b9aee90</t>
+  </si>
+  <si>
+    <t>6a96dab3c0fa1536b26f9921</t>
+  </si>
+  <si>
+    <t>6a96f578c0fa1536b26f9d2b</t>
+  </si>
+  <si>
+    <t>6a96f30bc0fa1536b26f9ce4</t>
+  </si>
+  <si>
+    <t>6a97024ac0fa1536b26f9e66</t>
+  </si>
+  <si>
+    <t>6a9eaedac0fa1536b27018ad</t>
+  </si>
+  <si>
+    <t>6a9f202ac0fa1536b2702479</t>
+  </si>
+  <si>
+    <t>6a9fd07f2235a0231b9af2e9</t>
+  </si>
+  <si>
+    <t>6a9ffa4d2235a0231b9afa43</t>
+  </si>
+  <si>
+    <t>6a9eb8c4c0fa1536b2701a64</t>
+  </si>
+  <si>
+    <t>6a9eb8c4c0fa1536b2701a65</t>
+  </si>
+  <si>
+    <t>6a984df4c0fa1536b26fb866</t>
+  </si>
+  <si>
+    <t>6a9a86c8c0fa1536b26fdbe6</t>
+  </si>
+  <si>
+    <t>6a996d15c0fa1536b26fcb8a</t>
+  </si>
+  <si>
+    <t>6a9ff9de2235a0231b9afa16</t>
+  </si>
+  <si>
+    <t>6aa11a442235a0231b9b0bf7</t>
+  </si>
+  <si>
+    <t>6aa11a442235a0231b9b0bf8</t>
+  </si>
+  <si>
+    <t>6aa11a442235a0231b9b0bf9</t>
+  </si>
+  <si>
+    <t>6aa10b4c2235a0231b9b095c</t>
+  </si>
+  <si>
+    <t>6a99e48fc0fa1536b26fd62e</t>
+  </si>
+  <si>
+    <t>6a9ea5fcc0fa1536b27016ee</t>
+  </si>
+  <si>
+    <t>6a9eaa25c0fa1536b27017be</t>
+  </si>
+  <si>
+    <t>6a9ea21dc0fa1536b2701662</t>
+  </si>
+  <si>
+    <t>6a9ea21dc0fa1536b2701664</t>
+  </si>
+  <si>
+    <t>6a9a82cdc0fa1536b26fdb19</t>
+  </si>
+  <si>
+    <t>6a9eaa26c0fa1536b27017c1</t>
+  </si>
+  <si>
+    <t>6a9a8e8ec0fa1536b26fdd55</t>
+  </si>
+  <si>
+    <t>6a9aa025c0fa1536b26fe054</t>
+  </si>
+  <si>
+    <t>6a9aa025c0fa1536b26fe056</t>
+  </si>
+  <si>
+    <t>6a9abfbdc0fa1536b26fe558</t>
+  </si>
+  <si>
+    <t>6a9abfbdc0fa1536b26fe559</t>
+  </si>
+  <si>
+    <t>6a9abfbcc0fa1536b26fe545</t>
+  </si>
+  <si>
+    <t>6a9af806c0fa1536b26feb6a</t>
+  </si>
+  <si>
+    <t>6a9a61fac0fa1536b26fd6ec</t>
+  </si>
+  <si>
+    <t>6a9ab537c0fa1536b26fe3ad</t>
+  </si>
+  <si>
+    <t>6a9adbd6c0fa1536b26fe913</t>
+  </si>
+  <si>
+    <t>6aa10f3d2235a0231b9b0a1c</t>
+  </si>
+  <si>
+    <t>6a9bcae7c0fa1536b26fef9b</t>
+  </si>
+  <si>
+    <t>6a9bcfa3c0fa1536b26ff047</t>
+  </si>
+  <si>
+    <t>6a9bcfa3c0fa1536b26ff049</t>
+  </si>
+  <si>
+    <t>6a9bd1f5c0fa1536b26ff07b</t>
+  </si>
+  <si>
+    <t>6a9be381c0fa1536b26ff34d</t>
+  </si>
+  <si>
+    <t>6a9be381c0fa1536b26ff34f</t>
+  </si>
+  <si>
+    <t>6a9c439ac0fa1536b26ffa50</t>
+  </si>
+  <si>
+    <t>6a9b9f8cc0fa1536b26fed6e</t>
+  </si>
+  <si>
+    <t>6a9bc3eec0fa1536b26fee9e</t>
+  </si>
+  <si>
+    <t>6a9ea1f3c0fa1536b270165e</t>
+  </si>
+  <si>
+    <t>6a9ea1f3c0fa1536b270165f</t>
+  </si>
+  <si>
+    <t>6a9bdc9bc0fa1536b26ff249</t>
+  </si>
+  <si>
+    <t>6a9be5e3c0fa1536b26ff3b2</t>
+  </si>
+  <si>
+    <t>6a9bf2cdc0fa1536b26ff4db</t>
+  </si>
+  <si>
+    <t>6a9c100bc0fa1536b26ff6e0</t>
+  </si>
+  <si>
+    <t>6a9c0323c0fa1536b26ff5e5</t>
+  </si>
+  <si>
+    <t>6a9c5e8dc0fa1536b26ffb4e</t>
+  </si>
+  <si>
+    <t>6a9d1b3ec0fa1536b26ffce4</t>
+  </si>
+  <si>
+    <t>6a9d9e9dc0fa1536b27005b9</t>
+  </si>
+  <si>
+    <t>6a9d9e9dc0fa1536b27005bb</t>
+  </si>
+  <si>
+    <t>6a9d5e0dc0fa1536b27001d8</t>
+  </si>
+  <si>
+    <t>6a9d5e0dc0fa1536b27001d9</t>
+  </si>
+  <si>
+    <t>6a9db266c0fa1536b270066b</t>
+  </si>
+  <si>
+    <t>6a9e79a9c0fa1536b2700e3b</t>
+  </si>
+  <si>
+    <t>6a9fbd282235a0231b9aef04</t>
+  </si>
+  <si>
+    <t>6a9e8c67c0fa1536b2701265</t>
+  </si>
+  <si>
+    <t>6aa12c1d2235a0231b9b0f4d</t>
+  </si>
+  <si>
+    <t>6a9ea375c0fa1536b270169d</t>
+  </si>
+  <si>
+    <t>6aa11be92235a0231b9b0c82</t>
+  </si>
+  <si>
+    <t>6aa11be92235a0231b9b0c84</t>
+  </si>
+  <si>
+    <t>6a9eba10c0fa1536b2701aa7</t>
+  </si>
+  <si>
+    <t>6a9ebed7c0fa1536b2701be8</t>
+  </si>
+  <si>
+    <t>6a9ebed7c0fa1536b2701be9</t>
+  </si>
+  <si>
+    <t>6a9ec25ec0fa1536b2701ca2</t>
+  </si>
+  <si>
+    <t>6a9ec37bc0fa1536b2701cbf</t>
+  </si>
+  <si>
+    <t>6a9ec3a9c0fa1536b2701cc6</t>
+  </si>
+  <si>
+    <t>6a9ec3a9c0fa1536b2701cc7</t>
+  </si>
+  <si>
+    <t>6a9ec4b4c0fa1536b2701cec</t>
+  </si>
+  <si>
+    <t>6a9ec4b4c0fa1536b2701ced</t>
+  </si>
+  <si>
+    <t>6a9ec845c0fa1536b2701d7c</t>
+  </si>
+  <si>
+    <t>6a9ec845c0fa1536b2701d7d</t>
+  </si>
+  <si>
+    <t>6a9ece11c0fa1536b2701e5a</t>
+  </si>
+  <si>
+    <t>6a9ece11c0fa1536b2701e5b</t>
+  </si>
+  <si>
+    <t>6a9ece11c0fa1536b2701e5e</t>
+  </si>
+  <si>
+    <t>6a9edd3cc0fa1536b270205c</t>
+  </si>
+  <si>
+    <t>6a9edd3cc0fa1536b270205d</t>
+  </si>
+  <si>
+    <t>6a9ed75cc0fa1536b2701fb4</t>
+  </si>
+  <si>
+    <t>6a9ed75cc0fa1536b2701fb5</t>
+  </si>
+  <si>
+    <t>6a9ee1f6c0fa1536b27020df</t>
+  </si>
+  <si>
+    <t>6a9eeb49c0fa1536b27021e0</t>
+  </si>
+  <si>
+    <t>6aa134b82235a0231b9b10cb</t>
+  </si>
+  <si>
+    <t>6a9ef380c0fa1536b2702276</t>
+  </si>
+  <si>
+    <t>6a9f018ec0fa1536b270236b</t>
+  </si>
+  <si>
+    <t>6a9f0af6c0fa1536b27023f6</t>
+  </si>
+  <si>
+    <t>6a9e7502c0fa1536b2700d15</t>
+  </si>
+  <si>
+    <t>6a9e88e6c0fa1536b27011b5</t>
+  </si>
+  <si>
+    <t>6a9eb693c0fa1536b2701a18</t>
+  </si>
+  <si>
+    <t>6a9ea502c0fa1536b27016da</t>
+  </si>
+  <si>
+    <t>6a9eae5fc0fa1536b270189a</t>
+  </si>
+  <si>
+    <t>6a9eae5fc0fa1536b2701894</t>
+  </si>
+  <si>
+    <t>6a9eaf98c0fa1536b27018dc</t>
+  </si>
+  <si>
+    <t>6a9eb0bdc0fa1536b27018f1</t>
+  </si>
+  <si>
+    <t>6a9eb30ac0fa1536b2701963</t>
+  </si>
+  <si>
+    <t>6a9eb30ac0fa1536b2701965</t>
+  </si>
+  <si>
+    <t>6a9eb30ac0fa1536b2701968</t>
+  </si>
+  <si>
+    <t>6a9eb56cc0fa1536b27019ee</t>
+  </si>
+  <si>
+    <t>6a9ebb44c0fa1536b2701b14</t>
+  </si>
+  <si>
+    <t>6a9ebdacc0fa1536b2701b84</t>
+  </si>
+  <si>
+    <t>6a9ec4a1c0fa1536b2701ce6</t>
+  </si>
+  <si>
+    <t>6a9ebffac0fa1536b2701c0e</t>
+  </si>
+  <si>
+    <t>6a9ec24bc0fa1536b2701c8e</t>
+  </si>
+  <si>
+    <t>6a9eca82c0fa1536b2701dcc</t>
+  </si>
+  <si>
+    <t>6a9ecf75c0fa1536b2701e9f</t>
+  </si>
+  <si>
+    <t>6a9ecf75c0fa1536b2701ea1</t>
+  </si>
+  <si>
+    <t>6a9ecf31c0fa1536b2701e8e</t>
+  </si>
+  <si>
+    <t>6a9edc17c0fa1536b2702048</t>
+  </si>
+  <si>
+    <t>6a9edf93c0fa1536b27020af</t>
+  </si>
+  <si>
+    <t>6a9ee336c0fa1536b2702101</t>
+  </si>
+  <si>
+    <t>6a9ef010c0fa1536b2702242</t>
+  </si>
+  <si>
+    <t>6a9eec7cc0fa1536b27021f0</t>
+  </si>
+  <si>
+    <t>6a9f0aebc0fa1536b27023e0</t>
+  </si>
+  <si>
+    <t>6a9f10cbc0fa1536b2702436</t>
+  </si>
+  <si>
+    <t>6a9f2cf0c0fa1536b270248e</t>
+  </si>
+  <si>
+    <t>6a9fb9932235a0231b9aee50</t>
+  </si>
+  <si>
+    <t>6a9fbf6f2235a0231b9aef89</t>
+  </si>
+  <si>
+    <t>6a9fc3012235a0231b9af02c</t>
+  </si>
+  <si>
+    <t>6a9fd0fb2235a0231b9af2f9</t>
+  </si>
+  <si>
+    <t>6a9fc68d2235a0231b9af0d5</t>
+  </si>
+  <si>
+    <t>6a9fcb262235a0231b9af1d9</t>
+  </si>
+  <si>
+    <t>6a9fcb262235a0231b9af1dd</t>
+  </si>
+  <si>
+    <t>6a9fd2312235a0231b9af36c</t>
+  </si>
+  <si>
+    <t>6a9fd9352235a0231b9af4a5</t>
+  </si>
+  <si>
+    <t>6a9fd3592235a0231b9af3b9</t>
+  </si>
+  <si>
+    <t>6a9fdf4b2235a0231b9af5a7</t>
+  </si>
+  <si>
+    <t>6a9fe8752235a0231b9af6f6</t>
+  </si>
+  <si>
+    <t>6a9fed2a2235a0231b9af7e3</t>
+  </si>
+  <si>
+    <t>6a9fed2a2235a0231b9af7e4</t>
+  </si>
+  <si>
+    <t>6a9fed2a2235a0231b9af7e6</t>
+  </si>
+  <si>
+    <t>6a9ff09d2235a0231b9af89a</t>
+  </si>
+  <si>
+    <t>6a9ff4262235a0231b9af93f</t>
+  </si>
+  <si>
+    <t>6aa02fe62235a0231b9b028d</t>
+  </si>
+  <si>
+    <t>6aa03cc92235a0231b9b03c5</t>
+  </si>
+  <si>
+    <t>6aa042ac2235a0231b9b045a</t>
+  </si>
+  <si>
+    <t>6aa04e5f2235a0231b9b052f</t>
+  </si>
+  <si>
+    <t>6a9f9fc12235a0231b9aebc9</t>
+  </si>
+  <si>
+    <t>6a9fb7382235a0231b9aeda9</t>
+  </si>
+  <si>
+    <t>6a9fb85e2235a0231b9aede0</t>
+  </si>
+  <si>
+    <t>6a9fb85e2235a0231b9aede1</t>
+  </si>
+  <si>
+    <t>6a9fb85e2235a0231b9aedd1</t>
+  </si>
+  <si>
+    <t>6a9fbab52235a0231b9aee69</t>
+  </si>
+  <si>
+    <t>6a9fbe5a2235a0231b9aef4a</t>
+  </si>
+  <si>
+    <t>6a9fbe5a2235a0231b9aef4b</t>
+  </si>
+  <si>
+    <t>6a9fbbe72235a0231b9aeead</t>
+  </si>
+  <si>
+    <t>6a9fbe442235a0231b9aef45</t>
+  </si>
+  <si>
+    <t>6a9fc0a12235a0231b9aefc8</t>
+  </si>
+  <si>
+    <t>6a9fc68d2235a0231b9af0d4</t>
+  </si>
+  <si>
+    <t>6a9fc6a02235a0231b9af0e4</t>
+  </si>
+  <si>
+    <t>6a9fc6a02235a0231b9af0e5</t>
+  </si>
+  <si>
+    <t>6a9fe9962235a0231b9af712</t>
+  </si>
+  <si>
+    <t>6a9fef852235a0231b9af862</t>
+  </si>
+  <si>
+    <t>6a9fef852235a0231b9af863</t>
+  </si>
+  <si>
+    <t>6a9fef852235a0231b9af866</t>
+  </si>
+  <si>
+    <t>6aa00a6f2235a0231b9afc76</t>
+  </si>
+  <si>
+    <t>6aa00a6f2235a0231b9afc78</t>
+  </si>
+  <si>
+    <t>6aa00cee2235a0231b9afcd8</t>
+  </si>
+  <si>
+    <t>6aa0177d2235a0231b9afeb1</t>
+  </si>
+  <si>
+    <t>6aa018792235a0231b9afef6</t>
+  </si>
+  <si>
+    <t>6aa01ad02235a0231b9aff49</t>
+  </si>
+  <si>
+    <t>6aa01ad02235a0231b9aff4b</t>
+  </si>
+  <si>
+    <t>6aa01fa12235a0231b9b005a</t>
+  </si>
+  <si>
+    <t>6aa024322235a0231b9b0122</t>
+  </si>
+  <si>
+    <t>6aa040532235a0231b9b041d</t>
+  </si>
+  <si>
+    <t>6aa040532235a0231b9b041e</t>
+  </si>
+  <si>
+    <t>6aa0ff592235a0231b9b07cd</t>
+  </si>
+  <si>
+    <t>6aa10b192235a0231b9b0955</t>
+  </si>
+  <si>
+    <t>6aa11a4e2235a0231b9b0c0b</t>
+  </si>
+  <si>
+    <t>6aa11a4e2235a0231b9b0c0c</t>
+  </si>
+  <si>
+    <t>6aa12d0c2235a0231b9b0f71</t>
+  </si>
+  <si>
+    <t>6aa142272235a0231b9b1312</t>
+  </si>
+  <si>
+    <t>6aa10c402235a0231b9b0988</t>
+  </si>
+  <si>
+    <t>6aa10c662235a0231b9b098b</t>
+  </si>
+  <si>
+    <t>6aa1180c2235a0231b9b0ba9</t>
+  </si>
+  <si>
+    <t>6aa11ca52235a0231b9b0c8f</t>
+  </si>
+  <si>
+    <t>6aa11ca52235a0231b9b0c92</t>
+  </si>
+  <si>
+    <t>6aa129912235a0231b9b0ed8</t>
+  </si>
+  <si>
+    <t>6aa129912235a0231b9b0eda</t>
+  </si>
+  <si>
+    <t>6aa12d192235a0231b9b0f84</t>
+  </si>
+  <si>
+    <t>6aa138c02235a0231b9b1197</t>
+  </si>
+  <si>
+    <t>1449-789072</t>
+  </si>
+  <si>
+    <t>1449-268141</t>
+  </si>
+  <si>
+    <t>1449-556602</t>
+  </si>
+  <si>
+    <t>1449-517908</t>
+  </si>
+  <si>
+    <t>1449-193883</t>
+  </si>
+  <si>
+    <t>1449-389329</t>
+  </si>
+  <si>
+    <t>1449-737753</t>
+  </si>
+  <si>
+    <t>1449-785784</t>
+  </si>
+  <si>
+    <t>1449-951086</t>
+  </si>
+  <si>
+    <t>1449-897583</t>
+  </si>
+  <si>
+    <t>1449-408336</t>
+  </si>
+  <si>
+    <t>1449-868734</t>
+  </si>
+  <si>
+    <t>1449-267469</t>
+  </si>
+  <si>
+    <t>1449-892797</t>
+  </si>
+  <si>
+    <t>1449-845966</t>
+  </si>
+  <si>
+    <t>1449-953736</t>
+  </si>
+  <si>
+    <t>1449-723261</t>
+  </si>
+  <si>
+    <t>1449-414623</t>
+  </si>
+  <si>
+    <t>26MPE0009459/1</t>
+  </si>
+  <si>
+    <t>26MPE0009464/1</t>
+  </si>
+  <si>
+    <t>26MPE0009464/2</t>
+  </si>
+  <si>
+    <t>26MPE0009529/1</t>
+  </si>
+  <si>
+    <t>26MPE0009531/1</t>
+  </si>
+  <si>
+    <t>326268163/1</t>
+  </si>
+  <si>
+    <t>326268648/1</t>
+  </si>
+  <si>
+    <t>326457560/1</t>
+  </si>
+  <si>
+    <t>326514935/1</t>
+  </si>
+  <si>
+    <t>326514935/2</t>
+  </si>
+  <si>
+    <t>326514935/3</t>
+  </si>
+  <si>
+    <t>326667031/1</t>
+  </si>
+  <si>
+    <t>326667031/2</t>
+  </si>
+  <si>
+    <t>326667888/1</t>
+  </si>
+  <si>
+    <t>326667888/2</t>
+  </si>
+  <si>
+    <t>326716883/1</t>
+  </si>
+  <si>
+    <t>326860551/1</t>
+  </si>
+  <si>
+    <t>326860551/2</t>
+  </si>
+  <si>
+    <t>326860551/3</t>
+  </si>
+  <si>
+    <t>326913668/1</t>
+  </si>
+  <si>
+    <t>326913668/2</t>
+  </si>
+  <si>
+    <t>326913716/1</t>
+  </si>
+  <si>
+    <t>326913716/2</t>
+  </si>
+  <si>
+    <t>326913792/1</t>
+  </si>
+  <si>
+    <t>326913792/2</t>
+  </si>
+  <si>
+    <t>326968119/1</t>
+  </si>
+  <si>
+    <t>326968119/2</t>
+  </si>
+  <si>
+    <t>326968124/1</t>
+  </si>
+  <si>
+    <t>326968124/2</t>
+  </si>
+  <si>
+    <t>326968124/3</t>
+  </si>
+  <si>
+    <t>327026656/1</t>
+  </si>
+  <si>
+    <t>327110047/1</t>
+  </si>
+  <si>
+    <t>327253153/1</t>
+  </si>
+  <si>
+    <t>327253190/1</t>
+  </si>
+  <si>
+    <t>327253262/1</t>
+  </si>
+  <si>
+    <t>327253320/1</t>
+  </si>
+  <si>
+    <t>327253389/1</t>
+  </si>
+  <si>
+    <t>327253398/1</t>
+  </si>
+  <si>
+    <t>327253474/1</t>
+  </si>
+  <si>
+    <t>327253477/1</t>
+  </si>
+  <si>
+    <t>327253532/1</t>
+  </si>
+  <si>
+    <t>327253611/1</t>
+  </si>
+  <si>
+    <t>327253630/1</t>
+  </si>
+  <si>
+    <t>327253731/1</t>
+  </si>
+  <si>
+    <t>327355244/1</t>
+  </si>
+  <si>
+    <t>327402525/1</t>
+  </si>
+  <si>
+    <t>327402525/2</t>
+  </si>
+  <si>
+    <t>51340047590KR/1</t>
+  </si>
+  <si>
+    <t>51340047669KR/1</t>
+  </si>
+  <si>
+    <t>540953052KR/1</t>
+  </si>
+  <si>
+    <t>540953052KR/2</t>
+  </si>
+  <si>
+    <t>540953052KR/3</t>
+  </si>
+  <si>
+    <t>540953052KR/4</t>
+  </si>
+  <si>
+    <t>159995579543940530</t>
+  </si>
+  <si>
+    <t>941155215KR/1</t>
+  </si>
+  <si>
+    <t>941155219KR/1</t>
+  </si>
+  <si>
+    <t>941155219KR/2</t>
+  </si>
+  <si>
+    <t>941155228KR/1</t>
+  </si>
+  <si>
+    <t>941155245KR/1</t>
+  </si>
+  <si>
+    <t>99003180/1</t>
+  </si>
+  <si>
+    <t>159995579543968398</t>
+  </si>
+  <si>
+    <t>159995579543968107</t>
+  </si>
+  <si>
+    <t>202609102601882901</t>
+  </si>
+  <si>
+    <t>202609072601895501</t>
+  </si>
+  <si>
+    <t>202609082601905401</t>
+  </si>
+  <si>
+    <t>202609082601900601</t>
+  </si>
+  <si>
+    <t>202609082601903501</t>
+  </si>
+  <si>
+    <t>202609092601909301</t>
+  </si>
+  <si>
+    <t>202609092601908401</t>
+  </si>
+  <si>
+    <t>202609092601908301</t>
+  </si>
+  <si>
+    <t>202609092601907701</t>
+  </si>
+  <si>
+    <t>202609102601915501</t>
+  </si>
+  <si>
+    <t>202609102601915701</t>
+  </si>
+  <si>
+    <t>159995579543873838</t>
+  </si>
+  <si>
+    <t>202609082601869401</t>
+  </si>
+  <si>
+    <t>202609092601870801</t>
+  </si>
+  <si>
+    <t>202609072601893301</t>
+  </si>
+  <si>
+    <t>202609082601906801</t>
+  </si>
+  <si>
+    <t>202609082601906101</t>
+  </si>
+  <si>
+    <t>202609082601900401</t>
+  </si>
+  <si>
+    <t>202609092601909001</t>
+  </si>
+  <si>
+    <t>202609102601915801</t>
+  </si>
+  <si>
+    <t>159995579543985029</t>
+  </si>
+  <si>
+    <t>159995579543982400</t>
+  </si>
+  <si>
+    <t>159995579543982417</t>
+  </si>
+  <si>
+    <t>159995579543987085</t>
+  </si>
+  <si>
+    <t>159995579543977949</t>
+  </si>
+  <si>
+    <t>159995579543977956</t>
+  </si>
+  <si>
+    <t>159995579543977963</t>
+  </si>
+  <si>
+    <t>159995579543940615</t>
+  </si>
+  <si>
+    <t>K-941</t>
+  </si>
+  <si>
+    <t>K-951</t>
+  </si>
+  <si>
+    <t>K-952</t>
+  </si>
+  <si>
+    <t>K-921</t>
+  </si>
+  <si>
+    <t>K-911</t>
+  </si>
+  <si>
+    <t>K-953</t>
+  </si>
+  <si>
+    <t>K-991</t>
+  </si>
+  <si>
+    <t>K-983</t>
+  </si>
+  <si>
+    <t>K-962</t>
+  </si>
+  <si>
+    <t>K-974</t>
+  </si>
+  <si>
+    <t>K-9131</t>
+  </si>
+  <si>
+    <t>K-922</t>
+  </si>
+  <si>
+    <t>K-999</t>
+  </si>
+  <si>
+    <t>K-902</t>
+  </si>
+  <si>
+    <t>K-918</t>
+  </si>
+  <si>
+    <t>K-931</t>
+  </si>
+  <si>
+    <t>K-943</t>
+  </si>
+  <si>
+    <t>K-963</t>
+  </si>
+  <si>
+    <t>K-982</t>
+  </si>
+  <si>
+    <t>K-9122</t>
+  </si>
+  <si>
+    <t>K-961</t>
+  </si>
+  <si>
+    <t>K-981</t>
+  </si>
+  <si>
+    <t>K-903</t>
+  </si>
+  <si>
+    <t>K-971</t>
+  </si>
+  <si>
+    <t>K-992</t>
+  </si>
+  <si>
+    <t>K-964</t>
+  </si>
+  <si>
+    <t>K-942</t>
+  </si>
+  <si>
+    <t>K-930</t>
+  </si>
+  <si>
+    <t>K-9132</t>
+  </si>
+  <si>
+    <t>K-998</t>
+  </si>
+  <si>
+    <t>K-9121</t>
+  </si>
+  <si>
+    <t>K-910</t>
+  </si>
+  <si>
+    <t>1-7497/2026</t>
+  </si>
+  <si>
+    <t>1040957306KR</t>
+  </si>
+  <si>
+    <t>1040957828KR</t>
+  </si>
+  <si>
+    <t>1040961529KR</t>
+  </si>
+  <si>
+    <t>1040961530KR</t>
+  </si>
+  <si>
+    <t>1340844601KR</t>
+  </si>
+  <si>
+    <t>260805-F00009726</t>
+  </si>
+  <si>
+    <t>260807-F00001879</t>
+  </si>
+  <si>
+    <t>260810-F00016277</t>
+  </si>
+  <si>
+    <t>260812-F00009928</t>
+  </si>
+  <si>
+    <t>260817-F00016117</t>
+  </si>
+  <si>
+    <t>260819-F00004383</t>
+  </si>
+  <si>
+    <t>260819-F00010282</t>
+  </si>
+  <si>
+    <t>260824-F00007847</t>
+  </si>
+  <si>
+    <t>260826-F00011180</t>
+  </si>
+  <si>
+    <t>260827-F00001748</t>
+  </si>
+  <si>
+    <t>260828-F00008093</t>
+  </si>
+  <si>
+    <t>260828-F00010612</t>
+  </si>
+  <si>
+    <t>260828-F00014474</t>
+  </si>
+  <si>
+    <t>260828-W00001952</t>
+  </si>
+  <si>
+    <t>260828-W00002139</t>
+  </si>
+  <si>
+    <t>260829-F00002835</t>
+  </si>
+  <si>
+    <t>260831-F00000915</t>
+  </si>
+  <si>
+    <t>260831-F00015697</t>
+  </si>
+  <si>
+    <t>260831-F00016318</t>
+  </si>
+  <si>
+    <t>260831-F00016776</t>
+  </si>
+  <si>
+    <t>260831-F00017057</t>
+  </si>
+  <si>
+    <t>260901-W00006579</t>
+  </si>
+  <si>
+    <t>260901-W00007879</t>
+  </si>
+  <si>
+    <t>260901-W00009487</t>
+  </si>
+  <si>
+    <t>260901-W00009544</t>
+  </si>
+  <si>
+    <t>260901-W00010370</t>
+  </si>
+  <si>
+    <t>260902-F00001750</t>
+  </si>
+  <si>
+    <t>260902-F00002670</t>
+  </si>
+  <si>
+    <t>260902-F00013918</t>
+  </si>
+  <si>
+    <t>260902-F00014199</t>
+  </si>
+  <si>
+    <t>260902-F00014764</t>
+  </si>
+  <si>
+    <t>260902-W00005915</t>
+  </si>
+  <si>
+    <t>260903-F00006877</t>
+  </si>
+  <si>
+    <t>260903-F00010004</t>
+  </si>
+  <si>
+    <t>260903-F00012484</t>
+  </si>
+  <si>
+    <t>260903-F00012548</t>
+  </si>
+  <si>
+    <t>260903-F00013419</t>
+  </si>
+  <si>
+    <t>260903-W00013799</t>
+  </si>
+  <si>
+    <t>260904-F00001156</t>
+  </si>
+  <si>
+    <t>260904-F00001195</t>
+  </si>
+  <si>
+    <t>260904-F00002428</t>
+  </si>
+  <si>
+    <t>260904-F00003217</t>
+  </si>
+  <si>
+    <t>260904-F00003934</t>
+  </si>
+  <si>
+    <t>260904-F00004222</t>
+  </si>
+  <si>
+    <t>260904-F00007047-1</t>
+  </si>
+  <si>
+    <t>260904-F00010402</t>
+  </si>
+  <si>
+    <t>260904-F00010779</t>
+  </si>
+  <si>
+    <t>260904-F00015735</t>
+  </si>
+  <si>
+    <t>260904-W00001453</t>
+  </si>
+  <si>
+    <t>260904-W00006715</t>
+  </si>
+  <si>
+    <t>260904-W00007305</t>
+  </si>
+  <si>
+    <t>260904-W00007936</t>
+  </si>
+  <si>
+    <t>260905-F00001222</t>
+  </si>
+  <si>
+    <t>260905-F00001591</t>
+  </si>
+  <si>
+    <t>260905-F00001785</t>
+  </si>
+  <si>
+    <t>260905-F00003078</t>
+  </si>
+  <si>
+    <t>260905-F00007080</t>
+  </si>
+  <si>
+    <t>260905-W00000683</t>
+  </si>
+  <si>
+    <t>260905-W00002010</t>
+  </si>
+  <si>
+    <t>260905-W00002286</t>
+  </si>
+  <si>
+    <t>260905-W00003290</t>
+  </si>
+  <si>
+    <t>260905-W00003851</t>
+  </si>
+  <si>
+    <t>260905-W00004613</t>
+  </si>
+  <si>
+    <t>260905-W00005436</t>
+  </si>
+  <si>
+    <t>260905-W00005451</t>
+  </si>
+  <si>
+    <t>260905-W00009844</t>
+  </si>
+  <si>
+    <t>260906-F00000575</t>
+  </si>
+  <si>
+    <t>260906-F00004719</t>
+  </si>
+  <si>
+    <t>260906-W00005344</t>
+  </si>
+  <si>
+    <t>260906-W00009645</t>
+  </si>
+  <si>
+    <t>260907-F00004345</t>
+  </si>
+  <si>
+    <t>260907-F00006088</t>
+  </si>
+  <si>
+    <t>260907-F00006610</t>
+  </si>
+  <si>
+    <t>260907-F00006666-1</t>
+  </si>
+  <si>
+    <t>260907-F00009642</t>
+  </si>
+  <si>
+    <t>260907-F00010803</t>
+  </si>
+  <si>
+    <t>260907-F00012734</t>
+  </si>
+  <si>
+    <t>260907-F00013472</t>
+  </si>
+  <si>
+    <t>260907-F00013639</t>
+  </si>
+  <si>
+    <t>260907-F00013881</t>
+  </si>
+  <si>
+    <t>260907-F00014188</t>
+  </si>
+  <si>
+    <t>260907-F00014279</t>
+  </si>
+  <si>
+    <t>260907-F00014614</t>
+  </si>
+  <si>
+    <t>260907-F00014900</t>
+  </si>
+  <si>
+    <t>260907-F00015721-1</t>
+  </si>
+  <si>
+    <t>260907-F00016023</t>
+  </si>
+  <si>
+    <t>260907-F00016980</t>
+  </si>
+  <si>
+    <t>260907-F00017520</t>
+  </si>
+  <si>
+    <t>260907-F00017829</t>
+  </si>
+  <si>
+    <t>260907-F00017861</t>
+  </si>
+  <si>
+    <t>260907-F00018388</t>
+  </si>
+  <si>
+    <t>260907-F00018525</t>
+  </si>
+  <si>
+    <t>260907-W00002975</t>
+  </si>
+  <si>
+    <t>260907-W00004397</t>
+  </si>
+  <si>
+    <t>260907-W00006299</t>
+  </si>
+  <si>
+    <t>260907-W00006417</t>
+  </si>
+  <si>
+    <t>260907-W00007104</t>
+  </si>
+  <si>
+    <t>260907-W00007119</t>
+  </si>
+  <si>
+    <t>260907-W00007206</t>
+  </si>
+  <si>
+    <t>260907-W00007230</t>
+  </si>
+  <si>
+    <t>260907-W00007344</t>
+  </si>
+  <si>
+    <t>260907-W00007361</t>
+  </si>
+  <si>
+    <t>260907-W00007616</t>
+  </si>
+  <si>
+    <t>260907-W00007972</t>
+  </si>
+  <si>
+    <t>260907-W00007986</t>
+  </si>
+  <si>
+    <t>260907-W00008292</t>
+  </si>
+  <si>
+    <t>260907-W00008328</t>
+  </si>
+  <si>
+    <t>260907-W00008487</t>
+  </si>
+  <si>
+    <t>260907-W00008984</t>
+  </si>
+  <si>
+    <t>260907-W00009212</t>
+  </si>
+  <si>
+    <t>260907-W00009353</t>
+  </si>
+  <si>
+    <t>260907-W00010091</t>
+  </si>
+  <si>
+    <t>260907-W00010328</t>
+  </si>
+  <si>
+    <t>260907-W00010364</t>
+  </si>
+  <si>
+    <t>260907-W00010507</t>
+  </si>
+  <si>
+    <t>260907-W00010599</t>
+  </si>
+  <si>
+    <t>260907-W00011880</t>
+  </si>
+  <si>
+    <t>260907-W00012599</t>
+  </si>
+  <si>
+    <t>260907-W00014081</t>
+  </si>
+  <si>
+    <t>260908-F00001607</t>
+  </si>
+  <si>
+    <t>260908-F00002220</t>
+  </si>
+  <si>
+    <t>260908-F00002604-1</t>
+  </si>
+  <si>
+    <t>260908-F00003082</t>
+  </si>
+  <si>
+    <t>260908-F00003260</t>
+  </si>
+  <si>
+    <t>260908-F00003860</t>
+  </si>
+  <si>
+    <t>260908-F00004722-3</t>
+  </si>
+  <si>
+    <t>260908-F00004848</t>
+  </si>
+  <si>
+    <t>260908-F00005206</t>
+  </si>
+  <si>
+    <t>260908-F00006705</t>
+  </si>
+  <si>
+    <t>260908-F00007732-1</t>
+  </si>
+  <si>
+    <t>260908-F00008214</t>
+  </si>
+  <si>
+    <t>260908-F00008300</t>
+  </si>
+  <si>
+    <t>260908-F00008760</t>
+  </si>
+  <si>
+    <t>260908-F00009051</t>
+  </si>
+  <si>
+    <t>260908-F00015700</t>
+  </si>
+  <si>
+    <t>260908-F00016408</t>
+  </si>
+  <si>
+    <t>260908-F00016717</t>
+  </si>
+  <si>
+    <t>260908-F00017090</t>
+  </si>
+  <si>
+    <t>260908-W00000946</t>
+  </si>
+  <si>
+    <t>260908-W00001607</t>
+  </si>
+  <si>
+    <t>260908-W00001860</t>
+  </si>
+  <si>
+    <t>260908-W00002018</t>
+  </si>
+  <si>
+    <t>260908-W00002202</t>
+  </si>
+  <si>
+    <t>260908-W00002216</t>
+  </si>
+  <si>
+    <t>260908-W00002284</t>
+  </si>
+  <si>
+    <t>260908-W00002387</t>
+  </si>
+  <si>
+    <t>260908-W00002624</t>
+  </si>
+  <si>
+    <t>260908-W00002691</t>
+  </si>
+  <si>
+    <t>260908-W00002995</t>
+  </si>
+  <si>
+    <t>260908-W00005252</t>
+  </si>
+  <si>
+    <t>260908-W00005612</t>
+  </si>
+  <si>
+    <t>260908-W00007249</t>
+  </si>
+  <si>
+    <t>260908-W00007482</t>
+  </si>
+  <si>
+    <t>260908-W00008016</t>
+  </si>
+  <si>
+    <t>260908-W00008231</t>
+  </si>
+  <si>
+    <t>260908-W00008356</t>
+  </si>
+  <si>
+    <t>260908-W00008472</t>
+  </si>
+  <si>
+    <t>260908-W00008906</t>
+  </si>
+  <si>
+    <t>260908-W00010806</t>
+  </si>
+  <si>
+    <t>260909-F00000634</t>
+  </si>
+  <si>
+    <t>260909-F00001115</t>
+  </si>
+  <si>
+    <t>260909-F00003670</t>
+  </si>
+  <si>
+    <t>260909-F00006195</t>
+  </si>
+  <si>
+    <t>260909-F00008619-1</t>
+  </si>
+  <si>
+    <t>260909-W00002405</t>
+  </si>
+  <si>
+    <t>260909-W00002464</t>
+  </si>
+  <si>
+    <t>260909-W00003105</t>
+  </si>
+  <si>
+    <t>260909-W00003510</t>
+  </si>
+  <si>
+    <t>260909-W00004288</t>
+  </si>
+  <si>
+    <t>260909-W00004664</t>
+  </si>
+  <si>
+    <t>260909-W00005341</t>
+  </si>
+  <si>
+    <t>267012718</t>
+  </si>
+  <si>
+    <t>267012766</t>
+  </si>
+  <si>
+    <t>267012783</t>
+  </si>
+  <si>
+    <t>267012824</t>
+  </si>
+  <si>
+    <t>267012827</t>
+  </si>
+  <si>
+    <t>267012856</t>
+  </si>
+  <si>
+    <t>267012868</t>
+  </si>
+  <si>
+    <t>267012878</t>
+  </si>
+  <si>
+    <t>267012882</t>
+  </si>
+  <si>
+    <t>267012887</t>
+  </si>
+  <si>
+    <t>267012896</t>
+  </si>
+  <si>
+    <t>267012900</t>
+  </si>
+  <si>
+    <t>267012917</t>
+  </si>
+  <si>
+    <t>267012929</t>
+  </si>
+  <si>
+    <t>267012952</t>
+  </si>
+  <si>
+    <t>267012960</t>
+  </si>
+  <si>
+    <t>267012982</t>
+  </si>
+  <si>
+    <t>267012993</t>
+  </si>
+  <si>
+    <t>26MPE0009459</t>
+  </si>
+  <si>
+    <t>26MPE0009464</t>
+  </si>
+  <si>
+    <t>26MPE0009529</t>
+  </si>
+  <si>
+    <t>26MPE0009531</t>
+  </si>
+  <si>
+    <t>326268163</t>
+  </si>
+  <si>
+    <t>326268648</t>
+  </si>
+  <si>
+    <t>326457560</t>
+  </si>
+  <si>
+    <t>326514935</t>
+  </si>
+  <si>
+    <t>326667031</t>
+  </si>
+  <si>
+    <t>326667888</t>
+  </si>
+  <si>
+    <t>326716883</t>
+  </si>
+  <si>
+    <t>326860551</t>
+  </si>
+  <si>
+    <t>326913668</t>
+  </si>
+  <si>
+    <t>326913716</t>
+  </si>
+  <si>
+    <t>326913792</t>
+  </si>
+  <si>
+    <t>326968119</t>
+  </si>
+  <si>
+    <t>326968124</t>
+  </si>
+  <si>
+    <t>327026656</t>
+  </si>
+  <si>
+    <t>327110047</t>
+  </si>
+  <si>
+    <t>327253153</t>
+  </si>
+  <si>
+    <t>327253190</t>
+  </si>
+  <si>
+    <t>327253262</t>
+  </si>
+  <si>
+    <t>327253320</t>
+  </si>
+  <si>
+    <t>327253389</t>
+  </si>
+  <si>
+    <t>327253398</t>
+  </si>
+  <si>
+    <t>327253474</t>
+  </si>
+  <si>
+    <t>327253477</t>
+  </si>
+  <si>
+    <t>327253532</t>
+  </si>
+  <si>
+    <t>327253611</t>
+  </si>
+  <si>
+    <t>327253630</t>
+  </si>
+  <si>
+    <t>327253731</t>
+  </si>
+  <si>
+    <t>327355244</t>
+  </si>
+  <si>
+    <t>327402525</t>
+  </si>
+  <si>
+    <t>51340047590KR</t>
+  </si>
+  <si>
+    <t>51340047669KR</t>
+  </si>
+  <si>
+    <t>540953052KR</t>
+  </si>
+  <si>
+    <t>73676-108003</t>
+  </si>
+  <si>
+    <t>941155215KR</t>
+  </si>
+  <si>
+    <t>941155219KR</t>
+  </si>
+  <si>
+    <t>941155228KR</t>
+  </si>
+  <si>
+    <t>941155245KR</t>
+  </si>
+  <si>
+    <t>99003180</t>
+  </si>
+  <si>
+    <t>ID5464_XD</t>
+  </si>
+  <si>
+    <t>ID5493_XD</t>
+  </si>
+  <si>
+    <t>NFD6-08-26-FVSN</t>
+  </si>
+  <si>
+    <t>NFD6-09-06-3YGR</t>
+  </si>
+  <si>
+    <t>NFD6-09-07-4YK3</t>
+  </si>
+  <si>
+    <t>NFD6-09-07-TUKZ</t>
+  </si>
+  <si>
+    <t>NFD6-09-07-TYUY</t>
+  </si>
+  <si>
+    <t>NFD6-09-08-CV7E</t>
+  </si>
+  <si>
+    <t>NFD6-09-08-QCQ3</t>
+  </si>
+  <si>
+    <t>NFD6-09-08-QXDJ</t>
+  </si>
+  <si>
+    <t>NFD6-09-08-WLCF</t>
+  </si>
+  <si>
+    <t>NFD6-09-09-FUFZ</t>
+  </si>
+  <si>
+    <t>NFD6-09-09-MR3H</t>
+  </si>
+  <si>
+    <t>NFE6-08-18-S7S4/CSXD</t>
+  </si>
+  <si>
+    <t>NFE6-09-02-53WH</t>
+  </si>
+  <si>
+    <t>NFE6-09-02-SCQM</t>
+  </si>
+  <si>
+    <t>NFE6-09-06-HJ27</t>
+  </si>
+  <si>
+    <t>NFE6-09-07-BV3Y</t>
+  </si>
+  <si>
+    <t>NFE6-09-07-KKNZ</t>
+  </si>
+  <si>
+    <t>NFE6-09-07-NQP5</t>
+  </si>
+  <si>
+    <t>NFE6-09-08-5DUD</t>
+  </si>
+  <si>
+    <t>NFE6-09-09-ABB5</t>
+  </si>
+  <si>
+    <t>R434320</t>
+  </si>
+  <si>
+    <t>R434826</t>
+  </si>
+  <si>
+    <t>R435278</t>
+  </si>
+  <si>
+    <t>SA26/H006465</t>
+  </si>
+  <si>
+    <t>SZL090802/2026</t>
   </si>
 </sst>
 </file>
@@ -1462,10 +3322,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC11F24F-E222-443E-8401-2ECBA69A40D4}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:C181"/>
+  <dimension ref="A1:C505"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1483,1982 +3343,5546 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>714</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>358</v>
       </c>
       <c r="C2" t="s">
-        <v>338</v>
+        <v>682</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>714</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>359</v>
       </c>
       <c r="C3" t="s">
-        <v>339</v>
+        <v>682</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>715</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>360</v>
       </c>
       <c r="C4" t="s">
-        <v>339</v>
+        <v>683</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>716</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>361</v>
       </c>
       <c r="C5" t="s">
-        <v>340</v>
+        <v>683</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>717</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>362</v>
       </c>
       <c r="C6" t="s">
-        <v>341</v>
+        <v>683</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>718</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="C7" t="s">
-        <v>342</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>719</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="C8" t="s">
-        <v>343</v>
+        <v>684</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>720</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="C9" t="s">
-        <v>343</v>
+        <v>685</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>721</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>366</v>
       </c>
       <c r="C10" t="s">
-        <v>344</v>
+        <v>686</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>722</v>
       </c>
       <c r="B11" t="s">
-        <v>167</v>
+        <v>367</v>
       </c>
       <c r="C11" t="s">
-        <v>345</v>
+        <v>687</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>723</v>
       </c>
       <c r="B12" t="s">
-        <v>168</v>
+        <v>368</v>
       </c>
       <c r="C12" t="s">
-        <v>346</v>
+        <v>688</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>724</v>
       </c>
       <c r="B14" t="s">
-        <v>170</v>
+        <v>369</v>
       </c>
       <c r="C14" t="s">
-        <v>339</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>724</v>
       </c>
       <c r="B15" t="s">
-        <v>171</v>
+        <v>370</v>
       </c>
       <c r="C15" t="s">
-        <v>347</v>
+        <v>689</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>725</v>
       </c>
       <c r="B16" t="s">
-        <v>172</v>
+        <v>371</v>
       </c>
       <c r="C16" t="s">
-        <v>346</v>
+        <v>690</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>726</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>372</v>
       </c>
       <c r="C17" t="s">
-        <v>341</v>
+        <v>691</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C19" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>727</v>
       </c>
       <c r="B20" t="s">
-        <v>176</v>
+        <v>373</v>
       </c>
       <c r="C20" t="s">
-        <v>341</v>
+        <v>692</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="C21" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>728</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>374</v>
       </c>
       <c r="C23" t="s">
-        <v>350</v>
+        <v>693</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>729</v>
       </c>
       <c r="B24" t="s">
-        <v>180</v>
+        <v>375</v>
       </c>
       <c r="C24" t="s">
-        <v>339</v>
+        <v>683</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>730</v>
       </c>
       <c r="B25" t="s">
-        <v>181</v>
+        <v>376</v>
       </c>
       <c r="C25" t="s">
-        <v>351</v>
+        <v>691</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>731</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>377</v>
       </c>
       <c r="C26" t="s">
-        <v>351</v>
+        <v>690</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>732</v>
       </c>
       <c r="B27" t="s">
-        <v>183</v>
+        <v>378</v>
       </c>
       <c r="C27" t="s">
-        <v>352</v>
+        <v>694</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>733</v>
       </c>
       <c r="B28" t="s">
-        <v>184</v>
+        <v>379</v>
       </c>
       <c r="C28" t="s">
-        <v>345</v>
+        <v>685</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>734</v>
       </c>
       <c r="B29" t="s">
-        <v>185</v>
+        <v>380</v>
       </c>
       <c r="C29" t="s">
-        <v>347</v>
+        <v>683</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="C30" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>735</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>381</v>
       </c>
       <c r="C31" t="s">
-        <v>348</v>
+        <v>694</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="C32" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="C33" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="C34" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>736</v>
       </c>
       <c r="B35" t="s">
-        <v>191</v>
+        <v>382</v>
       </c>
       <c r="C35" t="s">
-        <v>345</v>
+        <v>682</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>737</v>
       </c>
       <c r="B36" t="s">
-        <v>192</v>
+        <v>383</v>
       </c>
       <c r="C36" t="s">
-        <v>338</v>
+        <v>695</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>738</v>
       </c>
       <c r="B37" t="s">
-        <v>193</v>
+        <v>384</v>
       </c>
       <c r="C37" t="s">
-        <v>354</v>
+        <v>692</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>739</v>
       </c>
       <c r="B38" t="s">
-        <v>194</v>
+        <v>385</v>
       </c>
       <c r="C38" t="s">
-        <v>339</v>
+        <v>696</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>739</v>
       </c>
       <c r="B39" t="s">
-        <v>195</v>
+        <v>386</v>
       </c>
       <c r="C39" t="s">
-        <v>348</v>
+        <v>696</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>740</v>
       </c>
       <c r="B40" t="s">
-        <v>196</v>
+        <v>387</v>
       </c>
       <c r="C40" t="s">
-        <v>348</v>
+        <v>697</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>740</v>
       </c>
       <c r="B41" t="s">
-        <v>197</v>
+        <v>388</v>
       </c>
       <c r="C41" t="s">
-        <v>346</v>
+        <v>697</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="C42" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>741</v>
       </c>
       <c r="B43" t="s">
-        <v>199</v>
+        <v>389</v>
       </c>
       <c r="C43" t="s">
-        <v>342</v>
+        <v>698</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>742</v>
       </c>
       <c r="B44" t="s">
-        <v>200</v>
+        <v>390</v>
       </c>
       <c r="C44" t="s">
-        <v>353</v>
+        <v>699</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>743</v>
       </c>
       <c r="B45" t="s">
-        <v>201</v>
+        <v>391</v>
       </c>
       <c r="C45" t="s">
-        <v>353</v>
+        <v>687</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>744</v>
       </c>
       <c r="B46" t="s">
-        <v>202</v>
+        <v>392</v>
       </c>
       <c r="C46" t="s">
-        <v>356</v>
+        <v>700</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>745</v>
       </c>
       <c r="B47" t="s">
-        <v>203</v>
+        <v>393</v>
       </c>
       <c r="C47" t="s">
-        <v>356</v>
+        <v>701</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>746</v>
       </c>
       <c r="B48" t="s">
-        <v>204</v>
+        <v>394</v>
       </c>
       <c r="C48" t="s">
-        <v>356</v>
+        <v>691</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>43</v>
+        <v>747</v>
       </c>
       <c r="B49" t="s">
-        <v>205</v>
+        <v>395</v>
       </c>
       <c r="C49" t="s">
-        <v>345</v>
+        <v>702</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>206</v>
+        <v>168</v>
       </c>
       <c r="C50" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>44</v>
+        <v>748</v>
       </c>
       <c r="B51" t="s">
-        <v>207</v>
+        <v>396</v>
       </c>
       <c r="C51" t="s">
-        <v>354</v>
+        <v>688</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>45</v>
+        <v>749</v>
       </c>
       <c r="B52" t="s">
-        <v>208</v>
+        <v>397</v>
       </c>
       <c r="C52" t="s">
-        <v>340</v>
+        <v>690</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>750</v>
       </c>
       <c r="B53" t="s">
-        <v>209</v>
+        <v>398</v>
       </c>
       <c r="C53" t="s">
-        <v>346</v>
+        <v>700</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>750</v>
       </c>
       <c r="B54" t="s">
-        <v>210</v>
+        <v>399</v>
       </c>
       <c r="C54" t="s">
-        <v>356</v>
+        <v>700</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B55" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="C55" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>751</v>
       </c>
       <c r="B56" t="s">
-        <v>212</v>
+        <v>400</v>
       </c>
       <c r="C56" t="s">
-        <v>348</v>
+        <v>694</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>213</v>
+        <v>170</v>
       </c>
       <c r="C57" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>214</v>
+        <v>171</v>
       </c>
       <c r="C58" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>752</v>
       </c>
       <c r="B59" t="s">
-        <v>215</v>
+        <v>401</v>
       </c>
       <c r="C59" t="s">
-        <v>343</v>
+        <v>703</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>753</v>
       </c>
       <c r="B60" t="s">
-        <v>216</v>
+        <v>402</v>
       </c>
       <c r="C60" t="s">
-        <v>343</v>
+        <v>685</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>754</v>
       </c>
       <c r="B61" t="s">
-        <v>217</v>
+        <v>403</v>
       </c>
       <c r="C61" t="s">
-        <v>357</v>
+        <v>690</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>755</v>
       </c>
       <c r="B62" t="s">
-        <v>218</v>
+        <v>404</v>
       </c>
       <c r="C62" t="s">
-        <v>342</v>
+        <v>701</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>755</v>
       </c>
       <c r="B63" t="s">
-        <v>219</v>
+        <v>405</v>
       </c>
       <c r="C63" t="s">
-        <v>355</v>
+        <v>701</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>755</v>
       </c>
       <c r="B64" t="s">
-        <v>220</v>
+        <v>406</v>
       </c>
       <c r="C64" t="s">
-        <v>342</v>
+        <v>701</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>124</v>
+        <v>756</v>
       </c>
       <c r="B65" t="s">
-        <v>221</v>
+        <v>407</v>
       </c>
       <c r="C65" t="s">
-        <v>350</v>
+        <v>694</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>222</v>
+        <v>172</v>
       </c>
       <c r="C66" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>126</v>
+        <v>757</v>
       </c>
       <c r="B67" t="s">
-        <v>223</v>
+        <v>408</v>
       </c>
       <c r="C67" t="s">
-        <v>353</v>
+        <v>704</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>127</v>
+        <v>758</v>
       </c>
       <c r="B68" t="s">
-        <v>224</v>
+        <v>409</v>
       </c>
       <c r="C68" t="s">
-        <v>357</v>
+        <v>693</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>128</v>
+        <v>759</v>
       </c>
       <c r="B69" t="s">
-        <v>225</v>
+        <v>410</v>
       </c>
       <c r="C69" t="s">
-        <v>340</v>
+        <v>689</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>129</v>
+        <v>760</v>
       </c>
       <c r="B70" t="s">
-        <v>226</v>
+        <v>411</v>
       </c>
       <c r="C70" t="s">
-        <v>341</v>
+        <v>689</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>130</v>
+        <v>760</v>
       </c>
       <c r="B71" t="s">
-        <v>227</v>
+        <v>412</v>
       </c>
       <c r="C71" t="s">
-        <v>357</v>
+        <v>689</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>55</v>
+        <v>761</v>
       </c>
       <c r="B72" t="s">
-        <v>228</v>
+        <v>413</v>
       </c>
       <c r="C72" t="s">
-        <v>350</v>
+        <v>703</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="C73" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>57</v>
+        <v>762</v>
       </c>
       <c r="B74" t="s">
-        <v>230</v>
+        <v>414</v>
       </c>
       <c r="C74" t="s">
-        <v>343</v>
+        <v>689</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>58</v>
+        <v>763</v>
       </c>
       <c r="B75" t="s">
-        <v>231</v>
+        <v>415</v>
       </c>
       <c r="C75" t="s">
-        <v>344</v>
+        <v>697</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>59</v>
+        <v>764</v>
       </c>
       <c r="B76" t="s">
-        <v>232</v>
+        <v>416</v>
       </c>
       <c r="C76" t="s">
-        <v>344</v>
+        <v>692</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>60</v>
+        <v>764</v>
       </c>
       <c r="B77" t="s">
-        <v>233</v>
+        <v>417</v>
       </c>
       <c r="C77" t="s">
-        <v>343</v>
+        <v>692</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>61</v>
+        <v>765</v>
       </c>
       <c r="B78" t="s">
-        <v>234</v>
+        <v>418</v>
       </c>
       <c r="C78" t="s">
-        <v>356</v>
+        <v>694</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>61</v>
+        <v>765</v>
       </c>
       <c r="B79" t="s">
-        <v>235</v>
+        <v>419</v>
       </c>
       <c r="C79" t="s">
-        <v>356</v>
+        <v>694</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>62</v>
+        <v>766</v>
       </c>
       <c r="B80" t="s">
-        <v>236</v>
+        <v>420</v>
       </c>
       <c r="C80" t="s">
-        <v>349</v>
+        <v>697</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>63</v>
+        <v>767</v>
       </c>
       <c r="B81" t="s">
-        <v>237</v>
+        <v>421</v>
       </c>
       <c r="C81" t="s">
-        <v>343</v>
+        <v>694</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>63</v>
+        <v>768</v>
       </c>
       <c r="B82" t="s">
-        <v>238</v>
+        <v>422</v>
       </c>
       <c r="C82" t="s">
-        <v>343</v>
+        <v>693</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="B83" t="s">
-        <v>239</v>
+        <v>174</v>
       </c>
       <c r="C83" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>65</v>
+        <v>769</v>
       </c>
       <c r="B84" t="s">
-        <v>240</v>
+        <v>423</v>
       </c>
       <c r="C84" t="s">
-        <v>355</v>
+        <v>704</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>65</v>
+        <v>770</v>
       </c>
       <c r="B85" t="s">
-        <v>241</v>
+        <v>424</v>
       </c>
       <c r="C85" t="s">
-        <v>355</v>
+        <v>705</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="B86" t="s">
-        <v>242</v>
+        <v>175</v>
       </c>
       <c r="C86" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>67</v>
+        <v>771</v>
       </c>
       <c r="B87" t="s">
-        <v>243</v>
+        <v>425</v>
       </c>
       <c r="C87" t="s">
-        <v>339</v>
+        <v>683</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B88" t="s">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="C88" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>68</v>
+        <v>772</v>
       </c>
       <c r="B89" t="s">
-        <v>245</v>
+        <v>426</v>
       </c>
       <c r="C89" t="s">
-        <v>345</v>
+        <v>686</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>68</v>
+        <v>773</v>
       </c>
       <c r="B90" t="s">
-        <v>246</v>
+        <v>427</v>
       </c>
       <c r="C90" t="s">
-        <v>345</v>
+        <v>706</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>69</v>
+        <v>773</v>
       </c>
       <c r="B91" t="s">
-        <v>247</v>
+        <v>428</v>
       </c>
       <c r="C91" t="s">
-        <v>339</v>
+        <v>706</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>69</v>
+        <v>774</v>
       </c>
       <c r="B92" t="s">
-        <v>248</v>
+        <v>429</v>
       </c>
       <c r="C92" t="s">
-        <v>339</v>
+        <v>698</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>70</v>
+        <v>775</v>
       </c>
       <c r="B93" t="s">
-        <v>249</v>
+        <v>430</v>
       </c>
       <c r="C93" t="s">
-        <v>349</v>
+        <v>697</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>71</v>
+        <v>775</v>
       </c>
       <c r="B94" t="s">
-        <v>250</v>
+        <v>431</v>
       </c>
       <c r="C94" t="s">
-        <v>347</v>
+        <v>697</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="B95" t="s">
-        <v>251</v>
+        <v>177</v>
       </c>
       <c r="C95" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>72</v>
+        <v>776</v>
       </c>
       <c r="B96" t="s">
-        <v>252</v>
+        <v>432</v>
       </c>
       <c r="C96" t="s">
-        <v>353</v>
+        <v>704</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>73</v>
+        <v>777</v>
       </c>
       <c r="B97" t="s">
-        <v>253</v>
+        <v>433</v>
       </c>
       <c r="C97" t="s">
-        <v>353</v>
+        <v>696</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>74</v>
+        <v>778</v>
       </c>
       <c r="B98" t="s">
-        <v>254</v>
+        <v>434</v>
       </c>
       <c r="C98" t="s">
-        <v>349</v>
+        <v>692</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>75</v>
+        <v>779</v>
       </c>
       <c r="B99" t="s">
-        <v>255</v>
+        <v>435</v>
       </c>
       <c r="C99" t="s">
-        <v>348</v>
+        <v>694</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>76</v>
+        <v>779</v>
       </c>
       <c r="B100" t="s">
-        <v>256</v>
+        <v>436</v>
       </c>
       <c r="C100" t="s">
-        <v>349</v>
+        <v>694</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>76</v>
+        <v>780</v>
       </c>
       <c r="B101" t="s">
-        <v>257</v>
+        <v>437</v>
       </c>
       <c r="C101" t="s">
-        <v>349</v>
+        <v>706</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>3</v>
+        <v>781</v>
       </c>
       <c r="B102" t="s">
-        <v>258</v>
+        <v>438</v>
       </c>
       <c r="C102" t="s">
-        <v>339</v>
+        <v>707</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>77</v>
+        <v>782</v>
       </c>
       <c r="B103" t="s">
-        <v>259</v>
+        <v>439</v>
       </c>
       <c r="C103" t="s">
-        <v>347</v>
+        <v>691</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>78</v>
+        <v>783</v>
       </c>
       <c r="B104" t="s">
-        <v>260</v>
+        <v>440</v>
       </c>
       <c r="C104" t="s">
-        <v>345</v>
+        <v>698</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>79</v>
+        <v>784</v>
       </c>
       <c r="B105" t="s">
-        <v>261</v>
+        <v>441</v>
       </c>
       <c r="C105" t="s">
-        <v>356</v>
+        <v>689</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="B106" t="s">
-        <v>262</v>
+        <v>178</v>
       </c>
       <c r="C106" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>81</v>
+        <v>785</v>
       </c>
       <c r="B107" t="s">
-        <v>263</v>
+        <v>442</v>
       </c>
       <c r="C107" t="s">
-        <v>352</v>
+        <v>685</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="B108" t="s">
-        <v>264</v>
+        <v>179</v>
       </c>
       <c r="C108" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>83</v>
+        <v>786</v>
       </c>
       <c r="B109" t="s">
-        <v>265</v>
+        <v>443</v>
       </c>
       <c r="C109" t="s">
-        <v>351</v>
+        <v>694</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="B110" t="s">
-        <v>266</v>
+        <v>180</v>
       </c>
       <c r="C110" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>85</v>
+        <v>787</v>
       </c>
       <c r="B111" t="s">
-        <v>267</v>
+        <v>444</v>
       </c>
       <c r="C111" t="s">
-        <v>341</v>
+        <v>702</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>86</v>
+        <v>787</v>
       </c>
       <c r="B112" t="s">
-        <v>268</v>
+        <v>445</v>
       </c>
       <c r="C112" t="s">
-        <v>346</v>
+        <v>702</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>87</v>
+        <v>788</v>
       </c>
       <c r="B113" t="s">
-        <v>269</v>
+        <v>446</v>
       </c>
       <c r="C113" t="s">
-        <v>340</v>
+        <v>697</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>88</v>
+        <v>788</v>
       </c>
       <c r="B114" t="s">
-        <v>270</v>
+        <v>447</v>
       </c>
       <c r="C114" t="s">
-        <v>347</v>
+        <v>697</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="B115" t="s">
-        <v>271</v>
+        <v>181</v>
       </c>
       <c r="C115" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="B116" t="s">
-        <v>272</v>
+        <v>182</v>
       </c>
       <c r="C116" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="B117" t="s">
-        <v>273</v>
+        <v>183</v>
       </c>
       <c r="C117" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="B118" t="s">
-        <v>274</v>
+        <v>184</v>
       </c>
       <c r="C118" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>93</v>
+        <v>789</v>
       </c>
       <c r="B119" t="s">
-        <v>275</v>
+        <v>448</v>
       </c>
       <c r="C119" t="s">
-        <v>357</v>
+        <v>687</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="B120" t="s">
-        <v>276</v>
+        <v>185</v>
       </c>
       <c r="C120" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>94</v>
+        <v>790</v>
       </c>
       <c r="B121" t="s">
-        <v>277</v>
+        <v>449</v>
       </c>
       <c r="C121" t="s">
-        <v>338</v>
+        <v>692</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>94</v>
+        <v>791</v>
       </c>
       <c r="B122" t="s">
-        <v>278</v>
+        <v>450</v>
       </c>
       <c r="C122" t="s">
-        <v>338</v>
+        <v>690</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>95</v>
+        <v>792</v>
       </c>
       <c r="B123" t="s">
-        <v>279</v>
+        <v>451</v>
       </c>
       <c r="C123" t="s">
-        <v>350</v>
+        <v>702</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>96</v>
+        <v>793</v>
       </c>
       <c r="B124" t="s">
-        <v>280</v>
+        <v>452</v>
       </c>
       <c r="C124" t="s">
-        <v>338</v>
+        <v>707</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="B125" t="s">
-        <v>281</v>
+        <v>186</v>
       </c>
       <c r="C125" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>97</v>
+        <v>794</v>
       </c>
       <c r="B126" t="s">
-        <v>282</v>
+        <v>453</v>
       </c>
       <c r="C126" t="s">
-        <v>341</v>
+        <v>707</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>98</v>
+        <v>795</v>
       </c>
       <c r="B127" t="s">
-        <v>283</v>
+        <v>454</v>
       </c>
       <c r="C127" t="s">
-        <v>357</v>
+        <v>701</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>99</v>
+        <v>795</v>
       </c>
       <c r="B128" t="s">
-        <v>284</v>
+        <v>455</v>
       </c>
       <c r="C128" t="s">
-        <v>349</v>
+        <v>701</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="B129" t="s">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="C129" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>101</v>
+        <v>796</v>
       </c>
       <c r="B130" t="s">
-        <v>286</v>
+        <v>456</v>
       </c>
       <c r="C130" t="s">
-        <v>347</v>
+        <v>691</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>102</v>
+        <v>797</v>
       </c>
       <c r="B131" t="s">
-        <v>287</v>
+        <v>457</v>
       </c>
       <c r="C131" t="s">
-        <v>352</v>
+        <v>708</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>103</v>
+        <v>797</v>
       </c>
       <c r="B132" t="s">
-        <v>288</v>
+        <v>458</v>
       </c>
       <c r="C132" t="s">
-        <v>348</v>
+        <v>708</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="B133" t="s">
-        <v>289</v>
+        <v>188</v>
       </c>
       <c r="C133" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>105</v>
+        <v>798</v>
       </c>
       <c r="B134" t="s">
-        <v>290</v>
+        <v>459</v>
       </c>
       <c r="C134" t="s">
-        <v>340</v>
+        <v>696</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="B135" t="s">
-        <v>291</v>
+        <v>189</v>
       </c>
       <c r="C135" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>107</v>
+        <v>31</v>
       </c>
       <c r="B136" t="s">
-        <v>292</v>
+        <v>190</v>
       </c>
       <c r="C136" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>107</v>
+        <v>799</v>
       </c>
       <c r="B137" t="s">
-        <v>293</v>
+        <v>460</v>
       </c>
       <c r="C137" t="s">
-        <v>344</v>
+        <v>709</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="B138" t="s">
-        <v>294</v>
+        <v>191</v>
       </c>
       <c r="C138" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>108</v>
+        <v>800</v>
       </c>
       <c r="B139" t="s">
-        <v>295</v>
+        <v>461</v>
       </c>
       <c r="C139" t="s">
-        <v>352</v>
+        <v>692</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>109</v>
+        <v>800</v>
       </c>
       <c r="B140" t="s">
-        <v>296</v>
+        <v>462</v>
       </c>
       <c r="C140" t="s">
-        <v>352</v>
+        <v>692</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>110</v>
+        <v>801</v>
       </c>
       <c r="B141" t="s">
-        <v>297</v>
+        <v>463</v>
       </c>
       <c r="C141" t="s">
-        <v>348</v>
+        <v>708</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>111</v>
+        <v>801</v>
       </c>
       <c r="B142" t="s">
-        <v>298</v>
+        <v>464</v>
       </c>
       <c r="C142" t="s">
-        <v>344</v>
+        <v>708</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>112</v>
+        <v>802</v>
       </c>
       <c r="B143" t="s">
-        <v>299</v>
+        <v>465</v>
       </c>
       <c r="C143" t="s">
-        <v>352</v>
+        <v>688</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>113</v>
+        <v>802</v>
       </c>
       <c r="B144" t="s">
-        <v>300</v>
+        <v>466</v>
       </c>
       <c r="C144" t="s">
-        <v>343</v>
+        <v>688</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>114</v>
+        <v>803</v>
       </c>
       <c r="B145" t="s">
-        <v>301</v>
+        <v>467</v>
       </c>
       <c r="C145" t="s">
-        <v>341</v>
+        <v>694</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>115</v>
+        <v>803</v>
       </c>
       <c r="B146" t="s">
-        <v>302</v>
+        <v>468</v>
       </c>
       <c r="C146" t="s">
-        <v>344</v>
+        <v>694</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>116</v>
+        <v>803</v>
       </c>
       <c r="B147" t="s">
-        <v>303</v>
+        <v>469</v>
       </c>
       <c r="C147" t="s">
-        <v>352</v>
+        <v>694</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="B148" t="s">
-        <v>304</v>
+        <v>192</v>
       </c>
       <c r="C148" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="B149" t="s">
-        <v>305</v>
+        <v>193</v>
       </c>
       <c r="C149" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>119</v>
+        <v>804</v>
       </c>
       <c r="B150" t="s">
-        <v>306</v>
+        <v>470</v>
       </c>
       <c r="C150" t="s">
-        <v>350</v>
+        <v>682</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>120</v>
+        <v>804</v>
       </c>
       <c r="B151" t="s">
-        <v>307</v>
+        <v>471</v>
       </c>
       <c r="C151" t="s">
-        <v>355</v>
+        <v>682</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>121</v>
+        <v>805</v>
       </c>
       <c r="B152" t="s">
-        <v>308</v>
+        <v>472</v>
       </c>
       <c r="C152" t="s">
-        <v>343</v>
+        <v>686</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>122</v>
+        <v>805</v>
       </c>
       <c r="B153" t="s">
-        <v>309</v>
+        <v>473</v>
       </c>
       <c r="C153" t="s">
-        <v>348</v>
+        <v>686</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>131</v>
+        <v>806</v>
       </c>
       <c r="B154" t="s">
-        <v>310</v>
+        <v>474</v>
       </c>
       <c r="C154" t="s">
-        <v>355</v>
+        <v>686</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>131</v>
+        <v>807</v>
       </c>
       <c r="B155" t="s">
-        <v>311</v>
+        <v>475</v>
       </c>
       <c r="C155" t="s">
-        <v>355</v>
+        <v>692</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>132</v>
+        <v>808</v>
       </c>
       <c r="B156" t="s">
-        <v>312</v>
+        <v>476</v>
       </c>
       <c r="C156" t="s">
-        <v>351</v>
+        <v>688</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>133</v>
+        <v>809</v>
       </c>
       <c r="B157" t="s">
-        <v>313</v>
+        <v>477</v>
       </c>
       <c r="C157" t="s">
-        <v>353</v>
+        <v>708</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>134</v>
+        <v>810</v>
       </c>
       <c r="B158" t="s">
-        <v>314</v>
+        <v>478</v>
       </c>
       <c r="C158" t="s">
-        <v>348</v>
+        <v>697</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>135</v>
+        <v>811</v>
       </c>
       <c r="B159" t="s">
-        <v>315</v>
+        <v>479</v>
       </c>
       <c r="C159" t="s">
-        <v>346</v>
+        <v>689</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>136</v>
+        <v>812</v>
       </c>
       <c r="B160" t="s">
-        <v>316</v>
+        <v>480</v>
       </c>
       <c r="C160" t="s">
-        <v>343</v>
+        <v>696</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>137</v>
+        <v>813</v>
       </c>
       <c r="B161" t="s">
-        <v>317</v>
+        <v>481</v>
       </c>
       <c r="C161" t="s">
-        <v>346</v>
+        <v>697</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="B162" t="s">
-        <v>318</v>
+        <v>194</v>
       </c>
       <c r="C162" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>139</v>
+        <v>814</v>
       </c>
       <c r="B163" t="s">
-        <v>319</v>
+        <v>482</v>
       </c>
       <c r="C163" t="s">
-        <v>338</v>
+        <v>683</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>140</v>
+        <v>815</v>
       </c>
       <c r="B164" t="s">
-        <v>320</v>
+        <v>483</v>
       </c>
       <c r="C164" t="s">
-        <v>347</v>
+        <v>702</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>141</v>
+        <v>816</v>
       </c>
       <c r="B165" t="s">
-        <v>321</v>
+        <v>484</v>
       </c>
       <c r="C165" t="s">
-        <v>339</v>
+        <v>689</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>142</v>
+        <v>817</v>
       </c>
       <c r="B166" t="s">
-        <v>322</v>
+        <v>485</v>
       </c>
       <c r="C166" t="s">
-        <v>356</v>
+        <v>683</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>143</v>
+        <v>818</v>
       </c>
       <c r="B167" t="s">
-        <v>323</v>
+        <v>486</v>
       </c>
       <c r="C167" t="s">
-        <v>345</v>
+        <v>689</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>144</v>
+        <v>819</v>
       </c>
       <c r="B168" t="s">
-        <v>324</v>
+        <v>487</v>
       </c>
       <c r="C168" t="s">
-        <v>354</v>
+        <v>687</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>145</v>
+        <v>820</v>
       </c>
       <c r="B169" t="s">
-        <v>325</v>
+        <v>488</v>
       </c>
       <c r="C169" t="s">
-        <v>347</v>
+        <v>686</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>146</v>
+        <v>820</v>
       </c>
       <c r="B170" t="s">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="C170" t="s">
-        <v>353</v>
+        <v>686</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>147</v>
+        <v>821</v>
       </c>
       <c r="B171" t="s">
-        <v>327</v>
+        <v>490</v>
       </c>
       <c r="C171" t="s">
-        <v>354</v>
+        <v>694</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>148</v>
+        <v>822</v>
       </c>
       <c r="B172" t="s">
-        <v>328</v>
+        <v>491</v>
       </c>
       <c r="C172" t="s">
-        <v>357</v>
+        <v>691</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>149</v>
+        <v>823</v>
       </c>
       <c r="B173" t="s">
-        <v>329</v>
+        <v>492</v>
       </c>
       <c r="C173" t="s">
-        <v>348</v>
+        <v>707</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>150</v>
+        <v>824</v>
       </c>
       <c r="B174" t="s">
-        <v>330</v>
+        <v>493</v>
       </c>
       <c r="C174" t="s">
-        <v>354</v>
+        <v>696</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>151</v>
+        <v>825</v>
       </c>
       <c r="B175" t="s">
-        <v>331</v>
+        <v>494</v>
       </c>
       <c r="C175" t="s">
-        <v>354</v>
+        <v>703</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>152</v>
+        <v>826</v>
       </c>
       <c r="B176" t="s">
-        <v>332</v>
+        <v>495</v>
       </c>
       <c r="C176" t="s">
-        <v>340</v>
+        <v>705</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>153</v>
+        <v>827</v>
       </c>
       <c r="B177" t="s">
-        <v>333</v>
+        <v>496</v>
       </c>
       <c r="C177" t="s">
-        <v>355</v>
+        <v>708</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>154</v>
+        <v>828</v>
       </c>
       <c r="B178" t="s">
-        <v>334</v>
+        <v>497</v>
       </c>
       <c r="C178" t="s">
-        <v>356</v>
+        <v>708</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>155</v>
+        <v>829</v>
       </c>
       <c r="B179" t="s">
-        <v>335</v>
+        <v>498</v>
       </c>
       <c r="C179" t="s">
-        <v>345</v>
+        <v>697</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>156</v>
+        <v>829</v>
       </c>
       <c r="B180" t="s">
-        <v>336</v>
+        <v>499</v>
       </c>
       <c r="C180" t="s">
-        <v>352</v>
+        <v>697</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>830</v>
+      </c>
+      <c r="B181" t="s">
+        <v>500</v>
+      </c>
+      <c r="C181" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>36</v>
+      </c>
+      <c r="B182" t="s">
+        <v>195</v>
+      </c>
+      <c r="C182" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>36</v>
+      </c>
+      <c r="B183" t="s">
+        <v>196</v>
+      </c>
+      <c r="C183" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>37</v>
+      </c>
+      <c r="B184" t="s">
+        <v>197</v>
+      </c>
+      <c r="C184" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>831</v>
+      </c>
+      <c r="B185" t="s">
+        <v>501</v>
+      </c>
+      <c r="C185" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>832</v>
+      </c>
+      <c r="B186" t="s">
+        <v>502</v>
+      </c>
+      <c r="C186" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>833</v>
+      </c>
+      <c r="B187" t="s">
+        <v>503</v>
+      </c>
+      <c r="C187" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>834</v>
+      </c>
+      <c r="B188" t="s">
+        <v>504</v>
+      </c>
+      <c r="C188" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>835</v>
+      </c>
+      <c r="B189" t="s">
+        <v>505</v>
+      </c>
+      <c r="C189" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>38</v>
+      </c>
+      <c r="B190" t="s">
+        <v>198</v>
+      </c>
+      <c r="C190" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>39</v>
+      </c>
+      <c r="B191" t="s">
+        <v>199</v>
+      </c>
+      <c r="C191" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>836</v>
+      </c>
+      <c r="B192" t="s">
+        <v>506</v>
+      </c>
+      <c r="C192" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>837</v>
+      </c>
+      <c r="B193" t="s">
+        <v>507</v>
+      </c>
+      <c r="C193" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>40</v>
+      </c>
+      <c r="B194" t="s">
+        <v>200</v>
+      </c>
+      <c r="C194" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>838</v>
+      </c>
+      <c r="B195" t="s">
+        <v>508</v>
+      </c>
+      <c r="C195" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>41</v>
+      </c>
+      <c r="B196" t="s">
+        <v>201</v>
+      </c>
+      <c r="C196" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>42</v>
+      </c>
+      <c r="B197" t="s">
+        <v>202</v>
+      </c>
+      <c r="C197" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>42</v>
+      </c>
+      <c r="B198" t="s">
+        <v>203</v>
+      </c>
+      <c r="C198" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>42</v>
+      </c>
+      <c r="B199" t="s">
+        <v>204</v>
+      </c>
+      <c r="C199" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>839</v>
+      </c>
+      <c r="B200" t="s">
+        <v>509</v>
+      </c>
+      <c r="C200" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>840</v>
+      </c>
+      <c r="B201" t="s">
+        <v>510</v>
+      </c>
+      <c r="C201" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>841</v>
+      </c>
+      <c r="B202" t="s">
+        <v>511</v>
+      </c>
+      <c r="C202" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>43</v>
+      </c>
+      <c r="B203" t="s">
+        <v>205</v>
+      </c>
+      <c r="C203" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>842</v>
+      </c>
+      <c r="B204" t="s">
+        <v>512</v>
+      </c>
+      <c r="C204" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>843</v>
+      </c>
+      <c r="B205" t="s">
+        <v>513</v>
+      </c>
+      <c r="C205" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>844</v>
+      </c>
+      <c r="B206" t="s">
+        <v>514</v>
+      </c>
+      <c r="C206" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>844</v>
+      </c>
+      <c r="B207" t="s">
+        <v>515</v>
+      </c>
+      <c r="C207" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>845</v>
+      </c>
+      <c r="B208" t="s">
+        <v>516</v>
+      </c>
+      <c r="C208" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>846</v>
+      </c>
+      <c r="B209" t="s">
+        <v>517</v>
+      </c>
+      <c r="C209" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>847</v>
+      </c>
+      <c r="B210" t="s">
+        <v>518</v>
+      </c>
+      <c r="C210" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>848</v>
+      </c>
+      <c r="B211" t="s">
+        <v>519</v>
+      </c>
+      <c r="C211" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>849</v>
+      </c>
+      <c r="B212" t="s">
+        <v>520</v>
+      </c>
+      <c r="C212" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>850</v>
+      </c>
+      <c r="B213" t="s">
+        <v>521</v>
+      </c>
+      <c r="C213" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>851</v>
+      </c>
+      <c r="B214" t="s">
+        <v>522</v>
+      </c>
+      <c r="C214" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>851</v>
+      </c>
+      <c r="B215" t="s">
+        <v>523</v>
+      </c>
+      <c r="C215" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>852</v>
+      </c>
+      <c r="B216" t="s">
+        <v>524</v>
+      </c>
+      <c r="C216" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>853</v>
+      </c>
+      <c r="B217" t="s">
+        <v>525</v>
+      </c>
+      <c r="C217" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>44</v>
+      </c>
+      <c r="B218" t="s">
+        <v>206</v>
+      </c>
+      <c r="C218" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>44</v>
+      </c>
+      <c r="B219" t="s">
+        <v>207</v>
+      </c>
+      <c r="C219" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>45</v>
+      </c>
+      <c r="B220" t="s">
+        <v>208</v>
+      </c>
+      <c r="C220" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>854</v>
+      </c>
+      <c r="B221" t="s">
+        <v>526</v>
+      </c>
+      <c r="C221" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>46</v>
+      </c>
+      <c r="B222" t="s">
+        <v>209</v>
+      </c>
+      <c r="C222" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>855</v>
+      </c>
+      <c r="B223" t="s">
+        <v>527</v>
+      </c>
+      <c r="C223" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>856</v>
+      </c>
+      <c r="B224" t="s">
+        <v>528</v>
+      </c>
+      <c r="C224" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>857</v>
+      </c>
+      <c r="B225" t="s">
+        <v>529</v>
+      </c>
+      <c r="C225" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>858</v>
+      </c>
+      <c r="B226" t="s">
+        <v>530</v>
+      </c>
+      <c r="C226" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>859</v>
+      </c>
+      <c r="B227" t="s">
+        <v>531</v>
+      </c>
+      <c r="C227" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>860</v>
+      </c>
+      <c r="B228" t="s">
+        <v>532</v>
+      </c>
+      <c r="C228" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>860</v>
+      </c>
+      <c r="B229" t="s">
+        <v>533</v>
+      </c>
+      <c r="C229" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>861</v>
+      </c>
+      <c r="B230" t="s">
+        <v>534</v>
+      </c>
+      <c r="C230" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>47</v>
+      </c>
+      <c r="B231" t="s">
+        <v>210</v>
+      </c>
+      <c r="C231" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>47</v>
+      </c>
+      <c r="B232" t="s">
+        <v>211</v>
+      </c>
+      <c r="C232" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>862</v>
+      </c>
+      <c r="B233" t="s">
+        <v>535</v>
+      </c>
+      <c r="C233" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>863</v>
+      </c>
+      <c r="B234" t="s">
+        <v>536</v>
+      </c>
+      <c r="C234" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>863</v>
+      </c>
+      <c r="B235" t="s">
+        <v>537</v>
+      </c>
+      <c r="C235" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>864</v>
+      </c>
+      <c r="B236" t="s">
+        <v>538</v>
+      </c>
+      <c r="C236" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>865</v>
+      </c>
+      <c r="B237" t="s">
+        <v>539</v>
+      </c>
+      <c r="C237" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>866</v>
+      </c>
+      <c r="B238" t="s">
+        <v>540</v>
+      </c>
+      <c r="C238" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>867</v>
+      </c>
+      <c r="B239" t="s">
+        <v>541</v>
+      </c>
+      <c r="C239" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>48</v>
+      </c>
+      <c r="B240" t="s">
+        <v>212</v>
+      </c>
+      <c r="C240" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>48</v>
+      </c>
+      <c r="B241" t="s">
+        <v>213</v>
+      </c>
+      <c r="C241" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>868</v>
+      </c>
+      <c r="B242" t="s">
+        <v>542</v>
+      </c>
+      <c r="C242" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>868</v>
+      </c>
+      <c r="B243" t="s">
+        <v>543</v>
+      </c>
+      <c r="C243" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>869</v>
+      </c>
+      <c r="B244" t="s">
+        <v>544</v>
+      </c>
+      <c r="C244" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>49</v>
+      </c>
+      <c r="B245" t="s">
+        <v>214</v>
+      </c>
+      <c r="C245" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>870</v>
+      </c>
+      <c r="B246" t="s">
+        <v>545</v>
+      </c>
+      <c r="C246" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>870</v>
+      </c>
+      <c r="B247" t="s">
+        <v>546</v>
+      </c>
+      <c r="C247" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>870</v>
+      </c>
+      <c r="B248" t="s">
+        <v>547</v>
+      </c>
+      <c r="C248" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>871</v>
+      </c>
+      <c r="B249" t="s">
+        <v>548</v>
+      </c>
+      <c r="C249" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>871</v>
+      </c>
+      <c r="B250" t="s">
+        <v>549</v>
+      </c>
+      <c r="C250" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>872</v>
+      </c>
+      <c r="B251" t="s">
+        <v>550</v>
+      </c>
+      <c r="C251" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>873</v>
+      </c>
+      <c r="B252" t="s">
+        <v>551</v>
+      </c>
+      <c r="C252" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>874</v>
+      </c>
+      <c r="B253" t="s">
+        <v>552</v>
+      </c>
+      <c r="C253" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>875</v>
+      </c>
+      <c r="B254" t="s">
+        <v>553</v>
+      </c>
+      <c r="C254" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>875</v>
+      </c>
+      <c r="B255" t="s">
+        <v>554</v>
+      </c>
+      <c r="C255" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>876</v>
+      </c>
+      <c r="B256" t="s">
+        <v>555</v>
+      </c>
+      <c r="C256" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>877</v>
+      </c>
+      <c r="B257" t="s">
+        <v>556</v>
+      </c>
+      <c r="C257" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>50</v>
+      </c>
+      <c r="B258" t="s">
+        <v>215</v>
+      </c>
+      <c r="C258" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>50</v>
+      </c>
+      <c r="B259" t="s">
+        <v>216</v>
+      </c>
+      <c r="C259" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>51</v>
+      </c>
+      <c r="B260" t="s">
+        <v>217</v>
+      </c>
+      <c r="C260" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>878</v>
+      </c>
+      <c r="B261" t="s">
+        <v>557</v>
+      </c>
+      <c r="C261" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>878</v>
+      </c>
+      <c r="B262" t="s">
+        <v>558</v>
+      </c>
+      <c r="C262" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>52</v>
+      </c>
+      <c r="B263" t="s">
+        <v>218</v>
+      </c>
+      <c r="C263" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>879</v>
+      </c>
+      <c r="B264" t="s">
+        <v>559</v>
+      </c>
+      <c r="C264" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>880</v>
+      </c>
+      <c r="B265" t="s">
+        <v>560</v>
+      </c>
+      <c r="C265" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>881</v>
+      </c>
+      <c r="B266" t="s">
+        <v>561</v>
+      </c>
+      <c r="C266" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>881</v>
+      </c>
+      <c r="B267" t="s">
+        <v>562</v>
+      </c>
+      <c r="C267" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>882</v>
+      </c>
+      <c r="B268" t="s">
+        <v>563</v>
+      </c>
+      <c r="C268" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>883</v>
+      </c>
+      <c r="B269" t="s">
+        <v>564</v>
+      </c>
+      <c r="C269" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>53</v>
+      </c>
+      <c r="B270" t="s">
+        <v>219</v>
+      </c>
+      <c r="C270" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>884</v>
+      </c>
+      <c r="B271" t="s">
+        <v>565</v>
+      </c>
+      <c r="C271" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>885</v>
+      </c>
+      <c r="B272" t="s">
+        <v>566</v>
+      </c>
+      <c r="C272" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>886</v>
+      </c>
+      <c r="B273" t="s">
+        <v>567</v>
+      </c>
+      <c r="C273" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>887</v>
+      </c>
+      <c r="B274" t="s">
+        <v>568</v>
+      </c>
+      <c r="C274" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>887</v>
+      </c>
+      <c r="B275" t="s">
+        <v>569</v>
+      </c>
+      <c r="C275" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>888</v>
+      </c>
+      <c r="B276" t="s">
+        <v>570</v>
+      </c>
+      <c r="C276" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>888</v>
+      </c>
+      <c r="B277" t="s">
+        <v>571</v>
+      </c>
+      <c r="C277" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>889</v>
+      </c>
+      <c r="B278" t="s">
+        <v>572</v>
+      </c>
+      <c r="C278" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>54</v>
+      </c>
+      <c r="B279" t="s">
+        <v>220</v>
+      </c>
+      <c r="C279" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>890</v>
+      </c>
+      <c r="B280" t="s">
+        <v>573</v>
+      </c>
+      <c r="C280" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>891</v>
+      </c>
+      <c r="B281" t="s">
+        <v>574</v>
+      </c>
+      <c r="C281" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>892</v>
+      </c>
+      <c r="B282" t="s">
+        <v>575</v>
+      </c>
+      <c r="C282" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>893</v>
+      </c>
+      <c r="B283" t="s">
+        <v>576</v>
+      </c>
+      <c r="C283" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>894</v>
+      </c>
+      <c r="B284" t="s">
+        <v>577</v>
+      </c>
+      <c r="C284" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>895</v>
+      </c>
+      <c r="B285" t="s">
+        <v>578</v>
+      </c>
+      <c r="C285" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>896</v>
+      </c>
+      <c r="B286" t="s">
+        <v>579</v>
+      </c>
+      <c r="C286" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>897</v>
+      </c>
+      <c r="B287" t="s">
+        <v>580</v>
+      </c>
+      <c r="C287" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>898</v>
+      </c>
+      <c r="B288" t="s">
+        <v>581</v>
+      </c>
+      <c r="C288" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>124</v>
+      </c>
+      <c r="B289" t="s">
+        <v>221</v>
+      </c>
+      <c r="C289" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>899</v>
+      </c>
+      <c r="B290" t="s">
+        <v>582</v>
+      </c>
+      <c r="C290" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>125</v>
+      </c>
+      <c r="B291" t="s">
+        <v>222</v>
+      </c>
+      <c r="C291" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>900</v>
+      </c>
+      <c r="B292" t="s">
+        <v>583</v>
+      </c>
+      <c r="C292" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>901</v>
+      </c>
+      <c r="B293" t="s">
+        <v>584</v>
+      </c>
+      <c r="C293" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>902</v>
+      </c>
+      <c r="B294" t="s">
+        <v>585</v>
+      </c>
+      <c r="C294" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>126</v>
+      </c>
+      <c r="B295" t="s">
+        <v>223</v>
+      </c>
+      <c r="C295" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>127</v>
+      </c>
+      <c r="B296" t="s">
+        <v>224</v>
+      </c>
+      <c r="C296" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>128</v>
+      </c>
+      <c r="B297" t="s">
+        <v>225</v>
+      </c>
+      <c r="C297" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>903</v>
+      </c>
+      <c r="B298" t="s">
+        <v>586</v>
+      </c>
+      <c r="C298" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>904</v>
+      </c>
+      <c r="B299" t="s">
+        <v>587</v>
+      </c>
+      <c r="C299" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>905</v>
+      </c>
+      <c r="B300" t="s">
+        <v>588</v>
+      </c>
+      <c r="C300" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>906</v>
+      </c>
+      <c r="B301" t="s">
+        <v>589</v>
+      </c>
+      <c r="C301" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>129</v>
+      </c>
+      <c r="B302" t="s">
+        <v>226</v>
+      </c>
+      <c r="C302" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>907</v>
+      </c>
+      <c r="B303" t="s">
+        <v>590</v>
+      </c>
+      <c r="C303" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>908</v>
+      </c>
+      <c r="B304" t="s">
+        <v>591</v>
+      </c>
+      <c r="C304" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>909</v>
+      </c>
+      <c r="B305" t="s">
+        <v>592</v>
+      </c>
+      <c r="C305" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>910</v>
+      </c>
+      <c r="B306" t="s">
+        <v>593</v>
+      </c>
+      <c r="C306" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>910</v>
+      </c>
+      <c r="B307" t="s">
+        <v>594</v>
+      </c>
+      <c r="C307" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>130</v>
+      </c>
+      <c r="B308" t="s">
+        <v>227</v>
+      </c>
+      <c r="C308" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>911</v>
+      </c>
+      <c r="B309" t="s">
+        <v>595</v>
+      </c>
+      <c r="C309" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>912</v>
+      </c>
+      <c r="B310" t="s">
+        <v>596</v>
+      </c>
+      <c r="C310" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>55</v>
+      </c>
+      <c r="B311" t="s">
+        <v>228</v>
+      </c>
+      <c r="C311" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>913</v>
+      </c>
+      <c r="B312" t="s">
+        <v>597</v>
+      </c>
+      <c r="C312" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>914</v>
+      </c>
+      <c r="B313" t="s">
+        <v>598</v>
+      </c>
+      <c r="C313" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>56</v>
+      </c>
+      <c r="B314" t="s">
+        <v>229</v>
+      </c>
+      <c r="C314" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>915</v>
+      </c>
+      <c r="B315" t="s">
+        <v>599</v>
+      </c>
+      <c r="C315" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>57</v>
+      </c>
+      <c r="B316" t="s">
+        <v>230</v>
+      </c>
+      <c r="C316" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>916</v>
+      </c>
+      <c r="B317" t="s">
+        <v>600</v>
+      </c>
+      <c r="C317" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>916</v>
+      </c>
+      <c r="B318" t="s">
+        <v>601</v>
+      </c>
+      <c r="C318" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>916</v>
+      </c>
+      <c r="B319" t="s">
+        <v>602</v>
+      </c>
+      <c r="C319" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>58</v>
+      </c>
+      <c r="B320" t="s">
+        <v>231</v>
+      </c>
+      <c r="C320" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>59</v>
+      </c>
+      <c r="B321" t="s">
+        <v>232</v>
+      </c>
+      <c r="C321" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>60</v>
+      </c>
+      <c r="B322" t="s">
+        <v>233</v>
+      </c>
+      <c r="C322" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>61</v>
+      </c>
+      <c r="B323" t="s">
+        <v>234</v>
+      </c>
+      <c r="C323" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>61</v>
+      </c>
+      <c r="B324" t="s">
+        <v>235</v>
+      </c>
+      <c r="C324" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>62</v>
+      </c>
+      <c r="B325" t="s">
+        <v>236</v>
+      </c>
+      <c r="C325" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>917</v>
+      </c>
+      <c r="B326" t="s">
+        <v>603</v>
+      </c>
+      <c r="C326" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>917</v>
+      </c>
+      <c r="B327" t="s">
+        <v>604</v>
+      </c>
+      <c r="C327" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>63</v>
+      </c>
+      <c r="B328" t="s">
+        <v>237</v>
+      </c>
+      <c r="C328" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>63</v>
+      </c>
+      <c r="B329" t="s">
+        <v>238</v>
+      </c>
+      <c r="C329" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>64</v>
+      </c>
+      <c r="B330" t="s">
+        <v>239</v>
+      </c>
+      <c r="C330" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>918</v>
+      </c>
+      <c r="B331" t="s">
+        <v>605</v>
+      </c>
+      <c r="C331" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>918</v>
+      </c>
+      <c r="B332" t="s">
+        <v>606</v>
+      </c>
+      <c r="C332" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>919</v>
+      </c>
+      <c r="B333" t="s">
+        <v>607</v>
+      </c>
+      <c r="C333" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>65</v>
+      </c>
+      <c r="B334" t="s">
+        <v>240</v>
+      </c>
+      <c r="C334" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>65</v>
+      </c>
+      <c r="B335" t="s">
+        <v>241</v>
+      </c>
+      <c r="C335" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>66</v>
+      </c>
+      <c r="B336" t="s">
+        <v>242</v>
+      </c>
+      <c r="C336" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>67</v>
+      </c>
+      <c r="B337" t="s">
+        <v>243</v>
+      </c>
+      <c r="C337" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>67</v>
+      </c>
+      <c r="B338" t="s">
+        <v>244</v>
+      </c>
+      <c r="C338" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>68</v>
+      </c>
+      <c r="B339" t="s">
+        <v>245</v>
+      </c>
+      <c r="C339" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>68</v>
+      </c>
+      <c r="B340" t="s">
+        <v>246</v>
+      </c>
+      <c r="C340" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>69</v>
+      </c>
+      <c r="B341" t="s">
+        <v>247</v>
+      </c>
+      <c r="C341" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>69</v>
+      </c>
+      <c r="B342" t="s">
+        <v>248</v>
+      </c>
+      <c r="C342" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>70</v>
+      </c>
+      <c r="B343" t="s">
+        <v>249</v>
+      </c>
+      <c r="C343" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>71</v>
+      </c>
+      <c r="B344" t="s">
+        <v>250</v>
+      </c>
+      <c r="C344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>71</v>
+      </c>
+      <c r="B345" t="s">
+        <v>251</v>
+      </c>
+      <c r="C345" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>920</v>
+      </c>
+      <c r="B346" t="s">
+        <v>608</v>
+      </c>
+      <c r="C346" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>920</v>
+      </c>
+      <c r="B347" t="s">
+        <v>609</v>
+      </c>
+      <c r="C347" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>920</v>
+      </c>
+      <c r="B348" t="s">
+        <v>610</v>
+      </c>
+      <c r="C348" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>921</v>
+      </c>
+      <c r="B349" t="s">
+        <v>611</v>
+      </c>
+      <c r="C349" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>921</v>
+      </c>
+      <c r="B350" t="s">
+        <v>612</v>
+      </c>
+      <c r="C350" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>922</v>
+      </c>
+      <c r="B351" t="s">
+        <v>613</v>
+      </c>
+      <c r="C351" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>922</v>
+      </c>
+      <c r="B352" t="s">
+        <v>614</v>
+      </c>
+      <c r="C352" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>923</v>
+      </c>
+      <c r="B353" t="s">
+        <v>615</v>
+      </c>
+      <c r="C353" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>923</v>
+      </c>
+      <c r="B354" t="s">
+        <v>616</v>
+      </c>
+      <c r="C354" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>72</v>
+      </c>
+      <c r="B355" t="s">
+        <v>252</v>
+      </c>
+      <c r="C355" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>73</v>
+      </c>
+      <c r="B356" t="s">
+        <v>253</v>
+      </c>
+      <c r="C356" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>74</v>
+      </c>
+      <c r="B357" t="s">
+        <v>254</v>
+      </c>
+      <c r="C357" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>75</v>
+      </c>
+      <c r="B358" t="s">
+        <v>255</v>
+      </c>
+      <c r="C358" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>76</v>
+      </c>
+      <c r="B359" t="s">
+        <v>256</v>
+      </c>
+      <c r="C359" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>76</v>
+      </c>
+      <c r="B360" t="s">
+        <v>257</v>
+      </c>
+      <c r="C360" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>924</v>
+      </c>
+      <c r="B361" t="s">
+        <v>617</v>
+      </c>
+      <c r="C361" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>924</v>
+      </c>
+      <c r="B362" t="s">
+        <v>618</v>
+      </c>
+      <c r="C362" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>925</v>
+      </c>
+      <c r="B363" t="s">
+        <v>619</v>
+      </c>
+      <c r="C363" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>925</v>
+      </c>
+      <c r="B364" t="s">
+        <v>620</v>
+      </c>
+      <c r="C364" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>925</v>
+      </c>
+      <c r="B365" t="s">
+        <v>621</v>
+      </c>
+      <c r="C365" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>3</v>
+      </c>
+      <c r="B366" t="s">
+        <v>258</v>
+      </c>
+      <c r="C366" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>77</v>
+      </c>
+      <c r="B367" t="s">
+        <v>259</v>
+      </c>
+      <c r="C367" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>78</v>
+      </c>
+      <c r="B368" t="s">
+        <v>260</v>
+      </c>
+      <c r="C368" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>79</v>
+      </c>
+      <c r="B369" t="s">
+        <v>261</v>
+      </c>
+      <c r="C369" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>926</v>
+      </c>
+      <c r="B370" t="s">
+        <v>622</v>
+      </c>
+      <c r="C370" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>80</v>
+      </c>
+      <c r="B371" t="s">
+        <v>262</v>
+      </c>
+      <c r="C371" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>81</v>
+      </c>
+      <c r="B372" t="s">
+        <v>263</v>
+      </c>
+      <c r="C372" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>82</v>
+      </c>
+      <c r="B373" t="s">
+        <v>264</v>
+      </c>
+      <c r="C373" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>927</v>
+      </c>
+      <c r="B374" t="s">
+        <v>623</v>
+      </c>
+      <c r="C374" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>83</v>
+      </c>
+      <c r="B375" t="s">
+        <v>265</v>
+      </c>
+      <c r="C375" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>84</v>
+      </c>
+      <c r="B376" t="s">
+        <v>266</v>
+      </c>
+      <c r="C376" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>85</v>
+      </c>
+      <c r="B377" t="s">
+        <v>267</v>
+      </c>
+      <c r="C377" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>86</v>
+      </c>
+      <c r="B378" t="s">
+        <v>268</v>
+      </c>
+      <c r="C378" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>87</v>
+      </c>
+      <c r="B379" t="s">
+        <v>269</v>
+      </c>
+      <c r="C379" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>88</v>
+      </c>
+      <c r="B380" t="s">
+        <v>270</v>
+      </c>
+      <c r="C380" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>89</v>
+      </c>
+      <c r="B381" t="s">
+        <v>271</v>
+      </c>
+      <c r="C381" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>90</v>
+      </c>
+      <c r="B382" t="s">
+        <v>272</v>
+      </c>
+      <c r="C382" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>91</v>
+      </c>
+      <c r="B383" t="s">
+        <v>273</v>
+      </c>
+      <c r="C383" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>92</v>
+      </c>
+      <c r="B384" t="s">
+        <v>274</v>
+      </c>
+      <c r="C384" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>93</v>
+      </c>
+      <c r="B385" t="s">
+        <v>275</v>
+      </c>
+      <c r="C385" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>94</v>
+      </c>
+      <c r="B386" t="s">
+        <v>276</v>
+      </c>
+      <c r="C386" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>94</v>
+      </c>
+      <c r="B387" t="s">
+        <v>277</v>
+      </c>
+      <c r="C387" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>94</v>
+      </c>
+      <c r="B388" t="s">
+        <v>278</v>
+      </c>
+      <c r="C388" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>95</v>
+      </c>
+      <c r="B389" t="s">
+        <v>279</v>
+      </c>
+      <c r="C389" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>96</v>
+      </c>
+      <c r="B390" t="s">
+        <v>280</v>
+      </c>
+      <c r="C390" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>96</v>
+      </c>
+      <c r="B391" t="s">
+        <v>281</v>
+      </c>
+      <c r="C391" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>97</v>
+      </c>
+      <c r="B392" t="s">
+        <v>282</v>
+      </c>
+      <c r="C392" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>98</v>
+      </c>
+      <c r="B393" t="s">
+        <v>283</v>
+      </c>
+      <c r="C393" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>99</v>
+      </c>
+      <c r="B394" t="s">
+        <v>284</v>
+      </c>
+      <c r="C394" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>100</v>
+      </c>
+      <c r="B395" t="s">
+        <v>285</v>
+      </c>
+      <c r="C395" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>101</v>
+      </c>
+      <c r="B396" t="s">
+        <v>286</v>
+      </c>
+      <c r="C396" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>102</v>
+      </c>
+      <c r="B397" t="s">
+        <v>287</v>
+      </c>
+      <c r="C397" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>103</v>
+      </c>
+      <c r="B398" t="s">
+        <v>288</v>
+      </c>
+      <c r="C398" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>104</v>
+      </c>
+      <c r="B399" t="s">
+        <v>289</v>
+      </c>
+      <c r="C399" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>105</v>
+      </c>
+      <c r="B400" t="s">
+        <v>290</v>
+      </c>
+      <c r="C400" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>106</v>
+      </c>
+      <c r="B401" t="s">
+        <v>291</v>
+      </c>
+      <c r="C401" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>107</v>
+      </c>
+      <c r="B402" t="s">
+        <v>292</v>
+      </c>
+      <c r="C402" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>107</v>
+      </c>
+      <c r="B403" t="s">
+        <v>293</v>
+      </c>
+      <c r="C403" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>107</v>
+      </c>
+      <c r="B404" t="s">
+        <v>294</v>
+      </c>
+      <c r="C404" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>108</v>
+      </c>
+      <c r="B405" t="s">
+        <v>295</v>
+      </c>
+      <c r="C405" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>109</v>
+      </c>
+      <c r="B406" t="s">
+        <v>296</v>
+      </c>
+      <c r="C406" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>110</v>
+      </c>
+      <c r="B407" t="s">
+        <v>297</v>
+      </c>
+      <c r="C407" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>111</v>
+      </c>
+      <c r="B408" t="s">
+        <v>298</v>
+      </c>
+      <c r="C408" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>928</v>
+      </c>
+      <c r="B409" t="s">
+        <v>624</v>
+      </c>
+      <c r="C409" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>929</v>
+      </c>
+      <c r="B410" t="s">
+        <v>625</v>
+      </c>
+      <c r="C410" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>112</v>
+      </c>
+      <c r="B411" t="s">
+        <v>299</v>
+      </c>
+      <c r="C411" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>930</v>
+      </c>
+      <c r="B412" t="s">
+        <v>626</v>
+      </c>
+      <c r="C412" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>113</v>
+      </c>
+      <c r="B413" t="s">
+        <v>300</v>
+      </c>
+      <c r="C413" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>931</v>
+      </c>
+      <c r="B414" t="s">
+        <v>627</v>
+      </c>
+      <c r="C414" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>114</v>
+      </c>
+      <c r="B415" t="s">
+        <v>301</v>
+      </c>
+      <c r="C415" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>115</v>
+      </c>
+      <c r="B416" t="s">
+        <v>302</v>
+      </c>
+      <c r="C416" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>932</v>
+      </c>
+      <c r="B417" t="s">
+        <v>628</v>
+      </c>
+      <c r="C417" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>933</v>
+      </c>
+      <c r="B418" t="s">
+        <v>629</v>
+      </c>
+      <c r="C418" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>934</v>
+      </c>
+      <c r="B419" t="s">
+        <v>630</v>
+      </c>
+      <c r="C419" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>935</v>
+      </c>
+      <c r="B420" t="s">
+        <v>631</v>
+      </c>
+      <c r="C420" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>936</v>
+      </c>
+      <c r="B421" t="s">
+        <v>632</v>
+      </c>
+      <c r="C421" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>937</v>
+      </c>
+      <c r="B422" t="s">
+        <v>633</v>
+      </c>
+      <c r="C422" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>938</v>
+      </c>
+      <c r="B423" t="s">
+        <v>634</v>
+      </c>
+      <c r="C423" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>939</v>
+      </c>
+      <c r="B424" t="s">
+        <v>635</v>
+      </c>
+      <c r="C424" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>116</v>
+      </c>
+      <c r="B425" t="s">
+        <v>303</v>
+      </c>
+      <c r="C425" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>117</v>
+      </c>
+      <c r="B426" t="s">
+        <v>304</v>
+      </c>
+      <c r="C426" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>118</v>
+      </c>
+      <c r="B427" t="s">
+        <v>305</v>
+      </c>
+      <c r="C427" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>119</v>
+      </c>
+      <c r="B428" t="s">
+        <v>306</v>
+      </c>
+      <c r="C428" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>120</v>
+      </c>
+      <c r="B429" t="s">
+        <v>307</v>
+      </c>
+      <c r="C429" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>940</v>
+      </c>
+      <c r="B430" t="s">
+        <v>636</v>
+      </c>
+      <c r="C430" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>941</v>
+      </c>
+      <c r="B431" t="s">
+        <v>637</v>
+      </c>
+      <c r="C431" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>941</v>
+      </c>
+      <c r="B432" t="s">
+        <v>638</v>
+      </c>
+      <c r="C432" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>121</v>
+      </c>
+      <c r="B433" t="s">
+        <v>308</v>
+      </c>
+      <c r="C433" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>122</v>
+      </c>
+      <c r="B434" t="s">
+        <v>309</v>
+      </c>
+      <c r="C434" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>942</v>
+      </c>
+      <c r="B435" t="s">
+        <v>639</v>
+      </c>
+      <c r="C435" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>943</v>
+      </c>
+      <c r="B436" t="s">
+        <v>640</v>
+      </c>
+      <c r="C436" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>944</v>
+      </c>
+      <c r="B437" t="s">
+        <v>641</v>
+      </c>
+      <c r="C437" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>944</v>
+      </c>
+      <c r="B438" t="s">
+        <v>642</v>
+      </c>
+      <c r="C438" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>944</v>
+      </c>
+      <c r="B439" t="s">
+        <v>643</v>
+      </c>
+      <c r="C439" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>944</v>
+      </c>
+      <c r="B440" t="s">
+        <v>644</v>
+      </c>
+      <c r="C440" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>945</v>
+      </c>
+      <c r="B441" t="s">
+        <v>645</v>
+      </c>
+      <c r="C441" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>131</v>
+      </c>
+      <c r="B442" t="s">
+        <v>310</v>
+      </c>
+      <c r="C442" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>131</v>
+      </c>
+      <c r="B443" t="s">
+        <v>311</v>
+      </c>
+      <c r="C443" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>946</v>
+      </c>
+      <c r="B444" t="s">
+        <v>646</v>
+      </c>
+      <c r="C444" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>947</v>
+      </c>
+      <c r="B445" t="s">
+        <v>647</v>
+      </c>
+      <c r="C445" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>947</v>
+      </c>
+      <c r="B446" t="s">
+        <v>648</v>
+      </c>
+      <c r="C446" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>948</v>
+      </c>
+      <c r="B447" t="s">
+        <v>649</v>
+      </c>
+      <c r="C447" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>949</v>
+      </c>
+      <c r="B448" t="s">
+        <v>650</v>
+      </c>
+      <c r="C448" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>950</v>
+      </c>
+      <c r="B449" t="s">
+        <v>651</v>
+      </c>
+      <c r="C449" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>951</v>
+      </c>
+      <c r="B450" t="s">
+        <v>652</v>
+      </c>
+      <c r="C450" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>132</v>
+      </c>
+      <c r="B451" t="s">
+        <v>312</v>
+      </c>
+      <c r="C451" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>133</v>
+      </c>
+      <c r="B452" t="s">
+        <v>313</v>
+      </c>
+      <c r="C452" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>952</v>
+      </c>
+      <c r="B453" t="s">
+        <v>653</v>
+      </c>
+      <c r="C453" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>953</v>
+      </c>
+      <c r="B454" t="s">
+        <v>654</v>
+      </c>
+      <c r="C454" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>134</v>
+      </c>
+      <c r="B455" t="s">
+        <v>314</v>
+      </c>
+      <c r="C455" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>135</v>
+      </c>
+      <c r="B456" t="s">
+        <v>315</v>
+      </c>
+      <c r="C456" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>136</v>
+      </c>
+      <c r="B457" t="s">
+        <v>316</v>
+      </c>
+      <c r="C457" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>954</v>
+      </c>
+      <c r="B458" t="s">
+        <v>655</v>
+      </c>
+      <c r="C458" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>137</v>
+      </c>
+      <c r="B459" t="s">
+        <v>317</v>
+      </c>
+      <c r="C459" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>955</v>
+      </c>
+      <c r="B460" t="s">
+        <v>656</v>
+      </c>
+      <c r="C460" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>138</v>
+      </c>
+      <c r="B461" t="s">
+        <v>318</v>
+      </c>
+      <c r="C461" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>139</v>
+      </c>
+      <c r="B462" t="s">
+        <v>319</v>
+      </c>
+      <c r="C462" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>140</v>
+      </c>
+      <c r="B463" t="s">
+        <v>320</v>
+      </c>
+      <c r="C463" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>141</v>
+      </c>
+      <c r="B464" t="s">
+        <v>321</v>
+      </c>
+      <c r="C464" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>142</v>
+      </c>
+      <c r="B465" t="s">
+        <v>322</v>
+      </c>
+      <c r="C465" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>956</v>
+      </c>
+      <c r="B466" t="s">
+        <v>657</v>
+      </c>
+      <c r="C466" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>957</v>
+      </c>
+      <c r="B467" t="s">
+        <v>658</v>
+      </c>
+      <c r="C467" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>143</v>
+      </c>
+      <c r="B468" t="s">
+        <v>323</v>
+      </c>
+      <c r="C468" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>144</v>
+      </c>
+      <c r="B469" t="s">
+        <v>324</v>
+      </c>
+      <c r="C469" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>958</v>
+      </c>
+      <c r="B470" t="s">
+        <v>659</v>
+      </c>
+      <c r="C470" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>145</v>
+      </c>
+      <c r="B471" t="s">
+        <v>325</v>
+      </c>
+      <c r="C471" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>146</v>
+      </c>
+      <c r="B472" t="s">
+        <v>326</v>
+      </c>
+      <c r="C472" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>959</v>
+      </c>
+      <c r="B473" t="s">
+        <v>660</v>
+      </c>
+      <c r="C473" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>960</v>
+      </c>
+      <c r="B474" t="s">
+        <v>661</v>
+      </c>
+      <c r="C474" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>961</v>
+      </c>
+      <c r="B475" t="s">
+        <v>662</v>
+      </c>
+      <c r="C475" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>962</v>
+      </c>
+      <c r="B476" t="s">
+        <v>663</v>
+      </c>
+      <c r="C476" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>963</v>
+      </c>
+      <c r="B477" t="s">
+        <v>664</v>
+      </c>
+      <c r="C477" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>964</v>
+      </c>
+      <c r="B478" t="s">
+        <v>665</v>
+      </c>
+      <c r="C478" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>965</v>
+      </c>
+      <c r="B479" t="s">
+        <v>666</v>
+      </c>
+      <c r="C479" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>966</v>
+      </c>
+      <c r="B480" t="s">
+        <v>667</v>
+      </c>
+      <c r="C480" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>147</v>
+      </c>
+      <c r="B481" t="s">
+        <v>327</v>
+      </c>
+      <c r="C481" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>148</v>
+      </c>
+      <c r="B482" t="s">
+        <v>328</v>
+      </c>
+      <c r="C482" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>149</v>
+      </c>
+      <c r="B483" t="s">
+        <v>329</v>
+      </c>
+      <c r="C483" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>150</v>
+      </c>
+      <c r="B484" t="s">
+        <v>330</v>
+      </c>
+      <c r="C484" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>967</v>
+      </c>
+      <c r="B485" t="s">
+        <v>668</v>
+      </c>
+      <c r="C485" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>968</v>
+      </c>
+      <c r="B486" t="s">
+        <v>669</v>
+      </c>
+      <c r="C486" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>969</v>
+      </c>
+      <c r="B487" t="s">
+        <v>670</v>
+      </c>
+      <c r="C487" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>151</v>
+      </c>
+      <c r="B488" t="s">
+        <v>331</v>
+      </c>
+      <c r="C488" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>970</v>
+      </c>
+      <c r="B489" t="s">
+        <v>671</v>
+      </c>
+      <c r="C489" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>152</v>
+      </c>
+      <c r="B490" t="s">
+        <v>332</v>
+      </c>
+      <c r="C490" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>971</v>
+      </c>
+      <c r="B491" t="s">
+        <v>672</v>
+      </c>
+      <c r="C491" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>153</v>
+      </c>
+      <c r="B492" t="s">
+        <v>333</v>
+      </c>
+      <c r="C492" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>154</v>
+      </c>
+      <c r="B493" t="s">
+        <v>334</v>
+      </c>
+      <c r="C493" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>155</v>
+      </c>
+      <c r="B494" t="s">
+        <v>335</v>
+      </c>
+      <c r="C494" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>156</v>
+      </c>
+      <c r="B495" t="s">
+        <v>336</v>
+      </c>
+      <c r="C495" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>972</v>
+      </c>
+      <c r="B496" t="s">
+        <v>673</v>
+      </c>
+      <c r="C496" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>973</v>
+      </c>
+      <c r="B497" t="s">
+        <v>674</v>
+      </c>
+      <c r="C497" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>974</v>
+      </c>
+      <c r="B498" t="s">
+        <v>675</v>
+      </c>
+      <c r="C498" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>974</v>
+      </c>
+      <c r="B499" t="s">
+        <v>676</v>
+      </c>
+      <c r="C499" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
         <v>157</v>
       </c>
-      <c r="B181" t="s">
+      <c r="B500" t="s">
         <v>337</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C500" t="s">
         <v>343</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>975</v>
+      </c>
+      <c r="B501" t="s">
+        <v>677</v>
+      </c>
+      <c r="C501" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>976</v>
+      </c>
+      <c r="B502" t="s">
+        <v>678</v>
+      </c>
+      <c r="C502" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>976</v>
+      </c>
+      <c r="B503" t="s">
+        <v>679</v>
+      </c>
+      <c r="C503" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>976</v>
+      </c>
+      <c r="B504" t="s">
+        <v>680</v>
+      </c>
+      <c r="C504" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>977</v>
+      </c>
+      <c r="B505" t="s">
+        <v>681</v>
+      </c>
+      <c r="C505" t="s">
+        <v>708</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539A515E-10F6-4C76-9DB1-C15D3E4E8DAC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF7690B-A3CF-4B1F-B188-E1E34FA81532}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="378">
   <si>
     <t>UTK</t>
   </si>
@@ -42,9 +42,6 @@
     <t>260904-F00003881</t>
   </si>
   <si>
-    <t>1040959940</t>
-  </si>
-  <si>
     <t>248747198</t>
   </si>
   <si>
@@ -435,7 +432,736 @@
     <t>327532711</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>1040959946KR/1</t>
+  </si>
+  <si>
+    <t>1040959946KR/2</t>
+  </si>
+  <si>
+    <t>1040960081KR/1</t>
+  </si>
+  <si>
+    <t>1040961993KR/1</t>
+  </si>
+  <si>
+    <t>248747198/1</t>
+  </si>
+  <si>
+    <t>248747198/2</t>
+  </si>
+  <si>
+    <t>248747208/1</t>
+  </si>
+  <si>
+    <t>248747208/2</t>
+  </si>
+  <si>
+    <t>6a9b014ac0fa1536b26febf2</t>
+  </si>
+  <si>
+    <t>6a95a295c0fa1536b26f81cb</t>
+  </si>
+  <si>
+    <t>6aa00d7c2235a0231b9afcfa</t>
+  </si>
+  <si>
+    <t>6aa294862235a0231b9b2f00</t>
+  </si>
+  <si>
+    <t>6aa141e32235a0231b9b12f6</t>
+  </si>
+  <si>
+    <t>6aa01eb12235a0231b9b0001</t>
+  </si>
+  <si>
+    <t>6aa146df2235a0231b9b13d8</t>
+  </si>
+  <si>
+    <t>6a9a89e0c0fa1536b26fdc83</t>
+  </si>
+  <si>
+    <t>6a9aabd0c0fa1536b26fe229</t>
+  </si>
+  <si>
+    <t>6a9d4b49c0fa1536b2700065</t>
+  </si>
+  <si>
+    <t>6a9d6514c0fa1536b2700266</t>
+  </si>
+  <si>
+    <t>6a9de278c0fa1536b2700772</t>
+  </si>
+  <si>
+    <t>6a9e855cc0fa1536b2701111</t>
+  </si>
+  <si>
+    <t>6a9e855cc0fa1536b2701112</t>
+  </si>
+  <si>
+    <t>6a9ff1cf2235a0231b9af8e6</t>
+  </si>
+  <si>
+    <t>6aa00cef2235a0231b9afcdb</t>
+  </si>
+  <si>
+    <t>6aa01d322235a0231b9affc7</t>
+  </si>
+  <si>
+    <t>6aa028e52235a0231b9b01d9</t>
+  </si>
+  <si>
+    <t>6a9fbab62235a0231b9aee6c</t>
+  </si>
+  <si>
+    <t>6a9fc2f82235a0231b9af019</t>
+  </si>
+  <si>
+    <t>6a9ffeb52235a0231b9afacd</t>
+  </si>
+  <si>
+    <t>6a9ffb422235a0231b9afa55</t>
+  </si>
+  <si>
+    <t>6a9ffb842235a0231b9afa80</t>
+  </si>
+  <si>
+    <t>6aa008482235a0231b9afc18</t>
+  </si>
+  <si>
+    <t>6aa01f8d2235a0231b9b002c</t>
+  </si>
+  <si>
+    <t>6aa124d42235a0231b9b0e0a</t>
+  </si>
+  <si>
+    <t>6aa13e9f2235a0231b9b1273</t>
+  </si>
+  <si>
+    <t>6aa13e9f2235a0231b9b1274</t>
+  </si>
+  <si>
+    <t>6aa1421d2235a0231b9b1305</t>
+  </si>
+  <si>
+    <t>6aa1421d2235a0231b9b1307</t>
+  </si>
+  <si>
+    <t>6aa27e632235a0231b9b2b17</t>
+  </si>
+  <si>
+    <t>6aa15f6d2235a0231b9b1867</t>
+  </si>
+  <si>
+    <t>6aa159992235a0231b9b1739</t>
+  </si>
+  <si>
+    <t>6aa159992235a0231b9b173b</t>
+  </si>
+  <si>
+    <t>6aa15b052235a0231b9b1766</t>
+  </si>
+  <si>
+    <t>6aa159932235a0231b9b1715</t>
+  </si>
+  <si>
+    <t>6aa170fd2235a0231b9b1bc7</t>
+  </si>
+  <si>
+    <t>6aa177032235a0231b9b1cd5</t>
+  </si>
+  <si>
+    <t>6aa177032235a0231b9b1cd6</t>
+  </si>
+  <si>
+    <t>6aa184f82235a0231b9b1e55</t>
+  </si>
+  <si>
+    <t>6aa1a93d2235a0231b9b20e2</t>
+  </si>
+  <si>
+    <t>6aa116dc2235a0231b9b0b7b</t>
+  </si>
+  <si>
+    <t>6aa1192f2235a0231b9b0bdf</t>
+  </si>
+  <si>
+    <t>6aa12e2f2235a0231b9b0fa4</t>
+  </si>
+  <si>
+    <t>6aa179392235a0231b9b1d24</t>
+  </si>
+  <si>
+    <t>6aa17a662235a0231b9b1d3f</t>
+  </si>
+  <si>
+    <t>6aa17a662235a0231b9b1d40</t>
+  </si>
+  <si>
+    <t>6aa184f82235a0231b9b1e59</t>
+  </si>
+  <si>
+    <t>6aa278aa2235a0231b9b2a2d</t>
+  </si>
+  <si>
+    <t>6aa278ab2235a0231b9b2a35</t>
+  </si>
+  <si>
+    <t>6aa278ab2235a0231b9b2a36</t>
+  </si>
+  <si>
+    <t>6aa283382235a0231b9b2c13</t>
+  </si>
+  <si>
+    <t>6aa283382235a0231b9b2c14</t>
+  </si>
+  <si>
+    <t>325075144/1</t>
+  </si>
+  <si>
+    <t>325075144/2</t>
+  </si>
+  <si>
+    <t>325351057/1</t>
+  </si>
+  <si>
+    <t>325351057/2</t>
+  </si>
+  <si>
+    <t>325351057/3</t>
+  </si>
+  <si>
+    <t>325404790/1</t>
+  </si>
+  <si>
+    <t>325404790/2</t>
+  </si>
+  <si>
+    <t>325923206/1</t>
+  </si>
+  <si>
+    <t>326051405/1</t>
+  </si>
+  <si>
+    <t>326051792/1</t>
+  </si>
+  <si>
+    <t>326051792/2</t>
+  </si>
+  <si>
+    <t>326051792/3</t>
+  </si>
+  <si>
+    <t>326457006/1</t>
+  </si>
+  <si>
+    <t>326457006/2</t>
+  </si>
+  <si>
+    <t>326457006/3</t>
+  </si>
+  <si>
+    <t>326621802/1</t>
+  </si>
+  <si>
+    <t>326621802/2</t>
+  </si>
+  <si>
+    <t>326621802/3</t>
+  </si>
+  <si>
+    <t>326716475/1</t>
+  </si>
+  <si>
+    <t>326716475/2</t>
+  </si>
+  <si>
+    <t>326716475/3</t>
+  </si>
+  <si>
+    <t>326812959/1</t>
+  </si>
+  <si>
+    <t>326813413/1</t>
+  </si>
+  <si>
+    <t>326813413/2</t>
+  </si>
+  <si>
+    <t>326859823/1</t>
+  </si>
+  <si>
+    <t>326859823/2</t>
+  </si>
+  <si>
+    <t>326859823/3</t>
+  </si>
+  <si>
+    <t>326860392/1</t>
+  </si>
+  <si>
+    <t>326860392/2</t>
+  </si>
+  <si>
+    <t>326860392/3</t>
+  </si>
+  <si>
+    <t>326860477/1</t>
+  </si>
+  <si>
+    <t>326860477/2</t>
+  </si>
+  <si>
+    <t>326913793/1</t>
+  </si>
+  <si>
+    <t>326913793/2</t>
+  </si>
+  <si>
+    <t>326913793/3</t>
+  </si>
+  <si>
+    <t>326914340/1</t>
+  </si>
+  <si>
+    <t>326968001/1</t>
+  </si>
+  <si>
+    <t>326968112/1</t>
+  </si>
+  <si>
+    <t>327025861/1</t>
+  </si>
+  <si>
+    <t>327025861/2</t>
+  </si>
+  <si>
+    <t>327026119/1</t>
+  </si>
+  <si>
+    <t>327026119/2</t>
+  </si>
+  <si>
+    <t>327026296/1</t>
+  </si>
+  <si>
+    <t>327026296/2</t>
+  </si>
+  <si>
+    <t>327026789/1</t>
+  </si>
+  <si>
+    <t>327070614/1</t>
+  </si>
+  <si>
+    <t>327070614/2</t>
+  </si>
+  <si>
+    <t>327070621/1</t>
+  </si>
+  <si>
+    <t>327109839/1</t>
+  </si>
+  <si>
+    <t>327110051/1</t>
+  </si>
+  <si>
+    <t>327110051/2</t>
+  </si>
+  <si>
+    <t>327110051/3</t>
+  </si>
+  <si>
+    <t>327110330/1</t>
+  </si>
+  <si>
+    <t>327110330/2</t>
+  </si>
+  <si>
+    <t>327110385/1</t>
+  </si>
+  <si>
+    <t>327110385/2</t>
+  </si>
+  <si>
+    <t>327110469/1</t>
+  </si>
+  <si>
+    <t>327110583/1</t>
+  </si>
+  <si>
+    <t>327110583/2</t>
+  </si>
+  <si>
+    <t>327153223/1</t>
+  </si>
+  <si>
+    <t>327153223/2</t>
+  </si>
+  <si>
+    <t>327153367/1</t>
+  </si>
+  <si>
+    <t>327153392/1</t>
+  </si>
+  <si>
+    <t>327153398/1</t>
+  </si>
+  <si>
+    <t>327153398/2</t>
+  </si>
+  <si>
+    <t>327153398/3</t>
+  </si>
+  <si>
+    <t>327153594/1</t>
+  </si>
+  <si>
+    <t>327153594/2</t>
+  </si>
+  <si>
+    <t>327153907/1</t>
+  </si>
+  <si>
+    <t>327198642/1</t>
+  </si>
+  <si>
+    <t>327198649/1</t>
+  </si>
+  <si>
+    <t>327198894/1</t>
+  </si>
+  <si>
+    <t>327199086/1</t>
+  </si>
+  <si>
+    <t>327199096/1</t>
+  </si>
+  <si>
+    <t>327199098/1</t>
+  </si>
+  <si>
+    <t>327199261/1</t>
+  </si>
+  <si>
+    <t>327199360/1</t>
+  </si>
+  <si>
+    <t>327253360/1</t>
+  </si>
+  <si>
+    <t>327253360/2</t>
+  </si>
+  <si>
+    <t>327253410/1</t>
+  </si>
+  <si>
+    <t>327253426/1</t>
+  </si>
+  <si>
+    <t>327253522/1</t>
+  </si>
+  <si>
+    <t>327253767/1</t>
+  </si>
+  <si>
+    <t>327253767/2</t>
+  </si>
+  <si>
+    <t>327310558/1</t>
+  </si>
+  <si>
+    <t>327310559/1</t>
+  </si>
+  <si>
+    <t>327310748/1</t>
+  </si>
+  <si>
+    <t>327310792/1</t>
+  </si>
+  <si>
+    <t>327354465/1</t>
+  </si>
+  <si>
+    <t>327354513/1</t>
+  </si>
+  <si>
+    <t>327354574/1</t>
+  </si>
+  <si>
+    <t>327354744/1</t>
+  </si>
+  <si>
+    <t>327354785/1</t>
+  </si>
+  <si>
+    <t>327354896/1</t>
+  </si>
+  <si>
+    <t>327355073/1</t>
+  </si>
+  <si>
+    <t>327355164/1</t>
+  </si>
+  <si>
+    <t>327355184/1</t>
+  </si>
+  <si>
+    <t>327355269/1</t>
+  </si>
+  <si>
+    <t>327402513/1</t>
+  </si>
+  <si>
+    <t>327402631/1</t>
+  </si>
+  <si>
+    <t>327402729/1</t>
+  </si>
+  <si>
+    <t>327402818/1</t>
+  </si>
+  <si>
+    <t>327402991/1</t>
+  </si>
+  <si>
+    <t>327403006/1</t>
+  </si>
+  <si>
+    <t>327403268/1</t>
+  </si>
+  <si>
+    <t>327403268/2</t>
+  </si>
+  <si>
+    <t>327471207/1</t>
+  </si>
+  <si>
+    <t>327471379/1</t>
+  </si>
+  <si>
+    <t>327471648/1</t>
+  </si>
+  <si>
+    <t>327531763/1</t>
+  </si>
+  <si>
+    <t>327531772/1</t>
+  </si>
+  <si>
+    <t>327531792/1</t>
+  </si>
+  <si>
+    <t>327532044/1</t>
+  </si>
+  <si>
+    <t>327532260/1</t>
+  </si>
+  <si>
+    <t>327532435/1</t>
+  </si>
+  <si>
+    <t>327532450/1</t>
+  </si>
+  <si>
+    <t>327532487/1</t>
+  </si>
+  <si>
+    <t>327532524/1</t>
+  </si>
+  <si>
+    <t>327532524/2</t>
+  </si>
+  <si>
+    <t>327532579/1</t>
+  </si>
+  <si>
+    <t>327532711/1</t>
+  </si>
+  <si>
+    <t>741307893KR/1</t>
+  </si>
+  <si>
+    <t>741307893KR/2</t>
+  </si>
+  <si>
+    <t>741307893KR/3</t>
+  </si>
+  <si>
+    <t>741307893KR/4</t>
+  </si>
+  <si>
+    <t>741308199KR/1</t>
+  </si>
+  <si>
+    <t>840925658KR/1</t>
+  </si>
+  <si>
+    <t>840925658KR/2</t>
+  </si>
+  <si>
+    <t>941155208KR/1</t>
+  </si>
+  <si>
+    <t>941155208KR/2</t>
+  </si>
+  <si>
+    <t>941155208KR/3</t>
+  </si>
+  <si>
+    <t>941155208KR/4</t>
+  </si>
+  <si>
+    <t>159995579544025250</t>
+  </si>
+  <si>
+    <t>202609072601891401</t>
+  </si>
+  <si>
+    <t>202609072601893101</t>
+  </si>
+  <si>
+    <t>202609072601893102</t>
+  </si>
+  <si>
+    <t>202609102601914701</t>
+  </si>
+  <si>
+    <t>202609102601915101</t>
+  </si>
+  <si>
+    <t>202609102601916701</t>
+  </si>
+  <si>
+    <t>202609102601916601</t>
+  </si>
+  <si>
+    <t>202609102601918101</t>
+  </si>
+  <si>
+    <t>202609102601914501</t>
+  </si>
+  <si>
+    <t>159995579543982578</t>
+  </si>
+  <si>
+    <t>1040959940/1</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>SZ-814</t>
+  </si>
+  <si>
+    <t>SZ-803</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-860</t>
+  </si>
+  <si>
+    <t>1040959946KR</t>
+  </si>
+  <si>
+    <t>1040960081KR</t>
+  </si>
+  <si>
+    <t>1040961993KR</t>
+  </si>
+  <si>
+    <t>741307893KR</t>
+  </si>
+  <si>
+    <t>741308199KR</t>
+  </si>
+  <si>
+    <t>840925658KR</t>
+  </si>
+  <si>
+    <t>941155208KR</t>
+  </si>
+  <si>
+    <t>NFD6-09-03-GXJR/CSXD</t>
+  </si>
+  <si>
+    <t>NFD6-09-05-JR5Q</t>
+  </si>
+  <si>
+    <t>NFD6-09-06-4GU5</t>
+  </si>
+  <si>
+    <t>NFD6-09-09-7H44</t>
+  </si>
+  <si>
+    <t>NFD6-09-09-9C72</t>
+  </si>
+  <si>
+    <t>NFD6-09-09-PZD5</t>
+  </si>
+  <si>
+    <t>NFD6-09-09-T9WW</t>
+  </si>
+  <si>
+    <t>NFE6-09-09-U9JJ</t>
+  </si>
+  <si>
+    <t>NFE6-09-09-W7YZ</t>
+  </si>
+  <si>
+    <t>R434568</t>
   </si>
 </sst>
 </file>
@@ -478,9 +1204,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -797,7 +1522,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC11F24F-E222-443E-8401-2ECBA69A40D4}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C206"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
@@ -817,1059 +1542,2258 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B11" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="C6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="C7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="C8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>12</v>
       </c>
-      <c r="C10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>15</v>
       </c>
-      <c r="C14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B20" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>16</v>
       </c>
-      <c r="C15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B21" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>17</v>
       </c>
-      <c r="C16" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>18</v>
       </c>
-      <c r="C17" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>19</v>
       </c>
-      <c r="C18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B25" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>20</v>
       </c>
-      <c r="C19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B26" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>21</v>
       </c>
-      <c r="C20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>23</v>
       </c>
-      <c r="C22" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B29" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>24</v>
       </c>
-      <c r="C23" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B30" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>25</v>
       </c>
-      <c r="C24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B31" t="s">
+        <v>163</v>
+      </c>
+      <c r="C31" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>26</v>
       </c>
-      <c r="C25" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="B32" t="s">
+        <v>164</v>
+      </c>
+      <c r="C32" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>27</v>
       </c>
-      <c r="C26" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B33" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>28</v>
       </c>
-      <c r="C27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B34" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>29</v>
       </c>
-      <c r="C28" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C35" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>30</v>
       </c>
-      <c r="C29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="B36" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" t="s">
+        <v>169</v>
+      </c>
+      <c r="C37" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>31</v>
       </c>
-      <c r="C30" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="B38" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>32</v>
       </c>
-      <c r="C31" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="B40" t="s">
+        <v>172</v>
+      </c>
+      <c r="C40" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>33</v>
       </c>
-      <c r="C32" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="B41" t="s">
+        <v>173</v>
+      </c>
+      <c r="C41" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>34</v>
       </c>
-      <c r="C33" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="B42" t="s">
+        <v>174</v>
+      </c>
+      <c r="C42" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" t="s">
+        <v>175</v>
+      </c>
+      <c r="C43" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>35</v>
       </c>
-      <c r="C34" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="B44" t="s">
+        <v>176</v>
+      </c>
+      <c r="C44" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="B45" t="s">
+        <v>177</v>
+      </c>
+      <c r="C45" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="B46" t="s">
+        <v>178</v>
+      </c>
+      <c r="C46" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="B47" t="s">
+        <v>179</v>
+      </c>
+      <c r="C47" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" t="s">
+        <v>180</v>
+      </c>
+      <c r="C48" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="B49" t="s">
+        <v>181</v>
+      </c>
+      <c r="C49" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="B50" t="s">
+        <v>182</v>
+      </c>
+      <c r="C50" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="B51" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="B52" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="B53" t="s">
+        <v>185</v>
+      </c>
+      <c r="C53" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="B54" t="s">
+        <v>186</v>
+      </c>
+      <c r="C54" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="B55" t="s">
+        <v>187</v>
+      </c>
+      <c r="C55" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56" t="s">
+        <v>188</v>
+      </c>
+      <c r="C56" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="B57" t="s">
+        <v>189</v>
+      </c>
+      <c r="C57" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="B58" t="s">
+        <v>190</v>
+      </c>
+      <c r="C58" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="B59" t="s">
+        <v>191</v>
+      </c>
+      <c r="C59" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" t="s">
+        <v>192</v>
+      </c>
+      <c r="C60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="B61" t="s">
+        <v>193</v>
+      </c>
+      <c r="C61" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>49</v>
+      </c>
+      <c r="B62" t="s">
+        <v>194</v>
+      </c>
+      <c r="C62" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="B63" t="s">
+        <v>195</v>
+      </c>
+      <c r="C63" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>50</v>
+      </c>
+      <c r="B64" t="s">
+        <v>196</v>
+      </c>
+      <c r="C64" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="B65" t="s">
+        <v>197</v>
+      </c>
+      <c r="C65" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>51</v>
+      </c>
+      <c r="B66" t="s">
+        <v>198</v>
+      </c>
+      <c r="C66" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>51</v>
+      </c>
+      <c r="B67" t="s">
+        <v>199</v>
+      </c>
+      <c r="C67" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="B68" t="s">
+        <v>200</v>
+      </c>
+      <c r="C68" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>52</v>
+      </c>
+      <c r="B69" t="s">
+        <v>201</v>
+      </c>
+      <c r="C69" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="B70" t="s">
+        <v>202</v>
+      </c>
+      <c r="C70" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>54</v>
       </c>
-      <c r="C53" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="B71" t="s">
+        <v>203</v>
+      </c>
+      <c r="C71" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>55</v>
       </c>
-      <c r="C54" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="B72" t="s">
+        <v>204</v>
+      </c>
+      <c r="C72" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>55</v>
+      </c>
+      <c r="B73" t="s">
+        <v>205</v>
+      </c>
+      <c r="C73" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>55</v>
+      </c>
+      <c r="B74" t="s">
+        <v>206</v>
+      </c>
+      <c r="C74" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>56</v>
       </c>
-      <c r="C55" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="B75" t="s">
+        <v>207</v>
+      </c>
+      <c r="C75" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>56</v>
+      </c>
+      <c r="B76" t="s">
+        <v>208</v>
+      </c>
+      <c r="C76" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>56</v>
+      </c>
+      <c r="B77" t="s">
+        <v>209</v>
+      </c>
+      <c r="C77" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>57</v>
       </c>
-      <c r="C56" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="B78" t="s">
+        <v>210</v>
+      </c>
+      <c r="C78" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>57</v>
+      </c>
+      <c r="B79" t="s">
+        <v>211</v>
+      </c>
+      <c r="C79" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>57</v>
+      </c>
+      <c r="B80" t="s">
+        <v>212</v>
+      </c>
+      <c r="C80" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>58</v>
       </c>
-      <c r="C57" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+      <c r="B81" t="s">
+        <v>213</v>
+      </c>
+      <c r="C81" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>58</v>
+      </c>
+      <c r="B82" t="s">
+        <v>214</v>
+      </c>
+      <c r="C82" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>58</v>
+      </c>
+      <c r="B83" t="s">
+        <v>215</v>
+      </c>
+      <c r="C83" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>59</v>
       </c>
-      <c r="C58" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="B84" t="s">
+        <v>216</v>
+      </c>
+      <c r="C84" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>60</v>
       </c>
-      <c r="C59" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="B85" t="s">
+        <v>217</v>
+      </c>
+      <c r="C85" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>60</v>
+      </c>
+      <c r="B86" t="s">
+        <v>218</v>
+      </c>
+      <c r="C86" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>61</v>
       </c>
-      <c r="C60" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="B87" t="s">
+        <v>219</v>
+      </c>
+      <c r="C87" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>61</v>
+      </c>
+      <c r="B88" t="s">
+        <v>220</v>
+      </c>
+      <c r="C88" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>61</v>
+      </c>
+      <c r="B89" t="s">
+        <v>221</v>
+      </c>
+      <c r="C89" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>62</v>
       </c>
-      <c r="C61" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="B90" t="s">
+        <v>222</v>
+      </c>
+      <c r="C90" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>62</v>
+      </c>
+      <c r="B91" t="s">
+        <v>223</v>
+      </c>
+      <c r="C91" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>62</v>
+      </c>
+      <c r="B92" t="s">
+        <v>224</v>
+      </c>
+      <c r="C92" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>63</v>
       </c>
-      <c r="C62" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+      <c r="B93" t="s">
+        <v>225</v>
+      </c>
+      <c r="C93" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>63</v>
+      </c>
+      <c r="B94" t="s">
+        <v>226</v>
+      </c>
+      <c r="C94" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>64</v>
       </c>
-      <c r="C63" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="B95" t="s">
+        <v>227</v>
+      </c>
+      <c r="C95" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>64</v>
+      </c>
+      <c r="B96" t="s">
+        <v>228</v>
+      </c>
+      <c r="C96" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>64</v>
+      </c>
+      <c r="B97" t="s">
+        <v>229</v>
+      </c>
+      <c r="C97" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>65</v>
       </c>
-      <c r="C64" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="B98" t="s">
+        <v>230</v>
+      </c>
+      <c r="C98" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>66</v>
       </c>
-      <c r="C65" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="B99" t="s">
+        <v>231</v>
+      </c>
+      <c r="C99" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>67</v>
       </c>
-      <c r="C66" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="B100" t="s">
+        <v>232</v>
+      </c>
+      <c r="C100" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>68</v>
       </c>
-      <c r="C67" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="B101" t="s">
+        <v>233</v>
+      </c>
+      <c r="C101" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>68</v>
+      </c>
+      <c r="B102" t="s">
+        <v>234</v>
+      </c>
+      <c r="C102" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>69</v>
       </c>
-      <c r="C68" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+      <c r="B103" t="s">
+        <v>235</v>
+      </c>
+      <c r="C103" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>69</v>
+      </c>
+      <c r="B104" t="s">
+        <v>236</v>
+      </c>
+      <c r="C104" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>70</v>
       </c>
-      <c r="C69" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+      <c r="B105" t="s">
+        <v>237</v>
+      </c>
+      <c r="C105" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>70</v>
+      </c>
+      <c r="B106" t="s">
+        <v>238</v>
+      </c>
+      <c r="C106" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>71</v>
       </c>
-      <c r="C70" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="B107" t="s">
+        <v>239</v>
+      </c>
+      <c r="C107" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>72</v>
       </c>
-      <c r="C71" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="B108" t="s">
+        <v>240</v>
+      </c>
+      <c r="C108" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>72</v>
+      </c>
+      <c r="B109" t="s">
+        <v>241</v>
+      </c>
+      <c r="C109" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>73</v>
       </c>
-      <c r="C72" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+      <c r="B110" t="s">
+        <v>242</v>
+      </c>
+      <c r="C110" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>74</v>
       </c>
-      <c r="C73" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+      <c r="B111" t="s">
+        <v>243</v>
+      </c>
+      <c r="C111" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>75</v>
       </c>
-      <c r="C74" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="B112" t="s">
+        <v>244</v>
+      </c>
+      <c r="C112" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>75</v>
+      </c>
+      <c r="B113" t="s">
+        <v>245</v>
+      </c>
+      <c r="C113" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>75</v>
+      </c>
+      <c r="B114" t="s">
+        <v>246</v>
+      </c>
+      <c r="C114" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>76</v>
       </c>
-      <c r="C75" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="B115" t="s">
+        <v>247</v>
+      </c>
+      <c r="C115" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>76</v>
+      </c>
+      <c r="B116" t="s">
+        <v>248</v>
+      </c>
+      <c r="C116" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>77</v>
       </c>
-      <c r="C76" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+      <c r="B117" t="s">
+        <v>249</v>
+      </c>
+      <c r="C117" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>77</v>
+      </c>
+      <c r="B118" t="s">
+        <v>250</v>
+      </c>
+      <c r="C118" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>78</v>
       </c>
-      <c r="C77" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="B119" t="s">
+        <v>251</v>
+      </c>
+      <c r="C119" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>79</v>
       </c>
-      <c r="C78" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+      <c r="B120" t="s">
+        <v>252</v>
+      </c>
+      <c r="C120" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>79</v>
+      </c>
+      <c r="B121" t="s">
+        <v>253</v>
+      </c>
+      <c r="C121" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
         <v>80</v>
       </c>
-      <c r="C79" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+      <c r="B122" t="s">
+        <v>254</v>
+      </c>
+      <c r="C122" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>80</v>
+      </c>
+      <c r="B123" t="s">
+        <v>255</v>
+      </c>
+      <c r="C123" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
         <v>81</v>
       </c>
-      <c r="C80" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
+      <c r="B124" t="s">
+        <v>256</v>
+      </c>
+      <c r="C124" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
         <v>82</v>
       </c>
-      <c r="C81" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+      <c r="B125" t="s">
+        <v>257</v>
+      </c>
+      <c r="C125" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>83</v>
       </c>
-      <c r="C82" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
+      <c r="B126" t="s">
+        <v>258</v>
+      </c>
+      <c r="C126" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>83</v>
+      </c>
+      <c r="B127" t="s">
+        <v>259</v>
+      </c>
+      <c r="C127" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>83</v>
+      </c>
+      <c r="B128" t="s">
+        <v>260</v>
+      </c>
+      <c r="C128" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>84</v>
       </c>
-      <c r="C83" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
+      <c r="B129" t="s">
+        <v>261</v>
+      </c>
+      <c r="C129" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>84</v>
+      </c>
+      <c r="B130" t="s">
+        <v>262</v>
+      </c>
+      <c r="C130" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>85</v>
       </c>
-      <c r="C84" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+      <c r="B131" t="s">
+        <v>263</v>
+      </c>
+      <c r="C131" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
         <v>86</v>
       </c>
-      <c r="C85" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+      <c r="B132" t="s">
+        <v>264</v>
+      </c>
+      <c r="C132" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>87</v>
       </c>
-      <c r="C86" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+      <c r="B133" t="s">
+        <v>265</v>
+      </c>
+      <c r="C133" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>88</v>
       </c>
-      <c r="C87" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
+      <c r="B134" t="s">
+        <v>266</v>
+      </c>
+      <c r="C134" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>89</v>
       </c>
-      <c r="C88" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
+      <c r="B135" t="s">
+        <v>267</v>
+      </c>
+      <c r="C135" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>90</v>
       </c>
-      <c r="C89" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
+      <c r="B136" t="s">
+        <v>268</v>
+      </c>
+      <c r="C136" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>91</v>
       </c>
-      <c r="C90" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
+      <c r="B137" t="s">
+        <v>269</v>
+      </c>
+      <c r="C137" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>92</v>
       </c>
-      <c r="C91" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
+      <c r="B138" t="s">
+        <v>270</v>
+      </c>
+      <c r="C138" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
         <v>93</v>
       </c>
-      <c r="C92" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
+      <c r="B139" t="s">
+        <v>271</v>
+      </c>
+      <c r="C139" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
         <v>94</v>
       </c>
-      <c r="C93" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
+      <c r="B140" t="s">
+        <v>272</v>
+      </c>
+      <c r="C140" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>94</v>
+      </c>
+      <c r="B141" t="s">
+        <v>273</v>
+      </c>
+      <c r="C141" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>95</v>
       </c>
-      <c r="C94" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
+      <c r="B142" t="s">
+        <v>274</v>
+      </c>
+      <c r="C142" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>96</v>
       </c>
-      <c r="C95" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
+      <c r="B143" t="s">
+        <v>275</v>
+      </c>
+      <c r="C143" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>97</v>
       </c>
-      <c r="C96" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
+      <c r="B144" t="s">
+        <v>276</v>
+      </c>
+      <c r="C144" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>98</v>
       </c>
-      <c r="C97" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
+      <c r="B145" t="s">
+        <v>277</v>
+      </c>
+      <c r="C145" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>98</v>
+      </c>
+      <c r="B146" t="s">
+        <v>278</v>
+      </c>
+      <c r="C146" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>99</v>
       </c>
-      <c r="C98" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
+      <c r="B147" t="s">
+        <v>279</v>
+      </c>
+      <c r="C147" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>100</v>
       </c>
-      <c r="C99" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
+      <c r="B148" t="s">
+        <v>280</v>
+      </c>
+      <c r="C148" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>101</v>
       </c>
-      <c r="C100" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
+      <c r="B149" t="s">
+        <v>281</v>
+      </c>
+      <c r="C149" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
         <v>102</v>
       </c>
-      <c r="C101" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
+      <c r="B150" t="s">
+        <v>282</v>
+      </c>
+      <c r="C150" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
         <v>103</v>
       </c>
-      <c r="C102" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
+      <c r="B151" t="s">
+        <v>283</v>
+      </c>
+      <c r="C151" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
         <v>104</v>
       </c>
-      <c r="C103" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
+      <c r="B152" t="s">
+        <v>284</v>
+      </c>
+      <c r="C152" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
         <v>105</v>
       </c>
-      <c r="C104" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
+      <c r="B153" t="s">
+        <v>285</v>
+      </c>
+      <c r="C153" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
         <v>106</v>
       </c>
-      <c r="C105" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
+      <c r="B154" t="s">
+        <v>286</v>
+      </c>
+      <c r="C154" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
         <v>107</v>
       </c>
-      <c r="C106" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
+      <c r="B155" t="s">
+        <v>287</v>
+      </c>
+      <c r="C155" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
         <v>108</v>
       </c>
-      <c r="C107" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
+      <c r="B156" t="s">
+        <v>288</v>
+      </c>
+      <c r="C156" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>109</v>
       </c>
-      <c r="C108" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
+      <c r="B157" t="s">
+        <v>289</v>
+      </c>
+      <c r="C157" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
         <v>110</v>
       </c>
-      <c r="C109" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
+      <c r="B158" t="s">
+        <v>290</v>
+      </c>
+      <c r="C158" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>111</v>
       </c>
-      <c r="C110" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
+      <c r="B159" t="s">
+        <v>291</v>
+      </c>
+      <c r="C159" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
         <v>112</v>
       </c>
-      <c r="C111" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
+      <c r="B160" t="s">
+        <v>292</v>
+      </c>
+      <c r="C160" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
         <v>113</v>
       </c>
-      <c r="C112" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
+      <c r="B161" t="s">
+        <v>293</v>
+      </c>
+      <c r="C161" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
         <v>114</v>
       </c>
-      <c r="C113" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
+      <c r="B162" t="s">
+        <v>294</v>
+      </c>
+      <c r="C162" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
         <v>115</v>
       </c>
-      <c r="C114" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
+      <c r="B163" t="s">
+        <v>295</v>
+      </c>
+      <c r="C163" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
         <v>116</v>
       </c>
-      <c r="C115" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
+      <c r="B164" t="s">
+        <v>296</v>
+      </c>
+      <c r="C164" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
         <v>117</v>
       </c>
-      <c r="C116" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
+      <c r="B165" t="s">
+        <v>297</v>
+      </c>
+      <c r="C165" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
         <v>118</v>
       </c>
-      <c r="C117" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
+      <c r="B166" t="s">
+        <v>298</v>
+      </c>
+      <c r="C166" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
         <v>119</v>
       </c>
-      <c r="C118" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
+      <c r="B167" t="s">
+        <v>299</v>
+      </c>
+      <c r="C167" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>119</v>
+      </c>
+      <c r="B168" t="s">
+        <v>300</v>
+      </c>
+      <c r="C168" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
         <v>120</v>
       </c>
-      <c r="C119" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
+      <c r="B169" t="s">
+        <v>301</v>
+      </c>
+      <c r="C169" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
         <v>121</v>
       </c>
-      <c r="C120" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
+      <c r="B170" t="s">
+        <v>302</v>
+      </c>
+      <c r="C170" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
         <v>122</v>
       </c>
-      <c r="C121" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
+      <c r="B171" t="s">
+        <v>303</v>
+      </c>
+      <c r="C171" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
         <v>123</v>
       </c>
-      <c r="C122" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
+      <c r="B172" t="s">
+        <v>304</v>
+      </c>
+      <c r="C172" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
         <v>124</v>
       </c>
-      <c r="C123" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
+      <c r="B173" t="s">
+        <v>305</v>
+      </c>
+      <c r="C173" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
         <v>125</v>
       </c>
-      <c r="C124" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
+      <c r="B174" t="s">
+        <v>306</v>
+      </c>
+      <c r="C174" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
         <v>126</v>
       </c>
-      <c r="C125" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
+      <c r="B175" t="s">
+        <v>307</v>
+      </c>
+      <c r="C175" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
         <v>127</v>
       </c>
-      <c r="C126" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
+      <c r="B176" t="s">
+        <v>308</v>
+      </c>
+      <c r="C176" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
         <v>128</v>
       </c>
-      <c r="C127" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
+      <c r="B177" t="s">
+        <v>309</v>
+      </c>
+      <c r="C177" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
         <v>129</v>
       </c>
-      <c r="C128" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
+      <c r="B178" t="s">
+        <v>310</v>
+      </c>
+      <c r="C178" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
         <v>130</v>
       </c>
-      <c r="C129" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
+      <c r="B179" t="s">
+        <v>311</v>
+      </c>
+      <c r="C179" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
         <v>131</v>
       </c>
-      <c r="C130" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
+      <c r="B180" t="s">
+        <v>312</v>
+      </c>
+      <c r="C180" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>131</v>
+      </c>
+      <c r="B181" t="s">
+        <v>313</v>
+      </c>
+      <c r="C181" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
         <v>132</v>
       </c>
-      <c r="C131" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
+      <c r="B182" t="s">
+        <v>314</v>
+      </c>
+      <c r="C182" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
         <v>133</v>
       </c>
-      <c r="C132" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C133" t="s">
-        <v>135</v>
+      <c r="B183" t="s">
+        <v>315</v>
+      </c>
+      <c r="C183" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>364</v>
+      </c>
+      <c r="B184" t="s">
+        <v>316</v>
+      </c>
+      <c r="C184" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>364</v>
+      </c>
+      <c r="B185" t="s">
+        <v>317</v>
+      </c>
+      <c r="C185" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>364</v>
+      </c>
+      <c r="B186" t="s">
+        <v>318</v>
+      </c>
+      <c r="C186" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>364</v>
+      </c>
+      <c r="B187" t="s">
+        <v>319</v>
+      </c>
+      <c r="C187" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>365</v>
+      </c>
+      <c r="B188" t="s">
+        <v>320</v>
+      </c>
+      <c r="C188" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>366</v>
+      </c>
+      <c r="B189" t="s">
+        <v>321</v>
+      </c>
+      <c r="C189" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>366</v>
+      </c>
+      <c r="B190" t="s">
+        <v>322</v>
+      </c>
+      <c r="C190" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>367</v>
+      </c>
+      <c r="B191" t="s">
+        <v>323</v>
+      </c>
+      <c r="C191" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>367</v>
+      </c>
+      <c r="B192" t="s">
+        <v>324</v>
+      </c>
+      <c r="C192" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>367</v>
+      </c>
+      <c r="B193" t="s">
+        <v>325</v>
+      </c>
+      <c r="C193" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>367</v>
+      </c>
+      <c r="B194" t="s">
+        <v>326</v>
+      </c>
+      <c r="C194" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>368</v>
+      </c>
+      <c r="B195" t="s">
+        <v>327</v>
+      </c>
+      <c r="C195" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>369</v>
+      </c>
+      <c r="B196" t="s">
+        <v>328</v>
+      </c>
+      <c r="C196" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>370</v>
+      </c>
+      <c r="B197" t="s">
+        <v>329</v>
+      </c>
+      <c r="C197" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>370</v>
+      </c>
+      <c r="B198" t="s">
+        <v>330</v>
+      </c>
+      <c r="C198" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>371</v>
+      </c>
+      <c r="B199" t="s">
+        <v>331</v>
+      </c>
+      <c r="C199" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>372</v>
+      </c>
+      <c r="B200" t="s">
+        <v>332</v>
+      </c>
+      <c r="C200" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>373</v>
+      </c>
+      <c r="B201" t="s">
+        <v>333</v>
+      </c>
+      <c r="C201" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>374</v>
+      </c>
+      <c r="B202" t="s">
+        <v>334</v>
+      </c>
+      <c r="C202" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>375</v>
+      </c>
+      <c r="B203" t="s">
+        <v>335</v>
+      </c>
+      <c r="C203" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>376</v>
+      </c>
+      <c r="B204" t="s">
+        <v>336</v>
+      </c>
+      <c r="C204" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>377</v>
+      </c>
+      <c r="B205" t="s">
+        <v>337</v>
+      </c>
+      <c r="C205" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>1040959940</v>
+      </c>
+      <c r="B206" t="s">
+        <v>338</v>
+      </c>
+      <c r="C206" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF7690B-A3CF-4B1F-B188-E1E34FA81532}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06088505-385D-46E2-8E96-D9B7EFCB887F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="379">
   <si>
     <t>UTK</t>
   </si>
@@ -1162,6 +1162,9 @@
   </si>
   <si>
     <t>R434568</t>
+  </si>
+  <si>
+    <t>2026K/726</t>
   </si>
 </sst>
 </file>
@@ -1522,7 +1525,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC11F24F-E222-443E-8401-2ECBA69A40D4}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:C206"/>
+  <dimension ref="A1:C207"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
@@ -3796,6 +3799,17 @@
         <v>349</v>
       </c>
     </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>378</v>
+      </c>
+      <c r="B207" t="s">
+        <v>378</v>
+      </c>
+      <c r="C207" t="s">
+        <v>342</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C496" xr:uid="{544EFAB1-8998-46EF-B9E5-D4918C9DF0DC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06088505-385D-46E2-8E96-D9B7EFCB887F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A514853B-564D-475B-925B-EE58B196F897}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="776">
   <si>
     <t>UTK</t>
   </si>
@@ -1044,9 +1044,6 @@
     <t>159995579543982578</t>
   </si>
   <si>
-    <t>1040959940/1</t>
-  </si>
-  <si>
     <t>SZ-805</t>
   </si>
   <si>
@@ -1165,6 +1162,1200 @@
   </si>
   <si>
     <t>2026K/726</t>
+  </si>
+  <si>
+    <t>248747105/1</t>
+  </si>
+  <si>
+    <t>248747105/2</t>
+  </si>
+  <si>
+    <t>248747167/1</t>
+  </si>
+  <si>
+    <t>248747167/2</t>
+  </si>
+  <si>
+    <t>6aa009d42235a0231b9afc48</t>
+  </si>
+  <si>
+    <t>6aa00eaf2235a0231b9afd38</t>
+  </si>
+  <si>
+    <t>6a9acb16c0fa1536b26fe70f</t>
+  </si>
+  <si>
+    <t>6a9acb16c0fa1536b26fe710</t>
+  </si>
+  <si>
+    <t>6a97fc27c0fa1536b26faa91</t>
+  </si>
+  <si>
+    <t>6a9a7939c0fa1536b26fd963</t>
+  </si>
+  <si>
+    <t>6a8eedf3c0fa1536b26f1c5a</t>
+  </si>
+  <si>
+    <t>6a9920a5c0fa1536b26fbe52</t>
+  </si>
+  <si>
+    <t>6aa00cbc2235a0231b9afcb6</t>
+  </si>
+  <si>
+    <t>6a9e744ec0fa1536b2700cf3</t>
+  </si>
+  <si>
+    <t>6aa10b792235a0231b9b095f</t>
+  </si>
+  <si>
+    <t>6aa262f22235a0231b9b2575</t>
+  </si>
+  <si>
+    <t>6a9ed18ac0fa1536b2701ef5</t>
+  </si>
+  <si>
+    <t>6aa28fa72235a0231b9b2e25</t>
+  </si>
+  <si>
+    <t>6aa0fad52235a0231b9b0779</t>
+  </si>
+  <si>
+    <t>6a968acfc0fa1536b26f8a6b</t>
+  </si>
+  <si>
+    <t>6a9adcacc0fa1536b26fe931</t>
+  </si>
+  <si>
+    <t>6aa122a42235a0231b9b0da6</t>
+  </si>
+  <si>
+    <t>6aa014e42235a0231b9afe4b</t>
+  </si>
+  <si>
+    <t>6aa0081b2235a0231b9afc07</t>
+  </si>
+  <si>
+    <t>6a998729c0fa1536b26fd022</t>
+  </si>
+  <si>
+    <t>6aa262a12235a0231b9b2571</t>
+  </si>
+  <si>
+    <t>6aa01b162235a0231b9aff69</t>
+  </si>
+  <si>
+    <t>6aa25f032235a0231b9b24ca</t>
+  </si>
+  <si>
+    <t>6a9a96cdc0fa1536b26fdeff</t>
+  </si>
+  <si>
+    <t>6a9af924c0fa1536b26feb7c</t>
+  </si>
+  <si>
+    <t>6a9af924c0fa1536b26feb7d</t>
+  </si>
+  <si>
+    <t>6a9bbe09c0fa1536b26fee08</t>
+  </si>
+  <si>
+    <t>6a9fff5e2235a0231b9afb0d</t>
+  </si>
+  <si>
+    <t>6a9fff5e2235a0231b9afb0e</t>
+  </si>
+  <si>
+    <t>6a9c345cc0fa1536b26ff962</t>
+  </si>
+  <si>
+    <t>6a9d2e05c0fa1536b26ffe1f</t>
+  </si>
+  <si>
+    <t>6aa251ba2235a0231b9b22fc</t>
+  </si>
+  <si>
+    <t>6a9d7a26c0fa1536b27003b7</t>
+  </si>
+  <si>
+    <t>6a9d3e69c0fa1536b26fff79</t>
+  </si>
+  <si>
+    <t>6aa122242235a0231b9b0d7b</t>
+  </si>
+  <si>
+    <t>6aa15edc2235a0231b9b184e</t>
+  </si>
+  <si>
+    <t>6a9ecbb8c0fa1536b2701e02</t>
+  </si>
+  <si>
+    <t>6a9ecf30c0fa1536b2701e7e</t>
+  </si>
+  <si>
+    <t>6a9f018ec0fa1536b270236b</t>
+  </si>
+  <si>
+    <t>6a9e7ae9c0fa1536b2700ec6</t>
+  </si>
+  <si>
+    <t>6a9e7ae9c0fa1536b2700ec0</t>
+  </si>
+  <si>
+    <t>6a9e7ae9c0fa1536b2700ec1</t>
+  </si>
+  <si>
+    <t>6a9e7ae9c0fa1536b2700ec2</t>
+  </si>
+  <si>
+    <t>6aa117c62235a0231b9b0b87</t>
+  </si>
+  <si>
+    <t>6aa2636a2235a0231b9b2578</t>
+  </si>
+  <si>
+    <t>6a9edc17c0fa1536b2702048</t>
+  </si>
+  <si>
+    <t>6a9ee7ccc0fa1536b270216f</t>
+  </si>
+  <si>
+    <t>6a9ef010c0fa1536b2702242</t>
+  </si>
+  <si>
+    <t>6aa10bbc2235a0231b9b0962</t>
+  </si>
+  <si>
+    <t>6a9fc68d2235a0231b9af0d3</t>
+  </si>
+  <si>
+    <t>6a9fcea42235a0231b9af288</t>
+  </si>
+  <si>
+    <t>6aa252242235a0231b9b230a</t>
+  </si>
+  <si>
+    <t>6a9ffa0e2235a0231b9afa37</t>
+  </si>
+  <si>
+    <t>6aa013ca2235a0231b9afe2e</t>
+  </si>
+  <si>
+    <t>6aa019a92235a0231b9aff01</t>
+  </si>
+  <si>
+    <t>6aa019a92235a0231b9aff03</t>
+  </si>
+  <si>
+    <t>6aa01df02235a0231b9affd9</t>
+  </si>
+  <si>
+    <t>6aa027b62235a0231b9b018f</t>
+  </si>
+  <si>
+    <t>6aa1423d2235a0231b9b1318</t>
+  </si>
+  <si>
+    <t>6aa1423d2235a0231b9b1319</t>
+  </si>
+  <si>
+    <t>6aa027ba2235a0231b9b01a8</t>
+  </si>
+  <si>
+    <t>6aa027ba2235a0231b9b01a9</t>
+  </si>
+  <si>
+    <t>6aa02fee2235a0231b9b029c</t>
+  </si>
+  <si>
+    <t>6a9fbe5a2235a0231b9aef4a</t>
+  </si>
+  <si>
+    <t>6a9fbe5a2235a0231b9aef4b</t>
+  </si>
+  <si>
+    <t>6a9fc1db2235a0231b9aeffe</t>
+  </si>
+  <si>
+    <t>6a9fd0fb2235a0231b9af2f5</t>
+  </si>
+  <si>
+    <t>6a9fcc4b2235a0231b9af1fd</t>
+  </si>
+  <si>
+    <t>6a9ff13e2235a0231b9af8ba</t>
+  </si>
+  <si>
+    <t>6a9ff13e2235a0231b9af8bb</t>
+  </si>
+  <si>
+    <t>6a9ff13e2235a0231b9af8bc</t>
+  </si>
+  <si>
+    <t>6a9ff13e2235a0231b9af8bd</t>
+  </si>
+  <si>
+    <t>6a9ff13e2235a0231b9af8be</t>
+  </si>
+  <si>
+    <t>6a9ff13e2235a0231b9af8bf</t>
+  </si>
+  <si>
+    <t>6aa012f32235a0231b9afe0c</t>
+  </si>
+  <si>
+    <t>6aa002342235a0231b9afb48</t>
+  </si>
+  <si>
+    <t>6aa002342235a0231b9afb49</t>
+  </si>
+  <si>
+    <t>6aa008142235a0231b9afbf3</t>
+  </si>
+  <si>
+    <t>6aa00cef2235a0231b9afce5</t>
+  </si>
+  <si>
+    <t>6aa00cef2235a0231b9afce6</t>
+  </si>
+  <si>
+    <t>6aa00d132235a0231b9afcf1</t>
+  </si>
+  <si>
+    <t>6aa013ca2235a0231b9afe33</t>
+  </si>
+  <si>
+    <t>6aa0177d2235a0231b9afeb8</t>
+  </si>
+  <si>
+    <t>6aa020b12235a0231b9b0082</t>
+  </si>
+  <si>
+    <t>6aa027b92235a0231b9b019d</t>
+  </si>
+  <si>
+    <t>6aa02d8b2235a0231b9b024b</t>
+  </si>
+  <si>
+    <t>6aa033812235a0231b9b02dc</t>
+  </si>
+  <si>
+    <t>6aa032462235a0231b9b02d2</t>
+  </si>
+  <si>
+    <t>6aa032462235a0231b9b02d3</t>
+  </si>
+  <si>
+    <t>6aa040532235a0231b9b041d</t>
+  </si>
+  <si>
+    <t>6aa040532235a0231b9b041e</t>
+  </si>
+  <si>
+    <t>6aa055662235a0231b9b0595</t>
+  </si>
+  <si>
+    <t>6aa06a842235a0231b9b0650</t>
+  </si>
+  <si>
+    <t>6aa06a842235a0231b9b0651</t>
+  </si>
+  <si>
+    <t>6aa100802235a0231b9b07e6</t>
+  </si>
+  <si>
+    <t>6aa10d782235a0231b9b09c4</t>
+  </si>
+  <si>
+    <t>6aa113472235a0231b9b0ac8</t>
+  </si>
+  <si>
+    <t>6aa120442235a0231b9b0d4a</t>
+  </si>
+  <si>
+    <t>6aa120442235a0231b9b0d4b</t>
+  </si>
+  <si>
+    <t>6aa123ea2235a0231b9b0dee</t>
+  </si>
+  <si>
+    <t>6aa12d0c2235a0231b9b0f71</t>
+  </si>
+  <si>
+    <t>6aa15c332235a0231b9b17c5</t>
+  </si>
+  <si>
+    <t>6aa15c332235a0231b9b17c6</t>
+  </si>
+  <si>
+    <t>6aa15f6d2235a0231b9b186a</t>
+  </si>
+  <si>
+    <t>6aa15f6d2235a0231b9b186c</t>
+  </si>
+  <si>
+    <t>6aa167a22235a0231b9b19fa</t>
+  </si>
+  <si>
+    <t>6aa167a22235a0231b9b19fb</t>
+  </si>
+  <si>
+    <t>6aa167a22235a0231b9b19fc</t>
+  </si>
+  <si>
+    <t>6aa169002235a0231b9b1a36</t>
+  </si>
+  <si>
+    <t>6aa188772235a0231b9b1eb6</t>
+  </si>
+  <si>
+    <t>6aa0ff5a2235a0231b9b07d4</t>
+  </si>
+  <si>
+    <t>6aa11ca62235a0231b9b0ca4</t>
+  </si>
+  <si>
+    <t>6aa1285a2235a0231b9b0e7e</t>
+  </si>
+  <si>
+    <t>6aa1285a2235a0231b9b0e7f</t>
+  </si>
+  <si>
+    <t>6aa148082235a0231b9b13f8</t>
+  </si>
+  <si>
+    <t>6aa14ddf2235a0231b9b1517</t>
+  </si>
+  <si>
+    <t>6aa1573b2235a0231b9b169c</t>
+  </si>
+  <si>
+    <t>6aa167a02235a0231b9b19db</t>
+  </si>
+  <si>
+    <t>6aa167a02235a0231b9b19dc</t>
+  </si>
+  <si>
+    <t>6aa169002235a0231b9b1a3e</t>
+  </si>
+  <si>
+    <t>6aa16ea62235a0231b9b1b63</t>
+  </si>
+  <si>
+    <t>6aa171092235a0231b9b1bd4</t>
+  </si>
+  <si>
+    <t>6aa1b7552235a0231b9b2161</t>
+  </si>
+  <si>
+    <t>6aa1a3682235a0231b9b20b1</t>
+  </si>
+  <si>
+    <t>6aa1a3682235a0231b9b20b3</t>
+  </si>
+  <si>
+    <t>6aa250e42235a0231b9b22f3</t>
+  </si>
+  <si>
+    <t>6aa259062235a0231b9b238a</t>
+  </si>
+  <si>
+    <t>6aa25c902235a0231b9b2418</t>
+  </si>
+  <si>
+    <t>6aa269772235a0231b9b26e7</t>
+  </si>
+  <si>
+    <t>6aa239922235a0231b9b222d</t>
+  </si>
+  <si>
+    <t>6aa239922235a0231b9b222e</t>
+  </si>
+  <si>
+    <t>6aa239922235a0231b9b222f</t>
+  </si>
+  <si>
+    <t>6aa254752235a0231b9b2338</t>
+  </si>
+  <si>
+    <t>6aa2613f2235a0231b9b2521</t>
+  </si>
+  <si>
+    <t>6aa26d1b2235a0231b9b27cb</t>
+  </si>
+  <si>
+    <t>6aa279db2235a0231b9b2a56</t>
+  </si>
+  <si>
+    <t>6aa280ec2235a0231b9b2ba3</t>
+  </si>
+  <si>
+    <t>6aa287e92235a0231b9b2cb7</t>
+  </si>
+  <si>
+    <t>6aa287e92235a0231b9b2cb8</t>
+  </si>
+  <si>
+    <t>1449-207877</t>
+  </si>
+  <si>
+    <t>1449-408336</t>
+  </si>
+  <si>
+    <t>326397736/1</t>
+  </si>
+  <si>
+    <t>326397736/2</t>
+  </si>
+  <si>
+    <t>326622653/1</t>
+  </si>
+  <si>
+    <t>326622653/2</t>
+  </si>
+  <si>
+    <t>326860313/1</t>
+  </si>
+  <si>
+    <t>326860313/2</t>
+  </si>
+  <si>
+    <t>326968117/1</t>
+  </si>
+  <si>
+    <t>326968117/2</t>
+  </si>
+  <si>
+    <t>327026309/1</t>
+  </si>
+  <si>
+    <t>327026309/2</t>
+  </si>
+  <si>
+    <t>327110318/1</t>
+  </si>
+  <si>
+    <t>327199404/1</t>
+  </si>
+  <si>
+    <t>327199404/2</t>
+  </si>
+  <si>
+    <t>327253145/1</t>
+  </si>
+  <si>
+    <t>327253145/2</t>
+  </si>
+  <si>
+    <t>327253145/3</t>
+  </si>
+  <si>
+    <t>327253713/1</t>
+  </si>
+  <si>
+    <t>327254105/1</t>
+  </si>
+  <si>
+    <t>327354463/1</t>
+  </si>
+  <si>
+    <t>327355346/1</t>
+  </si>
+  <si>
+    <t>327402600/1</t>
+  </si>
+  <si>
+    <t>327402719/1</t>
+  </si>
+  <si>
+    <t>327532288/1</t>
+  </si>
+  <si>
+    <t>327532288/2</t>
+  </si>
+  <si>
+    <t>327532288/3</t>
+  </si>
+  <si>
+    <t>327532620/1</t>
+  </si>
+  <si>
+    <t>327532645/1</t>
+  </si>
+  <si>
+    <t>327532646/1</t>
+  </si>
+  <si>
+    <t>327662021/1</t>
+  </si>
+  <si>
+    <t>327763229/1</t>
+  </si>
+  <si>
+    <t>327763401/1</t>
+  </si>
+  <si>
+    <t>327763451/1</t>
+  </si>
+  <si>
+    <t>51340047568KR/1</t>
+  </si>
+  <si>
+    <t>51340047673KR/1</t>
+  </si>
+  <si>
+    <t>51340047726KR/1</t>
+  </si>
+  <si>
+    <t>741307823KR/1</t>
+  </si>
+  <si>
+    <t>741307823KR/2</t>
+  </si>
+  <si>
+    <t>941155212KR/1</t>
+  </si>
+  <si>
+    <t>941155224KR/1</t>
+  </si>
+  <si>
+    <t>941155239KR/1</t>
+  </si>
+  <si>
+    <t>941155243KR/1</t>
+  </si>
+  <si>
+    <t>99003165/1</t>
+  </si>
+  <si>
+    <t>99003232/1</t>
+  </si>
+  <si>
+    <t>202609022601868301</t>
+  </si>
+  <si>
+    <t>202609022601868302</t>
+  </si>
+  <si>
+    <t>202609022601868303</t>
+  </si>
+  <si>
+    <t>202609022601868304</t>
+  </si>
+  <si>
+    <t>202609102601875201</t>
+  </si>
+  <si>
+    <t>202609102601917101</t>
+  </si>
+  <si>
+    <t>202609102601915201</t>
+  </si>
+  <si>
+    <t>202609102601913901</t>
+  </si>
+  <si>
+    <t>202609102601917001</t>
+  </si>
+  <si>
+    <t>202609102601914601</t>
+  </si>
+  <si>
+    <t>159995579544041359</t>
+  </si>
+  <si>
+    <t>159995579544041366</t>
+  </si>
+  <si>
+    <t>159995579543986002</t>
+  </si>
+  <si>
+    <t>159995579543985975</t>
+  </si>
+  <si>
+    <t>159995579543985982</t>
+  </si>
+  <si>
+    <t>159995579543985999</t>
+  </si>
+  <si>
+    <t>159995579544007973</t>
+  </si>
+  <si>
+    <t>159995579544007980</t>
+  </si>
+  <si>
+    <t>159995579544007997</t>
+  </si>
+  <si>
+    <t>2026K/727</t>
+  </si>
+  <si>
+    <t>2026K/728</t>
+  </si>
+  <si>
+    <t>540953052KR/1</t>
+  </si>
+  <si>
+    <t>K-917</t>
+  </si>
+  <si>
+    <t>K-931</t>
+  </si>
+  <si>
+    <t>K-999</t>
+  </si>
+  <si>
+    <t>K-983</t>
+  </si>
+  <si>
+    <t>K-998</t>
+  </si>
+  <si>
+    <t>K-921</t>
+  </si>
+  <si>
+    <t>K-943</t>
+  </si>
+  <si>
+    <t>K-964</t>
+  </si>
+  <si>
+    <t>K-9121</t>
+  </si>
+  <si>
+    <t>K-915</t>
+  </si>
+  <si>
+    <t>K-992</t>
+  </si>
+  <si>
+    <t>K-942</t>
+  </si>
+  <si>
+    <t>K-971</t>
+  </si>
+  <si>
+    <t>K-962</t>
+  </si>
+  <si>
+    <t>K-961</t>
+  </si>
+  <si>
+    <t>K-982</t>
+  </si>
+  <si>
+    <t>K-981</t>
+  </si>
+  <si>
+    <t>K-963</t>
+  </si>
+  <si>
+    <t>K-9132</t>
+  </si>
+  <si>
+    <t>K-951</t>
+  </si>
+  <si>
+    <t>K-918</t>
+  </si>
+  <si>
+    <t>K-902</t>
+  </si>
+  <si>
+    <t>K-930</t>
+  </si>
+  <si>
+    <t>K-973</t>
+  </si>
+  <si>
+    <t>K-953</t>
+  </si>
+  <si>
+    <t>K-952</t>
+  </si>
+  <si>
+    <t>K-910</t>
+  </si>
+  <si>
+    <t>K-9122</t>
+  </si>
+  <si>
+    <t>K-911</t>
+  </si>
+  <si>
+    <t>K-941</t>
+  </si>
+  <si>
+    <t>248747105</t>
+  </si>
+  <si>
+    <t>248747167</t>
+  </si>
+  <si>
+    <t>260721-F00013474</t>
+  </si>
+  <si>
+    <t>260811-F00000518</t>
+  </si>
+  <si>
+    <t>260814-W00008737</t>
+  </si>
+  <si>
+    <t>260819-F00010282</t>
+  </si>
+  <si>
+    <t>260825-F00006332</t>
+  </si>
+  <si>
+    <t>260826-F00011319</t>
+  </si>
+  <si>
+    <t>260827-F00001612</t>
+  </si>
+  <si>
+    <t>260828-F00001529</t>
+  </si>
+  <si>
+    <t>260828-F00014474</t>
+  </si>
+  <si>
+    <t>260830-F00000512</t>
+  </si>
+  <si>
+    <t>260831-F00005995</t>
+  </si>
+  <si>
+    <t>260831-F00015697</t>
+  </si>
+  <si>
+    <t>260901-F00000975</t>
+  </si>
+  <si>
+    <t>260901-F00010002</t>
+  </si>
+  <si>
+    <t>260901-W00002927</t>
+  </si>
+  <si>
+    <t>260902-F00009504</t>
+  </si>
+  <si>
+    <t>260902-F00013473</t>
+  </si>
+  <si>
+    <t>260903-F00003664</t>
+  </si>
+  <si>
+    <t>260903-F00012263</t>
+  </si>
+  <si>
+    <t>260903-W00008932</t>
+  </si>
+  <si>
+    <t>260904-F00001740</t>
+  </si>
+  <si>
+    <t>260904-F00002382</t>
+  </si>
+  <si>
+    <t>260904-F00004031</t>
+  </si>
+  <si>
+    <t>260904-F00006138</t>
+  </si>
+  <si>
+    <t>260904-F00015766</t>
+  </si>
+  <si>
+    <t>260905-F00000511</t>
+  </si>
+  <si>
+    <t>260905-W00005579</t>
+  </si>
+  <si>
+    <t>260905-W00007896</t>
+  </si>
+  <si>
+    <t>260906-F00000942</t>
+  </si>
+  <si>
+    <t>260906-F00003069</t>
+  </si>
+  <si>
+    <t>260906-F00003970</t>
+  </si>
+  <si>
+    <t>260906-W00003690</t>
+  </si>
+  <si>
+    <t>260907-F00001599</t>
+  </si>
+  <si>
+    <t>260907-F00004549</t>
+  </si>
+  <si>
+    <t>260907-F00014866</t>
+  </si>
+  <si>
+    <t>260907-F00015373</t>
+  </si>
+  <si>
+    <t>260907-F00018388</t>
+  </si>
+  <si>
+    <t>260907-W00000701</t>
+  </si>
+  <si>
+    <t>260907-W00001289</t>
+  </si>
+  <si>
+    <t>260907-W00002178</t>
+  </si>
+  <si>
+    <t>260907-W00004127</t>
+  </si>
+  <si>
+    <t>260907-W00010091</t>
+  </si>
+  <si>
+    <t>260907-W00010375</t>
+  </si>
+  <si>
+    <t>260907-W00010507</t>
+  </si>
+  <si>
+    <t>260908-F00001684</t>
+  </si>
+  <si>
+    <t>260908-F00003287</t>
+  </si>
+  <si>
+    <t>260908-F00004022</t>
+  </si>
+  <si>
+    <t>260908-F00009503-1</t>
+  </si>
+  <si>
+    <t>260908-F00009697</t>
+  </si>
+  <si>
+    <t>260908-F00012733</t>
+  </si>
+  <si>
+    <t>260908-F00013623</t>
+  </si>
+  <si>
+    <t>260908-F00014088</t>
+  </si>
+  <si>
+    <t>260908-F00014956</t>
+  </si>
+  <si>
+    <t>260908-F00014960</t>
+  </si>
+  <si>
+    <t>260908-F00015080</t>
+  </si>
+  <si>
+    <t>260908-F00015673</t>
+  </si>
+  <si>
+    <t>260908-W00002216</t>
+  </si>
+  <si>
+    <t>260908-W00002687</t>
+  </si>
+  <si>
+    <t>260908-W00003051</t>
+  </si>
+  <si>
+    <t>260908-W00003244</t>
+  </si>
+  <si>
+    <t>260908-W00004511</t>
+  </si>
+  <si>
+    <t>260908-W00006512</t>
+  </si>
+  <si>
+    <t>260908-W00006530</t>
+  </si>
+  <si>
+    <t>260908-W00007162</t>
+  </si>
+  <si>
+    <t>260908-W00007366</t>
+  </si>
+  <si>
+    <t>260908-W00007529</t>
+  </si>
+  <si>
+    <t>260908-W00007909</t>
+  </si>
+  <si>
+    <t>260908-W00008163</t>
+  </si>
+  <si>
+    <t>260908-W00008678</t>
+  </si>
+  <si>
+    <t>260908-W00009122</t>
+  </si>
+  <si>
+    <t>260908-W00009597</t>
+  </si>
+  <si>
+    <t>260908-W00009652</t>
+  </si>
+  <si>
+    <t>260908-W00009854</t>
+  </si>
+  <si>
+    <t>260908-W00010806</t>
+  </si>
+  <si>
+    <t>260908-W00011635</t>
+  </si>
+  <si>
+    <t>260908-W00013008</t>
+  </si>
+  <si>
+    <t>260909-F00000505</t>
+  </si>
+  <si>
+    <t>260909-F00001799</t>
+  </si>
+  <si>
+    <t>260909-F00002451</t>
+  </si>
+  <si>
+    <t>260909-F00004022</t>
+  </si>
+  <si>
+    <t>260909-F00004783</t>
+  </si>
+  <si>
+    <t>260909-F00006195</t>
+  </si>
+  <si>
+    <t>260909-F00011645</t>
+  </si>
+  <si>
+    <t>260909-F00012205</t>
+  </si>
+  <si>
+    <t>260909-F00012275-3</t>
+  </si>
+  <si>
+    <t>260909-F00013186</t>
+  </si>
+  <si>
+    <t>260909-F00015339</t>
+  </si>
+  <si>
+    <t>260909-W00001636</t>
+  </si>
+  <si>
+    <t>260909-W00003543</t>
+  </si>
+  <si>
+    <t>260909-W00003595</t>
+  </si>
+  <si>
+    <t>260909-W00006219</t>
+  </si>
+  <si>
+    <t>260909-W00006614</t>
+  </si>
+  <si>
+    <t>260909-W00007245</t>
+  </si>
+  <si>
+    <t>260909-W00007426</t>
+  </si>
+  <si>
+    <t>260909-W00008388</t>
+  </si>
+  <si>
+    <t>260909-W00008553</t>
+  </si>
+  <si>
+    <t>260909-W00008916</t>
+  </si>
+  <si>
+    <t>260909-W00010169</t>
+  </si>
+  <si>
+    <t>260909-W00012058</t>
+  </si>
+  <si>
+    <t>260910-F00000702</t>
+  </si>
+  <si>
+    <t>260910-F00000941</t>
+  </si>
+  <si>
+    <t>260910-F00001684</t>
+  </si>
+  <si>
+    <t>260910-F00003292</t>
+  </si>
+  <si>
+    <t>260910-W00001221</t>
+  </si>
+  <si>
+    <t>260910-W00002518</t>
+  </si>
+  <si>
+    <t>260910-W00003131</t>
+  </si>
+  <si>
+    <t>260910-W00004398</t>
+  </si>
+  <si>
+    <t>260910-W00005225</t>
+  </si>
+  <si>
+    <t>260910-W00005903</t>
+  </si>
+  <si>
+    <t>260910-W00006461</t>
+  </si>
+  <si>
+    <t>267012881</t>
+  </si>
+  <si>
+    <t>267012896</t>
+  </si>
+  <si>
+    <t>326397736</t>
+  </si>
+  <si>
+    <t>326622653</t>
+  </si>
+  <si>
+    <t>326860313</t>
+  </si>
+  <si>
+    <t>326968117</t>
+  </si>
+  <si>
+    <t>327026309</t>
+  </si>
+  <si>
+    <t>327110318</t>
+  </si>
+  <si>
+    <t>327199404</t>
+  </si>
+  <si>
+    <t>327253145</t>
+  </si>
+  <si>
+    <t>327253713</t>
+  </si>
+  <si>
+    <t>327254105</t>
+  </si>
+  <si>
+    <t>327354463</t>
+  </si>
+  <si>
+    <t>327355346</t>
+  </si>
+  <si>
+    <t>327402600</t>
+  </si>
+  <si>
+    <t>327402719</t>
+  </si>
+  <si>
+    <t>327532288</t>
+  </si>
+  <si>
+    <t>327532620</t>
+  </si>
+  <si>
+    <t>327532645</t>
+  </si>
+  <si>
+    <t>327532646</t>
+  </si>
+  <si>
+    <t>327662021</t>
+  </si>
+  <si>
+    <t>327763229</t>
+  </si>
+  <si>
+    <t>327763401</t>
+  </si>
+  <si>
+    <t>327763451</t>
+  </si>
+  <si>
+    <t>51340047568KR</t>
+  </si>
+  <si>
+    <t>51340047673KR</t>
+  </si>
+  <si>
+    <t>51340047726KR</t>
+  </si>
+  <si>
+    <t>741307823KR</t>
+  </si>
+  <si>
+    <t>941155212KR</t>
+  </si>
+  <si>
+    <t>941155224KR</t>
+  </si>
+  <si>
+    <t>941155239KR</t>
+  </si>
+  <si>
+    <t>941155243KR</t>
+  </si>
+  <si>
+    <t>99003165</t>
+  </si>
+  <si>
+    <t>99003232</t>
+  </si>
+  <si>
+    <t>NFD6-09-01-JNG3</t>
+  </si>
+  <si>
+    <t>NFD6-09-03-BDGL</t>
+  </si>
+  <si>
+    <t>NFD6-09-09-BUZC</t>
+  </si>
+  <si>
+    <t>NFD6-09-09-WTGD</t>
+  </si>
+  <si>
+    <t>NFE6-09-09-9KJR</t>
+  </si>
+  <si>
+    <t>NFE6-09-09-C9SE</t>
+  </si>
+  <si>
+    <t>NFE6-09-09-HMPJ</t>
+  </si>
+  <si>
+    <t>P-NSH26-11186</t>
+  </si>
+  <si>
+    <t>R435029</t>
+  </si>
+  <si>
+    <t>R435038</t>
+  </si>
+  <si>
+    <t>R435638</t>
   </si>
 </sst>
 </file>
@@ -1525,7 +2716,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC11F24F-E222-443E-8401-2ECBA69A40D4}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:C207"/>
+  <dimension ref="A1:C417"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
@@ -1546,472 +2737,472 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B2" t="s">
         <v>134</v>
       </c>
       <c r="C2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B3" t="s">
         <v>135</v>
       </c>
       <c r="C3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B4" t="s">
         <v>136</v>
       </c>
       <c r="C4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B5" t="s">
         <v>137</v>
       </c>
       <c r="C5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>619</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>378</v>
       </c>
       <c r="C6" t="s">
-        <v>341</v>
+        <v>589</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>619</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>379</v>
       </c>
       <c r="C7" t="s">
-        <v>341</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>620</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>380</v>
       </c>
       <c r="C8" t="s">
-        <v>342</v>
+        <v>590</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>620</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>381</v>
       </c>
       <c r="C9" t="s">
-        <v>342</v>
+        <v>590</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C11" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C12" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C13" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>621</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>382</v>
       </c>
       <c r="C14" t="s">
-        <v>346</v>
+        <v>591</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>622</v>
       </c>
       <c r="B16" t="s">
-        <v>148</v>
+        <v>383</v>
       </c>
       <c r="C16" t="s">
-        <v>347</v>
+        <v>592</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>623</v>
       </c>
       <c r="B17" t="s">
-        <v>149</v>
+        <v>384</v>
       </c>
       <c r="C17" t="s">
-        <v>348</v>
+        <v>593</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>623</v>
       </c>
       <c r="B18" t="s">
-        <v>150</v>
+        <v>385</v>
       </c>
       <c r="C18" t="s">
-        <v>339</v>
+        <v>593</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>624</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>386</v>
       </c>
       <c r="C19" t="s">
-        <v>342</v>
+        <v>594</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C20" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>625</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>387</v>
       </c>
       <c r="C21" t="s">
-        <v>349</v>
+        <v>595</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>626</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>388</v>
       </c>
       <c r="C22" t="s">
-        <v>350</v>
+        <v>590</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>627</v>
       </c>
       <c r="B23" t="s">
-        <v>155</v>
+        <v>389</v>
       </c>
       <c r="C23" t="s">
-        <v>350</v>
+        <v>596</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>628</v>
       </c>
       <c r="B24" t="s">
-        <v>156</v>
+        <v>390</v>
       </c>
       <c r="C24" t="s">
-        <v>342</v>
+        <v>597</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>629</v>
       </c>
       <c r="B25" t="s">
-        <v>157</v>
+        <v>391</v>
       </c>
       <c r="C25" t="s">
-        <v>347</v>
+        <v>591</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>630</v>
       </c>
       <c r="B26" t="s">
-        <v>158</v>
+        <v>392</v>
       </c>
       <c r="C26" t="s">
-        <v>344</v>
+        <v>591</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C27" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>631</v>
       </c>
       <c r="B28" t="s">
-        <v>160</v>
+        <v>393</v>
       </c>
       <c r="C28" t="s">
-        <v>351</v>
+        <v>598</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>632</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>394</v>
       </c>
       <c r="C29" t="s">
-        <v>342</v>
+        <v>599</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>633</v>
       </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>395</v>
       </c>
       <c r="C30" t="s">
-        <v>343</v>
+        <v>598</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="C31" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C32" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>634</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>396</v>
       </c>
       <c r="C33" t="s">
-        <v>352</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>635</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>397</v>
       </c>
       <c r="C34" t="s">
-        <v>348</v>
+        <v>601</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>636</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>398</v>
       </c>
       <c r="C35" t="s">
-        <v>344</v>
+        <v>602</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>637</v>
       </c>
       <c r="B36" t="s">
-        <v>168</v>
+        <v>399</v>
       </c>
       <c r="C36" t="s">
-        <v>343</v>
+        <v>603</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>638</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>400</v>
       </c>
       <c r="C37" t="s">
-        <v>343</v>
+        <v>604</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>639</v>
       </c>
       <c r="B38" t="s">
-        <v>170</v>
+        <v>401</v>
       </c>
       <c r="C38" t="s">
-        <v>343</v>
+        <v>591</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="C39" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="C40" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>640</v>
       </c>
       <c r="B41" t="s">
-        <v>173</v>
+        <v>402</v>
       </c>
       <c r="C41" t="s">
-        <v>353</v>
+        <v>601</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>641</v>
       </c>
       <c r="B42" t="s">
-        <v>174</v>
+        <v>403</v>
       </c>
       <c r="C42" t="s">
-        <v>354</v>
+        <v>593</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>642</v>
       </c>
       <c r="B43" t="s">
-        <v>175</v>
+        <v>404</v>
       </c>
       <c r="C43" t="s">
-        <v>354</v>
+        <v>605</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="C44" t="s">
         <v>347</v>
@@ -2019,1099 +3210,1099 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>643</v>
       </c>
       <c r="B45" t="s">
-        <v>177</v>
+        <v>405</v>
       </c>
       <c r="C45" t="s">
-        <v>347</v>
+        <v>590</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>644</v>
       </c>
       <c r="B46" t="s">
-        <v>178</v>
+        <v>406</v>
       </c>
       <c r="C46" t="s">
-        <v>339</v>
+        <v>606</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>645</v>
       </c>
       <c r="B47" t="s">
-        <v>179</v>
+        <v>407</v>
       </c>
       <c r="C47" t="s">
-        <v>340</v>
+        <v>606</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>645</v>
       </c>
       <c r="B48" t="s">
-        <v>180</v>
+        <v>408</v>
       </c>
       <c r="C48" t="s">
-        <v>340</v>
+        <v>606</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="C49" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>40</v>
+        <v>646</v>
       </c>
       <c r="B50" t="s">
-        <v>182</v>
+        <v>409</v>
       </c>
       <c r="C50" t="s">
-        <v>345</v>
+        <v>607</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>647</v>
       </c>
       <c r="B51" t="s">
-        <v>183</v>
+        <v>410</v>
       </c>
       <c r="C51" t="s">
-        <v>342</v>
+        <v>605</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>42</v>
+        <v>647</v>
       </c>
       <c r="B52" t="s">
-        <v>184</v>
+        <v>411</v>
       </c>
       <c r="C52" t="s">
-        <v>342</v>
+        <v>605</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>43</v>
+        <v>648</v>
       </c>
       <c r="B53" t="s">
-        <v>185</v>
+        <v>412</v>
       </c>
       <c r="C53" t="s">
-        <v>343</v>
+        <v>604</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>44</v>
+        <v>649</v>
       </c>
       <c r="B54" t="s">
-        <v>186</v>
+        <v>413</v>
       </c>
       <c r="C54" t="s">
-        <v>345</v>
+        <v>599</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>650</v>
       </c>
       <c r="B56" t="s">
-        <v>188</v>
+        <v>414</v>
       </c>
       <c r="C56" t="s">
-        <v>352</v>
+        <v>589</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>651</v>
       </c>
       <c r="B57" t="s">
-        <v>189</v>
+        <v>415</v>
       </c>
       <c r="C57" t="s">
-        <v>355</v>
+        <v>595</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>47</v>
+        <v>652</v>
       </c>
       <c r="B58" t="s">
-        <v>190</v>
+        <v>416</v>
       </c>
       <c r="C58" t="s">
-        <v>340</v>
+        <v>591</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="B60" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>49</v>
+        <v>653</v>
       </c>
       <c r="B61" t="s">
-        <v>193</v>
+        <v>417</v>
       </c>
       <c r="C61" t="s">
-        <v>353</v>
+        <v>597</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>49</v>
+        <v>654</v>
       </c>
       <c r="B62" t="s">
-        <v>194</v>
+        <v>418</v>
       </c>
       <c r="C62" t="s">
-        <v>353</v>
+        <v>608</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>655</v>
       </c>
       <c r="B63" t="s">
-        <v>195</v>
+        <v>419</v>
       </c>
       <c r="C63" t="s">
-        <v>344</v>
+        <v>603</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>50</v>
+        <v>656</v>
       </c>
       <c r="B64" t="s">
-        <v>196</v>
+        <v>420</v>
       </c>
       <c r="C64" t="s">
-        <v>344</v>
+        <v>599</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>51</v>
+        <v>657</v>
       </c>
       <c r="B65" t="s">
-        <v>197</v>
+        <v>421</v>
       </c>
       <c r="C65" t="s">
-        <v>351</v>
+        <v>590</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>51</v>
+        <v>658</v>
       </c>
       <c r="B66" t="s">
-        <v>198</v>
+        <v>422</v>
       </c>
       <c r="C66" t="s">
-        <v>351</v>
+        <v>609</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>51</v>
+        <v>659</v>
       </c>
       <c r="B67" t="s">
-        <v>199</v>
+        <v>423</v>
       </c>
       <c r="C67" t="s">
-        <v>351</v>
+        <v>606</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>52</v>
+        <v>659</v>
       </c>
       <c r="B68" t="s">
-        <v>200</v>
+        <v>424</v>
       </c>
       <c r="C68" t="s">
-        <v>342</v>
+        <v>606</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>52</v>
+        <v>659</v>
       </c>
       <c r="B69" t="s">
-        <v>201</v>
+        <v>425</v>
       </c>
       <c r="C69" t="s">
-        <v>342</v>
+        <v>606</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>53</v>
+        <v>660</v>
       </c>
       <c r="B70" t="s">
-        <v>202</v>
+        <v>426</v>
       </c>
       <c r="C70" t="s">
-        <v>356</v>
+        <v>610</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="C71" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="C72" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>55</v>
+        <v>661</v>
       </c>
       <c r="B73" t="s">
-        <v>205</v>
+        <v>427</v>
       </c>
       <c r="C73" t="s">
-        <v>340</v>
+        <v>608</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>55</v>
+        <v>662</v>
       </c>
       <c r="B74" t="s">
-        <v>206</v>
+        <v>428</v>
       </c>
       <c r="C74" t="s">
-        <v>340</v>
+        <v>611</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>56</v>
+        <v>663</v>
       </c>
       <c r="B75" t="s">
-        <v>207</v>
+        <v>429</v>
       </c>
       <c r="C75" t="s">
-        <v>339</v>
+        <v>601</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>56</v>
+        <v>664</v>
       </c>
       <c r="B76" t="s">
-        <v>208</v>
+        <v>430</v>
       </c>
       <c r="C76" t="s">
-        <v>339</v>
+        <v>601</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>56</v>
+        <v>665</v>
       </c>
       <c r="B77" t="s">
-        <v>209</v>
+        <v>431</v>
       </c>
       <c r="C77" t="s">
-        <v>339</v>
+        <v>602</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>57</v>
+        <v>666</v>
       </c>
       <c r="B78" t="s">
-        <v>210</v>
+        <v>432</v>
       </c>
       <c r="C78" t="s">
-        <v>349</v>
+        <v>606</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>57</v>
+        <v>667</v>
       </c>
       <c r="B79" t="s">
-        <v>211</v>
+        <v>433</v>
       </c>
       <c r="C79" t="s">
-        <v>349</v>
+        <v>607</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="B80" t="s">
-        <v>212</v>
+        <v>156</v>
       </c>
       <c r="C80" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>58</v>
+        <v>668</v>
       </c>
       <c r="B81" t="s">
-        <v>213</v>
+        <v>434</v>
       </c>
       <c r="C81" t="s">
-        <v>343</v>
+        <v>608</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>58</v>
+        <v>669</v>
       </c>
       <c r="B82" t="s">
-        <v>214</v>
+        <v>435</v>
       </c>
       <c r="C82" t="s">
-        <v>343</v>
+        <v>600</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="B83" t="s">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="C83" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>670</v>
       </c>
       <c r="B84" t="s">
-        <v>216</v>
+        <v>436</v>
       </c>
       <c r="C84" t="s">
-        <v>348</v>
+        <v>599</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>60</v>
+        <v>671</v>
       </c>
       <c r="B85" t="s">
-        <v>217</v>
+        <v>437</v>
       </c>
       <c r="C85" t="s">
-        <v>355</v>
+        <v>603</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>60</v>
+        <v>671</v>
       </c>
       <c r="B86" t="s">
-        <v>218</v>
+        <v>438</v>
       </c>
       <c r="C86" t="s">
-        <v>355</v>
+        <v>603</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>61</v>
+        <v>672</v>
       </c>
       <c r="B87" t="s">
-        <v>219</v>
+        <v>439</v>
       </c>
       <c r="C87" t="s">
-        <v>358</v>
+        <v>609</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="B88" t="s">
-        <v>220</v>
+        <v>158</v>
       </c>
       <c r="C88" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>61</v>
+        <v>673</v>
       </c>
       <c r="B89" t="s">
-        <v>221</v>
+        <v>440</v>
       </c>
       <c r="C89" t="s">
-        <v>358</v>
+        <v>612</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>62</v>
+        <v>674</v>
       </c>
       <c r="B90" t="s">
-        <v>222</v>
+        <v>441</v>
       </c>
       <c r="C90" t="s">
-        <v>340</v>
+        <v>605</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>62</v>
+        <v>674</v>
       </c>
       <c r="B91" t="s">
-        <v>223</v>
+        <v>442</v>
       </c>
       <c r="C91" t="s">
-        <v>340</v>
+        <v>605</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="B92" t="s">
-        <v>224</v>
+        <v>159</v>
       </c>
       <c r="C92" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>63</v>
+        <v>675</v>
       </c>
       <c r="B93" t="s">
-        <v>225</v>
+        <v>443</v>
       </c>
       <c r="C93" t="s">
-        <v>346</v>
+        <v>595</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>63</v>
+        <v>675</v>
       </c>
       <c r="B94" t="s">
-        <v>226</v>
+        <v>444</v>
       </c>
       <c r="C94" t="s">
-        <v>346</v>
+        <v>595</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>64</v>
+        <v>676</v>
       </c>
       <c r="B95" t="s">
-        <v>227</v>
+        <v>445</v>
       </c>
       <c r="C95" t="s">
-        <v>353</v>
+        <v>592</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="B96" t="s">
-        <v>228</v>
+        <v>160</v>
       </c>
       <c r="C96" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>64</v>
+        <v>677</v>
       </c>
       <c r="B97" t="s">
-        <v>229</v>
+        <v>446</v>
       </c>
       <c r="C97" t="s">
-        <v>353</v>
+        <v>606</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>65</v>
+        <v>677</v>
       </c>
       <c r="B98" t="s">
-        <v>230</v>
+        <v>447</v>
       </c>
       <c r="C98" t="s">
-        <v>348</v>
+        <v>606</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>66</v>
+        <v>678</v>
       </c>
       <c r="B99" t="s">
-        <v>231</v>
+        <v>448</v>
       </c>
       <c r="C99" t="s">
-        <v>356</v>
+        <v>595</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="B100" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
       <c r="C100" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>68</v>
+        <v>679</v>
       </c>
       <c r="B101" t="s">
-        <v>233</v>
+        <v>449</v>
       </c>
       <c r="C101" t="s">
-        <v>344</v>
+        <v>613</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>68</v>
+        <v>680</v>
       </c>
       <c r="B102" t="s">
-        <v>234</v>
+        <v>450</v>
       </c>
       <c r="C102" t="s">
-        <v>344</v>
+        <v>613</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>69</v>
+        <v>681</v>
       </c>
       <c r="B103" t="s">
-        <v>235</v>
+        <v>451</v>
       </c>
       <c r="C103" t="s">
-        <v>342</v>
+        <v>590</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>69</v>
+        <v>681</v>
       </c>
       <c r="B104" t="s">
-        <v>236</v>
+        <v>452</v>
       </c>
       <c r="C104" t="s">
-        <v>342</v>
+        <v>590</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>70</v>
+        <v>681</v>
       </c>
       <c r="B105" t="s">
-        <v>237</v>
+        <v>453</v>
       </c>
       <c r="C105" t="s">
-        <v>359</v>
+        <v>590</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>70</v>
+        <v>681</v>
       </c>
       <c r="B106" t="s">
-        <v>238</v>
+        <v>454</v>
       </c>
       <c r="C106" t="s">
-        <v>359</v>
+        <v>590</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>71</v>
+        <v>681</v>
       </c>
       <c r="B107" t="s">
-        <v>239</v>
+        <v>455</v>
       </c>
       <c r="C107" t="s">
-        <v>355</v>
+        <v>590</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>72</v>
+        <v>681</v>
       </c>
       <c r="B108" t="s">
-        <v>240</v>
+        <v>456</v>
       </c>
       <c r="C108" t="s">
-        <v>348</v>
+        <v>590</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="B109" t="s">
-        <v>241</v>
+        <v>162</v>
       </c>
       <c r="C109" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>242</v>
+        <v>163</v>
       </c>
       <c r="C110" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>164</v>
       </c>
       <c r="C111" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>75</v>
+        <v>682</v>
       </c>
       <c r="B112" t="s">
-        <v>244</v>
+        <v>457</v>
       </c>
       <c r="C112" t="s">
-        <v>357</v>
+        <v>607</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>75</v>
+        <v>683</v>
       </c>
       <c r="B113" t="s">
-        <v>245</v>
+        <v>458</v>
       </c>
       <c r="C113" t="s">
-        <v>357</v>
+        <v>589</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>75</v>
+        <v>683</v>
       </c>
       <c r="B114" t="s">
-        <v>246</v>
+        <v>459</v>
       </c>
       <c r="C114" t="s">
-        <v>357</v>
+        <v>589</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>76</v>
+        <v>684</v>
       </c>
       <c r="B115" t="s">
-        <v>247</v>
+        <v>460</v>
       </c>
       <c r="C115" t="s">
-        <v>350</v>
+        <v>591</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="B116" t="s">
-        <v>248</v>
+        <v>165</v>
       </c>
       <c r="C116" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>77</v>
+        <v>685</v>
       </c>
       <c r="B117" t="s">
-        <v>249</v>
+        <v>461</v>
       </c>
       <c r="C117" t="s">
-        <v>345</v>
+        <v>612</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>77</v>
+        <v>685</v>
       </c>
       <c r="B118" t="s">
-        <v>250</v>
+        <v>462</v>
       </c>
       <c r="C118" t="s">
-        <v>345</v>
+        <v>612</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>78</v>
+        <v>686</v>
       </c>
       <c r="B119" t="s">
-        <v>251</v>
+        <v>463</v>
       </c>
       <c r="C119" t="s">
-        <v>339</v>
+        <v>592</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>79</v>
+        <v>687</v>
       </c>
       <c r="B120" t="s">
-        <v>252</v>
+        <v>464</v>
       </c>
       <c r="C120" t="s">
-        <v>354</v>
+        <v>603</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>79</v>
+        <v>688</v>
       </c>
       <c r="B121" t="s">
-        <v>253</v>
+        <v>465</v>
       </c>
       <c r="C121" t="s">
-        <v>354</v>
+        <v>612</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="B122" t="s">
-        <v>254</v>
+        <v>166</v>
       </c>
       <c r="C122" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>80</v>
+        <v>689</v>
       </c>
       <c r="B123" t="s">
-        <v>255</v>
+        <v>466</v>
       </c>
       <c r="C123" t="s">
-        <v>356</v>
+        <v>595</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>81</v>
+        <v>690</v>
       </c>
       <c r="B124" t="s">
-        <v>256</v>
+        <v>467</v>
       </c>
       <c r="C124" t="s">
-        <v>345</v>
+        <v>595</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>82</v>
+        <v>691</v>
       </c>
       <c r="B125" t="s">
-        <v>257</v>
+        <v>468</v>
       </c>
       <c r="C125" t="s">
-        <v>349</v>
+        <v>607</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>83</v>
+        <v>692</v>
       </c>
       <c r="B126" t="s">
-        <v>258</v>
+        <v>469</v>
       </c>
       <c r="C126" t="s">
-        <v>360</v>
+        <v>614</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>83</v>
+        <v>693</v>
       </c>
       <c r="B127" t="s">
-        <v>259</v>
+        <v>470</v>
       </c>
       <c r="C127" t="s">
-        <v>360</v>
+        <v>605</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>83</v>
+        <v>693</v>
       </c>
       <c r="B128" t="s">
-        <v>260</v>
+        <v>471</v>
       </c>
       <c r="C128" t="s">
-        <v>360</v>
+        <v>605</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>84</v>
+        <v>694</v>
       </c>
       <c r="B129" t="s">
-        <v>261</v>
+        <v>472</v>
       </c>
       <c r="C129" t="s">
-        <v>342</v>
+        <v>593</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>84</v>
+        <v>694</v>
       </c>
       <c r="B130" t="s">
-        <v>262</v>
+        <v>473</v>
       </c>
       <c r="C130" t="s">
-        <v>342</v>
+        <v>593</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>85</v>
+        <v>695</v>
       </c>
       <c r="B131" t="s">
-        <v>263</v>
+        <v>474</v>
       </c>
       <c r="C131" t="s">
-        <v>339</v>
+        <v>595</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>86</v>
+        <v>696</v>
       </c>
       <c r="B132" t="s">
-        <v>264</v>
+        <v>475</v>
       </c>
       <c r="C132" t="s">
-        <v>355</v>
+        <v>609</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>87</v>
+        <v>696</v>
       </c>
       <c r="B133" t="s">
-        <v>265</v>
+        <v>476</v>
       </c>
       <c r="C133" t="s">
-        <v>355</v>
+        <v>609</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>88</v>
+        <v>697</v>
       </c>
       <c r="B134" t="s">
-        <v>266</v>
+        <v>477</v>
       </c>
       <c r="C134" t="s">
-        <v>356</v>
+        <v>612</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>89</v>
+        <v>698</v>
       </c>
       <c r="B135" t="s">
-        <v>267</v>
+        <v>478</v>
       </c>
       <c r="C135" t="s">
-        <v>357</v>
+        <v>602</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>90</v>
+        <v>699</v>
       </c>
       <c r="B136" t="s">
-        <v>268</v>
+        <v>479</v>
       </c>
       <c r="C136" t="s">
-        <v>341</v>
+        <v>602</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>91</v>
+        <v>700</v>
       </c>
       <c r="B137" t="s">
-        <v>269</v>
+        <v>480</v>
       </c>
       <c r="C137" t="s">
-        <v>348</v>
+        <v>592</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>92</v>
+        <v>700</v>
       </c>
       <c r="B138" t="s">
-        <v>270</v>
+        <v>481</v>
       </c>
       <c r="C138" t="s">
-        <v>346</v>
+        <v>592</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>93</v>
+        <v>701</v>
       </c>
       <c r="B139" t="s">
-        <v>271</v>
+        <v>482</v>
       </c>
       <c r="C139" t="s">
-        <v>355</v>
+        <v>608</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="B140" t="s">
-        <v>272</v>
+        <v>167</v>
       </c>
       <c r="C140" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="B141" t="s">
-        <v>273</v>
+        <v>168</v>
       </c>
       <c r="C141" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="B142" t="s">
-        <v>274</v>
+        <v>169</v>
       </c>
       <c r="C142" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>96</v>
+        <v>702</v>
       </c>
       <c r="B143" t="s">
-        <v>275</v>
+        <v>483</v>
       </c>
       <c r="C143" t="s">
-        <v>350</v>
+        <v>615</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="B144" t="s">
-        <v>276</v>
+        <v>170</v>
       </c>
       <c r="C144" t="s">
         <v>342</v>
@@ -3119,695 +4310,3005 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="B145" t="s">
-        <v>277</v>
+        <v>171</v>
       </c>
       <c r="C145" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="B146" t="s">
-        <v>278</v>
+        <v>172</v>
       </c>
       <c r="C146" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="B147" t="s">
-        <v>279</v>
+        <v>173</v>
       </c>
       <c r="C147" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="B148" t="s">
-        <v>280</v>
+        <v>174</v>
       </c>
       <c r="C148" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="B149" t="s">
-        <v>281</v>
+        <v>175</v>
       </c>
       <c r="C149" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="B150" t="s">
-        <v>282</v>
+        <v>176</v>
       </c>
       <c r="C150" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="B151" t="s">
-        <v>283</v>
+        <v>177</v>
       </c>
       <c r="C151" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>104</v>
+        <v>703</v>
       </c>
       <c r="B152" t="s">
-        <v>284</v>
+        <v>484</v>
       </c>
       <c r="C152" t="s">
-        <v>354</v>
+        <v>591</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>105</v>
+        <v>703</v>
       </c>
       <c r="B153" t="s">
-        <v>285</v>
+        <v>485</v>
       </c>
       <c r="C153" t="s">
-        <v>356</v>
+        <v>591</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>106</v>
+        <v>704</v>
       </c>
       <c r="B154" t="s">
-        <v>286</v>
+        <v>486</v>
       </c>
       <c r="C154" t="s">
-        <v>339</v>
+        <v>599</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>107</v>
+        <v>704</v>
       </c>
       <c r="B155" t="s">
-        <v>287</v>
+        <v>487</v>
       </c>
       <c r="C155" t="s">
-        <v>360</v>
+        <v>599</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>108</v>
+        <v>705</v>
       </c>
       <c r="B156" t="s">
-        <v>288</v>
+        <v>488</v>
       </c>
       <c r="C156" t="s">
-        <v>350</v>
+        <v>614</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>109</v>
+        <v>705</v>
       </c>
       <c r="B157" t="s">
-        <v>289</v>
+        <v>489</v>
       </c>
       <c r="C157" t="s">
-        <v>342</v>
+        <v>614</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>110</v>
+        <v>705</v>
       </c>
       <c r="B158" t="s">
-        <v>290</v>
+        <v>490</v>
       </c>
       <c r="C158" t="s">
-        <v>341</v>
+        <v>614</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>111</v>
+        <v>706</v>
       </c>
       <c r="B159" t="s">
-        <v>291</v>
+        <v>491</v>
       </c>
       <c r="C159" t="s">
-        <v>351</v>
+        <v>613</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="B160" t="s">
-        <v>292</v>
+        <v>178</v>
       </c>
       <c r="C160" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="B161" t="s">
-        <v>293</v>
+        <v>179</v>
       </c>
       <c r="C161" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="B162" t="s">
-        <v>294</v>
+        <v>180</v>
       </c>
       <c r="C162" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>115</v>
+        <v>707</v>
       </c>
       <c r="B163" t="s">
-        <v>295</v>
+        <v>492</v>
       </c>
       <c r="C163" t="s">
-        <v>360</v>
+        <v>613</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="B164" t="s">
-        <v>296</v>
+        <v>181</v>
       </c>
       <c r="C164" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>117</v>
+        <v>40</v>
       </c>
       <c r="B165" t="s">
-        <v>297</v>
+        <v>182</v>
       </c>
       <c r="C165" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>118</v>
+        <v>708</v>
       </c>
       <c r="B166" t="s">
-        <v>298</v>
+        <v>493</v>
       </c>
       <c r="C166" t="s">
-        <v>340</v>
+        <v>600</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="B167" t="s">
-        <v>299</v>
+        <v>183</v>
       </c>
       <c r="C167" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="B168" t="s">
-        <v>300</v>
+        <v>184</v>
       </c>
       <c r="C168" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>120</v>
+        <v>709</v>
       </c>
       <c r="B169" t="s">
-        <v>301</v>
+        <v>494</v>
       </c>
       <c r="C169" t="s">
-        <v>359</v>
+        <v>607</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>121</v>
+        <v>710</v>
       </c>
       <c r="B170" t="s">
-        <v>302</v>
+        <v>495</v>
       </c>
       <c r="C170" t="s">
-        <v>351</v>
+        <v>603</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>122</v>
+        <v>710</v>
       </c>
       <c r="B171" t="s">
-        <v>303</v>
+        <v>496</v>
       </c>
       <c r="C171" t="s">
-        <v>349</v>
+        <v>603</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="B172" t="s">
-        <v>304</v>
+        <v>185</v>
       </c>
       <c r="C172" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>124</v>
+        <v>711</v>
       </c>
       <c r="B173" t="s">
-        <v>305</v>
+        <v>497</v>
       </c>
       <c r="C173" t="s">
-        <v>350</v>
+        <v>613</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>125</v>
+        <v>712</v>
       </c>
       <c r="B174" t="s">
-        <v>306</v>
+        <v>498</v>
       </c>
       <c r="C174" t="s">
-        <v>356</v>
+        <v>614</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>126</v>
+        <v>713</v>
       </c>
       <c r="B175" t="s">
-        <v>307</v>
+        <v>499</v>
       </c>
       <c r="C175" t="s">
-        <v>345</v>
+        <v>598</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>127</v>
+        <v>714</v>
       </c>
       <c r="B176" t="s">
-        <v>308</v>
+        <v>500</v>
       </c>
       <c r="C176" t="s">
-        <v>344</v>
+        <v>590</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>128</v>
+        <v>714</v>
       </c>
       <c r="B177" t="s">
-        <v>309</v>
+        <v>501</v>
       </c>
       <c r="C177" t="s">
-        <v>343</v>
+        <v>590</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>129</v>
+        <v>715</v>
       </c>
       <c r="B178" t="s">
-        <v>310</v>
+        <v>502</v>
       </c>
       <c r="C178" t="s">
-        <v>355</v>
+        <v>591</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>130</v>
+        <v>716</v>
       </c>
       <c r="B179" t="s">
-        <v>311</v>
+        <v>503</v>
       </c>
       <c r="C179" t="s">
-        <v>344</v>
+        <v>598</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>131</v>
+        <v>717</v>
       </c>
       <c r="B180" t="s">
-        <v>312</v>
+        <v>504</v>
       </c>
       <c r="C180" t="s">
-        <v>356</v>
+        <v>597</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="B181" t="s">
-        <v>313</v>
+        <v>186</v>
       </c>
       <c r="C181" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="B182" t="s">
-        <v>314</v>
+        <v>187</v>
       </c>
       <c r="C182" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="B183" t="s">
-        <v>315</v>
+        <v>188</v>
       </c>
       <c r="C183" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>364</v>
+        <v>46</v>
       </c>
       <c r="B184" t="s">
-        <v>316</v>
+        <v>189</v>
       </c>
       <c r="C184" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>364</v>
+        <v>718</v>
       </c>
       <c r="B185" t="s">
-        <v>317</v>
+        <v>505</v>
       </c>
       <c r="C185" t="s">
-        <v>355</v>
+        <v>593</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>364</v>
+        <v>719</v>
       </c>
       <c r="B186" t="s">
-        <v>318</v>
+        <v>506</v>
       </c>
       <c r="C186" t="s">
-        <v>355</v>
+        <v>592</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>364</v>
+        <v>719</v>
       </c>
       <c r="B187" t="s">
-        <v>319</v>
+        <v>507</v>
       </c>
       <c r="C187" t="s">
-        <v>355</v>
+        <v>592</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>365</v>
+        <v>720</v>
       </c>
       <c r="B188" t="s">
-        <v>320</v>
+        <v>508</v>
       </c>
       <c r="C188" t="s">
-        <v>340</v>
+        <v>611</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>366</v>
+        <v>721</v>
       </c>
       <c r="B189" t="s">
-        <v>321</v>
+        <v>509</v>
       </c>
       <c r="C189" t="s">
-        <v>351</v>
+        <v>608</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>366</v>
+        <v>722</v>
       </c>
       <c r="B190" t="s">
-        <v>322</v>
+        <v>510</v>
       </c>
       <c r="C190" t="s">
-        <v>351</v>
+        <v>591</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>367</v>
+        <v>723</v>
       </c>
       <c r="B191" t="s">
-        <v>323</v>
+        <v>511</v>
       </c>
       <c r="C191" t="s">
-        <v>341</v>
+        <v>607</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>367</v>
+        <v>47</v>
       </c>
       <c r="B192" t="s">
-        <v>324</v>
+        <v>190</v>
       </c>
       <c r="C192" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>367</v>
+        <v>48</v>
       </c>
       <c r="B193" t="s">
-        <v>325</v>
+        <v>191</v>
       </c>
       <c r="C193" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>367</v>
+        <v>48</v>
       </c>
       <c r="B194" t="s">
-        <v>326</v>
+        <v>192</v>
       </c>
       <c r="C194" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>368</v>
+        <v>49</v>
       </c>
       <c r="B195" t="s">
-        <v>327</v>
+        <v>193</v>
       </c>
       <c r="C195" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>369</v>
+        <v>49</v>
       </c>
       <c r="B196" t="s">
-        <v>328</v>
+        <v>194</v>
       </c>
       <c r="C196" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>370</v>
+        <v>724</v>
       </c>
       <c r="B197" t="s">
-        <v>329</v>
+        <v>512</v>
       </c>
       <c r="C197" t="s">
-        <v>342</v>
+        <v>601</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>370</v>
+        <v>724</v>
       </c>
       <c r="B198" t="s">
-        <v>330</v>
+        <v>513</v>
       </c>
       <c r="C198" t="s">
-        <v>342</v>
+        <v>601</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>371</v>
+        <v>724</v>
       </c>
       <c r="B199" t="s">
-        <v>331</v>
+        <v>514</v>
       </c>
       <c r="C199" t="s">
-        <v>343</v>
+        <v>601</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>372</v>
+        <v>725</v>
       </c>
       <c r="B200" t="s">
-        <v>332</v>
+        <v>515</v>
       </c>
       <c r="C200" t="s">
-        <v>357</v>
+        <v>614</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>373</v>
+        <v>726</v>
       </c>
       <c r="B201" t="s">
-        <v>333</v>
+        <v>516</v>
       </c>
       <c r="C201" t="s">
-        <v>359</v>
+        <v>611</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>374</v>
+        <v>727</v>
       </c>
       <c r="B202" t="s">
-        <v>334</v>
+        <v>517</v>
       </c>
       <c r="C202" t="s">
-        <v>343</v>
+        <v>614</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>375</v>
+        <v>728</v>
       </c>
       <c r="B203" t="s">
-        <v>335</v>
+        <v>518</v>
       </c>
       <c r="C203" t="s">
-        <v>347</v>
+        <v>590</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>376</v>
+        <v>729</v>
       </c>
       <c r="B204" t="s">
-        <v>336</v>
+        <v>519</v>
       </c>
       <c r="C204" t="s">
-        <v>339</v>
+        <v>601</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>377</v>
+        <v>730</v>
       </c>
       <c r="B205" t="s">
-        <v>337</v>
+        <v>520</v>
       </c>
       <c r="C205" t="s">
-        <v>348</v>
+        <v>597</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206">
-        <v>1040959940</v>
+      <c r="A206" t="s">
+        <v>730</v>
       </c>
       <c r="B206" t="s">
-        <v>338</v>
+        <v>521</v>
       </c>
       <c r="C206" t="s">
-        <v>349</v>
+        <v>597</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>378</v>
+        <v>731</v>
       </c>
       <c r="B207" t="s">
-        <v>378</v>
+        <v>522</v>
       </c>
       <c r="C207" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>732</v>
+      </c>
+      <c r="B208" t="s">
+        <v>523</v>
+      </c>
+      <c r="C208" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>50</v>
+      </c>
+      <c r="B209" t="s">
+        <v>195</v>
+      </c>
+      <c r="C209" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>50</v>
+      </c>
+      <c r="B210" t="s">
+        <v>196</v>
+      </c>
+      <c r="C210" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>51</v>
+      </c>
+      <c r="B211" t="s">
+        <v>197</v>
+      </c>
+      <c r="C211" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>51</v>
+      </c>
+      <c r="B212" t="s">
+        <v>198</v>
+      </c>
+      <c r="C212" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>51</v>
+      </c>
+      <c r="B213" t="s">
+        <v>199</v>
+      </c>
+      <c r="C213" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>52</v>
+      </c>
+      <c r="B214" t="s">
+        <v>200</v>
+      </c>
+      <c r="C214" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>52</v>
+      </c>
+      <c r="B215" t="s">
+        <v>201</v>
+      </c>
+      <c r="C215" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>53</v>
+      </c>
+      <c r="B216" t="s">
+        <v>202</v>
+      </c>
+      <c r="C216" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>54</v>
+      </c>
+      <c r="B217" t="s">
+        <v>203</v>
+      </c>
+      <c r="C217" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>55</v>
+      </c>
+      <c r="B218" t="s">
+        <v>204</v>
+      </c>
+      <c r="C218" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>55</v>
+      </c>
+      <c r="B219" t="s">
+        <v>205</v>
+      </c>
+      <c r="C219" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>55</v>
+      </c>
+      <c r="B220" t="s">
+        <v>206</v>
+      </c>
+      <c r="C220" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>733</v>
+      </c>
+      <c r="B221" t="s">
+        <v>524</v>
+      </c>
+      <c r="C221" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>733</v>
+      </c>
+      <c r="B222" t="s">
+        <v>525</v>
+      </c>
+      <c r="C222" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>56</v>
+      </c>
+      <c r="B223" t="s">
+        <v>207</v>
+      </c>
+      <c r="C223" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>56</v>
+      </c>
+      <c r="B224" t="s">
+        <v>208</v>
+      </c>
+      <c r="C224" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>56</v>
+      </c>
+      <c r="B225" t="s">
+        <v>209</v>
+      </c>
+      <c r="C225" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>57</v>
+      </c>
+      <c r="B226" t="s">
+        <v>210</v>
+      </c>
+      <c r="C226" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>57</v>
+      </c>
+      <c r="B227" t="s">
+        <v>211</v>
+      </c>
+      <c r="C227" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>57</v>
+      </c>
+      <c r="B228" t="s">
+        <v>212</v>
+      </c>
+      <c r="C228" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>734</v>
+      </c>
+      <c r="B229" t="s">
+        <v>526</v>
+      </c>
+      <c r="C229" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>734</v>
+      </c>
+      <c r="B230" t="s">
+        <v>527</v>
+      </c>
+      <c r="C230" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>58</v>
+      </c>
+      <c r="B231" t="s">
+        <v>213</v>
+      </c>
+      <c r="C231" t="s">
         <v>342</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>58</v>
+      </c>
+      <c r="B232" t="s">
+        <v>214</v>
+      </c>
+      <c r="C232" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>58</v>
+      </c>
+      <c r="B233" t="s">
+        <v>215</v>
+      </c>
+      <c r="C233" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>59</v>
+      </c>
+      <c r="B234" t="s">
+        <v>216</v>
+      </c>
+      <c r="C234" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>60</v>
+      </c>
+      <c r="B235" t="s">
+        <v>217</v>
+      </c>
+      <c r="C235" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>60</v>
+      </c>
+      <c r="B236" t="s">
+        <v>218</v>
+      </c>
+      <c r="C236" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>61</v>
+      </c>
+      <c r="B237" t="s">
+        <v>219</v>
+      </c>
+      <c r="C237" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>61</v>
+      </c>
+      <c r="B238" t="s">
+        <v>220</v>
+      </c>
+      <c r="C238" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>61</v>
+      </c>
+      <c r="B239" t="s">
+        <v>221</v>
+      </c>
+      <c r="C239" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>735</v>
+      </c>
+      <c r="B240" t="s">
+        <v>528</v>
+      </c>
+      <c r="C240" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>735</v>
+      </c>
+      <c r="B241" t="s">
+        <v>529</v>
+      </c>
+      <c r="C241" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>62</v>
+      </c>
+      <c r="B242" t="s">
+        <v>222</v>
+      </c>
+      <c r="C242" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>62</v>
+      </c>
+      <c r="B243" t="s">
+        <v>223</v>
+      </c>
+      <c r="C243" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>62</v>
+      </c>
+      <c r="B244" t="s">
+        <v>224</v>
+      </c>
+      <c r="C244" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>63</v>
+      </c>
+      <c r="B245" t="s">
+        <v>225</v>
+      </c>
+      <c r="C245" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>63</v>
+      </c>
+      <c r="B246" t="s">
+        <v>226</v>
+      </c>
+      <c r="C246" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>64</v>
+      </c>
+      <c r="B247" t="s">
+        <v>227</v>
+      </c>
+      <c r="C247" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>64</v>
+      </c>
+      <c r="B248" t="s">
+        <v>228</v>
+      </c>
+      <c r="C248" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>64</v>
+      </c>
+      <c r="B249" t="s">
+        <v>229</v>
+      </c>
+      <c r="C249" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>65</v>
+      </c>
+      <c r="B250" t="s">
+        <v>230</v>
+      </c>
+      <c r="C250" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>66</v>
+      </c>
+      <c r="B251" t="s">
+        <v>231</v>
+      </c>
+      <c r="C251" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>67</v>
+      </c>
+      <c r="B252" t="s">
+        <v>232</v>
+      </c>
+      <c r="C252" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>736</v>
+      </c>
+      <c r="B253" t="s">
+        <v>530</v>
+      </c>
+      <c r="C253" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>736</v>
+      </c>
+      <c r="B254" t="s">
+        <v>531</v>
+      </c>
+      <c r="C254" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>68</v>
+      </c>
+      <c r="B255" t="s">
+        <v>233</v>
+      </c>
+      <c r="C255" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>68</v>
+      </c>
+      <c r="B256" t="s">
+        <v>234</v>
+      </c>
+      <c r="C256" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>69</v>
+      </c>
+      <c r="B257" t="s">
+        <v>235</v>
+      </c>
+      <c r="C257" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>69</v>
+      </c>
+      <c r="B258" t="s">
+        <v>236</v>
+      </c>
+      <c r="C258" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>70</v>
+      </c>
+      <c r="B259" t="s">
+        <v>237</v>
+      </c>
+      <c r="C259" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>70</v>
+      </c>
+      <c r="B260" t="s">
+        <v>238</v>
+      </c>
+      <c r="C260" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>737</v>
+      </c>
+      <c r="B261" t="s">
+        <v>532</v>
+      </c>
+      <c r="C261" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>737</v>
+      </c>
+      <c r="B262" t="s">
+        <v>533</v>
+      </c>
+      <c r="C262" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>71</v>
+      </c>
+      <c r="B263" t="s">
+        <v>239</v>
+      </c>
+      <c r="C263" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>72</v>
+      </c>
+      <c r="B264" t="s">
+        <v>240</v>
+      </c>
+      <c r="C264" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>72</v>
+      </c>
+      <c r="B265" t="s">
+        <v>241</v>
+      </c>
+      <c r="C265" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>73</v>
+      </c>
+      <c r="B266" t="s">
+        <v>242</v>
+      </c>
+      <c r="C266" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>74</v>
+      </c>
+      <c r="B267" t="s">
+        <v>243</v>
+      </c>
+      <c r="C267" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>75</v>
+      </c>
+      <c r="B268" t="s">
+        <v>244</v>
+      </c>
+      <c r="C268" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>75</v>
+      </c>
+      <c r="B269" t="s">
+        <v>245</v>
+      </c>
+      <c r="C269" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>75</v>
+      </c>
+      <c r="B270" t="s">
+        <v>246</v>
+      </c>
+      <c r="C270" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>738</v>
+      </c>
+      <c r="B271" t="s">
+        <v>534</v>
+      </c>
+      <c r="C271" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>76</v>
+      </c>
+      <c r="B272" t="s">
+        <v>247</v>
+      </c>
+      <c r="C272" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>76</v>
+      </c>
+      <c r="B273" t="s">
+        <v>248</v>
+      </c>
+      <c r="C273" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>77</v>
+      </c>
+      <c r="B274" t="s">
+        <v>249</v>
+      </c>
+      <c r="C274" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>77</v>
+      </c>
+      <c r="B275" t="s">
+        <v>250</v>
+      </c>
+      <c r="C275" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>78</v>
+      </c>
+      <c r="B276" t="s">
+        <v>251</v>
+      </c>
+      <c r="C276" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>79</v>
+      </c>
+      <c r="B277" t="s">
+        <v>252</v>
+      </c>
+      <c r="C277" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>79</v>
+      </c>
+      <c r="B278" t="s">
+        <v>253</v>
+      </c>
+      <c r="C278" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>80</v>
+      </c>
+      <c r="B279" t="s">
+        <v>254</v>
+      </c>
+      <c r="C279" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>80</v>
+      </c>
+      <c r="B280" t="s">
+        <v>255</v>
+      </c>
+      <c r="C280" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>81</v>
+      </c>
+      <c r="B281" t="s">
+        <v>256</v>
+      </c>
+      <c r="C281" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>82</v>
+      </c>
+      <c r="B282" t="s">
+        <v>257</v>
+      </c>
+      <c r="C282" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>83</v>
+      </c>
+      <c r="B283" t="s">
+        <v>258</v>
+      </c>
+      <c r="C283" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>83</v>
+      </c>
+      <c r="B284" t="s">
+        <v>259</v>
+      </c>
+      <c r="C284" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>83</v>
+      </c>
+      <c r="B285" t="s">
+        <v>260</v>
+      </c>
+      <c r="C285" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>84</v>
+      </c>
+      <c r="B286" t="s">
+        <v>261</v>
+      </c>
+      <c r="C286" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>84</v>
+      </c>
+      <c r="B287" t="s">
+        <v>262</v>
+      </c>
+      <c r="C287" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>85</v>
+      </c>
+      <c r="B288" t="s">
+        <v>263</v>
+      </c>
+      <c r="C288" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>86</v>
+      </c>
+      <c r="B289" t="s">
+        <v>264</v>
+      </c>
+      <c r="C289" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>87</v>
+      </c>
+      <c r="B290" t="s">
+        <v>265</v>
+      </c>
+      <c r="C290" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>88</v>
+      </c>
+      <c r="B291" t="s">
+        <v>266</v>
+      </c>
+      <c r="C291" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>89</v>
+      </c>
+      <c r="B292" t="s">
+        <v>267</v>
+      </c>
+      <c r="C292" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>90</v>
+      </c>
+      <c r="B293" t="s">
+        <v>268</v>
+      </c>
+      <c r="C293" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>91</v>
+      </c>
+      <c r="B294" t="s">
+        <v>269</v>
+      </c>
+      <c r="C294" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>92</v>
+      </c>
+      <c r="B295" t="s">
+        <v>270</v>
+      </c>
+      <c r="C295" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>93</v>
+      </c>
+      <c r="B296" t="s">
+        <v>271</v>
+      </c>
+      <c r="C296" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>739</v>
+      </c>
+      <c r="B297" t="s">
+        <v>535</v>
+      </c>
+      <c r="C297" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>739</v>
+      </c>
+      <c r="B298" t="s">
+        <v>536</v>
+      </c>
+      <c r="C298" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>740</v>
+      </c>
+      <c r="B299" t="s">
+        <v>537</v>
+      </c>
+      <c r="C299" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>740</v>
+      </c>
+      <c r="B300" t="s">
+        <v>538</v>
+      </c>
+      <c r="C300" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>740</v>
+      </c>
+      <c r="B301" t="s">
+        <v>539</v>
+      </c>
+      <c r="C301" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>94</v>
+      </c>
+      <c r="B302" t="s">
+        <v>272</v>
+      </c>
+      <c r="C302" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>94</v>
+      </c>
+      <c r="B303" t="s">
+        <v>273</v>
+      </c>
+      <c r="C303" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>95</v>
+      </c>
+      <c r="B304" t="s">
+        <v>274</v>
+      </c>
+      <c r="C304" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>96</v>
+      </c>
+      <c r="B305" t="s">
+        <v>275</v>
+      </c>
+      <c r="C305" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>97</v>
+      </c>
+      <c r="B306" t="s">
+        <v>276</v>
+      </c>
+      <c r="C306" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>741</v>
+      </c>
+      <c r="B307" t="s">
+        <v>540</v>
+      </c>
+      <c r="C307" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>98</v>
+      </c>
+      <c r="B308" t="s">
+        <v>277</v>
+      </c>
+      <c r="C308" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>98</v>
+      </c>
+      <c r="B309" t="s">
+        <v>278</v>
+      </c>
+      <c r="C309" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>742</v>
+      </c>
+      <c r="B310" t="s">
+        <v>541</v>
+      </c>
+      <c r="C310" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>99</v>
+      </c>
+      <c r="B311" t="s">
+        <v>279</v>
+      </c>
+      <c r="C311" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>100</v>
+      </c>
+      <c r="B312" t="s">
+        <v>280</v>
+      </c>
+      <c r="C312" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>101</v>
+      </c>
+      <c r="B313" t="s">
+        <v>281</v>
+      </c>
+      <c r="C313" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>102</v>
+      </c>
+      <c r="B314" t="s">
+        <v>282</v>
+      </c>
+      <c r="C314" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>743</v>
+      </c>
+      <c r="B315" t="s">
+        <v>542</v>
+      </c>
+      <c r="C315" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>103</v>
+      </c>
+      <c r="B316" t="s">
+        <v>283</v>
+      </c>
+      <c r="C316" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>104</v>
+      </c>
+      <c r="B317" t="s">
+        <v>284</v>
+      </c>
+      <c r="C317" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>105</v>
+      </c>
+      <c r="B318" t="s">
+        <v>285</v>
+      </c>
+      <c r="C318" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>106</v>
+      </c>
+      <c r="B319" t="s">
+        <v>286</v>
+      </c>
+      <c r="C319" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>107</v>
+      </c>
+      <c r="B320" t="s">
+        <v>287</v>
+      </c>
+      <c r="C320" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>108</v>
+      </c>
+      <c r="B321" t="s">
+        <v>288</v>
+      </c>
+      <c r="C321" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>109</v>
+      </c>
+      <c r="B322" t="s">
+        <v>289</v>
+      </c>
+      <c r="C322" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>110</v>
+      </c>
+      <c r="B323" t="s">
+        <v>290</v>
+      </c>
+      <c r="C323" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>111</v>
+      </c>
+      <c r="B324" t="s">
+        <v>291</v>
+      </c>
+      <c r="C324" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>112</v>
+      </c>
+      <c r="B325" t="s">
+        <v>292</v>
+      </c>
+      <c r="C325" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>744</v>
+      </c>
+      <c r="B326" t="s">
+        <v>543</v>
+      </c>
+      <c r="C326" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>113</v>
+      </c>
+      <c r="B327" t="s">
+        <v>293</v>
+      </c>
+      <c r="C327" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>745</v>
+      </c>
+      <c r="B328" t="s">
+        <v>544</v>
+      </c>
+      <c r="C328" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>114</v>
+      </c>
+      <c r="B329" t="s">
+        <v>294</v>
+      </c>
+      <c r="C329" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>746</v>
+      </c>
+      <c r="B330" t="s">
+        <v>545</v>
+      </c>
+      <c r="C330" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>115</v>
+      </c>
+      <c r="B331" t="s">
+        <v>295</v>
+      </c>
+      <c r="C331" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>116</v>
+      </c>
+      <c r="B332" t="s">
+        <v>296</v>
+      </c>
+      <c r="C332" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>117</v>
+      </c>
+      <c r="B333" t="s">
+        <v>297</v>
+      </c>
+      <c r="C333" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>118</v>
+      </c>
+      <c r="B334" t="s">
+        <v>298</v>
+      </c>
+      <c r="C334" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>119</v>
+      </c>
+      <c r="B335" t="s">
+        <v>299</v>
+      </c>
+      <c r="C335" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>119</v>
+      </c>
+      <c r="B336" t="s">
+        <v>300</v>
+      </c>
+      <c r="C336" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>120</v>
+      </c>
+      <c r="B337" t="s">
+        <v>301</v>
+      </c>
+      <c r="C337" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>121</v>
+      </c>
+      <c r="B338" t="s">
+        <v>302</v>
+      </c>
+      <c r="C338" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>122</v>
+      </c>
+      <c r="B339" t="s">
+        <v>303</v>
+      </c>
+      <c r="C339" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>123</v>
+      </c>
+      <c r="B340" t="s">
+        <v>304</v>
+      </c>
+      <c r="C340" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>124</v>
+      </c>
+      <c r="B341" t="s">
+        <v>305</v>
+      </c>
+      <c r="C341" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>125</v>
+      </c>
+      <c r="B342" t="s">
+        <v>306</v>
+      </c>
+      <c r="C342" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>126</v>
+      </c>
+      <c r="B343" t="s">
+        <v>307</v>
+      </c>
+      <c r="C343" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>127</v>
+      </c>
+      <c r="B344" t="s">
+        <v>308</v>
+      </c>
+      <c r="C344" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>747</v>
+      </c>
+      <c r="B345" t="s">
+        <v>546</v>
+      </c>
+      <c r="C345" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>747</v>
+      </c>
+      <c r="B346" t="s">
+        <v>547</v>
+      </c>
+      <c r="C346" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>747</v>
+      </c>
+      <c r="B347" t="s">
+        <v>548</v>
+      </c>
+      <c r="C347" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>128</v>
+      </c>
+      <c r="B348" t="s">
+        <v>309</v>
+      </c>
+      <c r="C348" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>129</v>
+      </c>
+      <c r="B349" t="s">
+        <v>310</v>
+      </c>
+      <c r="C349" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>130</v>
+      </c>
+      <c r="B350" t="s">
+        <v>311</v>
+      </c>
+      <c r="C350" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>131</v>
+      </c>
+      <c r="B351" t="s">
+        <v>312</v>
+      </c>
+      <c r="C351" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>131</v>
+      </c>
+      <c r="B352" t="s">
+        <v>313</v>
+      </c>
+      <c r="C352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>132</v>
+      </c>
+      <c r="B353" t="s">
+        <v>314</v>
+      </c>
+      <c r="C353" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>748</v>
+      </c>
+      <c r="B354" t="s">
+        <v>549</v>
+      </c>
+      <c r="C354" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>749</v>
+      </c>
+      <c r="B355" t="s">
+        <v>550</v>
+      </c>
+      <c r="C355" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>750</v>
+      </c>
+      <c r="B356" t="s">
+        <v>551</v>
+      </c>
+      <c r="C356" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>133</v>
+      </c>
+      <c r="B357" t="s">
+        <v>315</v>
+      </c>
+      <c r="C357" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>751</v>
+      </c>
+      <c r="B358" t="s">
+        <v>552</v>
+      </c>
+      <c r="C358" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>752</v>
+      </c>
+      <c r="B359" t="s">
+        <v>553</v>
+      </c>
+      <c r="C359" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>753</v>
+      </c>
+      <c r="B360" t="s">
+        <v>554</v>
+      </c>
+      <c r="C360" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>754</v>
+      </c>
+      <c r="B361" t="s">
+        <v>555</v>
+      </c>
+      <c r="C361" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>755</v>
+      </c>
+      <c r="B362" t="s">
+        <v>556</v>
+      </c>
+      <c r="C362" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>756</v>
+      </c>
+      <c r="B363" t="s">
+        <v>557</v>
+      </c>
+      <c r="C363" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>757</v>
+      </c>
+      <c r="B364" t="s">
+        <v>558</v>
+      </c>
+      <c r="C364" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>758</v>
+      </c>
+      <c r="B365" t="s">
+        <v>559</v>
+      </c>
+      <c r="C365" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>758</v>
+      </c>
+      <c r="B366" t="s">
+        <v>560</v>
+      </c>
+      <c r="C366" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>363</v>
+      </c>
+      <c r="B367" t="s">
+        <v>316</v>
+      </c>
+      <c r="C367" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>363</v>
+      </c>
+      <c r="B368" t="s">
+        <v>317</v>
+      </c>
+      <c r="C368" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>363</v>
+      </c>
+      <c r="B369" t="s">
+        <v>318</v>
+      </c>
+      <c r="C369" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>363</v>
+      </c>
+      <c r="B370" t="s">
+        <v>319</v>
+      </c>
+      <c r="C370" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>364</v>
+      </c>
+      <c r="B371" t="s">
+        <v>320</v>
+      </c>
+      <c r="C371" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>365</v>
+      </c>
+      <c r="B372" t="s">
+        <v>321</v>
+      </c>
+      <c r="C372" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>365</v>
+      </c>
+      <c r="B373" t="s">
+        <v>322</v>
+      </c>
+      <c r="C373" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>366</v>
+      </c>
+      <c r="B374" t="s">
+        <v>323</v>
+      </c>
+      <c r="C374" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>366</v>
+      </c>
+      <c r="B375" t="s">
+        <v>324</v>
+      </c>
+      <c r="C375" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>366</v>
+      </c>
+      <c r="B376" t="s">
+        <v>325</v>
+      </c>
+      <c r="C376" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>366</v>
+      </c>
+      <c r="B377" t="s">
+        <v>326</v>
+      </c>
+      <c r="C377" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>759</v>
+      </c>
+      <c r="B378" t="s">
+        <v>561</v>
+      </c>
+      <c r="C378" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>760</v>
+      </c>
+      <c r="B379" t="s">
+        <v>562</v>
+      </c>
+      <c r="C379" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>761</v>
+      </c>
+      <c r="B380" t="s">
+        <v>563</v>
+      </c>
+      <c r="C380" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>762</v>
+      </c>
+      <c r="B381" t="s">
+        <v>564</v>
+      </c>
+      <c r="C381" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>763</v>
+      </c>
+      <c r="B382" t="s">
+        <v>565</v>
+      </c>
+      <c r="C382" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>764</v>
+      </c>
+      <c r="B383" t="s">
+        <v>566</v>
+      </c>
+      <c r="C383" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>765</v>
+      </c>
+      <c r="B384" t="s">
+        <v>567</v>
+      </c>
+      <c r="C384" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>765</v>
+      </c>
+      <c r="B385" t="s">
+        <v>568</v>
+      </c>
+      <c r="C385" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>765</v>
+      </c>
+      <c r="B386" t="s">
+        <v>569</v>
+      </c>
+      <c r="C386" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>765</v>
+      </c>
+      <c r="B387" t="s">
+        <v>570</v>
+      </c>
+      <c r="C387" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>766</v>
+      </c>
+      <c r="B388" t="s">
+        <v>571</v>
+      </c>
+      <c r="C388" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>367</v>
+      </c>
+      <c r="B389" t="s">
+        <v>327</v>
+      </c>
+      <c r="C389" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>368</v>
+      </c>
+      <c r="B390" t="s">
+        <v>328</v>
+      </c>
+      <c r="C390" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>369</v>
+      </c>
+      <c r="B391" t="s">
+        <v>329</v>
+      </c>
+      <c r="C391" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>369</v>
+      </c>
+      <c r="B392" t="s">
+        <v>330</v>
+      </c>
+      <c r="C392" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>370</v>
+      </c>
+      <c r="B393" t="s">
+        <v>331</v>
+      </c>
+      <c r="C393" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>371</v>
+      </c>
+      <c r="B394" t="s">
+        <v>332</v>
+      </c>
+      <c r="C394" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>767</v>
+      </c>
+      <c r="B395" t="s">
+        <v>572</v>
+      </c>
+      <c r="C395" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>372</v>
+      </c>
+      <c r="B396" t="s">
+        <v>333</v>
+      </c>
+      <c r="C396" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>373</v>
+      </c>
+      <c r="B397" t="s">
+        <v>334</v>
+      </c>
+      <c r="C397" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>768</v>
+      </c>
+      <c r="B398" t="s">
+        <v>573</v>
+      </c>
+      <c r="C398" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>769</v>
+      </c>
+      <c r="B399" t="s">
+        <v>574</v>
+      </c>
+      <c r="C399" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>770</v>
+      </c>
+      <c r="B400" t="s">
+        <v>575</v>
+      </c>
+      <c r="C400" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>771</v>
+      </c>
+      <c r="B401" t="s">
+        <v>576</v>
+      </c>
+      <c r="C401" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>374</v>
+      </c>
+      <c r="B402" t="s">
+        <v>335</v>
+      </c>
+      <c r="C402" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>375</v>
+      </c>
+      <c r="B403" t="s">
+        <v>336</v>
+      </c>
+      <c r="C403" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>772</v>
+      </c>
+      <c r="B404" t="s">
+        <v>577</v>
+      </c>
+      <c r="C404" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>772</v>
+      </c>
+      <c r="B405" t="s">
+        <v>578</v>
+      </c>
+      <c r="C405" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>376</v>
+      </c>
+      <c r="B406" t="s">
+        <v>337</v>
+      </c>
+      <c r="C406" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>773</v>
+      </c>
+      <c r="B407" t="s">
+        <v>579</v>
+      </c>
+      <c r="C407" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>774</v>
+      </c>
+      <c r="B408" t="s">
+        <v>580</v>
+      </c>
+      <c r="C408" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>774</v>
+      </c>
+      <c r="B409" t="s">
+        <v>581</v>
+      </c>
+      <c r="C409" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>774</v>
+      </c>
+      <c r="B410" t="s">
+        <v>582</v>
+      </c>
+      <c r="C410" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>775</v>
+      </c>
+      <c r="B411" t="s">
+        <v>583</v>
+      </c>
+      <c r="C411" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>775</v>
+      </c>
+      <c r="B412" t="s">
+        <v>584</v>
+      </c>
+      <c r="C412" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>775</v>
+      </c>
+      <c r="B413" t="s">
+        <v>585</v>
+      </c>
+      <c r="C413" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>377</v>
+      </c>
+      <c r="B414" t="s">
+        <v>377</v>
+      </c>
+      <c r="C414" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>586</v>
+      </c>
+      <c r="B415" t="s">
+        <v>586</v>
+      </c>
+      <c r="C415" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>587</v>
+      </c>
+      <c r="B416" t="s">
+        <v>587</v>
+      </c>
+      <c r="C416" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>588</v>
+      </c>
+      <c r="B417" t="s">
+        <v>588</v>
+      </c>
+      <c r="C417" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\HunyaCs1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDCCE24-DECA-4B8F-B97F-01F8F2EDB571}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2FAF10-CA2C-4EA4-8ECB-E0BB8A48CE2B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21576" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -3695,7 +3695,7 @@
         <v>126</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -4652,7 +4652,7 @@
         <v>207</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -4663,7 +4663,7 @@
         <v>208</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -4674,7 +4674,7 @@
         <v>209</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -4949,7 +4949,7 @@
         <v>234</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
@@ -6401,7 +6401,7 @@
         <v>365</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
@@ -6412,7 +6412,7 @@
         <v>366</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
@@ -6456,7 +6456,7 @@
         <v>370</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
@@ -6764,7 +6764,7 @@
         <v>396</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
@@ -6775,7 +6775,7 @@
         <v>397</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
@@ -6786,7 +6786,7 @@
         <v>398</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
@@ -6852,7 +6852,7 @@
         <v>403</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
@@ -7369,7 +7369,7 @@
         <v>450</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
@@ -7380,7 +7380,7 @@
         <v>451</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
@@ -7666,7 +7666,7 @@
         <v>476</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
@@ -7754,7 +7754,7 @@
         <v>484</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
@@ -7820,7 +7820,7 @@
         <v>490</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
@@ -7831,7 +7831,7 @@
         <v>491</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
@@ -8007,7 +8007,7 @@
         <v>507</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
@@ -8172,7 +8172,7 @@
         <v>521</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
@@ -8183,7 +8183,7 @@
         <v>522</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A4E08C-7153-447B-85DF-2C5C389CE49B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E899BB-27B5-48CC-95D9-A0DB92DAE42E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Munka1!$A$1:$C$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Munka1!$A$1:$C$405</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="793">
   <si>
     <t>UTK</t>
   </si>
@@ -2404,6 +2404,9 @@
   </si>
   <si>
     <t>NFD6-09-17-56AG</t>
+  </si>
+  <si>
+    <t>K-920</t>
   </si>
 </sst>
 </file>
@@ -3649,7 +3652,7 @@
         <v>199</v>
       </c>
       <c r="C80" t="s">
-        <v>774</v>
+        <v>792</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -4936,7 +4939,7 @@
         <v>316</v>
       </c>
       <c r="C197" t="s">
-        <v>774</v>
+        <v>792</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4947,7 +4950,7 @@
         <v>317</v>
       </c>
       <c r="C198" t="s">
-        <v>774</v>
+        <v>792</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -6421,7 +6424,7 @@
         <v>451</v>
       </c>
       <c r="C332" t="s">
-        <v>774</v>
+        <v>792</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -6663,7 +6666,7 @@
         <v>473</v>
       </c>
       <c r="C354" t="s">
-        <v>774</v>
+        <v>792</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -6894,7 +6897,7 @@
         <v>494</v>
       </c>
       <c r="C375" t="s">
-        <v>774</v>
+        <v>792</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -7228,7 +7231,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C175" xr:uid="{544EFAB1-8998-46EF-B9E5-D4918C9DF0DC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0A35C0-597B-476C-88D2-73B985F1CA5F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BB8896-A94E-4494-AC42-18F80ECDFDE3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="780">
   <si>
     <t>UTK</t>
   </si>
@@ -2365,6 +2365,9 @@
   </si>
   <si>
     <t>SZ-821</t>
+  </si>
+  <si>
+    <t>K-917</t>
   </si>
 </sst>
 </file>
@@ -3599,7 +3602,7 @@
         <v>182</v>
       </c>
       <c r="C79" t="s">
-        <v>749</v>
+        <v>779</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3610,7 +3613,7 @@
         <v>183</v>
       </c>
       <c r="C80" t="s">
-        <v>749</v>
+        <v>779</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -4633,7 +4636,7 @@
         <v>276</v>
       </c>
       <c r="C173" t="s">
-        <v>749</v>
+        <v>779</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4644,7 +4647,7 @@
         <v>277</v>
       </c>
       <c r="C174" t="s">
-        <v>749</v>
+        <v>779</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4941,7 +4944,7 @@
         <v>304</v>
       </c>
       <c r="C201" t="s">
-        <v>749</v>
+        <v>779</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -5029,7 +5032,7 @@
         <v>312</v>
       </c>
       <c r="C209" t="s">
-        <v>749</v>
+        <v>779</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -5040,7 +5043,7 @@
         <v>313</v>
       </c>
       <c r="C210" t="s">
-        <v>749</v>
+        <v>779</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B098D858-359E-49FE-87DD-2CBB8CE9679D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2275373D-AAAC-4CC3-B319-15A99984B813}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="639">
   <si>
     <t>UTK</t>
   </si>
@@ -321,7 +321,1630 @@
     <t>99003273</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>159995579544389406</t>
+  </si>
+  <si>
+    <t>6ab391cc219e3d74bbe3a352</t>
+  </si>
+  <si>
+    <t>6aaa9f60f7fbdc73ea0a7f74</t>
+  </si>
+  <si>
+    <t>6ab0e35d73749ba5fc07aead</t>
+  </si>
+  <si>
+    <t>6ab1500873749ba5fc07c434</t>
+  </si>
+  <si>
+    <t>6aa910f4f7fbdc73ea0a58dc</t>
+  </si>
+  <si>
+    <t>6aa8123a2235a0231b9b8df4</t>
+  </si>
+  <si>
+    <t>6aa8123a2235a0231b9b8df5</t>
+  </si>
+  <si>
+    <t>6ab2679173749ba5fc07d70e</t>
+  </si>
+  <si>
+    <t>6aabb2a5f7fbdc73ea0a8ea8</t>
+  </si>
+  <si>
+    <t>6aae6f6173749ba5fc079929</t>
+  </si>
+  <si>
+    <t>6aaceef5f7fbdc73ea0aa828</t>
+  </si>
+  <si>
+    <t>6ab15cb673749ba5fc07c591</t>
+  </si>
+  <si>
+    <t>6ab270ce73749ba5fc07d902</t>
+  </si>
+  <si>
+    <t>6ab133eb73749ba5fc07bfc5</t>
+  </si>
+  <si>
+    <t>6ab0ff4c73749ba5fc07b557</t>
+  </si>
+  <si>
+    <t>6ab0f64c73749ba5fc07b32e</t>
+  </si>
+  <si>
+    <t>6aaa92a2f7fbdc73ea0a7d2c</t>
+  </si>
+  <si>
+    <t>6ab3b68e219e3d74bbe3aa15</t>
+  </si>
+  <si>
+    <t>6ab386d8219e3d74bbe3a103</t>
+  </si>
+  <si>
+    <t>6ab386d8219e3d74bbe3a104</t>
+  </si>
+  <si>
+    <t>6ab147b573749ba5fc07c352</t>
+  </si>
+  <si>
+    <t>6ab284aa73749ba5fc07dc9e</t>
+  </si>
+  <si>
+    <t>6ab2269373749ba5fc07ca18</t>
+  </si>
+  <si>
+    <t>6ab247b573749ba5fc07d102</t>
+  </si>
+  <si>
+    <t>6aa7b9fc2235a0231b9b7bd7</t>
+  </si>
+  <si>
+    <t>6aad040273749ba5fc077e6b</t>
+  </si>
+  <si>
+    <t>6ab212bb73749ba5fc07c8f4</t>
+  </si>
+  <si>
+    <t>6ab37d70219e3d74bbe39eca</t>
+  </si>
+  <si>
+    <t>6ab278b873749ba5fc07da38</t>
+  </si>
+  <si>
+    <t>6aa9185cf7fbdc73ea0a5a2f</t>
+  </si>
+  <si>
+    <t>6aa9185cf7fbdc73ea0a5a30</t>
+  </si>
+  <si>
+    <t>6aa97acef7fbdc73ea0a6a74</t>
+  </si>
+  <si>
+    <t>6aa97acef7fbdc73ea0a6a75</t>
+  </si>
+  <si>
+    <t>6ab3b760219e3d74bbe3aa3e</t>
+  </si>
+  <si>
+    <t>6ab37ce0219e3d74bbe39ec6</t>
+  </si>
+  <si>
+    <t>6ab37ce0219e3d74bbe39ec7</t>
+  </si>
+  <si>
+    <t>6aaa91d1f7fbdc73ea0a7d1d</t>
+  </si>
+  <si>
+    <t>6ab24a9273749ba5fc07d177</t>
+  </si>
+  <si>
+    <t>6aad0a2f73749ba5fc077fce</t>
+  </si>
+  <si>
+    <t>6aabb6b9f7fbdc73ea0a8f65</t>
+  </si>
+  <si>
+    <t>6aabc269f7fbdc73ea0a9133</t>
+  </si>
+  <si>
+    <t>6aabc269f7fbdc73ea0a9134</t>
+  </si>
+  <si>
+    <t>6ab22c4973749ba5fc07caef</t>
+  </si>
+  <si>
+    <t>6aac0537f7fbdc73ea0a9b8d</t>
+  </si>
+  <si>
+    <t>6aab95dff7fbdc73ea0a8920</t>
+  </si>
+  <si>
+    <t>6aab95f5f7fbdc73ea0a894b</t>
+  </si>
+  <si>
+    <t>6aac2989f7fbdc73ea0a9e8e</t>
+  </si>
+  <si>
+    <t>6aac3c5bf7fbdc73ea0a9f14</t>
+  </si>
+  <si>
+    <t>6aac3c5bf7fbdc73ea0a9f15</t>
+  </si>
+  <si>
+    <t>6aacf4aaf7fbdc73ea0aa9ba</t>
+  </si>
+  <si>
+    <t>6ab2816d73749ba5fc07dbc0</t>
+  </si>
+  <si>
+    <t>6aacfed473749ba5fc077ccf</t>
+  </si>
+  <si>
+    <t>6aacfed473749ba5fc077cd1</t>
+  </si>
+  <si>
+    <t>6ab23dea73749ba5fc07cebc</t>
+  </si>
+  <si>
+    <t>6aad084673749ba5fc077fa2</t>
+  </si>
+  <si>
+    <t>6aad119b73749ba5fc07813d</t>
+  </si>
+  <si>
+    <t>6ab2512b73749ba5fc07d317</t>
+  </si>
+  <si>
+    <t>6aad2db673749ba5fc0786b9</t>
+  </si>
+  <si>
+    <t>6aad6aa373749ba5fc078f2f</t>
+  </si>
+  <si>
+    <t>6aacf0c7f7fbdc73ea0aa8ae</t>
+  </si>
+  <si>
+    <t>6aad0e1e73749ba5fc0780a4</t>
+  </si>
+  <si>
+    <t>6aad7fb673749ba5fc079040</t>
+  </si>
+  <si>
+    <t>6aad7fb673749ba5fc079045</t>
+  </si>
+  <si>
+    <t>6aad8dc373749ba5fc079087</t>
+  </si>
+  <si>
+    <t>6aae5d3673749ba5fc079771</t>
+  </si>
+  <si>
+    <t>6ab3984b219e3d74bbe3a489</t>
+  </si>
+  <si>
+    <t>6aae9da773749ba5fc079c5d</t>
+  </si>
+  <si>
+    <t>6aaeaa8e73749ba5fc079d2d</t>
+  </si>
+  <si>
+    <t>6aaeaa8e73749ba5fc079d2e</t>
+  </si>
+  <si>
+    <t>6aae52ed73749ba5fc079614</t>
+  </si>
+  <si>
+    <t>6aae52ed73749ba5fc079615</t>
+  </si>
+  <si>
+    <t>6aae5f8d73749ba5fc0797c6</t>
+  </si>
+  <si>
+    <t>6aae5f8d73749ba5fc0797c8</t>
+  </si>
+  <si>
+    <t>6aae82be73749ba5fc079a87</t>
+  </si>
+  <si>
+    <t>6ab29e7273749ba5fc07e071</t>
+  </si>
+  <si>
+    <t>6aaec32a73749ba5fc079e5b</t>
+  </si>
+  <si>
+    <t>6ab3aecf219e3d74bbe3a8a2</t>
+  </si>
+  <si>
+    <t>6aaf85ae73749ba5fc07a052</t>
+  </si>
+  <si>
+    <t>6aaff50673749ba5fc07a74c</t>
+  </si>
+  <si>
+    <t>6ab0025673749ba5fc07a80f</t>
+  </si>
+  <si>
+    <t>6ab01e1273749ba5fc07a957</t>
+  </si>
+  <si>
+    <t>6ab030ce73749ba5fc07a9ea</t>
+  </si>
+  <si>
+    <t>6ab0cdd173749ba5fc07ab1e</t>
+  </si>
+  <si>
+    <t>6ab0dabb73749ba5fc07ac8c</t>
+  </si>
+  <si>
+    <t>6ab117c173749ba5fc07ba55</t>
+  </si>
+  <si>
+    <t>6ab117c173749ba5fc07ba58</t>
+  </si>
+  <si>
+    <t>6ab118cd73749ba5fc07ba7c</t>
+  </si>
+  <si>
+    <t>6ab11dbb73749ba5fc07bb8d</t>
+  </si>
+  <si>
+    <t>6ab11dbb73749ba5fc07bb8e</t>
+  </si>
+  <si>
+    <t>6ab1224173749ba5fc07bc6f</t>
+  </si>
+  <si>
+    <t>6ab1294873749ba5fc07bd7e</t>
+  </si>
+  <si>
+    <t>6ab38603219e3d74bbe3a0f8</t>
+  </si>
+  <si>
+    <t>6ab1362273749ba5fc07c004</t>
+  </si>
+  <si>
+    <t>6ab15bff73749ba5fc07c58b</t>
+  </si>
+  <si>
+    <t>6ab155c673749ba5fc07c4fd</t>
+  </si>
+  <si>
+    <t>6ab1662a73749ba5fc07c67f</t>
+  </si>
+  <si>
+    <t>6ab1617f73749ba5fc07c613</t>
+  </si>
+  <si>
+    <t>6ab1617f73749ba5fc07c616</t>
+  </si>
+  <si>
+    <t>6ab0f49273749ba5fc07b2b1</t>
+  </si>
+  <si>
+    <t>6ab102ed73749ba5fc07b609</t>
+  </si>
+  <si>
+    <t>6ab110a073749ba5fc07b8c0</t>
+  </si>
+  <si>
+    <t>6ab110a073749ba5fc07b8c1</t>
+  </si>
+  <si>
+    <t>6ab12cc873749ba5fc07be36</t>
+  </si>
+  <si>
+    <t>6ab12f1073749ba5fc07be86</t>
+  </si>
+  <si>
+    <t>6ab1387f73749ba5fc07c098</t>
+  </si>
+  <si>
+    <t>6ab1387a73749ba5fc07c07d</t>
+  </si>
+  <si>
+    <t>6ab13f8473749ba5fc07c1d9</t>
+  </si>
+  <si>
+    <t>6ab1455673749ba5fc07c2ec</t>
+  </si>
+  <si>
+    <t>6ab1455673749ba5fc07c2ed</t>
+  </si>
+  <si>
+    <t>6ab1511673749ba5fc07c45c</t>
+  </si>
+  <si>
+    <t>6ab15a7473749ba5fc07c552</t>
+  </si>
+  <si>
+    <t>6ab15a7473749ba5fc07c553</t>
+  </si>
+  <si>
+    <t>6ab1768e73749ba5fc07c76c</t>
+  </si>
+  <si>
+    <t>6ab2334573749ba5fc07cc53</t>
+  </si>
+  <si>
+    <t>6ab2334573749ba5fc07cc54</t>
+  </si>
+  <si>
+    <t>6ab2334573749ba5fc07cc56</t>
+  </si>
+  <si>
+    <t>6ab2333f73749ba5fc07cc27</t>
+  </si>
+  <si>
+    <t>6ab2333f73749ba5fc07cc2a</t>
+  </si>
+  <si>
+    <t>6ab2418b73749ba5fc07cf85</t>
+  </si>
+  <si>
+    <t>6ab2418b73749ba5fc07cf88</t>
+  </si>
+  <si>
+    <t>6ab2407e73749ba5fc07cf39</t>
+  </si>
+  <si>
+    <t>6ab243b673749ba5fc07d009</t>
+  </si>
+  <si>
+    <t>6ab2498e73749ba5fc07d168</t>
+  </si>
+  <si>
+    <t>6ab2498a73749ba5fc07d157</t>
+  </si>
+  <si>
+    <t>6ab24d1273749ba5fc07d218</t>
+  </si>
+  <si>
+    <t>6ab25d7173749ba5fc07d51f</t>
+  </si>
+  <si>
+    <t>6ab260f973749ba5fc07d5b7</t>
+  </si>
+  <si>
+    <t>6ab2624073749ba5fc07d622</t>
+  </si>
+  <si>
+    <t>6ab273b573749ba5fc07d991</t>
+  </si>
+  <si>
+    <t>6ab288d573749ba5fc07dd70</t>
+  </si>
+  <si>
+    <t>6ab29df573749ba5fc07e06b</t>
+  </si>
+  <si>
+    <t>6ab2b42773749ba5fc07e29e</t>
+  </si>
+  <si>
+    <t>6ab2b0a473749ba5fc07e243</t>
+  </si>
+  <si>
+    <t>6ab2b42b73749ba5fc07e2a8</t>
+  </si>
+  <si>
+    <t>6ab2b42773749ba5fc07e29d</t>
+  </si>
+  <si>
+    <t>6ab2320d73749ba5fc07cbed</t>
+  </si>
+  <si>
+    <t>6ab2320d73749ba5fc07cbee</t>
+  </si>
+  <si>
+    <t>6ab2417173749ba5fc07cf82</t>
+  </si>
+  <si>
+    <t>6ab24f5873749ba5fc07d276</t>
+  </si>
+  <si>
+    <t>6ab258c173749ba5fc07d440</t>
+  </si>
+  <si>
+    <t>6ab260fa73749ba5fc07d5c8</t>
+  </si>
+  <si>
+    <t>6ab260fa73749ba5fc07d5ca</t>
+  </si>
+  <si>
+    <t>6ab2773473749ba5fc07da11</t>
+  </si>
+  <si>
+    <t>6ab2935873749ba5fc07df16</t>
+  </si>
+  <si>
+    <t>6ab28fdb73749ba5fc07de84</t>
+  </si>
+  <si>
+    <t>6ab2922a73749ba5fc07defd</t>
+  </si>
+  <si>
+    <t>6ab29cba73749ba5fc07e041</t>
+  </si>
+  <si>
+    <t>6ab2a16573749ba5fc07e0af</t>
+  </si>
+  <si>
+    <t>6ab2b0a473749ba5fc07e249</t>
+  </si>
+  <si>
+    <t>6ab2cdee73749ba5fc07e42c</t>
+  </si>
+  <si>
+    <t>6ab37459219e3d74bbe39dc8</t>
+  </si>
+  <si>
+    <t>6ab37edc219e3d74bbe39f13</t>
+  </si>
+  <si>
+    <t>6ab37edc219e3d74bbe39f14</t>
+  </si>
+  <si>
+    <t>6ab38133219e3d74bbe39f9c</t>
+  </si>
+  <si>
+    <t>6ab38982219e3d74bbe3a190</t>
+  </si>
+  <si>
+    <t>6ab38982219e3d74bbe3a191</t>
+  </si>
+  <si>
+    <t>6ab39527219e3d74bbe3a3d8</t>
+  </si>
+  <si>
+    <t>6ab39537219e3d74bbe3a3e4</t>
+  </si>
+  <si>
+    <t>6ab39791219e3d74bbe3a469</t>
+  </si>
+  <si>
+    <t>6ab39d6f219e3d74bbe3a5a3</t>
+  </si>
+  <si>
+    <t>6ab3a76d219e3d74bbe3a76d</t>
+  </si>
+  <si>
+    <t>6ab3a76d219e3d74bbe3a76e</t>
+  </si>
+  <si>
+    <t>6ab3a46d219e3d74bbe3a6cf</t>
+  </si>
+  <si>
+    <t>6ab3ab66219e3d74bbe3a7fa</t>
+  </si>
+  <si>
+    <t>6ab3aa44219e3d74bbe3a7d6</t>
+  </si>
+  <si>
+    <t>6ab3b017219e3d74bbe3a8fd</t>
+  </si>
+  <si>
+    <t>6ab35964219e3d74bbe39ca0</t>
+  </si>
+  <si>
+    <t>6ab37a2d219e3d74bbe39e3d</t>
+  </si>
+  <si>
+    <t>6ab37326219e3d74bbe39d8c</t>
+  </si>
+  <si>
+    <t>6ab38cf4219e3d74bbe3a228</t>
+  </si>
+  <si>
+    <t>6ab38cf4219e3d74bbe3a229</t>
+  </si>
+  <si>
+    <t>1449-953736_2</t>
+  </si>
+  <si>
+    <t>1449-412512</t>
+  </si>
+  <si>
+    <t>1449-281639</t>
+  </si>
+  <si>
+    <t>1449-196819</t>
+  </si>
+  <si>
+    <t>1449-410146</t>
+  </si>
+  <si>
+    <t>26MPE0010014/1</t>
+  </si>
+  <si>
+    <t>26MPE0010015/1</t>
+  </si>
+  <si>
+    <t>26MPE0010049/1</t>
+  </si>
+  <si>
+    <t>26MPE0010050/1</t>
+  </si>
+  <si>
+    <t>26MPE0010052/1</t>
+  </si>
+  <si>
+    <t>26MPE0010053/1</t>
+  </si>
+  <si>
+    <t>322076425/1</t>
+  </si>
+  <si>
+    <t>322076425/2</t>
+  </si>
+  <si>
+    <t>325458600/1</t>
+  </si>
+  <si>
+    <t>325458600/2</t>
+  </si>
+  <si>
+    <t>327403294/1</t>
+  </si>
+  <si>
+    <t>327403294/2</t>
+  </si>
+  <si>
+    <t>327763638/1</t>
+  </si>
+  <si>
+    <t>327763638/2</t>
+  </si>
+  <si>
+    <t>327763638/3</t>
+  </si>
+  <si>
+    <t>327990077/1</t>
+  </si>
+  <si>
+    <t>328123701/1</t>
+  </si>
+  <si>
+    <t>328123701/2</t>
+  </si>
+  <si>
+    <t>328383402/1</t>
+  </si>
+  <si>
+    <t>328541384/1</t>
+  </si>
+  <si>
+    <t>328541384/2</t>
+  </si>
+  <si>
+    <t>328596769/1</t>
+  </si>
+  <si>
+    <t>328597438/1</t>
+  </si>
+  <si>
+    <t>328946354/1</t>
+  </si>
+  <si>
+    <t>329015520/1</t>
+  </si>
+  <si>
+    <t>329015520/2</t>
+  </si>
+  <si>
+    <t>329063235/1</t>
+  </si>
+  <si>
+    <t>329063235/2</t>
+  </si>
+  <si>
+    <t>329063411/1</t>
+  </si>
+  <si>
+    <t>329063694/1</t>
+  </si>
+  <si>
+    <t>329134422/1</t>
+  </si>
+  <si>
+    <t>329135060/1</t>
+  </si>
+  <si>
+    <t>329204729/1</t>
+  </si>
+  <si>
+    <t>329204754/1</t>
+  </si>
+  <si>
+    <t>329204765/1</t>
+  </si>
+  <si>
+    <t>329205251/1</t>
+  </si>
+  <si>
+    <t>329205251/2</t>
+  </si>
+  <si>
+    <t>329205251/3</t>
+  </si>
+  <si>
+    <t>329272422/1</t>
+  </si>
+  <si>
+    <t>329272672/1</t>
+  </si>
+  <si>
+    <t>329272672/2</t>
+  </si>
+  <si>
+    <t>329272672/3</t>
+  </si>
+  <si>
+    <t>329272815/1</t>
+  </si>
+  <si>
+    <t>329320348/1</t>
+  </si>
+  <si>
+    <t>329320676/1</t>
+  </si>
+  <si>
+    <t>329320704/1</t>
+  </si>
+  <si>
+    <t>329375188/1</t>
+  </si>
+  <si>
+    <t>329375213/1</t>
+  </si>
+  <si>
+    <t>329375311/1</t>
+  </si>
+  <si>
+    <t>329375311/2</t>
+  </si>
+  <si>
+    <t>329375558/1</t>
+  </si>
+  <si>
+    <t>329375562/1</t>
+  </si>
+  <si>
+    <t>329375767/1</t>
+  </si>
+  <si>
+    <t>329375792/1</t>
+  </si>
+  <si>
+    <t>329375829/1</t>
+  </si>
+  <si>
+    <t>329375855/1</t>
+  </si>
+  <si>
+    <t>329430969/1</t>
+  </si>
+  <si>
+    <t>329484344/1</t>
+  </si>
+  <si>
+    <t>329484351/1</t>
+  </si>
+  <si>
+    <t>329484381/1</t>
+  </si>
+  <si>
+    <t>329484381/2</t>
+  </si>
+  <si>
+    <t>329484490/1</t>
+  </si>
+  <si>
+    <t>329484506/1</t>
+  </si>
+  <si>
+    <t>329484557/1</t>
+  </si>
+  <si>
+    <t>329484572/1</t>
+  </si>
+  <si>
+    <t>329484662/1</t>
+  </si>
+  <si>
+    <t>329484723/1</t>
+  </si>
+  <si>
+    <t>329484818/1</t>
+  </si>
+  <si>
+    <t>329535624/1</t>
+  </si>
+  <si>
+    <t>329535815/1</t>
+  </si>
+  <si>
+    <t>329535839/1</t>
+  </si>
+  <si>
+    <t>329535969/1</t>
+  </si>
+  <si>
+    <t>329536057/1</t>
+  </si>
+  <si>
+    <t>329536227/1</t>
+  </si>
+  <si>
+    <t>329536493/1</t>
+  </si>
+  <si>
+    <t>329536493/2</t>
+  </si>
+  <si>
+    <t>329536493/3</t>
+  </si>
+  <si>
+    <t>329536521/1</t>
+  </si>
+  <si>
+    <t>329583831/1</t>
+  </si>
+  <si>
+    <t>329583839/1</t>
+  </si>
+  <si>
+    <t>329583995/1</t>
+  </si>
+  <si>
+    <t>329584115/1</t>
+  </si>
+  <si>
+    <t>329584211/1</t>
+  </si>
+  <si>
+    <t>329584452/1</t>
+  </si>
+  <si>
+    <t>329584565/1</t>
+  </si>
+  <si>
+    <t>329584565/2</t>
+  </si>
+  <si>
+    <t>329584611/1</t>
+  </si>
+  <si>
+    <t>329633598/1</t>
+  </si>
+  <si>
+    <t>329633694/1</t>
+  </si>
+  <si>
+    <t>329633694/2</t>
+  </si>
+  <si>
+    <t>329633694/3</t>
+  </si>
+  <si>
+    <t>329633712/1</t>
+  </si>
+  <si>
+    <t>329633872/1</t>
+  </si>
+  <si>
+    <t>329633890/1</t>
+  </si>
+  <si>
+    <t>329633931/1</t>
+  </si>
+  <si>
+    <t>329633987/1</t>
+  </si>
+  <si>
+    <t>329634010/1</t>
+  </si>
+  <si>
+    <t>329634010/2</t>
+  </si>
+  <si>
+    <t>329634011/1</t>
+  </si>
+  <si>
+    <t>329634098/1</t>
+  </si>
+  <si>
+    <t>329634120/1</t>
+  </si>
+  <si>
+    <t>329634194/1</t>
+  </si>
+  <si>
+    <t>329634388/1</t>
+  </si>
+  <si>
+    <t>329690209/1</t>
+  </si>
+  <si>
+    <t>329738796/1</t>
+  </si>
+  <si>
+    <t>329738796/2</t>
+  </si>
+  <si>
+    <t>329738796/3</t>
+  </si>
+  <si>
+    <t>329739097/1</t>
+  </si>
+  <si>
+    <t>329788104/1</t>
+  </si>
+  <si>
+    <t>159995579544430870</t>
+  </si>
+  <si>
+    <t>159995579544430887</t>
+  </si>
+  <si>
+    <t>840928581KR/1</t>
+  </si>
+  <si>
+    <t>840928581KR/2</t>
+  </si>
+  <si>
+    <t>99003273/1</t>
+  </si>
+  <si>
+    <t>159995579544442125</t>
+  </si>
+  <si>
+    <t>159995579543968183</t>
+  </si>
+  <si>
+    <t>159995579544286026</t>
+  </si>
+  <si>
+    <t>159995579544439156</t>
+  </si>
+  <si>
+    <t>159995579544438548</t>
+  </si>
+  <si>
+    <t>202609182601900201</t>
+  </si>
+  <si>
+    <t>202609182601900202</t>
+  </si>
+  <si>
+    <t>202609182601900203</t>
+  </si>
+  <si>
+    <t>202609212601968201</t>
+  </si>
+  <si>
+    <t>202609212601974201</t>
+  </si>
+  <si>
+    <t>202609222601976701</t>
+  </si>
+  <si>
+    <t>202609222601977801</t>
+  </si>
+  <si>
+    <t>202609232601983901</t>
+  </si>
+  <si>
+    <t>202609232601985801</t>
+  </si>
+  <si>
+    <t>202609232601984401</t>
+  </si>
+  <si>
+    <t>202609232601984101</t>
+  </si>
+  <si>
+    <t>202609232601985601</t>
+  </si>
+  <si>
+    <t>202609232601984601</t>
+  </si>
+  <si>
+    <t>202609232601984301</t>
+  </si>
+  <si>
+    <t>202609182601928201</t>
+  </si>
+  <si>
+    <t>202609232601956401</t>
+  </si>
+  <si>
+    <t>202609232601956402</t>
+  </si>
+  <si>
+    <t>202609212601963501</t>
+  </si>
+  <si>
+    <t>202609212601962501</t>
+  </si>
+  <si>
+    <t>202609232601978601</t>
+  </si>
+  <si>
+    <t>202609222601980101</t>
+  </si>
+  <si>
+    <t>202609222601976501</t>
+  </si>
+  <si>
+    <t>202609232601987101</t>
+  </si>
+  <si>
+    <t>202609232601984801</t>
+  </si>
+  <si>
+    <t>202609232601985001</t>
+  </si>
+  <si>
+    <t>159995579544442439</t>
+  </si>
+  <si>
+    <t>1-7925  SZ0323/2026</t>
+  </si>
+  <si>
+    <t>260825-F00012532-1</t>
+  </si>
+  <si>
+    <t>260903-F00007055</t>
+  </si>
+  <si>
+    <t>260907-F00011940</t>
+  </si>
+  <si>
+    <t>260907-F00014880</t>
+  </si>
+  <si>
+    <t>260908-F00008384</t>
+  </si>
+  <si>
+    <t>260908-F00013908-1</t>
+  </si>
+  <si>
+    <t>260910-F00002395</t>
+  </si>
+  <si>
+    <t>260911-F00000575</t>
+  </si>
+  <si>
+    <t>260911-F00001330</t>
+  </si>
+  <si>
+    <t>260911-F00003253</t>
+  </si>
+  <si>
+    <t>260911-F00008963</t>
+  </si>
+  <si>
+    <t>260911-F00014087</t>
+  </si>
+  <si>
+    <t>260914-F00006959</t>
+  </si>
+  <si>
+    <t>260914-F00015385</t>
+  </si>
+  <si>
+    <t>260915-F00001832</t>
+  </si>
+  <si>
+    <t>260915-F00006998</t>
+  </si>
+  <si>
+    <t>260915-F00011044</t>
+  </si>
+  <si>
+    <t>260915-F00014941</t>
+  </si>
+  <si>
+    <t>260915-W00012340</t>
+  </si>
+  <si>
+    <t>260916-F00002431</t>
+  </si>
+  <si>
+    <t>260916-F00010973</t>
+  </si>
+  <si>
+    <t>260916-F00011034</t>
+  </si>
+  <si>
+    <t>260916-F00012610</t>
+  </si>
+  <si>
+    <t>260916-W00004542</t>
+  </si>
+  <si>
+    <t>260917-F00009530</t>
+  </si>
+  <si>
+    <t>260917-W00002194</t>
+  </si>
+  <si>
+    <t>260917-W00002237</t>
+  </si>
+  <si>
+    <t>260917-W00009789</t>
+  </si>
+  <si>
+    <t>260917-W00012460</t>
+  </si>
+  <si>
+    <t>260918-F00004625</t>
+  </si>
+  <si>
+    <t>260918-F00005814</t>
+  </si>
+  <si>
+    <t>260918-F00006245</t>
+  </si>
+  <si>
+    <t>260918-F00007594</t>
+  </si>
+  <si>
+    <t>260918-F00008235</t>
+  </si>
+  <si>
+    <t>260918-F00011036</t>
+  </si>
+  <si>
+    <t>260918-F00016726</t>
+  </si>
+  <si>
+    <t>260918-W00005538</t>
+  </si>
+  <si>
+    <t>260918-W00017794</t>
+  </si>
+  <si>
+    <t>260918-W00018297-2</t>
+  </si>
+  <si>
+    <t>260918-W00019406</t>
+  </si>
+  <si>
+    <t>260919-F00003307</t>
+  </si>
+  <si>
+    <t>260919-F00005703</t>
+  </si>
+  <si>
+    <t>260919-F00006302</t>
+  </si>
+  <si>
+    <t>260919-F00006757</t>
+  </si>
+  <si>
+    <t>260919-W00004726</t>
+  </si>
+  <si>
+    <t>260919-W00007740</t>
+  </si>
+  <si>
+    <t>260919-W00011632</t>
+  </si>
+  <si>
+    <t>260919-W00011719</t>
+  </si>
+  <si>
+    <t>260920-W00001871</t>
+  </si>
+  <si>
+    <t>260920-W00010078</t>
+  </si>
+  <si>
+    <t>260920-W00010483</t>
+  </si>
+  <si>
+    <t>260920-W00011954</t>
+  </si>
+  <si>
+    <t>260921-F00000990</t>
+  </si>
+  <si>
+    <t>260921-F00010179</t>
+  </si>
+  <si>
+    <t>260921-F00011126</t>
+  </si>
+  <si>
+    <t>260921-F00011316</t>
+  </si>
+  <si>
+    <t>260921-F00013964</t>
+  </si>
+  <si>
+    <t>260921-F00016442</t>
+  </si>
+  <si>
+    <t>260921-F00017689</t>
+  </si>
+  <si>
+    <t>260921-F00017765</t>
+  </si>
+  <si>
+    <t>260921-F00017825</t>
+  </si>
+  <si>
+    <t>260921-W00004706</t>
+  </si>
+  <si>
+    <t>260921-W00006090</t>
+  </si>
+  <si>
+    <t>260921-W00007263</t>
+  </si>
+  <si>
+    <t>260921-W00009694</t>
+  </si>
+  <si>
+    <t>260921-W00009964</t>
+  </si>
+  <si>
+    <t>260921-W00010683</t>
+  </si>
+  <si>
+    <t>260921-W00010734</t>
+  </si>
+  <si>
+    <t>260921-W00011192</t>
+  </si>
+  <si>
+    <t>260922-F00001922</t>
+  </si>
+  <si>
+    <t>260922-F00002116</t>
+  </si>
+  <si>
+    <t>260922-F00003316</t>
+  </si>
+  <si>
+    <t>260922-F00004438</t>
+  </si>
+  <si>
+    <t>260922-F00004663</t>
+  </si>
+  <si>
+    <t>260922-F00005172</t>
+  </si>
+  <si>
+    <t>260922-F00005683</t>
+  </si>
+  <si>
+    <t>260922-F00007629</t>
+  </si>
+  <si>
+    <t>260922-F00007795</t>
+  </si>
+  <si>
+    <t>260922-F00008336</t>
+  </si>
+  <si>
+    <t>260922-F00010290</t>
+  </si>
+  <si>
+    <t>260922-F00012985</t>
+  </si>
+  <si>
+    <t>260922-F00014912</t>
+  </si>
+  <si>
+    <t>260922-F00015882-2</t>
+  </si>
+  <si>
+    <t>260922-F00016179</t>
+  </si>
+  <si>
+    <t>260922-F00016188</t>
+  </si>
+  <si>
+    <t>260922-W00004179</t>
+  </si>
+  <si>
+    <t>260922-W00004206</t>
+  </si>
+  <si>
+    <t>260922-W00006044</t>
+  </si>
+  <si>
+    <t>260922-W00006410</t>
+  </si>
+  <si>
+    <t>260922-W00010453</t>
+  </si>
+  <si>
+    <t>260922-W00010633</t>
+  </si>
+  <si>
+    <t>260922-W00010804</t>
+  </si>
+  <si>
+    <t>260922-W00011496</t>
+  </si>
+  <si>
+    <t>260922-W00011869</t>
+  </si>
+  <si>
+    <t>260922-W00012940</t>
+  </si>
+  <si>
+    <t>260922-W00014253-2</t>
+  </si>
+  <si>
+    <t>260923-F00000534</t>
+  </si>
+  <si>
+    <t>260923-F00001295</t>
+  </si>
+  <si>
+    <t>260923-F00001453</t>
+  </si>
+  <si>
+    <t>260923-F00002773</t>
+  </si>
+  <si>
+    <t>260923-F00004075</t>
+  </si>
+  <si>
+    <t>260923-F00004181</t>
+  </si>
+  <si>
+    <t>260923-F00005025</t>
+  </si>
+  <si>
+    <t>260923-F00006027</t>
+  </si>
+  <si>
+    <t>260923-F00006420</t>
+  </si>
+  <si>
+    <t>260923-F00006677</t>
+  </si>
+  <si>
+    <t>260923-F00006822</t>
+  </si>
+  <si>
+    <t>260923-F00007591</t>
+  </si>
+  <si>
+    <t>260923-W00000203</t>
+  </si>
+  <si>
+    <t>260923-W00001231</t>
+  </si>
+  <si>
+    <t>260923-W00001316</t>
+  </si>
+  <si>
+    <t>260923-W00003141</t>
+  </si>
+  <si>
+    <t>267013406</t>
+  </si>
+  <si>
+    <t>267013426</t>
+  </si>
+  <si>
+    <t>267013603</t>
+  </si>
+  <si>
+    <t>267013640</t>
+  </si>
+  <si>
+    <t>267013650</t>
+  </si>
+  <si>
+    <t>26MPE0010014</t>
+  </si>
+  <si>
+    <t>26MPE0010015</t>
+  </si>
+  <si>
+    <t>26MPE0010049</t>
+  </si>
+  <si>
+    <t>26MPE0010050</t>
+  </si>
+  <si>
+    <t>26MPE0010052</t>
+  </si>
+  <si>
+    <t>26MPE0010053</t>
+  </si>
+  <si>
+    <t>325458600</t>
+  </si>
+  <si>
+    <t>329015520</t>
+  </si>
+  <si>
+    <t>329063411</t>
+  </si>
+  <si>
+    <t>329063694</t>
+  </si>
+  <si>
+    <t>329134422</t>
+  </si>
+  <si>
+    <t>329272672</t>
+  </si>
+  <si>
+    <t>329484344</t>
+  </si>
+  <si>
+    <t>329484381</t>
+  </si>
+  <si>
+    <t>329484557</t>
+  </si>
+  <si>
+    <t>329484662</t>
+  </si>
+  <si>
+    <t>329484723</t>
+  </si>
+  <si>
+    <t>329584211</t>
+  </si>
+  <si>
+    <t>329633931</t>
+  </si>
+  <si>
+    <t>329634010</t>
+  </si>
+  <si>
+    <t>329634098</t>
+  </si>
+  <si>
+    <t>329634120</t>
+  </si>
+  <si>
+    <t>329690209</t>
+  </si>
+  <si>
+    <t>329738796</t>
+  </si>
+  <si>
+    <t>329739097</t>
+  </si>
+  <si>
+    <t>329788104</t>
+  </si>
+  <si>
+    <t>73676-108122</t>
+  </si>
+  <si>
+    <t>840928581KR</t>
+  </si>
+  <si>
+    <t>ID1234_XD</t>
+  </si>
+  <si>
+    <t>ID5489_XD</t>
+  </si>
+  <si>
+    <t>ID5525_XD</t>
+  </si>
+  <si>
+    <t>ID5541_XD</t>
+  </si>
+  <si>
+    <t>ID5544_XD</t>
+  </si>
+  <si>
+    <t>NFD6-09-07-BUAR</t>
+  </si>
+  <si>
+    <t>NFD6-09-19-H7DK</t>
+  </si>
+  <si>
+    <t>NFD6-09-20-KAGX</t>
+  </si>
+  <si>
+    <t>NFD6-09-21-2KLN</t>
+  </si>
+  <si>
+    <t>NFD6-09-21-XFEZ</t>
+  </si>
+  <si>
+    <t>NFD6-09-22-6DY3</t>
+  </si>
+  <si>
+    <t>NFD6-09-22-LF9J</t>
+  </si>
+  <si>
+    <t>NFD6-09-22-NDAM</t>
+  </si>
+  <si>
+    <t>NFD6-09-22-PQQC</t>
+  </si>
+  <si>
+    <t>NFD6-09-22-VYEN</t>
+  </si>
+  <si>
+    <t>NFD6-09-22-W5QU</t>
+  </si>
+  <si>
+    <t>NFD6-09-22-WXZG</t>
+  </si>
+  <si>
+    <t>NFE6-09-11-X478</t>
+  </si>
+  <si>
+    <t>NFE6-09-17-MHXV</t>
+  </si>
+  <si>
+    <t>NFE6-09-18-GKTZ</t>
+  </si>
+  <si>
+    <t>NFE6-09-18-YWZM</t>
+  </si>
+  <si>
+    <t>NFE6-09-21-KSFP</t>
+  </si>
+  <si>
+    <t>NFE6-09-21-NLHU</t>
+  </si>
+  <si>
+    <t>NFE6-09-21-YZ3J</t>
+  </si>
+  <si>
+    <t>NFE6-09-22-7ZMH</t>
+  </si>
+  <si>
+    <t>NFE6-09-22-BMEX</t>
+  </si>
+  <si>
+    <t>NFE6-09-22-UZC3</t>
+  </si>
+  <si>
+    <t>SA26/H006781</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>SZ-803</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>K-982</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>K-921</t>
+  </si>
+  <si>
+    <t>K-962</t>
+  </si>
+  <si>
+    <t>K-941</t>
+  </si>
+  <si>
+    <t>K-931</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>K-915</t>
+  </si>
+  <si>
+    <t>K-912</t>
+  </si>
+  <si>
+    <t>K-992</t>
+  </si>
+  <si>
+    <t>K-963</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>K-983</t>
+  </si>
+  <si>
+    <t>K-964</t>
+  </si>
+  <si>
+    <t>K-9131</t>
+  </si>
+  <si>
+    <t>SZ-810</t>
+  </si>
+  <si>
+    <t>K-961</t>
+  </si>
+  <si>
+    <t>K-951</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>K-999</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>K-942</t>
+  </si>
+  <si>
+    <t>K-981</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>K-920</t>
+  </si>
+  <si>
+    <t>K-971</t>
+  </si>
+  <si>
+    <t>K-943</t>
+  </si>
+  <si>
+    <t>K-952</t>
+  </si>
+  <si>
+    <t>K-991</t>
+  </si>
+  <si>
+    <t>K-9122</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>K-917</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>SZ-870</t>
+  </si>
+  <si>
+    <t>K-906</t>
+  </si>
+  <si>
+    <t>K-930</t>
+  </si>
+  <si>
+    <t>K-9121</t>
+  </si>
+  <si>
+    <t>K-902</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>SZ-826</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
   </si>
 </sst>
 </file>
@@ -364,9 +1987,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -683,11 +2305,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC11F24F-E222-443E-8401-2ECBA69A40D4}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C323"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -703,755 +2325,3545 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>420</v>
+      </c>
+      <c r="B5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>421</v>
+      </c>
+      <c r="B8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>421</v>
+      </c>
+      <c r="B9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>423</v>
+      </c>
+      <c r="B11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>424</v>
+      </c>
+      <c r="B12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>425</v>
+      </c>
+      <c r="B13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>426</v>
+      </c>
+      <c r="B16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>427</v>
+      </c>
+      <c r="B17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>428</v>
+      </c>
+      <c r="B18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>429</v>
+      </c>
+      <c r="B19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>430</v>
+      </c>
+      <c r="B20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>431</v>
+      </c>
+      <c r="B21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>431</v>
+      </c>
+      <c r="B22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>432</v>
+      </c>
+      <c r="B25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>433</v>
+      </c>
+      <c r="B26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>12</v>
       </c>
-      <c r="C10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>434</v>
+      </c>
+      <c r="B28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>435</v>
+      </c>
+      <c r="B29" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>436</v>
+      </c>
+      <c r="B30" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>437</v>
+      </c>
+      <c r="B31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B32" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>438</v>
+      </c>
+      <c r="B34" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>438</v>
+      </c>
+      <c r="B35" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>439</v>
+      </c>
+      <c r="B36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>440</v>
+      </c>
+      <c r="B37" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>440</v>
+      </c>
+      <c r="B38" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>441</v>
+      </c>
+      <c r="B39" t="s">
+        <v>134</v>
+      </c>
+      <c r="C39" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>442</v>
+      </c>
+      <c r="B40" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>443</v>
+      </c>
+      <c r="B41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>14</v>
       </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B43" t="s">
+        <v>138</v>
+      </c>
+      <c r="C43" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>139</v>
+      </c>
+      <c r="C44" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>444</v>
+      </c>
+      <c r="B45" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B46" t="s">
+        <v>141</v>
+      </c>
+      <c r="C46" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>445</v>
+      </c>
+      <c r="B47" t="s">
+        <v>142</v>
+      </c>
+      <c r="C47" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>446</v>
+      </c>
+      <c r="B48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>447</v>
+      </c>
+      <c r="B49" t="s">
+        <v>144</v>
+      </c>
+      <c r="C49" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>448</v>
+      </c>
+      <c r="B50" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>448</v>
+      </c>
+      <c r="B51" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B52" t="s">
+        <v>147</v>
+      </c>
+      <c r="C52" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>18</v>
       </c>
-      <c r="C16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B53" t="s">
+        <v>148</v>
+      </c>
+      <c r="C53" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>449</v>
+      </c>
+      <c r="B54" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>449</v>
+      </c>
+      <c r="B55" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>450</v>
+      </c>
+      <c r="B56" t="s">
+        <v>151</v>
+      </c>
+      <c r="C56" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>451</v>
+      </c>
+      <c r="B57" t="s">
+        <v>152</v>
+      </c>
+      <c r="C57" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>452</v>
+      </c>
+      <c r="B58" t="s">
+        <v>153</v>
+      </c>
+      <c r="C58" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>453</v>
+      </c>
+      <c r="B59" t="s">
+        <v>154</v>
+      </c>
+      <c r="C59" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>454</v>
+      </c>
+      <c r="B60" t="s">
+        <v>155</v>
+      </c>
+      <c r="C60" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>455</v>
+      </c>
+      <c r="B61" t="s">
+        <v>156</v>
+      </c>
+      <c r="C61" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>456</v>
+      </c>
+      <c r="B62" t="s">
+        <v>157</v>
+      </c>
+      <c r="C62" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>19</v>
       </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B63" t="s">
+        <v>158</v>
+      </c>
+      <c r="C63" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>457</v>
+      </c>
+      <c r="B64" t="s">
+        <v>159</v>
+      </c>
+      <c r="C64" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>458</v>
+      </c>
+      <c r="B65" t="s">
+        <v>160</v>
+      </c>
+      <c r="C65" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>459</v>
+      </c>
+      <c r="B66" t="s">
+        <v>161</v>
+      </c>
+      <c r="C66" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>460</v>
+      </c>
+      <c r="B67" t="s">
+        <v>162</v>
+      </c>
+      <c r="C67" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>461</v>
+      </c>
+      <c r="B68" t="s">
+        <v>163</v>
+      </c>
+      <c r="C68" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>462</v>
+      </c>
+      <c r="B69" t="s">
+        <v>164</v>
+      </c>
+      <c r="C69" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>463</v>
+      </c>
+      <c r="B70" t="s">
+        <v>165</v>
+      </c>
+      <c r="C70" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>463</v>
+      </c>
+      <c r="B71" t="s">
+        <v>166</v>
+      </c>
+      <c r="C71" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>464</v>
+      </c>
+      <c r="B72" t="s">
+        <v>167</v>
+      </c>
+      <c r="C72" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>464</v>
+      </c>
+      <c r="B73" t="s">
+        <v>168</v>
+      </c>
+      <c r="C73" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>20</v>
       </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B74" t="s">
+        <v>169</v>
+      </c>
+      <c r="C74" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>20</v>
+      </c>
+      <c r="B75" t="s">
+        <v>170</v>
+      </c>
+      <c r="C75" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>465</v>
+      </c>
+      <c r="B76" t="s">
+        <v>171</v>
+      </c>
+      <c r="C76" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>466</v>
+      </c>
+      <c r="B77" t="s">
+        <v>172</v>
+      </c>
+      <c r="C77" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>467</v>
+      </c>
+      <c r="B78" t="s">
+        <v>173</v>
+      </c>
+      <c r="C78" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>21</v>
       </c>
-      <c r="C19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B79" t="s">
+        <v>174</v>
+      </c>
+      <c r="C79" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>468</v>
+      </c>
+      <c r="B80" t="s">
+        <v>175</v>
+      </c>
+      <c r="C80" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>22</v>
       </c>
-      <c r="C20" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B81" t="s">
+        <v>176</v>
+      </c>
+      <c r="C81" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>469</v>
+      </c>
+      <c r="B82" t="s">
+        <v>177</v>
+      </c>
+      <c r="C82" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>470</v>
+      </c>
+      <c r="B83" t="s">
+        <v>178</v>
+      </c>
+      <c r="C83" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>471</v>
+      </c>
+      <c r="B84" t="s">
+        <v>179</v>
+      </c>
+      <c r="C84" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>23</v>
       </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B85" t="s">
+        <v>180</v>
+      </c>
+      <c r="C85" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>472</v>
+      </c>
+      <c r="B86" t="s">
+        <v>181</v>
+      </c>
+      <c r="C86" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>24</v>
       </c>
-      <c r="C22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B87" t="s">
+        <v>182</v>
+      </c>
+      <c r="C87" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" t="s">
+        <v>183</v>
+      </c>
+      <c r="C88" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>473</v>
+      </c>
+      <c r="B89" t="s">
+        <v>184</v>
+      </c>
+      <c r="C89" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>25</v>
       </c>
-      <c r="C23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B90" t="s">
+        <v>185</v>
+      </c>
+      <c r="C90" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" t="s">
+        <v>186</v>
+      </c>
+      <c r="C91" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>474</v>
+      </c>
+      <c r="B92" t="s">
+        <v>187</v>
+      </c>
+      <c r="C92" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>475</v>
+      </c>
+      <c r="B93" t="s">
+        <v>188</v>
+      </c>
+      <c r="C93" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B94" t="s">
+        <v>189</v>
+      </c>
+      <c r="C94" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>476</v>
+      </c>
+      <c r="B95" t="s">
+        <v>190</v>
+      </c>
+      <c r="C95" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>477</v>
+      </c>
+      <c r="B96" t="s">
+        <v>191</v>
+      </c>
+      <c r="C96" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>27</v>
       </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="B97" t="s">
+        <v>192</v>
+      </c>
+      <c r="C97" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>478</v>
+      </c>
+      <c r="B98" t="s">
+        <v>193</v>
+      </c>
+      <c r="C98" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>479</v>
+      </c>
+      <c r="B99" t="s">
+        <v>194</v>
+      </c>
+      <c r="C99" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>480</v>
+      </c>
+      <c r="B100" t="s">
+        <v>195</v>
+      </c>
+      <c r="C100" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>481</v>
+      </c>
+      <c r="B101" t="s">
+        <v>196</v>
+      </c>
+      <c r="C101" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>482</v>
+      </c>
+      <c r="B102" t="s">
+        <v>197</v>
+      </c>
+      <c r="C102" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>483</v>
+      </c>
+      <c r="B103" t="s">
+        <v>198</v>
+      </c>
+      <c r="C103" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>483</v>
+      </c>
+      <c r="B104" t="s">
+        <v>199</v>
+      </c>
+      <c r="C104" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>484</v>
+      </c>
+      <c r="B105" t="s">
+        <v>200</v>
+      </c>
+      <c r="C105" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>485</v>
+      </c>
+      <c r="B106" t="s">
+        <v>201</v>
+      </c>
+      <c r="C106" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>486</v>
+      </c>
+      <c r="B107" t="s">
+        <v>202</v>
+      </c>
+      <c r="C107" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>487</v>
+      </c>
+      <c r="B108" t="s">
+        <v>203</v>
+      </c>
+      <c r="C108" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>488</v>
+      </c>
+      <c r="B109" t="s">
+        <v>204</v>
+      </c>
+      <c r="C109" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>28</v>
       </c>
-      <c r="C26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B110" t="s">
+        <v>205</v>
+      </c>
+      <c r="C110" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>28</v>
+      </c>
+      <c r="B111" t="s">
+        <v>206</v>
+      </c>
+      <c r="C111" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>29</v>
       </c>
-      <c r="C27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B112" t="s">
+        <v>207</v>
+      </c>
+      <c r="C112" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>30</v>
       </c>
-      <c r="C28" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B113" t="s">
+        <v>208</v>
+      </c>
+      <c r="C113" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>30</v>
+      </c>
+      <c r="B114" t="s">
+        <v>209</v>
+      </c>
+      <c r="C114" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>31</v>
       </c>
-      <c r="C29" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="B115" t="s">
+        <v>210</v>
+      </c>
+      <c r="C115" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>489</v>
+      </c>
+      <c r="B116" t="s">
+        <v>211</v>
+      </c>
+      <c r="C116" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>489</v>
+      </c>
+      <c r="B117" t="s">
+        <v>212</v>
+      </c>
+      <c r="C117" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>489</v>
+      </c>
+      <c r="B118" t="s">
+        <v>213</v>
+      </c>
+      <c r="C118" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>490</v>
+      </c>
+      <c r="B119" t="s">
+        <v>214</v>
+      </c>
+      <c r="C119" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>490</v>
+      </c>
+      <c r="B120" t="s">
+        <v>215</v>
+      </c>
+      <c r="C120" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>491</v>
+      </c>
+      <c r="B121" t="s">
+        <v>216</v>
+      </c>
+      <c r="C121" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>491</v>
+      </c>
+      <c r="B122" t="s">
+        <v>217</v>
+      </c>
+      <c r="C122" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>32</v>
       </c>
-      <c r="C30" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="B123" t="s">
+        <v>218</v>
+      </c>
+      <c r="C123" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>492</v>
+      </c>
+      <c r="B124" t="s">
+        <v>219</v>
+      </c>
+      <c r="C124" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>493</v>
+      </c>
+      <c r="B125" t="s">
+        <v>220</v>
+      </c>
+      <c r="C125" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>494</v>
+      </c>
+      <c r="B126" t="s">
+        <v>221</v>
+      </c>
+      <c r="C126" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>495</v>
+      </c>
+      <c r="B127" t="s">
+        <v>222</v>
+      </c>
+      <c r="C127" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>496</v>
+      </c>
+      <c r="B128" t="s">
+        <v>223</v>
+      </c>
+      <c r="C128" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>497</v>
+      </c>
+      <c r="B129" t="s">
+        <v>224</v>
+      </c>
+      <c r="C129" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>498</v>
+      </c>
+      <c r="B130" t="s">
+        <v>225</v>
+      </c>
+      <c r="C130" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>499</v>
+      </c>
+      <c r="B131" t="s">
+        <v>226</v>
+      </c>
+      <c r="C131" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>500</v>
+      </c>
+      <c r="B132" t="s">
+        <v>227</v>
+      </c>
+      <c r="C132" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>501</v>
+      </c>
+      <c r="B133" t="s">
+        <v>228</v>
+      </c>
+      <c r="C133" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>33</v>
       </c>
-      <c r="C31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="B134" t="s">
+        <v>229</v>
+      </c>
+      <c r="C134" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>502</v>
+      </c>
+      <c r="B135" t="s">
+        <v>230</v>
+      </c>
+      <c r="C135" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>503</v>
+      </c>
+      <c r="B136" t="s">
+        <v>231</v>
+      </c>
+      <c r="C136" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>504</v>
+      </c>
+      <c r="B137" t="s">
+        <v>232</v>
+      </c>
+      <c r="C137" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>34</v>
       </c>
-      <c r="C32" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="B138" t="s">
+        <v>233</v>
+      </c>
+      <c r="C138" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>34</v>
+      </c>
+      <c r="B139" t="s">
+        <v>234</v>
+      </c>
+      <c r="C139" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>505</v>
+      </c>
+      <c r="B140" t="s">
+        <v>235</v>
+      </c>
+      <c r="C140" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>506</v>
+      </c>
+      <c r="B141" t="s">
+        <v>236</v>
+      </c>
+      <c r="C141" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>507</v>
+      </c>
+      <c r="B142" t="s">
+        <v>237</v>
+      </c>
+      <c r="C142" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>508</v>
+      </c>
+      <c r="B143" t="s">
+        <v>238</v>
+      </c>
+      <c r="C143" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>508</v>
+      </c>
+      <c r="B144" t="s">
+        <v>239</v>
+      </c>
+      <c r="C144" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>35</v>
       </c>
-      <c r="C33" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="B145" t="s">
+        <v>240</v>
+      </c>
+      <c r="C145" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>509</v>
+      </c>
+      <c r="B146" t="s">
+        <v>241</v>
+      </c>
+      <c r="C146" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>510</v>
+      </c>
+      <c r="B147" t="s">
+        <v>242</v>
+      </c>
+      <c r="C147" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>511</v>
+      </c>
+      <c r="B148" t="s">
+        <v>243</v>
+      </c>
+      <c r="C148" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>512</v>
+      </c>
+      <c r="B149" t="s">
+        <v>244</v>
+      </c>
+      <c r="C149" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>513</v>
+      </c>
+      <c r="B150" t="s">
+        <v>245</v>
+      </c>
+      <c r="C150" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>514</v>
+      </c>
+      <c r="B151" t="s">
+        <v>246</v>
+      </c>
+      <c r="C151" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>515</v>
+      </c>
+      <c r="B152" t="s">
+        <v>247</v>
+      </c>
+      <c r="C152" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>516</v>
+      </c>
+      <c r="B153" t="s">
+        <v>248</v>
+      </c>
+      <c r="C153" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>517</v>
+      </c>
+      <c r="B154" t="s">
+        <v>249</v>
+      </c>
+      <c r="C154" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>517</v>
+      </c>
+      <c r="B155" t="s">
+        <v>250</v>
+      </c>
+      <c r="C155" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>518</v>
+      </c>
+      <c r="B156" t="s">
+        <v>251</v>
+      </c>
+      <c r="C156" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>519</v>
+      </c>
+      <c r="B157" t="s">
+        <v>252</v>
+      </c>
+      <c r="C157" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>519</v>
+      </c>
+      <c r="B158" t="s">
+        <v>253</v>
+      </c>
+      <c r="C158" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>520</v>
+      </c>
+      <c r="B159" t="s">
+        <v>254</v>
+      </c>
+      <c r="C159" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>521</v>
+      </c>
+      <c r="B160" t="s">
+        <v>255</v>
+      </c>
+      <c r="C160" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
         <v>36</v>
       </c>
-      <c r="C34" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="B161" t="s">
+        <v>256</v>
+      </c>
+      <c r="C161" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>522</v>
+      </c>
+      <c r="B162" t="s">
+        <v>257</v>
+      </c>
+      <c r="C162" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>523</v>
+      </c>
+      <c r="B163" t="s">
+        <v>258</v>
+      </c>
+      <c r="C163" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>523</v>
+      </c>
+      <c r="B164" t="s">
+        <v>259</v>
+      </c>
+      <c r="C164" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>524</v>
+      </c>
+      <c r="B165" t="s">
+        <v>260</v>
+      </c>
+      <c r="C165" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>525</v>
+      </c>
+      <c r="B166" t="s">
+        <v>261</v>
+      </c>
+      <c r="C166" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>526</v>
+      </c>
+      <c r="B167" t="s">
+        <v>262</v>
+      </c>
+      <c r="C167" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>527</v>
+      </c>
+      <c r="B168" t="s">
+        <v>263</v>
+      </c>
+      <c r="C168" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>528</v>
+      </c>
+      <c r="B169" t="s">
+        <v>264</v>
+      </c>
+      <c r="C169" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>529</v>
+      </c>
+      <c r="B170" t="s">
+        <v>265</v>
+      </c>
+      <c r="C170" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>530</v>
+      </c>
+      <c r="B171" t="s">
+        <v>266</v>
+      </c>
+      <c r="C171" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>531</v>
+      </c>
+      <c r="B172" t="s">
+        <v>267</v>
+      </c>
+      <c r="C172" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>531</v>
+      </c>
+      <c r="B173" t="s">
+        <v>268</v>
+      </c>
+      <c r="C173" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>532</v>
+      </c>
+      <c r="B174" t="s">
+        <v>269</v>
+      </c>
+      <c r="C174" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>533</v>
+      </c>
+      <c r="B175" t="s">
+        <v>270</v>
+      </c>
+      <c r="C175" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>534</v>
+      </c>
+      <c r="B176" t="s">
+        <v>271</v>
+      </c>
+      <c r="C176" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>535</v>
+      </c>
+      <c r="B177" t="s">
+        <v>272</v>
+      </c>
+      <c r="C177" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>536</v>
+      </c>
+      <c r="B178" t="s">
+        <v>273</v>
+      </c>
+      <c r="C178" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>537</v>
+      </c>
+      <c r="B179" t="s">
+        <v>274</v>
+      </c>
+      <c r="C179" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>538</v>
+      </c>
+      <c r="B180" t="s">
+        <v>275</v>
+      </c>
+      <c r="C180" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>539</v>
+      </c>
+      <c r="B181" t="s">
+        <v>276</v>
+      </c>
+      <c r="C181" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>540</v>
+      </c>
+      <c r="B182" t="s">
+        <v>277</v>
+      </c>
+      <c r="C182" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>541</v>
+      </c>
+      <c r="B183" t="s">
+        <v>278</v>
+      </c>
+      <c r="C183" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>542</v>
+      </c>
+      <c r="B184" t="s">
+        <v>279</v>
+      </c>
+      <c r="C184" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
         <v>37</v>
       </c>
-      <c r="C35" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="B185" t="s">
+        <v>280</v>
+      </c>
+      <c r="C185" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>37</v>
+      </c>
+      <c r="B186" t="s">
+        <v>281</v>
+      </c>
+      <c r="C186" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>543</v>
+      </c>
+      <c r="B187" t="s">
+        <v>282</v>
+      </c>
+      <c r="C187" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>543</v>
+      </c>
+      <c r="B188" t="s">
+        <v>283</v>
+      </c>
+      <c r="C188" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
         <v>38</v>
       </c>
-      <c r="C36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="B189" t="s">
+        <v>284</v>
+      </c>
+      <c r="C189" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>38</v>
+      </c>
+      <c r="B190" t="s">
+        <v>285</v>
+      </c>
+      <c r="C190" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
         <v>39</v>
       </c>
-      <c r="C37" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="B191" t="s">
+        <v>286</v>
+      </c>
+      <c r="C191" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>39</v>
+      </c>
+      <c r="B192" t="s">
+        <v>287</v>
+      </c>
+      <c r="C192" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>39</v>
+      </c>
+      <c r="B193" t="s">
+        <v>288</v>
+      </c>
+      <c r="C193" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
         <v>40</v>
       </c>
-      <c r="C38" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="B194" t="s">
+        <v>289</v>
+      </c>
+      <c r="C194" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
         <v>41</v>
       </c>
-      <c r="C39" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="B195" t="s">
+        <v>290</v>
+      </c>
+      <c r="C195" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>41</v>
+      </c>
+      <c r="B196" t="s">
+        <v>291</v>
+      </c>
+      <c r="C196" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
         <v>42</v>
       </c>
-      <c r="C40" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="B197" t="s">
+        <v>292</v>
+      </c>
+      <c r="C197" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
         <v>43</v>
       </c>
-      <c r="C41" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="B198" t="s">
+        <v>293</v>
+      </c>
+      <c r="C198" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>43</v>
+      </c>
+      <c r="B199" t="s">
+        <v>294</v>
+      </c>
+      <c r="C199" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
         <v>44</v>
       </c>
-      <c r="C42" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="B200" t="s">
+        <v>295</v>
+      </c>
+      <c r="C200" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
         <v>45</v>
       </c>
-      <c r="C43" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="B201" t="s">
+        <v>296</v>
+      </c>
+      <c r="C201" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
         <v>4</v>
       </c>
-      <c r="C44" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="B202" t="s">
+        <v>297</v>
+      </c>
+      <c r="C202" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>544</v>
+      </c>
+      <c r="B203" t="s">
+        <v>298</v>
+      </c>
+      <c r="C203" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>544</v>
+      </c>
+      <c r="B204" t="s">
+        <v>299</v>
+      </c>
+      <c r="C204" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="B205" t="s">
+        <v>300</v>
+      </c>
+      <c r="C205" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>46</v>
+      </c>
+      <c r="B206" t="s">
+        <v>301</v>
+      </c>
+      <c r="C206" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>545</v>
+      </c>
+      <c r="B207" t="s">
+        <v>302</v>
+      </c>
+      <c r="C207" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>546</v>
+      </c>
+      <c r="B208" t="s">
+        <v>303</v>
+      </c>
+      <c r="C208" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>547</v>
+      </c>
+      <c r="B209" t="s">
+        <v>304</v>
+      </c>
+      <c r="C209" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="B210" t="s">
+        <v>305</v>
+      </c>
+      <c r="C210" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="B211" t="s">
+        <v>306</v>
+      </c>
+      <c r="C211" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="B212" t="s">
+        <v>307</v>
+      </c>
+      <c r="C212" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="B213" t="s">
+        <v>308</v>
+      </c>
+      <c r="C213" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="B214" t="s">
+        <v>309</v>
+      </c>
+      <c r="C214" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>51</v>
+      </c>
+      <c r="B215" t="s">
+        <v>310</v>
+      </c>
+      <c r="C215" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>51</v>
+      </c>
+      <c r="B216" t="s">
+        <v>311</v>
+      </c>
+      <c r="C216" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="B217" t="s">
+        <v>312</v>
+      </c>
+      <c r="C217" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>548</v>
+      </c>
+      <c r="B218" t="s">
+        <v>313</v>
+      </c>
+      <c r="C218" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>548</v>
+      </c>
+      <c r="B219" t="s">
+        <v>314</v>
+      </c>
+      <c r="C219" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>548</v>
+      </c>
+      <c r="B220" t="s">
+        <v>315</v>
+      </c>
+      <c r="C220" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="B221" t="s">
+        <v>316</v>
+      </c>
+      <c r="C221" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
         <v>54</v>
       </c>
-      <c r="C53" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="B222" t="s">
+        <v>317</v>
+      </c>
+      <c r="C222" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
         <v>55</v>
       </c>
-      <c r="C54" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="B223" t="s">
+        <v>318</v>
+      </c>
+      <c r="C223" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
         <v>56</v>
       </c>
-      <c r="C55" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="B224" t="s">
+        <v>319</v>
+      </c>
+      <c r="C224" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
         <v>57</v>
       </c>
-      <c r="C56" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="B225" t="s">
+        <v>320</v>
+      </c>
+      <c r="C225" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
         <v>58</v>
       </c>
-      <c r="C57" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+      <c r="B226" t="s">
+        <v>321</v>
+      </c>
+      <c r="C226" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
         <v>59</v>
       </c>
-      <c r="C58" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="B227" t="s">
+        <v>322</v>
+      </c>
+      <c r="C227" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>59</v>
+      </c>
+      <c r="B228" t="s">
+        <v>323</v>
+      </c>
+      <c r="C228" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
         <v>60</v>
       </c>
-      <c r="C59" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="B229" t="s">
+        <v>324</v>
+      </c>
+      <c r="C229" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
         <v>61</v>
       </c>
-      <c r="C60" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="B230" t="s">
+        <v>325</v>
+      </c>
+      <c r="C230" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
         <v>62</v>
       </c>
-      <c r="C61" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="B231" t="s">
+        <v>326</v>
+      </c>
+      <c r="C231" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
         <v>63</v>
       </c>
-      <c r="C62" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+      <c r="B232" t="s">
+        <v>327</v>
+      </c>
+      <c r="C232" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
         <v>64</v>
       </c>
-      <c r="C63" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="B233" t="s">
+        <v>328</v>
+      </c>
+      <c r="C233" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
         <v>65</v>
       </c>
-      <c r="C64" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="B234" t="s">
+        <v>329</v>
+      </c>
+      <c r="C234" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
         <v>66</v>
       </c>
-      <c r="C65" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="B235" t="s">
+        <v>330</v>
+      </c>
+      <c r="C235" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>549</v>
+      </c>
+      <c r="B236" t="s">
+        <v>331</v>
+      </c>
+      <c r="C236" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
         <v>67</v>
       </c>
-      <c r="C66" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="B237" t="s">
+        <v>332</v>
+      </c>
+      <c r="C237" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>550</v>
+      </c>
+      <c r="B238" t="s">
+        <v>333</v>
+      </c>
+      <c r="C238" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>550</v>
+      </c>
+      <c r="B239" t="s">
+        <v>334</v>
+      </c>
+      <c r="C239" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
         <v>68</v>
       </c>
-      <c r="C67" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="B240" t="s">
+        <v>335</v>
+      </c>
+      <c r="C240" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
         <v>69</v>
       </c>
-      <c r="C68" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+      <c r="B241" t="s">
+        <v>336</v>
+      </c>
+      <c r="C241" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>551</v>
+      </c>
+      <c r="B242" t="s">
+        <v>337</v>
+      </c>
+      <c r="C242" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
         <v>70</v>
       </c>
-      <c r="C69" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+      <c r="B243" t="s">
+        <v>338</v>
+      </c>
+      <c r="C243" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>552</v>
+      </c>
+      <c r="B244" t="s">
+        <v>339</v>
+      </c>
+      <c r="C244" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>553</v>
+      </c>
+      <c r="B245" t="s">
+        <v>340</v>
+      </c>
+      <c r="C245" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
         <v>71</v>
       </c>
-      <c r="C70" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="B246" t="s">
+        <v>341</v>
+      </c>
+      <c r="C246" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
         <v>72</v>
       </c>
-      <c r="C71" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="B247" t="s">
+        <v>342</v>
+      </c>
+      <c r="C247" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
         <v>73</v>
       </c>
-      <c r="C72" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+      <c r="B248" t="s">
+        <v>343</v>
+      </c>
+      <c r="C248" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
         <v>74</v>
       </c>
-      <c r="C73" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+      <c r="B249" t="s">
+        <v>344</v>
+      </c>
+      <c r="C249" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
         <v>75</v>
       </c>
-      <c r="C74" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="B250" t="s">
+        <v>345</v>
+      </c>
+      <c r="C250" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
         <v>76</v>
       </c>
-      <c r="C75" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="B251" t="s">
+        <v>346</v>
+      </c>
+      <c r="C251" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
         <v>77</v>
       </c>
-      <c r="C76" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+      <c r="B252" t="s">
+        <v>347</v>
+      </c>
+      <c r="C252" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
         <v>78</v>
       </c>
-      <c r="C77" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="B253" t="s">
+        <v>348</v>
+      </c>
+      <c r="C253" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>78</v>
+      </c>
+      <c r="B254" t="s">
+        <v>349</v>
+      </c>
+      <c r="C254" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>78</v>
+      </c>
+      <c r="B255" t="s">
+        <v>350</v>
+      </c>
+      <c r="C255" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
         <v>79</v>
       </c>
-      <c r="C78" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+      <c r="B256" t="s">
+        <v>351</v>
+      </c>
+      <c r="C256" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
         <v>80</v>
       </c>
-      <c r="C79" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+      <c r="B257" t="s">
+        <v>352</v>
+      </c>
+      <c r="C257" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
         <v>81</v>
       </c>
-      <c r="C80" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
+      <c r="B258" t="s">
+        <v>353</v>
+      </c>
+      <c r="C258" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
         <v>82</v>
       </c>
-      <c r="C81" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+      <c r="B259" t="s">
+        <v>354</v>
+      </c>
+      <c r="C259" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
         <v>83</v>
       </c>
-      <c r="C82" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
+      <c r="B260" t="s">
+        <v>355</v>
+      </c>
+      <c r="C260" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>554</v>
+      </c>
+      <c r="B261" t="s">
+        <v>356</v>
+      </c>
+      <c r="C261" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
         <v>84</v>
       </c>
-      <c r="C83" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
+      <c r="B262" t="s">
+        <v>357</v>
+      </c>
+      <c r="C262" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
         <v>85</v>
       </c>
-      <c r="C84" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+      <c r="B263" t="s">
+        <v>358</v>
+      </c>
+      <c r="C263" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>85</v>
+      </c>
+      <c r="B264" t="s">
+        <v>359</v>
+      </c>
+      <c r="C264" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
         <v>86</v>
       </c>
-      <c r="C85" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+      <c r="B265" t="s">
+        <v>360</v>
+      </c>
+      <c r="C265" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
         <v>87</v>
       </c>
-      <c r="C86" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+      <c r="B266" t="s">
+        <v>361</v>
+      </c>
+      <c r="C266" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
         <v>88</v>
       </c>
-      <c r="C87" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
+      <c r="B267" t="s">
+        <v>362</v>
+      </c>
+      <c r="C267" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>88</v>
+      </c>
+      <c r="B268" t="s">
+        <v>363</v>
+      </c>
+      <c r="C268" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>88</v>
+      </c>
+      <c r="B269" t="s">
+        <v>364</v>
+      </c>
+      <c r="C269" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
         <v>89</v>
       </c>
-      <c r="C88" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
+      <c r="B270" t="s">
+        <v>365</v>
+      </c>
+      <c r="C270" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
         <v>90</v>
       </c>
-      <c r="C89" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
+      <c r="B271" t="s">
+        <v>366</v>
+      </c>
+      <c r="C271" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
         <v>91</v>
       </c>
-      <c r="C90" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
+      <c r="B272" t="s">
+        <v>367</v>
+      </c>
+      <c r="C272" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>555</v>
+      </c>
+      <c r="B273" t="s">
+        <v>368</v>
+      </c>
+      <c r="C273" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
         <v>92</v>
       </c>
-      <c r="C91" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
+      <c r="B274" t="s">
+        <v>369</v>
+      </c>
+      <c r="C274" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>556</v>
+      </c>
+      <c r="B275" t="s">
+        <v>370</v>
+      </c>
+      <c r="C275" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>556</v>
+      </c>
+      <c r="B276" t="s">
+        <v>371</v>
+      </c>
+      <c r="C276" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
         <v>93</v>
       </c>
-      <c r="C92" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
+      <c r="B277" t="s">
+        <v>372</v>
+      </c>
+      <c r="C277" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>557</v>
+      </c>
+      <c r="B278" t="s">
+        <v>373</v>
+      </c>
+      <c r="C278" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>558</v>
+      </c>
+      <c r="B279" t="s">
+        <v>374</v>
+      </c>
+      <c r="C279" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
         <v>94</v>
       </c>
-      <c r="C93" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
+      <c r="B280" t="s">
+        <v>375</v>
+      </c>
+      <c r="C280" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
         <v>95</v>
       </c>
-      <c r="C94" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
+      <c r="B281" t="s">
+        <v>376</v>
+      </c>
+      <c r="C281" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>559</v>
+      </c>
+      <c r="B282" t="s">
+        <v>377</v>
+      </c>
+      <c r="C282" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>560</v>
+      </c>
+      <c r="B283" t="s">
+        <v>378</v>
+      </c>
+      <c r="C283" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>560</v>
+      </c>
+      <c r="B284" t="s">
+        <v>379</v>
+      </c>
+      <c r="C284" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>560</v>
+      </c>
+      <c r="B285" t="s">
+        <v>380</v>
+      </c>
+      <c r="C285" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>561</v>
+      </c>
+      <c r="B286" t="s">
+        <v>381</v>
+      </c>
+      <c r="C286" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>562</v>
+      </c>
+      <c r="B287" t="s">
+        <v>382</v>
+      </c>
+      <c r="C287" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>563</v>
+      </c>
+      <c r="B288" t="s">
+        <v>383</v>
+      </c>
+      <c r="C288" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>563</v>
+      </c>
+      <c r="B289" t="s">
+        <v>384</v>
+      </c>
+      <c r="C289" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>564</v>
+      </c>
+      <c r="B290" t="s">
+        <v>385</v>
+      </c>
+      <c r="C290" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>564</v>
+      </c>
+      <c r="B291" t="s">
+        <v>386</v>
+      </c>
+      <c r="C291" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
         <v>96</v>
       </c>
-      <c r="C95" t="s">
-        <v>97</v>
+      <c r="B292" t="s">
+        <v>387</v>
+      </c>
+      <c r="C292" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>565</v>
+      </c>
+      <c r="B293" t="s">
+        <v>388</v>
+      </c>
+      <c r="C293" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>566</v>
+      </c>
+      <c r="B294" t="s">
+        <v>389</v>
+      </c>
+      <c r="C294" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>567</v>
+      </c>
+      <c r="B295" t="s">
+        <v>390</v>
+      </c>
+      <c r="C295" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>568</v>
+      </c>
+      <c r="B296" t="s">
+        <v>391</v>
+      </c>
+      <c r="C296" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>569</v>
+      </c>
+      <c r="B297" t="s">
+        <v>392</v>
+      </c>
+      <c r="C297" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>570</v>
+      </c>
+      <c r="B298" t="s">
+        <v>393</v>
+      </c>
+      <c r="C298" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>570</v>
+      </c>
+      <c r="B299" t="s">
+        <v>394</v>
+      </c>
+      <c r="C299" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>570</v>
+      </c>
+      <c r="B300" t="s">
+        <v>395</v>
+      </c>
+      <c r="C300" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>571</v>
+      </c>
+      <c r="B301" t="s">
+        <v>396</v>
+      </c>
+      <c r="C301" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>572</v>
+      </c>
+      <c r="B302" t="s">
+        <v>397</v>
+      </c>
+      <c r="C302" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>573</v>
+      </c>
+      <c r="B303" t="s">
+        <v>398</v>
+      </c>
+      <c r="C303" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>574</v>
+      </c>
+      <c r="B304" t="s">
+        <v>399</v>
+      </c>
+      <c r="C304" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>575</v>
+      </c>
+      <c r="B305" t="s">
+        <v>400</v>
+      </c>
+      <c r="C305" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>576</v>
+      </c>
+      <c r="B306" t="s">
+        <v>401</v>
+      </c>
+      <c r="C306" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>577</v>
+      </c>
+      <c r="B307" t="s">
+        <v>402</v>
+      </c>
+      <c r="C307" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>578</v>
+      </c>
+      <c r="B308" t="s">
+        <v>403</v>
+      </c>
+      <c r="C308" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>579</v>
+      </c>
+      <c r="B309" t="s">
+        <v>404</v>
+      </c>
+      <c r="C309" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>580</v>
+      </c>
+      <c r="B310" t="s">
+        <v>405</v>
+      </c>
+      <c r="C310" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>581</v>
+      </c>
+      <c r="B311" t="s">
+        <v>406</v>
+      </c>
+      <c r="C311" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>582</v>
+      </c>
+      <c r="B312" t="s">
+        <v>407</v>
+      </c>
+      <c r="C312" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>583</v>
+      </c>
+      <c r="B313" t="s">
+        <v>408</v>
+      </c>
+      <c r="C313" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>583</v>
+      </c>
+      <c r="B314" t="s">
+        <v>409</v>
+      </c>
+      <c r="C314" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>584</v>
+      </c>
+      <c r="B315" t="s">
+        <v>410</v>
+      </c>
+      <c r="C315" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>585</v>
+      </c>
+      <c r="B316" t="s">
+        <v>411</v>
+      </c>
+      <c r="C316" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>586</v>
+      </c>
+      <c r="B317" t="s">
+        <v>412</v>
+      </c>
+      <c r="C317" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>587</v>
+      </c>
+      <c r="B318" t="s">
+        <v>413</v>
+      </c>
+      <c r="C318" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>588</v>
+      </c>
+      <c r="B319" t="s">
+        <v>414</v>
+      </c>
+      <c r="C319" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>589</v>
+      </c>
+      <c r="B320" t="s">
+        <v>415</v>
+      </c>
+      <c r="C320" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>590</v>
+      </c>
+      <c r="B321" t="s">
+        <v>416</v>
+      </c>
+      <c r="C321" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>591</v>
+      </c>
+      <c r="B322" t="s">
+        <v>417</v>
+      </c>
+      <c r="C322" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>592</v>
+      </c>
+      <c r="B323" t="s">
+        <v>418</v>
+      </c>
+      <c r="C323" t="s">
+        <v>632</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87E1A4C-F71D-44AA-831E-9A8D31037D4C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4058C9AF-E103-4C07-B956-A27BEDE3E3CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="718">
   <si>
     <t>UTK</t>
   </si>
@@ -279,7 +279,1909 @@
     <t>99003323</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>1340846706KR/1</t>
+  </si>
+  <si>
+    <t>1340846706KR/2</t>
+  </si>
+  <si>
+    <t>1340846706KR/3</t>
+  </si>
+  <si>
+    <t>1340846706KR/4</t>
+  </si>
+  <si>
+    <t>1340846769KR/1</t>
+  </si>
+  <si>
+    <t>159995579544390211</t>
+  </si>
+  <si>
+    <t>159995579544390228</t>
+  </si>
+  <si>
+    <t>159995579544390235</t>
+  </si>
+  <si>
+    <t>159995579544529444</t>
+  </si>
+  <si>
+    <t>159995579544529451</t>
+  </si>
+  <si>
+    <t>248747288/1</t>
+  </si>
+  <si>
+    <t>248747313/2/1</t>
+  </si>
+  <si>
+    <t>248747313/2/2</t>
+  </si>
+  <si>
+    <t>6aac1aeef7fbdc73ea0a9d98</t>
+  </si>
+  <si>
+    <t>6aaec38b73749ba5fc079e72</t>
+  </si>
+  <si>
+    <t>6ab28b2773749ba5fc07ddd8</t>
+  </si>
+  <si>
+    <t>6ab28b2773749ba5fc07ddd9</t>
+  </si>
+  <si>
+    <t>6ab4ccba219e3d74bbe3ba10</t>
+  </si>
+  <si>
+    <t>6aad27b973749ba5fc07858a</t>
+  </si>
+  <si>
+    <t>6aafdc0a73749ba5fc07a5b6</t>
+  </si>
+  <si>
+    <t>6a992210c0fa1536b26fbea2</t>
+  </si>
+  <si>
+    <t>6a992210c0fa1536b26fbea5</t>
+  </si>
+  <si>
+    <t>6ab2822273749ba5fc07dc03</t>
+  </si>
+  <si>
+    <t>6ab2822273749ba5fc07dc04</t>
+  </si>
+  <si>
+    <t>6ab3d10a219e3d74bbe3aec8</t>
+  </si>
+  <si>
+    <t>6ab3bd46219e3d74bbe3ab38</t>
+  </si>
+  <si>
+    <t>6aaa91a3f7fbdc73ea0a7cff</t>
+  </si>
+  <si>
+    <t>6aac1506f7fbdc73ea0a9d21</t>
+  </si>
+  <si>
+    <t>6ab2742a73749ba5fc07d9b2</t>
+  </si>
+  <si>
+    <t>6ab26cd173749ba5fc07d837</t>
+  </si>
+  <si>
+    <t>6ab26cd173749ba5fc07d838</t>
+  </si>
+  <si>
+    <t>6ab3a75e219e3d74bbe3a76a</t>
+  </si>
+  <si>
+    <t>6ab3afc3219e3d74bbe3a8cd</t>
+  </si>
+  <si>
+    <t>6ab27e9f73749ba5fc07db45</t>
+  </si>
+  <si>
+    <t>6ab27e9f73749ba5fc07db46</t>
+  </si>
+  <si>
+    <t>6ab4e4ad219e3d74bbe3be3e</t>
+  </si>
+  <si>
+    <t>6aa412d82235a0231b9b51c9</t>
+  </si>
+  <si>
+    <t>6ab3b1ed219e3d74bbe3a942</t>
+  </si>
+  <si>
+    <t>6ab3e4b3219e3d74bbe3b23d</t>
+  </si>
+  <si>
+    <t>6ab501f2219e3d74bbe3c285</t>
+  </si>
+  <si>
+    <t>6ab0e82573749ba5fc07afcb</t>
+  </si>
+  <si>
+    <t>6ab385e5219e3d74bbe3a0d0</t>
+  </si>
+  <si>
+    <t>6ab3c971219e3d74bbe3ad4c</t>
+  </si>
+  <si>
+    <t>6ab3e8c9219e3d74bbe3b2ff</t>
+  </si>
+  <si>
+    <t>6ab2682c73749ba5fc07d754</t>
+  </si>
+  <si>
+    <t>6aa93a66f7fbdc73ea0a6052</t>
+  </si>
+  <si>
+    <t>6aa93a66f7fbdc73ea0a6054</t>
+  </si>
+  <si>
+    <t>6ab0dec573749ba5fc07ad65</t>
+  </si>
+  <si>
+    <t>6ab387d1219e3d74bbe3a14e</t>
+  </si>
+  <si>
+    <t>6ab3ae28219e3d74bbe3a899</t>
+  </si>
+  <si>
+    <t>6aaaa016f7fbdc73ea0a7fa2</t>
+  </si>
+  <si>
+    <t>6aaaa0faf7fbdc73ea0a7fba</t>
+  </si>
+  <si>
+    <t>6aaaa0faf7fbdc73ea0a7fbb</t>
+  </si>
+  <si>
+    <t>6aaa69e1f7fbdc73ea0a7634</t>
+  </si>
+  <si>
+    <t>6aaa69e1f7fbdc73ea0a7635</t>
+  </si>
+  <si>
+    <t>6aaa9671f7fbdc73ea0a7e01</t>
+  </si>
+  <si>
+    <t>6aaa9671f7fbdc73ea0a7e02</t>
+  </si>
+  <si>
+    <t>6aaaa35ef7fbdc73ea0a8031</t>
+  </si>
+  <si>
+    <t>6ab4f9c4219e3d74bbe3c15c</t>
+  </si>
+  <si>
+    <t>6ab3c4a9219e3d74bbe3ac84</t>
+  </si>
+  <si>
+    <t>6ab3d680219e3d74bbe3afc3</t>
+  </si>
+  <si>
+    <t>6ab2719773749ba5fc07d93e</t>
+  </si>
+  <si>
+    <t>6aab9ce6f7fbdc73ea0a8a6c</t>
+  </si>
+  <si>
+    <t>6aabe0eaf7fbdc73ea0a95d0</t>
+  </si>
+  <si>
+    <t>6ab4e50f219e3d74bbe3be44</t>
+  </si>
+  <si>
+    <t>6aabf315f7fbdc73ea0a992d</t>
+  </si>
+  <si>
+    <t>6aabf315f7fbdc73ea0a992e</t>
+  </si>
+  <si>
+    <t>6aacf0bbf7fbdc73ea0aa878</t>
+  </si>
+  <si>
+    <t>6ab28f0b73749ba5fc07de6f</t>
+  </si>
+  <si>
+    <t>6ab4de42219e3d74bbe3bcdf</t>
+  </si>
+  <si>
+    <t>6aafd4b273749ba5fc07a535</t>
+  </si>
+  <si>
+    <t>6ab290e573749ba5fc07dea8</t>
+  </si>
+  <si>
+    <t>6ab3f6f7219e3d74bbe3b4cc</t>
+  </si>
+  <si>
+    <t>6aad627673749ba5fc078e76</t>
+  </si>
+  <si>
+    <t>6aae368773749ba5fc079256</t>
+  </si>
+  <si>
+    <t>6ab3dc24219e3d74bbe3b0e7</t>
+  </si>
+  <si>
+    <t>6aae83e573749ba5fc079aa0</t>
+  </si>
+  <si>
+    <t>6aae411773749ba5fc07938c</t>
+  </si>
+  <si>
+    <t>6aae945473749ba5fc079bc7</t>
+  </si>
+  <si>
+    <t>6aaea4ad73749ba5fc079cd1</t>
+  </si>
+  <si>
+    <t>6aaed5e673749ba5fc079f10</t>
+  </si>
+  <si>
+    <t>6aafc3ce73749ba5fc07a3fa</t>
+  </si>
+  <si>
+    <t>6aafd0b573749ba5fc07a4f5</t>
+  </si>
+  <si>
+    <t>6aaff3d673749ba5fc07a746</t>
+  </si>
+  <si>
+    <t>6ab3beee219e3d74bbe3ab68</t>
+  </si>
+  <si>
+    <t>6ab3cbd2219e3d74bbe3adb6</t>
+  </si>
+  <si>
+    <t>6ab122fa73749ba5fc07bc82</t>
+  </si>
+  <si>
+    <t>6ab12f1b73749ba5fc07be98</t>
+  </si>
+  <si>
+    <t>6ab12f1b73749ba5fc07be9a</t>
+  </si>
+  <si>
+    <t>6ab4e24b219e3d74bbe3bda4</t>
+  </si>
+  <si>
+    <t>6ab1581f73749ba5fc07c530</t>
+  </si>
+  <si>
+    <t>6ab15f2473749ba5fc07c5cc</t>
+  </si>
+  <si>
+    <t>6ab15f2473749ba5fc07c5cd</t>
+  </si>
+  <si>
+    <t>6ab17d9573749ba5fc07c7d0</t>
+  </si>
+  <si>
+    <t>6ab0e41d73749ba5fc07aec6</t>
+  </si>
+  <si>
+    <t>6ab0e41d73749ba5fc07aec7</t>
+  </si>
+  <si>
+    <t>6ab3bce4219e3d74bbe3ab15</t>
+  </si>
+  <si>
+    <t>6ab1028d73749ba5fc07b5f2</t>
+  </si>
+  <si>
+    <t>6ab12a6d73749ba5fc07bda6</t>
+  </si>
+  <si>
+    <t>6ab12a6d73749ba5fc07bda7</t>
+  </si>
+  <si>
+    <t>6ab126e973749ba5fc07bd22</t>
+  </si>
+  <si>
+    <t>6ab12f1c73749ba5fc07beab</t>
+  </si>
+  <si>
+    <t>6ab12f1c73749ba5fc07beac</t>
+  </si>
+  <si>
+    <t>6ab12f3b73749ba5fc07becc</t>
+  </si>
+  <si>
+    <t>6ab13c0273749ba5fc07c106</t>
+  </si>
+  <si>
+    <t>6ab3d796219e3d74bbe3b013</t>
+  </si>
+  <si>
+    <t>6ab14c8373749ba5fc07c3ce</t>
+  </si>
+  <si>
+    <t>6ab2253873749ba5fc07c9d9</t>
+  </si>
+  <si>
+    <t>6ab25c5973749ba5fc07d504</t>
+  </si>
+  <si>
+    <t>6ab4f703219e3d74bbe3c0e9</t>
+  </si>
+  <si>
+    <t>6ab27abc73749ba5fc07da8f</t>
+  </si>
+  <si>
+    <t>6ab27abc73749ba5fc07da90</t>
+  </si>
+  <si>
+    <t>6ab27abb73749ba5fc07da83</t>
+  </si>
+  <si>
+    <t>6ab50530219e3d74bbe3c329</t>
+  </si>
+  <si>
+    <t>6ab2841d73749ba5fc07dc8b</t>
+  </si>
+  <si>
+    <t>6ab2910373749ba5fc07dec2</t>
+  </si>
+  <si>
+    <t>6ab28d9273749ba5fc07de3d</t>
+  </si>
+  <si>
+    <t>6ab295d773749ba5fc07df83</t>
+  </si>
+  <si>
+    <t>6ab3a524219e3d74bbe3a6e4</t>
+  </si>
+  <si>
+    <t>6ab2a64673749ba5fc07e146</t>
+  </si>
+  <si>
+    <t>6ab2a64673749ba5fc07e148</t>
+  </si>
+  <si>
+    <t>6ab2ae4d73749ba5fc07e222</t>
+  </si>
+  <si>
+    <t>6ab2ca6673749ba5fc07e405</t>
+  </si>
+  <si>
+    <t>6ab21bd773749ba5fc07c92e</t>
+  </si>
+  <si>
+    <t>6ab21bc873749ba5fc07c923</t>
+  </si>
+  <si>
+    <t>6ab25fd573749ba5fc07d58d</t>
+  </si>
+  <si>
+    <t>6ab25fd573749ba5fc07d58e</t>
+  </si>
+  <si>
+    <t>6ab24ab873749ba5fc07d197</t>
+  </si>
+  <si>
+    <t>6ab24ab873749ba5fc07d198</t>
+  </si>
+  <si>
+    <t>6ab2703c73749ba5fc07d8f2</t>
+  </si>
+  <si>
+    <t>6ab2715e73749ba5fc07d912</t>
+  </si>
+  <si>
+    <t>6ab287be73749ba5fc07dd2c</t>
+  </si>
+  <si>
+    <t>6ab288d573749ba5fc07dd71</t>
+  </si>
+  <si>
+    <t>6ab28b8173749ba5fc07dde3</t>
+  </si>
+  <si>
+    <t>6ab28eaf73749ba5fc07de64</t>
+  </si>
+  <si>
+    <t>6ab28eaf73749ba5fc07de65</t>
+  </si>
+  <si>
+    <t>6ab2935873749ba5fc07df10</t>
+  </si>
+  <si>
+    <t>6ab2986e73749ba5fc07dfcd</t>
+  </si>
+  <si>
+    <t>6ab2986e73749ba5fc07dfce</t>
+  </si>
+  <si>
+    <t>6ab2a61773749ba5fc07e135</t>
+  </si>
+  <si>
+    <t>6ab2a61773749ba5fc07e136</t>
+  </si>
+  <si>
+    <t>6ab2a86f73749ba5fc07e176</t>
+  </si>
+  <si>
+    <t>6ab2ad1b73749ba5fc07e1e8</t>
+  </si>
+  <si>
+    <t>6ab2b7b373749ba5fc07e306</t>
+  </si>
+  <si>
+    <t>6ab2b68473749ba5fc07e2d5</t>
+  </si>
+  <si>
+    <t>6ab2eb3a73749ba5fc07e4c2</t>
+  </si>
+  <si>
+    <t>6ab370cf219e3d74bbe39d4d</t>
+  </si>
+  <si>
+    <t>6ab3800f219e3d74bbe39f61</t>
+  </si>
+  <si>
+    <t>6ab3800f219e3d74bbe39f63</t>
+  </si>
+  <si>
+    <t>6ab37db6219e3d74bbe39ed9</t>
+  </si>
+  <si>
+    <t>6ab37db6219e3d74bbe39edb</t>
+  </si>
+  <si>
+    <t>6ab38266219e3d74bbe39ff9</t>
+  </si>
+  <si>
+    <t>6ab38266219e3d74bbe39ffc</t>
+  </si>
+  <si>
+    <t>6ab3871a219e3d74bbe3a116</t>
+  </si>
+  <si>
+    <t>6ab38ae3219e3d74bbe3a1d3</t>
+  </si>
+  <si>
+    <t>6ab38ae3219e3d74bbe3a1d5</t>
+  </si>
+  <si>
+    <t>6ab4b206219e3d74bbe3b8e5</t>
+  </si>
+  <si>
+    <t>6ab393fc219e3d74bbe3a3b1</t>
+  </si>
+  <si>
+    <t>6ab39653219e3d74bbe3a403</t>
+  </si>
+  <si>
+    <t>6ab39652219e3d74bbe3a3fd</t>
+  </si>
+  <si>
+    <t>6ab39b0d219e3d74bbe3a4ed</t>
+  </si>
+  <si>
+    <t>6ab39b0d219e3d74bbe3a4ef</t>
+  </si>
+  <si>
+    <t>6ab3b65b219e3d74bbe3aa0f</t>
+  </si>
+  <si>
+    <t>6ab3a100219e3d74bbe3a629</t>
+  </si>
+  <si>
+    <t>6ab3b4c4219e3d74bbe3a9c8</t>
+  </si>
+  <si>
+    <t>6ab3b5f5219e3d74bbe3a9eb</t>
+  </si>
+  <si>
+    <t>6ab3baa4219e3d74bbe3aab4</t>
+  </si>
+  <si>
+    <t>6ab3baa4219e3d74bbe3aab5</t>
+  </si>
+  <si>
+    <t>6ab3bf53219e3d74bbe3ab72</t>
+  </si>
+  <si>
+    <t>6ab3bf53219e3d74bbe3ab73</t>
+  </si>
+  <si>
+    <t>6ab3c2dd219e3d74bbe3ac20</t>
+  </si>
+  <si>
+    <t>6ab3cd78219e3d74bbe3ae13</t>
+  </si>
+  <si>
+    <t>6ab3cd78219e3d74bbe3ae16</t>
+  </si>
+  <si>
+    <t>6ab3d6d4219e3d74bbe3affb</t>
+  </si>
+  <si>
+    <t>6ab3ed03219e3d74bbe3b391</t>
+  </si>
+  <si>
+    <t>6ab3f2e4219e3d74bbe3b44c</t>
+  </si>
+  <si>
+    <t>6ab3f415219e3d74bbe3b461</t>
+  </si>
+  <si>
+    <t>6ab3f415219e3d74bbe3b463</t>
+  </si>
+  <si>
+    <t>6ab3f8c3219e3d74bbe3b4f2</t>
+  </si>
+  <si>
+    <t>6ab405a1219e3d74bbe3b638</t>
+  </si>
+  <si>
+    <t>6ab41866219e3d74bbe3b75c</t>
+  </si>
+  <si>
+    <t>6ab41866219e3d74bbe3b75f</t>
+  </si>
+  <si>
+    <t>6ab40f08219e3d74bbe3b6da</t>
+  </si>
+  <si>
+    <t>6ab40f08219e3d74bbe3b6db</t>
+  </si>
+  <si>
+    <t>6ab370cf219e3d74bbe39d57</t>
+  </si>
+  <si>
+    <t>6ab37eef219e3d74bbe39f42</t>
+  </si>
+  <si>
+    <t>6ab37eef219e3d74bbe39f44</t>
+  </si>
+  <si>
+    <t>6ab38a9d219e3d74bbe3a1ac</t>
+  </si>
+  <si>
+    <t>6ab38d01219e3d74bbe3a255</t>
+  </si>
+  <si>
+    <t>6ab38cf4219e3d74bbe3a228</t>
+  </si>
+  <si>
+    <t>6ab38cf4219e3d74bbe3a229</t>
+  </si>
+  <si>
+    <t>6ab39538219e3d74bbe3a3ec</t>
+  </si>
+  <si>
+    <t>6ab3ab66219e3d74bbe3a7fd</t>
+  </si>
+  <si>
+    <t>6ab3aeef219e3d74bbe3a8ae</t>
+  </si>
+  <si>
+    <t>6ab3b02c219e3d74bbe3a903</t>
+  </si>
+  <si>
+    <t>6ab3b02c219e3d74bbe3a904</t>
+  </si>
+  <si>
+    <t>6ab3b02c219e3d74bbe3a906</t>
+  </si>
+  <si>
+    <t>6ab3b153219e3d74bbe3a93e</t>
+  </si>
+  <si>
+    <t>6ab3b153219e3d74bbe3a93f</t>
+  </si>
+  <si>
+    <t>6ab3b4c5219e3d74bbe3a9d8</t>
+  </si>
+  <si>
+    <t>6ab3b973219e3d74bbe3aa6f</t>
+  </si>
+  <si>
+    <t>6ab3c78a219e3d74bbe3ace6</t>
+  </si>
+  <si>
+    <t>6ab3c2dc219e3d74bbe3ac14</t>
+  </si>
+  <si>
+    <t>6ab3c9e3219e3d74bbe3ad5f</t>
+  </si>
+  <si>
+    <t>6ab3d211219e3d74bbe3aee8</t>
+  </si>
+  <si>
+    <t>6ab3d0ea219e3d74bbe3aec0</t>
+  </si>
+  <si>
+    <t>6ab3db83219e3d74bbe3b0dd</t>
+  </si>
+  <si>
+    <t>6ab3dc9e219e3d74bbe3b0f8</t>
+  </si>
+  <si>
+    <t>6ab3dc9e219e3d74bbe3b0fa</t>
+  </si>
+  <si>
+    <t>6ab3e61a219e3d74bbe3b290</t>
+  </si>
+  <si>
+    <t>6ab3eaaf219e3d74bbe3b340</t>
+  </si>
+  <si>
+    <t>6ab3f1bd219e3d74bbe3b42e</t>
+  </si>
+  <si>
+    <t>6ab3f1bd219e3d74bbe3b426</t>
+  </si>
+  <si>
+    <t>6ab40348219e3d74bbe3b5fc</t>
+  </si>
+  <si>
+    <t>6ab40b7f219e3d74bbe3b68f</t>
+  </si>
+  <si>
+    <t>6ab412ba219e3d74bbe3b717</t>
+  </si>
+  <si>
+    <t>6ab419d8219e3d74bbe3b770</t>
+  </si>
+  <si>
+    <t>6ab42093219e3d74bbe3b7a0</t>
+  </si>
+  <si>
+    <t>6ab42eaa219e3d74bbe3b820</t>
+  </si>
+  <si>
+    <t>6ab43b86219e3d74bbe3b854</t>
+  </si>
+  <si>
+    <t>6ab44036219e3d74bbe3b863</t>
+  </si>
+  <si>
+    <t>6ab4d3e7219e3d74bbe3bb04</t>
+  </si>
+  <si>
+    <t>6ab4dfc3219e3d74bbe3bd47</t>
+  </si>
+  <si>
+    <t>6ab4e1ff219e3d74bbe3bd7a</t>
+  </si>
+  <si>
+    <t>6ab4f136219e3d74bbe3c068</t>
+  </si>
+  <si>
+    <t>6ab4ffd8219e3d74bbe3c234</t>
+  </si>
+  <si>
+    <t>6ab4fcf5219e3d74bbe3c1d5</t>
+  </si>
+  <si>
+    <t>6ab50081219e3d74bbe3c257</t>
+  </si>
+  <si>
+    <t>6ab4fe1a219e3d74bbe3c1f8</t>
+  </si>
+  <si>
+    <t>6ab4c378219e3d74bbe3b957</t>
+  </si>
+  <si>
+    <t>6ab4d647219e3d74bbe3bb56</t>
+  </si>
+  <si>
+    <t>6ab4d647219e3d74bbe3bb57</t>
+  </si>
+  <si>
+    <t>6ab4de84219e3d74bbe3bd07</t>
+  </si>
+  <si>
+    <t>6ab4e451219e3d74bbe3be2f</t>
+  </si>
+  <si>
+    <t>6ab4f006219e3d74bbe3c03c</t>
+  </si>
+  <si>
+    <t>6ab4ff41219e3d74bbe3c22a</t>
+  </si>
+  <si>
+    <t>6ab4ff41219e3d74bbe3c22b</t>
+  </si>
+  <si>
+    <t>6ab502c9219e3d74bbe3c29b</t>
+  </si>
+  <si>
+    <t>1449-473329</t>
+  </si>
+  <si>
+    <t>1449-301261/1</t>
+  </si>
+  <si>
+    <t>1449-301261/2</t>
+  </si>
+  <si>
+    <t>1449-471396</t>
+  </si>
+  <si>
+    <t>1449-660394</t>
+  </si>
+  <si>
+    <t>1449-676787</t>
+  </si>
+  <si>
+    <t>1449-848315</t>
+  </si>
+  <si>
+    <t>1449-378449</t>
+  </si>
+  <si>
+    <t>1449-934504</t>
+  </si>
+  <si>
+    <t>26MPE0010117/1</t>
+  </si>
+  <si>
+    <t>26MPE0010121/1</t>
+  </si>
+  <si>
+    <t>26MPE0010184/1</t>
+  </si>
+  <si>
+    <t>26MPE0010241/1</t>
+  </si>
+  <si>
+    <t>323852992/1</t>
+  </si>
+  <si>
+    <t>327990077/1</t>
+  </si>
+  <si>
+    <t>328281329/1</t>
+  </si>
+  <si>
+    <t>328644736/1</t>
+  </si>
+  <si>
+    <t>328701311/1</t>
+  </si>
+  <si>
+    <t>328701614/1</t>
+  </si>
+  <si>
+    <t>328893014/1</t>
+  </si>
+  <si>
+    <t>329204789/1</t>
+  </si>
+  <si>
+    <t>329204811/1</t>
+  </si>
+  <si>
+    <t>329205046/1</t>
+  </si>
+  <si>
+    <t>329205339/1</t>
+  </si>
+  <si>
+    <t>329320691/1</t>
+  </si>
+  <si>
+    <t>329320864/1</t>
+  </si>
+  <si>
+    <t>329320864/2</t>
+  </si>
+  <si>
+    <t>329320864/3</t>
+  </si>
+  <si>
+    <t>329375914/1</t>
+  </si>
+  <si>
+    <t>329431052/1</t>
+  </si>
+  <si>
+    <t>329431052/2</t>
+  </si>
+  <si>
+    <t>329431545/1</t>
+  </si>
+  <si>
+    <t>329431545/2</t>
+  </si>
+  <si>
+    <t>329484176/1</t>
+  </si>
+  <si>
+    <t>329484176/2</t>
+  </si>
+  <si>
+    <t>329484599/1</t>
+  </si>
+  <si>
+    <t>329484786/1</t>
+  </si>
+  <si>
+    <t>329484786/2</t>
+  </si>
+  <si>
+    <t>329535606/1</t>
+  </si>
+  <si>
+    <t>329535606/2</t>
+  </si>
+  <si>
+    <t>329535894/1</t>
+  </si>
+  <si>
+    <t>329536243/1</t>
+  </si>
+  <si>
+    <t>329536361/1</t>
+  </si>
+  <si>
+    <t>329583716/1</t>
+  </si>
+  <si>
+    <t>329583910/1</t>
+  </si>
+  <si>
+    <t>329584223/1</t>
+  </si>
+  <si>
+    <t>329584422/1</t>
+  </si>
+  <si>
+    <t>329584422/2</t>
+  </si>
+  <si>
+    <t>329584503/1</t>
+  </si>
+  <si>
+    <t>329584580/1</t>
+  </si>
+  <si>
+    <t>329584633/1</t>
+  </si>
+  <si>
+    <t>329584633/2</t>
+  </si>
+  <si>
+    <t>329584633/3</t>
+  </si>
+  <si>
+    <t>329584675/1</t>
+  </si>
+  <si>
+    <t>329633631/1</t>
+  </si>
+  <si>
+    <t>329633782/1</t>
+  </si>
+  <si>
+    <t>329633793/1</t>
+  </si>
+  <si>
+    <t>329633818/1</t>
+  </si>
+  <si>
+    <t>329633818/2</t>
+  </si>
+  <si>
+    <t>329634044/1</t>
+  </si>
+  <si>
+    <t>329634044/2</t>
+  </si>
+  <si>
+    <t>329634419/1</t>
+  </si>
+  <si>
+    <t>329634593/1</t>
+  </si>
+  <si>
+    <t>329689509/1</t>
+  </si>
+  <si>
+    <t>329689565/1</t>
+  </si>
+  <si>
+    <t>329689638/1</t>
+  </si>
+  <si>
+    <t>329689704/1</t>
+  </si>
+  <si>
+    <t>329689763/1</t>
+  </si>
+  <si>
+    <t>329690037/1</t>
+  </si>
+  <si>
+    <t>329690037/2</t>
+  </si>
+  <si>
+    <t>329690137/1</t>
+  </si>
+  <si>
+    <t>329690316/1</t>
+  </si>
+  <si>
+    <t>329690374/1</t>
+  </si>
+  <si>
+    <t>329738333/1</t>
+  </si>
+  <si>
+    <t>329738420/1</t>
+  </si>
+  <si>
+    <t>329738564/1</t>
+  </si>
+  <si>
+    <t>329738564/2</t>
+  </si>
+  <si>
+    <t>329738673/1</t>
+  </si>
+  <si>
+    <t>329738673/2</t>
+  </si>
+  <si>
+    <t>329738753/1</t>
+  </si>
+  <si>
+    <t>329738846/1</t>
+  </si>
+  <si>
+    <t>329738862/1</t>
+  </si>
+  <si>
+    <t>329738905/1</t>
+  </si>
+  <si>
+    <t>329739012/1</t>
+  </si>
+  <si>
+    <t>329739065/1</t>
+  </si>
+  <si>
+    <t>329788078/1</t>
+  </si>
+  <si>
+    <t>329788119/1</t>
+  </si>
+  <si>
+    <t>329788171/1</t>
+  </si>
+  <si>
+    <t>329788239/1</t>
+  </si>
+  <si>
+    <t>329788318/1</t>
+  </si>
+  <si>
+    <t>329788904/1</t>
+  </si>
+  <si>
+    <t>329841385/1</t>
+  </si>
+  <si>
+    <t>329892099/1</t>
+  </si>
+  <si>
+    <t>329892253/1</t>
+  </si>
+  <si>
+    <t>329892300/1</t>
+  </si>
+  <si>
+    <t>329892300/2</t>
+  </si>
+  <si>
+    <t>51340048124KR/1</t>
+  </si>
+  <si>
+    <t>99003323/1</t>
+  </si>
+  <si>
+    <t>159995579544465759</t>
+  </si>
+  <si>
+    <t>159995579544464981</t>
+  </si>
+  <si>
+    <t>159995579544466442</t>
+  </si>
+  <si>
+    <t>202609242601951601</t>
+  </si>
+  <si>
+    <t>202609162601946601</t>
+  </si>
+  <si>
+    <t>202609242601959901</t>
+  </si>
+  <si>
+    <t>202609222601981001</t>
+  </si>
+  <si>
+    <t>202609232601984901</t>
+  </si>
+  <si>
+    <t>202609232601986701</t>
+  </si>
+  <si>
+    <t>202609232601987901</t>
+  </si>
+  <si>
+    <t>202609242601989401</t>
+  </si>
+  <si>
+    <t>202609242601992101</t>
+  </si>
+  <si>
+    <t>202609242601991001</t>
+  </si>
+  <si>
+    <t>202609242601990001</t>
+  </si>
+  <si>
+    <t>202609242601990901</t>
+  </si>
+  <si>
+    <t>202609252601993601</t>
+  </si>
+  <si>
+    <t>202609252601995701</t>
+  </si>
+  <si>
+    <t>202609242601958401</t>
+  </si>
+  <si>
+    <t>202609182601958501</t>
+  </si>
+  <si>
+    <t>202609212601964301</t>
+  </si>
+  <si>
+    <t>202609232601988201</t>
+  </si>
+  <si>
+    <t>202609242601992801</t>
+  </si>
+  <si>
+    <t>202609252601996401</t>
+  </si>
+  <si>
+    <t>159995579544494919</t>
+  </si>
+  <si>
+    <t>159995579544494926</t>
+  </si>
+  <si>
+    <t>159995579544494933</t>
+  </si>
+  <si>
+    <t>159995579544433376</t>
+  </si>
+  <si>
+    <t>159995579544433437</t>
+  </si>
+  <si>
+    <t>159995579544433444</t>
+  </si>
+  <si>
+    <t>159995579544459376</t>
+  </si>
+  <si>
+    <t>159995579544462376</t>
+  </si>
+  <si>
+    <t>1340846706KR</t>
+  </si>
+  <si>
+    <t>1340846769KR</t>
+  </si>
+  <si>
+    <t>2026/12888</t>
+  </si>
+  <si>
+    <t>2026/13065</t>
+  </si>
+  <si>
+    <t>248747313/2</t>
+  </si>
+  <si>
+    <t>260819-W00005955</t>
+  </si>
+  <si>
+    <t>260825-F00007441</t>
+  </si>
+  <si>
+    <t>260827-W00004104</t>
+  </si>
+  <si>
+    <t>260901-F00011496</t>
+  </si>
+  <si>
+    <t>260901-F00015399-4</t>
+  </si>
+  <si>
+    <t>260903-F00001523</t>
+  </si>
+  <si>
+    <t>260905-F00005181</t>
+  </si>
+  <si>
+    <t>260908-F00002235</t>
+  </si>
+  <si>
+    <t>260908-F00015662-1</t>
+  </si>
+  <si>
+    <t>260910-W00004211</t>
+  </si>
+  <si>
+    <t>260911-F00012108</t>
+  </si>
+  <si>
+    <t>260911-W00005368</t>
+  </si>
+  <si>
+    <t>260911-W00010723</t>
+  </si>
+  <si>
+    <t>260912-F00002315</t>
+  </si>
+  <si>
+    <t>260912-F00005648</t>
+  </si>
+  <si>
+    <t>260915-F00002725-2</t>
+  </si>
+  <si>
+    <t>260915-F00005424</t>
+  </si>
+  <si>
+    <t>260915-F00010119</t>
+  </si>
+  <si>
+    <t>260915-F00013603</t>
+  </si>
+  <si>
+    <t>260915-W00007525</t>
+  </si>
+  <si>
+    <t>260915-W00007652</t>
+  </si>
+  <si>
+    <t>260915-W00009729</t>
+  </si>
+  <si>
+    <t>260916-F00002036</t>
+  </si>
+  <si>
+    <t>260916-F00009443</t>
+  </si>
+  <si>
+    <t>260916-F00011771</t>
+  </si>
+  <si>
+    <t>260916-W00004190</t>
+  </si>
+  <si>
+    <t>260916-W00006155</t>
+  </si>
+  <si>
+    <t>260916-W00008370</t>
+  </si>
+  <si>
+    <t>260917-F00006988-1</t>
+  </si>
+  <si>
+    <t>260917-F00007859</t>
+  </si>
+  <si>
+    <t>260917-F00008240</t>
+  </si>
+  <si>
+    <t>260917-F00012575</t>
+  </si>
+  <si>
+    <t>260917-W00002408</t>
+  </si>
+  <si>
+    <t>260917-W00006833</t>
+  </si>
+  <si>
+    <t>260917-W00007466</t>
+  </si>
+  <si>
+    <t>260917-W00007938</t>
+  </si>
+  <si>
+    <t>260918-F00014714-1</t>
+  </si>
+  <si>
+    <t>260918-W00016304</t>
+  </si>
+  <si>
+    <t>260919-F00000634</t>
+  </si>
+  <si>
+    <t>260919-F00004869</t>
+  </si>
+  <si>
+    <t>260919-F00005234</t>
+  </si>
+  <si>
+    <t>260919-W00003564</t>
+  </si>
+  <si>
+    <t>260919-W00009239</t>
+  </si>
+  <si>
+    <t>260919-W00012451</t>
+  </si>
+  <si>
+    <t>260920-F00002429</t>
+  </si>
+  <si>
+    <t>260920-W00006791</t>
+  </si>
+  <si>
+    <t>260920-W00008835</t>
+  </si>
+  <si>
+    <t>260920-W00011900</t>
+  </si>
+  <si>
+    <t>260921-F00011090</t>
+  </si>
+  <si>
+    <t>260921-F00012891</t>
+  </si>
+  <si>
+    <t>260921-F00013666</t>
+  </si>
+  <si>
+    <t>260921-F00017121</t>
+  </si>
+  <si>
+    <t>260921-F00017500</t>
+  </si>
+  <si>
+    <t>260921-F00018294</t>
+  </si>
+  <si>
+    <t>260921-W00002876</t>
+  </si>
+  <si>
+    <t>260921-W00003824</t>
+  </si>
+  <si>
+    <t>260921-W00005963</t>
+  </si>
+  <si>
+    <t>260921-W00009009</t>
+  </si>
+  <si>
+    <t>260921-W00009139</t>
+  </si>
+  <si>
+    <t>260921-W00009971</t>
+  </si>
+  <si>
+    <t>260921-W00009995</t>
+  </si>
+  <si>
+    <t>260921-W00011004</t>
+  </si>
+  <si>
+    <t>260921-W00011416</t>
+  </si>
+  <si>
+    <t>260921-W00012271</t>
+  </si>
+  <si>
+    <t>260922-F00000704</t>
+  </si>
+  <si>
+    <t>260922-F00007547</t>
+  </si>
+  <si>
+    <t>260922-F00008426</t>
+  </si>
+  <si>
+    <t>260922-F00010048</t>
+  </si>
+  <si>
+    <t>260922-F00011224</t>
+  </si>
+  <si>
+    <t>260922-F00013631</t>
+  </si>
+  <si>
+    <t>260922-F00014293</t>
+  </si>
+  <si>
+    <t>260922-F00015124</t>
+  </si>
+  <si>
+    <t>260922-F00015417</t>
+  </si>
+  <si>
+    <t>260922-F00015909</t>
+  </si>
+  <si>
+    <t>260922-W00001342</t>
+  </si>
+  <si>
+    <t>260922-W00002375</t>
+  </si>
+  <si>
+    <t>260922-W00004999</t>
+  </si>
+  <si>
+    <t>260922-W00008075</t>
+  </si>
+  <si>
+    <t>260922-W00008124</t>
+  </si>
+  <si>
+    <t>260922-W00010084</t>
+  </si>
+  <si>
+    <t>260922-W00010289</t>
+  </si>
+  <si>
+    <t>260922-W00010502</t>
+  </si>
+  <si>
+    <t>260922-W00010879</t>
+  </si>
+  <si>
+    <t>260922-W00011246</t>
+  </si>
+  <si>
+    <t>260922-W00012181</t>
+  </si>
+  <si>
+    <t>260922-W00012189</t>
+  </si>
+  <si>
+    <t>260922-W00013226</t>
+  </si>
+  <si>
+    <t>260923-F00000449</t>
+  </si>
+  <si>
+    <t>260923-F00001022</t>
+  </si>
+  <si>
+    <t>260923-F00001228</t>
+  </si>
+  <si>
+    <t>260923-F00001411</t>
+  </si>
+  <si>
+    <t>260923-F00002436</t>
+  </si>
+  <si>
+    <t>260923-F00002523</t>
+  </si>
+  <si>
+    <t>260923-F00002902</t>
+  </si>
+  <si>
+    <t>260923-F00003900</t>
+  </si>
+  <si>
+    <t>260923-F00004255</t>
+  </si>
+  <si>
+    <t>260923-F00004414</t>
+  </si>
+  <si>
+    <t>260923-F00004497</t>
+  </si>
+  <si>
+    <t>260923-F00008109-1</t>
+  </si>
+  <si>
+    <t>260923-F00008297</t>
+  </si>
+  <si>
+    <t>260923-F00008847</t>
+  </si>
+  <si>
+    <t>260923-F00009175</t>
+  </si>
+  <si>
+    <t>260923-F00009372</t>
+  </si>
+  <si>
+    <t>260923-F00010916</t>
+  </si>
+  <si>
+    <t>260923-F00011786</t>
+  </si>
+  <si>
+    <t>260923-F00014560</t>
+  </si>
+  <si>
+    <t>260923-F00014870</t>
+  </si>
+  <si>
+    <t>260923-F00015080</t>
+  </si>
+  <si>
+    <t>260923-F00015763</t>
+  </si>
+  <si>
+    <t>260923-F00016059</t>
+  </si>
+  <si>
+    <t>260923-W00001279</t>
+  </si>
+  <si>
+    <t>260923-W00001768</t>
+  </si>
+  <si>
+    <t>260923-W00002950</t>
+  </si>
+  <si>
+    <t>260923-W00003141</t>
+  </si>
+  <si>
+    <t>260923-W00003898</t>
+  </si>
+  <si>
+    <t>260923-W00005542</t>
+  </si>
+  <si>
+    <t>260923-W00005802</t>
+  </si>
+  <si>
+    <t>260923-W00005998</t>
+  </si>
+  <si>
+    <t>260923-W00006233</t>
+  </si>
+  <si>
+    <t>260923-W00006474</t>
+  </si>
+  <si>
+    <t>260923-W00006951-2</t>
+  </si>
+  <si>
+    <t>260923-W00007571-2</t>
+  </si>
+  <si>
+    <t>260923-W00008256</t>
+  </si>
+  <si>
+    <t>260923-W00008260</t>
+  </si>
+  <si>
+    <t>260923-W00009014</t>
+  </si>
+  <si>
+    <t>260923-W00009051</t>
+  </si>
+  <si>
+    <t>260923-W00009638</t>
+  </si>
+  <si>
+    <t>260923-W00010539</t>
+  </si>
+  <si>
+    <t>260923-W00010584</t>
+  </si>
+  <si>
+    <t>260923-W00012005</t>
+  </si>
+  <si>
+    <t>260923-W00012738</t>
+  </si>
+  <si>
+    <t>260923-W00012756</t>
+  </si>
+  <si>
+    <t>260923-W00013493</t>
+  </si>
+  <si>
+    <t>260923-W00015051</t>
+  </si>
+  <si>
+    <t>260924-F00001048-5</t>
+  </si>
+  <si>
+    <t>260924-F00003050</t>
+  </si>
+  <si>
+    <t>260924-F00003372</t>
+  </si>
+  <si>
+    <t>260924-F00005263</t>
+  </si>
+  <si>
+    <t>260924-F00006809</t>
+  </si>
+  <si>
+    <t>260924-F00006873</t>
+  </si>
+  <si>
+    <t>260924-F00006951</t>
+  </si>
+  <si>
+    <t>260924-W00000836</t>
+  </si>
+  <si>
+    <t>260924-W00002890</t>
+  </si>
+  <si>
+    <t>260924-W00003825</t>
+  </si>
+  <si>
+    <t>260924-W00004469</t>
+  </si>
+  <si>
+    <t>260924-W00005745</t>
+  </si>
+  <si>
+    <t>260924-W00005825</t>
+  </si>
+  <si>
+    <t>267013543</t>
+  </si>
+  <si>
+    <t>267013670</t>
+  </si>
+  <si>
+    <t>267013711</t>
+  </si>
+  <si>
+    <t>267013715</t>
+  </si>
+  <si>
+    <t>267013729</t>
+  </si>
+  <si>
+    <t>267013735</t>
+  </si>
+  <si>
+    <t>267013750</t>
+  </si>
+  <si>
+    <t>267013766</t>
+  </si>
+  <si>
+    <t>26MPE0010117</t>
+  </si>
+  <si>
+    <t>26MPE0010121</t>
+  </si>
+  <si>
+    <t>26MPE0010184</t>
+  </si>
+  <si>
+    <t>26MPE0010241</t>
+  </si>
+  <si>
+    <t>328281329</t>
+  </si>
+  <si>
+    <t>328644736</t>
+  </si>
+  <si>
+    <t>328701311</t>
+  </si>
+  <si>
+    <t>328701614</t>
+  </si>
+  <si>
+    <t>329320691</t>
+  </si>
+  <si>
+    <t>329320864</t>
+  </si>
+  <si>
+    <t>329431052</t>
+  </si>
+  <si>
+    <t>329484176</t>
+  </si>
+  <si>
+    <t>329484599</t>
+  </si>
+  <si>
+    <t>329484786</t>
+  </si>
+  <si>
+    <t>329536243</t>
+  </si>
+  <si>
+    <t>329583716</t>
+  </si>
+  <si>
+    <t>329584633</t>
+  </si>
+  <si>
+    <t>329633793</t>
+  </si>
+  <si>
+    <t>329634419</t>
+  </si>
+  <si>
+    <t>329634593</t>
+  </si>
+  <si>
+    <t>329738862</t>
+  </si>
+  <si>
+    <t>329739065</t>
+  </si>
+  <si>
+    <t>329788119</t>
+  </si>
+  <si>
+    <t>329788239</t>
+  </si>
+  <si>
+    <t>329788318</t>
+  </si>
+  <si>
+    <t>329788904</t>
+  </si>
+  <si>
+    <t>329841385</t>
+  </si>
+  <si>
+    <t>329892099</t>
+  </si>
+  <si>
+    <t>329892253</t>
+  </si>
+  <si>
+    <t>329892300</t>
+  </si>
+  <si>
+    <t>51340048124KR</t>
+  </si>
+  <si>
+    <t>ID5545_XD</t>
+  </si>
+  <si>
+    <t>ID5549_XD</t>
+  </si>
+  <si>
+    <t>NFD6-09-10-D4W2_CSXD</t>
+  </si>
+  <si>
+    <t>NFD6-09-14-D3B6</t>
+  </si>
+  <si>
+    <t>NFD6-09-15-VKRS</t>
+  </si>
+  <si>
+    <t>NFD6-09-17-4KD6</t>
+  </si>
+  <si>
+    <t>NFD6-09-21-UBR6</t>
+  </si>
+  <si>
+    <t>NFD6-09-22-4QB4</t>
+  </si>
+  <si>
+    <t>NFD6-09-22-CS7X</t>
+  </si>
+  <si>
+    <t>NFD6-09-22-D4Q2</t>
+  </si>
+  <si>
+    <t>NFD6-09-23-6RV8</t>
+  </si>
+  <si>
+    <t>NFD6-09-23-DEBC</t>
+  </si>
+  <si>
+    <t>NFD6-09-23-GXEJ</t>
+  </si>
+  <si>
+    <t>NFD6-09-23-YCKP</t>
+  </si>
+  <si>
+    <t>NFD6-09-23-ZMXZ</t>
+  </si>
+  <si>
+    <t>NFD6-09-24-GSTW</t>
+  </si>
+  <si>
+    <t>NFD6-09-24-M5EG</t>
+  </si>
+  <si>
+    <t>NFE6-09-17-E6MG</t>
+  </si>
+  <si>
+    <t>NFE6-09-17-SEJM</t>
+  </si>
+  <si>
+    <t>NFE6-09-18-JN4X</t>
+  </si>
+  <si>
+    <t>NFE6-09-22-FK5R</t>
+  </si>
+  <si>
+    <t>NFE6-09-23-TJZM</t>
+  </si>
+  <si>
+    <t>NFE6-09-24-4Q5Q</t>
+  </si>
+  <si>
+    <t>P-NSH26-11825+11795</t>
+  </si>
+  <si>
+    <t>R437046</t>
+  </si>
+  <si>
+    <t>R437306</t>
+  </si>
+  <si>
+    <t>SA26/H006786</t>
+  </si>
+  <si>
+    <t>SZL20260924/01</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>SZ-804</t>
+  </si>
+  <si>
+    <t>K-943</t>
+  </si>
+  <si>
+    <t>K-971</t>
+  </si>
+  <si>
+    <t>SZ-818</t>
+  </si>
+  <si>
+    <t>K-973</t>
+  </si>
+  <si>
+    <t>K-998</t>
+  </si>
+  <si>
+    <t>K-942</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>K-982</t>
+  </si>
+  <si>
+    <t>K-9122</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>K-961</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>K-906</t>
+  </si>
+  <si>
+    <t>K-921</t>
+  </si>
+  <si>
+    <t>K-925</t>
+  </si>
+  <si>
+    <t>K-991</t>
+  </si>
+  <si>
+    <t>K-917</t>
+  </si>
+  <si>
+    <t>K-931</t>
+  </si>
+  <si>
+    <t>K-981</t>
+  </si>
+  <si>
+    <t>K-999</t>
+  </si>
+  <si>
+    <t>K-915</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>K-9121</t>
+  </si>
+  <si>
+    <t>K-930</t>
+  </si>
+  <si>
+    <t>K-941</t>
+  </si>
+  <si>
+    <t>K-952</t>
+  </si>
+  <si>
+    <t>K-929</t>
+  </si>
+  <si>
+    <t>K-963</t>
+  </si>
+  <si>
+    <t>K-918</t>
+  </si>
+  <si>
+    <t>K-962</t>
+  </si>
+  <si>
+    <t>K-964</t>
+  </si>
+  <si>
+    <t>SZ-803</t>
+  </si>
+  <si>
+    <t>SZ-835</t>
+  </si>
+  <si>
+    <t>K-983</t>
+  </si>
+  <si>
+    <t>K-902</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-850</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-870</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>K-951</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>SZ-826</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
   </si>
 </sst>
 </file>
@@ -322,9 +2224,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -641,10 +2542,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC11F24F-E222-443E-8401-2ECBA69A40D4}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C368"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -661,643 +2562,4040 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>451</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>452</v>
+      </c>
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>452</v>
+      </c>
+      <c r="B8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>452</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>453</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>453</v>
+      </c>
+      <c r="B11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>454</v>
+      </c>
+      <c r="B13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>454</v>
+      </c>
+      <c r="B14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>455</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>456</v>
+      </c>
+      <c r="B16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>457</v>
+      </c>
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>458</v>
+      </c>
+      <c r="B20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>459</v>
+      </c>
+      <c r="B21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>460</v>
+      </c>
+      <c r="B22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>460</v>
+      </c>
+      <c r="B23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>461</v>
+      </c>
+      <c r="B27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>8</v>
       </c>
-      <c r="C6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>462</v>
+      </c>
+      <c r="B29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>463</v>
+      </c>
+      <c r="B30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>9</v>
       </c>
-      <c r="C7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>10</v>
       </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B33" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>464</v>
+      </c>
+      <c r="B34" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>465</v>
+      </c>
+      <c r="B35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>465</v>
+      </c>
+      <c r="B36" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>466</v>
+      </c>
+      <c r="B37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>467</v>
+      </c>
+      <c r="B38" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>468</v>
+      </c>
+      <c r="B39" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>469</v>
+      </c>
+      <c r="B40" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>470</v>
+      </c>
+      <c r="B41" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>471</v>
+      </c>
+      <c r="B42" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>472</v>
+      </c>
+      <c r="B43" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B44" t="s">
+        <v>125</v>
+      </c>
+      <c r="C44" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>473</v>
+      </c>
+      <c r="B45" t="s">
+        <v>126</v>
+      </c>
+      <c r="C45" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>474</v>
+      </c>
+      <c r="B46" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>475</v>
+      </c>
+      <c r="B47" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>475</v>
+      </c>
+      <c r="B48" t="s">
+        <v>129</v>
+      </c>
+      <c r="C48" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>476</v>
+      </c>
+      <c r="B49" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>477</v>
+      </c>
+      <c r="B50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>478</v>
+      </c>
+      <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>479</v>
+      </c>
+      <c r="B52" t="s">
+        <v>133</v>
+      </c>
+      <c r="C52" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>12</v>
       </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C53" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>480</v>
+      </c>
+      <c r="B55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>480</v>
+      </c>
+      <c r="B56" t="s">
+        <v>137</v>
+      </c>
+      <c r="C56" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>481</v>
+      </c>
+      <c r="B57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C57" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>481</v>
+      </c>
+      <c r="B58" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>482</v>
+      </c>
+      <c r="B59" t="s">
+        <v>140</v>
+      </c>
+      <c r="C59" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>483</v>
+      </c>
+      <c r="B60" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>484</v>
+      </c>
+      <c r="B61" t="s">
+        <v>142</v>
+      </c>
+      <c r="C61" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>485</v>
+      </c>
+      <c r="B62" t="s">
+        <v>143</v>
+      </c>
+      <c r="C62" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>486</v>
+      </c>
+      <c r="B63" t="s">
+        <v>144</v>
+      </c>
+      <c r="C63" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>487</v>
+      </c>
+      <c r="B64" t="s">
+        <v>145</v>
+      </c>
+      <c r="C64" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>488</v>
+      </c>
+      <c r="B65" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>489</v>
+      </c>
+      <c r="B66" t="s">
+        <v>147</v>
+      </c>
+      <c r="C66" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>490</v>
+      </c>
+      <c r="B67" t="s">
+        <v>148</v>
+      </c>
+      <c r="C67" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>490</v>
+      </c>
+      <c r="B68" t="s">
+        <v>149</v>
+      </c>
+      <c r="C68" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B69" t="s">
+        <v>150</v>
+      </c>
+      <c r="C69" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>14</v>
       </c>
-      <c r="C12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B70" t="s">
+        <v>151</v>
+      </c>
+      <c r="C70" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B71" t="s">
+        <v>152</v>
+      </c>
+      <c r="C71" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B72" t="s">
+        <v>153</v>
+      </c>
+      <c r="C72" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>17</v>
       </c>
-      <c r="C15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B73" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>491</v>
+      </c>
+      <c r="B74" t="s">
+        <v>155</v>
+      </c>
+      <c r="C74" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>492</v>
+      </c>
+      <c r="B75" t="s">
+        <v>156</v>
+      </c>
+      <c r="C75" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>493</v>
+      </c>
+      <c r="B76" t="s">
+        <v>157</v>
+      </c>
+      <c r="C76" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>494</v>
+      </c>
+      <c r="B77" t="s">
+        <v>158</v>
+      </c>
+      <c r="C77" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>495</v>
+      </c>
+      <c r="B78" t="s">
+        <v>159</v>
+      </c>
+      <c r="C78" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>496</v>
+      </c>
+      <c r="B79" t="s">
+        <v>160</v>
+      </c>
+      <c r="C79" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>497</v>
+      </c>
+      <c r="B80" t="s">
+        <v>161</v>
+      </c>
+      <c r="C80" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>18</v>
       </c>
-      <c r="C16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B81" t="s">
+        <v>162</v>
+      </c>
+      <c r="C81" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>498</v>
+      </c>
+      <c r="B82" t="s">
+        <v>163</v>
+      </c>
+      <c r="C82" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>499</v>
+      </c>
+      <c r="B83" t="s">
+        <v>164</v>
+      </c>
+      <c r="C83" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>500</v>
+      </c>
+      <c r="B84" t="s">
+        <v>165</v>
+      </c>
+      <c r="C84" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>501</v>
+      </c>
+      <c r="B85" t="s">
+        <v>166</v>
+      </c>
+      <c r="C85" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>502</v>
+      </c>
+      <c r="B86" t="s">
+        <v>167</v>
+      </c>
+      <c r="C86" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>19</v>
       </c>
-      <c r="C17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B87" t="s">
+        <v>168</v>
+      </c>
+      <c r="C87" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>503</v>
+      </c>
+      <c r="B88" t="s">
+        <v>169</v>
+      </c>
+      <c r="C88" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>504</v>
+      </c>
+      <c r="B89" t="s">
+        <v>170</v>
+      </c>
+      <c r="C89" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>504</v>
+      </c>
+      <c r="B90" t="s">
+        <v>171</v>
+      </c>
+      <c r="C90" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>505</v>
+      </c>
+      <c r="B91" t="s">
+        <v>172</v>
+      </c>
+      <c r="C91" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>506</v>
+      </c>
+      <c r="B92" t="s">
+        <v>173</v>
+      </c>
+      <c r="C92" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>507</v>
+      </c>
+      <c r="B93" t="s">
+        <v>174</v>
+      </c>
+      <c r="C93" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>507</v>
+      </c>
+      <c r="B94" t="s">
+        <v>175</v>
+      </c>
+      <c r="C94" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>508</v>
+      </c>
+      <c r="B95" t="s">
+        <v>176</v>
+      </c>
+      <c r="C95" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>509</v>
+      </c>
+      <c r="B96" t="s">
+        <v>177</v>
+      </c>
+      <c r="C96" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>509</v>
+      </c>
+      <c r="B97" t="s">
+        <v>178</v>
+      </c>
+      <c r="C97" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>510</v>
+      </c>
+      <c r="B98" t="s">
+        <v>179</v>
+      </c>
+      <c r="C98" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>511</v>
+      </c>
+      <c r="B99" t="s">
+        <v>180</v>
+      </c>
+      <c r="C99" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>512</v>
+      </c>
+      <c r="B100" t="s">
+        <v>181</v>
+      </c>
+      <c r="C100" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>512</v>
+      </c>
+      <c r="B101" t="s">
+        <v>182</v>
+      </c>
+      <c r="C101" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>513</v>
+      </c>
+      <c r="B102" t="s">
+        <v>183</v>
+      </c>
+      <c r="C102" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>514</v>
+      </c>
+      <c r="B103" t="s">
+        <v>184</v>
+      </c>
+      <c r="C103" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>514</v>
+      </c>
+      <c r="B104" t="s">
+        <v>185</v>
+      </c>
+      <c r="C104" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>515</v>
+      </c>
+      <c r="B105" t="s">
+        <v>186</v>
+      </c>
+      <c r="C105" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>516</v>
+      </c>
+      <c r="B106" t="s">
+        <v>187</v>
+      </c>
+      <c r="C106" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>517</v>
+      </c>
+      <c r="B107" t="s">
+        <v>188</v>
+      </c>
+      <c r="C107" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>518</v>
+      </c>
+      <c r="B108" t="s">
+        <v>189</v>
+      </c>
+      <c r="C108" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>519</v>
+      </c>
+      <c r="B109" t="s">
+        <v>190</v>
+      </c>
+      <c r="C109" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>520</v>
+      </c>
+      <c r="B110" t="s">
+        <v>191</v>
+      </c>
+      <c r="C110" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>521</v>
+      </c>
+      <c r="B111" t="s">
+        <v>192</v>
+      </c>
+      <c r="C111" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>522</v>
+      </c>
+      <c r="B112" t="s">
+        <v>193</v>
+      </c>
+      <c r="C112" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>522</v>
+      </c>
+      <c r="B113" t="s">
+        <v>194</v>
+      </c>
+      <c r="C113" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>523</v>
+      </c>
+      <c r="B114" t="s">
+        <v>195</v>
+      </c>
+      <c r="C114" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>20</v>
       </c>
-      <c r="C18" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B115" t="s">
+        <v>196</v>
+      </c>
+      <c r="C115" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>21</v>
       </c>
-      <c r="C19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B116" t="s">
+        <v>197</v>
+      </c>
+      <c r="C116" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>524</v>
+      </c>
+      <c r="B117" t="s">
+        <v>198</v>
+      </c>
+      <c r="C117" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>22</v>
       </c>
-      <c r="C20" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B118" t="s">
+        <v>199</v>
+      </c>
+      <c r="C118" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>525</v>
+      </c>
+      <c r="B119" t="s">
+        <v>200</v>
+      </c>
+      <c r="C119" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>526</v>
+      </c>
+      <c r="B120" t="s">
+        <v>201</v>
+      </c>
+      <c r="C120" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>527</v>
+      </c>
+      <c r="B121" t="s">
+        <v>202</v>
+      </c>
+      <c r="C121" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>527</v>
+      </c>
+      <c r="B122" t="s">
+        <v>203</v>
+      </c>
+      <c r="C122" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>528</v>
+      </c>
+      <c r="B123" t="s">
+        <v>204</v>
+      </c>
+      <c r="C123" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
         <v>23</v>
       </c>
-      <c r="C21" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B124" t="s">
+        <v>205</v>
+      </c>
+      <c r="C124" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>529</v>
+      </c>
+      <c r="B125" t="s">
+        <v>206</v>
+      </c>
+      <c r="C125" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>24</v>
       </c>
-      <c r="C22" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B126" t="s">
+        <v>207</v>
+      </c>
+      <c r="C126" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>530</v>
+      </c>
+      <c r="B127" t="s">
+        <v>208</v>
+      </c>
+      <c r="C127" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>530</v>
+      </c>
+      <c r="B128" t="s">
+        <v>209</v>
+      </c>
+      <c r="C128" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>531</v>
+      </c>
+      <c r="B129" t="s">
+        <v>210</v>
+      </c>
+      <c r="C129" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>531</v>
+      </c>
+      <c r="B130" t="s">
+        <v>211</v>
+      </c>
+      <c r="C130" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>532</v>
+      </c>
+      <c r="B131" t="s">
+        <v>212</v>
+      </c>
+      <c r="C131" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>533</v>
+      </c>
+      <c r="B132" t="s">
+        <v>213</v>
+      </c>
+      <c r="C132" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>25</v>
       </c>
-      <c r="C23" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B133" t="s">
+        <v>214</v>
+      </c>
+      <c r="C133" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>534</v>
+      </c>
+      <c r="B134" t="s">
+        <v>215</v>
+      </c>
+      <c r="C134" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>535</v>
+      </c>
+      <c r="B135" t="s">
+        <v>216</v>
+      </c>
+      <c r="C135" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>536</v>
+      </c>
+      <c r="B136" t="s">
+        <v>217</v>
+      </c>
+      <c r="C136" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>536</v>
+      </c>
+      <c r="B137" t="s">
+        <v>218</v>
+      </c>
+      <c r="C137" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>537</v>
+      </c>
+      <c r="B138" t="s">
+        <v>219</v>
+      </c>
+      <c r="C138" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>538</v>
+      </c>
+      <c r="B139" t="s">
+        <v>220</v>
+      </c>
+      <c r="C139" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>538</v>
+      </c>
+      <c r="B140" t="s">
+        <v>221</v>
+      </c>
+      <c r="C140" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
         <v>26</v>
       </c>
-      <c r="C24" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B141" t="s">
+        <v>222</v>
+      </c>
+      <c r="C141" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>26</v>
+      </c>
+      <c r="B142" t="s">
+        <v>223</v>
+      </c>
+      <c r="C142" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>539</v>
+      </c>
+      <c r="B143" t="s">
+        <v>224</v>
+      </c>
+      <c r="C143" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>540</v>
+      </c>
+      <c r="B144" t="s">
+        <v>225</v>
+      </c>
+      <c r="C144" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>27</v>
       </c>
-      <c r="C25" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="B145" t="s">
+        <v>226</v>
+      </c>
+      <c r="C145" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>541</v>
+      </c>
+      <c r="B146" t="s">
+        <v>227</v>
+      </c>
+      <c r="C146" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>28</v>
       </c>
-      <c r="C26" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B147" t="s">
+        <v>228</v>
+      </c>
+      <c r="C147" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>542</v>
+      </c>
+      <c r="B148" t="s">
+        <v>229</v>
+      </c>
+      <c r="C148" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>543</v>
+      </c>
+      <c r="B149" t="s">
+        <v>230</v>
+      </c>
+      <c r="C149" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>543</v>
+      </c>
+      <c r="B150" t="s">
+        <v>231</v>
+      </c>
+      <c r="C150" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>544</v>
+      </c>
+      <c r="B151" t="s">
+        <v>232</v>
+      </c>
+      <c r="C151" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>544</v>
+      </c>
+      <c r="B152" t="s">
+        <v>233</v>
+      </c>
+      <c r="C152" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>545</v>
+      </c>
+      <c r="B153" t="s">
+        <v>234</v>
+      </c>
+      <c r="C153" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>545</v>
+      </c>
+      <c r="B154" t="s">
+        <v>235</v>
+      </c>
+      <c r="C154" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>546</v>
+      </c>
+      <c r="B155" t="s">
+        <v>236</v>
+      </c>
+      <c r="C155" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>547</v>
+      </c>
+      <c r="B156" t="s">
+        <v>237</v>
+      </c>
+      <c r="C156" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>547</v>
+      </c>
+      <c r="B157" t="s">
+        <v>238</v>
+      </c>
+      <c r="C157" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>548</v>
+      </c>
+      <c r="B158" t="s">
+        <v>239</v>
+      </c>
+      <c r="C158" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>29</v>
       </c>
-      <c r="C27" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B159" t="s">
+        <v>240</v>
+      </c>
+      <c r="C159" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>549</v>
+      </c>
+      <c r="B160" t="s">
+        <v>241</v>
+      </c>
+      <c r="C160" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>550</v>
+      </c>
+      <c r="B161" t="s">
+        <v>242</v>
+      </c>
+      <c r="C161" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>551</v>
+      </c>
+      <c r="B162" t="s">
+        <v>243</v>
+      </c>
+      <c r="C162" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>551</v>
+      </c>
+      <c r="B163" t="s">
+        <v>244</v>
+      </c>
+      <c r="C163" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>552</v>
+      </c>
+      <c r="B164" t="s">
+        <v>245</v>
+      </c>
+      <c r="C164" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
         <v>30</v>
       </c>
-      <c r="C28" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B165" t="s">
+        <v>246</v>
+      </c>
+      <c r="C165" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>553</v>
+      </c>
+      <c r="B166" t="s">
+        <v>247</v>
+      </c>
+      <c r="C166" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>554</v>
+      </c>
+      <c r="B167" t="s">
+        <v>248</v>
+      </c>
+      <c r="C167" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>555</v>
+      </c>
+      <c r="B168" t="s">
+        <v>249</v>
+      </c>
+      <c r="C168" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>555</v>
+      </c>
+      <c r="B169" t="s">
+        <v>250</v>
+      </c>
+      <c r="C169" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>556</v>
+      </c>
+      <c r="B170" t="s">
+        <v>251</v>
+      </c>
+      <c r="C170" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>556</v>
+      </c>
+      <c r="B171" t="s">
+        <v>252</v>
+      </c>
+      <c r="C171" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>557</v>
+      </c>
+      <c r="B172" t="s">
+        <v>253</v>
+      </c>
+      <c r="C172" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>558</v>
+      </c>
+      <c r="B173" t="s">
+        <v>254</v>
+      </c>
+      <c r="C173" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>558</v>
+      </c>
+      <c r="B174" t="s">
+        <v>255</v>
+      </c>
+      <c r="C174" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>559</v>
+      </c>
+      <c r="B175" t="s">
+        <v>256</v>
+      </c>
+      <c r="C175" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
         <v>31</v>
       </c>
-      <c r="C29" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="B176" t="s">
+        <v>257</v>
+      </c>
+      <c r="C176" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>560</v>
+      </c>
+      <c r="B177" t="s">
+        <v>258</v>
+      </c>
+      <c r="C177" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>561</v>
+      </c>
+      <c r="B178" t="s">
+        <v>259</v>
+      </c>
+      <c r="C178" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>561</v>
+      </c>
+      <c r="B179" t="s">
+        <v>260</v>
+      </c>
+      <c r="C179" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>562</v>
+      </c>
+      <c r="B180" t="s">
+        <v>261</v>
+      </c>
+      <c r="C180" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>563</v>
+      </c>
+      <c r="B181" t="s">
+        <v>262</v>
+      </c>
+      <c r="C181" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
         <v>32</v>
       </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="B182" t="s">
+        <v>263</v>
+      </c>
+      <c r="C182" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>32</v>
+      </c>
+      <c r="B183" t="s">
+        <v>264</v>
+      </c>
+      <c r="C183" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>564</v>
+      </c>
+      <c r="B184" t="s">
+        <v>265</v>
+      </c>
+      <c r="C184" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>564</v>
+      </c>
+      <c r="B185" t="s">
+        <v>266</v>
+      </c>
+      <c r="C185" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>565</v>
+      </c>
+      <c r="B186" t="s">
+        <v>267</v>
+      </c>
+      <c r="C186" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>566</v>
+      </c>
+      <c r="B187" t="s">
+        <v>268</v>
+      </c>
+      <c r="C187" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>566</v>
+      </c>
+      <c r="B188" t="s">
+        <v>269</v>
+      </c>
+      <c r="C188" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>567</v>
+      </c>
+      <c r="B189" t="s">
+        <v>270</v>
+      </c>
+      <c r="C189" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
         <v>33</v>
       </c>
-      <c r="C31" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="B190" t="s">
+        <v>271</v>
+      </c>
+      <c r="C190" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>568</v>
+      </c>
+      <c r="B191" t="s">
+        <v>272</v>
+      </c>
+      <c r="C191" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>568</v>
+      </c>
+      <c r="B192" t="s">
+        <v>273</v>
+      </c>
+      <c r="C192" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>569</v>
+      </c>
+      <c r="B193" t="s">
+        <v>274</v>
+      </c>
+      <c r="C193" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>570</v>
+      </c>
+      <c r="B194" t="s">
+        <v>275</v>
+      </c>
+      <c r="C194" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>571</v>
+      </c>
+      <c r="B195" t="s">
+        <v>276</v>
+      </c>
+      <c r="C195" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
         <v>34</v>
       </c>
-      <c r="C32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="B196" t="s">
+        <v>277</v>
+      </c>
+      <c r="C196" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>34</v>
+      </c>
+      <c r="B197" t="s">
+        <v>278</v>
+      </c>
+      <c r="C197" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>34</v>
+      </c>
+      <c r="B198" t="s">
+        <v>279</v>
+      </c>
+      <c r="C198" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>572</v>
+      </c>
+      <c r="B199" t="s">
+        <v>280</v>
+      </c>
+      <c r="C199" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>572</v>
+      </c>
+      <c r="B200" t="s">
+        <v>281</v>
+      </c>
+      <c r="C200" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>573</v>
+      </c>
+      <c r="B201" t="s">
+        <v>282</v>
+      </c>
+      <c r="C201" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>574</v>
+      </c>
+      <c r="B202" t="s">
+        <v>283</v>
+      </c>
+      <c r="C202" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>575</v>
+      </c>
+      <c r="B203" t="s">
+        <v>284</v>
+      </c>
+      <c r="C203" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
         <v>35</v>
       </c>
-      <c r="C33" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="B204" t="s">
+        <v>285</v>
+      </c>
+      <c r="C204" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>576</v>
+      </c>
+      <c r="B205" t="s">
+        <v>286</v>
+      </c>
+      <c r="C205" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>577</v>
+      </c>
+      <c r="B206" t="s">
+        <v>287</v>
+      </c>
+      <c r="C206" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>578</v>
+      </c>
+      <c r="B207" t="s">
+        <v>288</v>
+      </c>
+      <c r="C207" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>579</v>
+      </c>
+      <c r="B208" t="s">
+        <v>289</v>
+      </c>
+      <c r="C208" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>580</v>
+      </c>
+      <c r="B209" t="s">
+        <v>290</v>
+      </c>
+      <c r="C209" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>580</v>
+      </c>
+      <c r="B210" t="s">
+        <v>291</v>
+      </c>
+      <c r="C210" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>581</v>
+      </c>
+      <c r="B211" t="s">
+        <v>292</v>
+      </c>
+      <c r="C211" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
         <v>36</v>
       </c>
-      <c r="C34" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="B212" t="s">
+        <v>293</v>
+      </c>
+      <c r="C212" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>582</v>
+      </c>
+      <c r="B213" t="s">
+        <v>294</v>
+      </c>
+      <c r="C213" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>583</v>
+      </c>
+      <c r="B214" t="s">
+        <v>295</v>
+      </c>
+      <c r="C214" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
         <v>37</v>
       </c>
-      <c r="C35" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="B215" t="s">
+        <v>296</v>
+      </c>
+      <c r="C215" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>584</v>
+      </c>
+      <c r="B216" t="s">
+        <v>297</v>
+      </c>
+      <c r="C216" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>585</v>
+      </c>
+      <c r="B217" t="s">
+        <v>298</v>
+      </c>
+      <c r="C217" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>586</v>
+      </c>
+      <c r="B218" t="s">
+        <v>299</v>
+      </c>
+      <c r="C218" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>587</v>
+      </c>
+      <c r="B219" t="s">
+        <v>300</v>
+      </c>
+      <c r="C219" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
         <v>38</v>
       </c>
-      <c r="C36" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="B220" t="s">
+        <v>301</v>
+      </c>
+      <c r="C220" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
         <v>39</v>
       </c>
-      <c r="C37" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="B221" t="s">
+        <v>302</v>
+      </c>
+      <c r="C221" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>588</v>
+      </c>
+      <c r="B222" t="s">
+        <v>303</v>
+      </c>
+      <c r="C222" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>589</v>
+      </c>
+      <c r="B223" t="s">
+        <v>304</v>
+      </c>
+      <c r="C223" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>590</v>
+      </c>
+      <c r="B224" t="s">
+        <v>305</v>
+      </c>
+      <c r="C224" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>591</v>
+      </c>
+      <c r="B225" t="s">
+        <v>306</v>
+      </c>
+      <c r="C225" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>592</v>
+      </c>
+      <c r="B226" t="s">
+        <v>307</v>
+      </c>
+      <c r="C226" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>593</v>
+      </c>
+      <c r="B227" t="s">
+        <v>308</v>
+      </c>
+      <c r="C227" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
         <v>40</v>
       </c>
-      <c r="C38" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="B228" t="s">
+        <v>309</v>
+      </c>
+      <c r="C228" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>594</v>
+      </c>
+      <c r="B229" t="s">
+        <v>310</v>
+      </c>
+      <c r="C229" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>595</v>
+      </c>
+      <c r="B230" t="s">
+        <v>311</v>
+      </c>
+      <c r="C230" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>596</v>
+      </c>
+      <c r="B231" t="s">
+        <v>312</v>
+      </c>
+      <c r="C231" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>597</v>
+      </c>
+      <c r="B232" t="s">
+        <v>313</v>
+      </c>
+      <c r="C232" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>597</v>
+      </c>
+      <c r="B233" t="s">
+        <v>314</v>
+      </c>
+      <c r="C233" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
         <v>41</v>
       </c>
-      <c r="C39" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="B234" t="s">
+        <v>315</v>
+      </c>
+      <c r="C234" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>598</v>
+      </c>
+      <c r="B235" t="s">
+        <v>316</v>
+      </c>
+      <c r="C235" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>599</v>
+      </c>
+      <c r="B236" t="s">
+        <v>317</v>
+      </c>
+      <c r="C236" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>600</v>
+      </c>
+      <c r="B237" t="s">
+        <v>318</v>
+      </c>
+      <c r="C237" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>600</v>
+      </c>
+      <c r="B238" t="s">
+        <v>319</v>
+      </c>
+      <c r="C238" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>601</v>
+      </c>
+      <c r="B239" t="s">
+        <v>320</v>
+      </c>
+      <c r="C239" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>602</v>
+      </c>
+      <c r="B240" t="s">
+        <v>321</v>
+      </c>
+      <c r="C240" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>603</v>
+      </c>
+      <c r="B241" t="s">
+        <v>322</v>
+      </c>
+      <c r="C241" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>603</v>
+      </c>
+      <c r="B242" t="s">
+        <v>323</v>
+      </c>
+      <c r="C242" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>604</v>
+      </c>
+      <c r="B243" t="s">
+        <v>324</v>
+      </c>
+      <c r="C243" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>605</v>
+      </c>
+      <c r="B244" t="s">
+        <v>325</v>
+      </c>
+      <c r="C244" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>606</v>
+      </c>
+      <c r="B245" t="s">
+        <v>326</v>
+      </c>
+      <c r="C245" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>607</v>
+      </c>
+      <c r="B246" t="s">
+        <v>327</v>
+      </c>
+      <c r="C246" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>608</v>
+      </c>
+      <c r="B247" t="s">
+        <v>328</v>
+      </c>
+      <c r="C247" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>609</v>
+      </c>
+      <c r="B248" t="s">
+        <v>329</v>
+      </c>
+      <c r="C248" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>610</v>
+      </c>
+      <c r="B249" t="s">
+        <v>330</v>
+      </c>
+      <c r="C249" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>611</v>
+      </c>
+      <c r="B250" t="s">
+        <v>331</v>
+      </c>
+      <c r="C250" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>612</v>
+      </c>
+      <c r="B251" t="s">
+        <v>332</v>
+      </c>
+      <c r="C251" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>613</v>
+      </c>
+      <c r="B252" t="s">
+        <v>333</v>
+      </c>
+      <c r="C252" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
         <v>42</v>
       </c>
-      <c r="C40" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="B253" t="s">
+        <v>334</v>
+      </c>
+      <c r="C253" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
         <v>3</v>
       </c>
-      <c r="C41" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="B254" t="s">
+        <v>335</v>
+      </c>
+      <c r="C254" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>614</v>
+      </c>
+      <c r="B255" t="s">
+        <v>336</v>
+      </c>
+      <c r="C255" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>615</v>
+      </c>
+      <c r="B256" t="s">
+        <v>337</v>
+      </c>
+      <c r="C256" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>616</v>
+      </c>
+      <c r="B257" t="s">
+        <v>338</v>
+      </c>
+      <c r="C257" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>617</v>
+      </c>
+      <c r="B258" t="s">
+        <v>339</v>
+      </c>
+      <c r="C258" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="B259" t="s">
+        <v>340</v>
+      </c>
+      <c r="C259" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="B260" t="s">
+        <v>341</v>
+      </c>
+      <c r="C260" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="B261" t="s">
+        <v>342</v>
+      </c>
+      <c r="C261" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="B262" t="s">
+        <v>343</v>
+      </c>
+      <c r="C262" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="B263" t="s">
+        <v>344</v>
+      </c>
+      <c r="C263" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>618</v>
+      </c>
+      <c r="B264" t="s">
+        <v>345</v>
+      </c>
+      <c r="C264" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>619</v>
+      </c>
+      <c r="B265" t="s">
+        <v>346</v>
+      </c>
+      <c r="C265" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>619</v>
+      </c>
+      <c r="B266" t="s">
+        <v>347</v>
+      </c>
+      <c r="C266" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>619</v>
+      </c>
+      <c r="B267" t="s">
+        <v>348</v>
+      </c>
+      <c r="C267" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="B268" t="s">
+        <v>349</v>
+      </c>
+      <c r="C268" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>620</v>
+      </c>
+      <c r="B269" t="s">
+        <v>350</v>
+      </c>
+      <c r="C269" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>620</v>
+      </c>
+      <c r="B270" t="s">
+        <v>351</v>
+      </c>
+      <c r="C270" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="B271" t="s">
+        <v>352</v>
+      </c>
+      <c r="C271" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>49</v>
+      </c>
+      <c r="B272" t="s">
+        <v>353</v>
+      </c>
+      <c r="C272" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>621</v>
+      </c>
+      <c r="B273" t="s">
+        <v>354</v>
+      </c>
+      <c r="C273" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>621</v>
+      </c>
+      <c r="B274" t="s">
+        <v>355</v>
+      </c>
+      <c r="C274" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>622</v>
+      </c>
+      <c r="B275" t="s">
+        <v>356</v>
+      </c>
+      <c r="C275" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>623</v>
+      </c>
+      <c r="B276" t="s">
+        <v>357</v>
+      </c>
+      <c r="C276" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>623</v>
+      </c>
+      <c r="B277" t="s">
+        <v>358</v>
+      </c>
+      <c r="C277" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="B278" t="s">
+        <v>359</v>
+      </c>
+      <c r="C278" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>50</v>
+      </c>
+      <c r="B279" t="s">
+        <v>360</v>
+      </c>
+      <c r="C279" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="B280" t="s">
+        <v>361</v>
+      </c>
+      <c r="C280" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>624</v>
+      </c>
+      <c r="B281" t="s">
+        <v>362</v>
+      </c>
+      <c r="C281" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="B282" t="s">
+        <v>363</v>
+      </c>
+      <c r="C282" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>625</v>
+      </c>
+      <c r="B283" t="s">
+        <v>364</v>
+      </c>
+      <c r="C283" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="B284" t="s">
+        <v>365</v>
+      </c>
+      <c r="C284" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
         <v>54</v>
       </c>
-      <c r="C53" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="B285" t="s">
+        <v>366</v>
+      </c>
+      <c r="C285" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
         <v>55</v>
       </c>
-      <c r="C54" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="B286" t="s">
+        <v>367</v>
+      </c>
+      <c r="C286" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>55</v>
+      </c>
+      <c r="B287" t="s">
+        <v>368</v>
+      </c>
+      <c r="C287" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
         <v>56</v>
       </c>
-      <c r="C55" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="B288" t="s">
+        <v>369</v>
+      </c>
+      <c r="C288" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
         <v>57</v>
       </c>
-      <c r="C56" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="B289" t="s">
+        <v>370</v>
+      </c>
+      <c r="C289" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>626</v>
+      </c>
+      <c r="B290" t="s">
+        <v>371</v>
+      </c>
+      <c r="C290" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>626</v>
+      </c>
+      <c r="B291" t="s">
+        <v>372</v>
+      </c>
+      <c r="C291" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>626</v>
+      </c>
+      <c r="B292" t="s">
+        <v>373</v>
+      </c>
+      <c r="C292" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
         <v>58</v>
       </c>
-      <c r="C57" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+      <c r="B293" t="s">
+        <v>374</v>
+      </c>
+      <c r="C293" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
         <v>59</v>
       </c>
-      <c r="C58" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="B294" t="s">
+        <v>375</v>
+      </c>
+      <c r="C294" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
         <v>60</v>
       </c>
-      <c r="C59" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="B295" t="s">
+        <v>376</v>
+      </c>
+      <c r="C295" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>627</v>
+      </c>
+      <c r="B296" t="s">
+        <v>377</v>
+      </c>
+      <c r="C296" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
         <v>61</v>
       </c>
-      <c r="C60" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="B297" t="s">
+        <v>378</v>
+      </c>
+      <c r="C297" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>61</v>
+      </c>
+      <c r="B298" t="s">
+        <v>379</v>
+      </c>
+      <c r="C298" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
         <v>62</v>
       </c>
-      <c r="C61" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="B299" t="s">
+        <v>380</v>
+      </c>
+      <c r="C299" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>62</v>
+      </c>
+      <c r="B300" t="s">
+        <v>381</v>
+      </c>
+      <c r="C300" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>628</v>
+      </c>
+      <c r="B301" t="s">
+        <v>382</v>
+      </c>
+      <c r="C301" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>629</v>
+      </c>
+      <c r="B302" t="s">
+        <v>383</v>
+      </c>
+      <c r="C302" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
         <v>63</v>
       </c>
-      <c r="C62" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+      <c r="B303" t="s">
+        <v>384</v>
+      </c>
+      <c r="C303" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
         <v>64</v>
       </c>
-      <c r="C63" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="B304" t="s">
+        <v>385</v>
+      </c>
+      <c r="C304" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
         <v>65</v>
       </c>
-      <c r="C64" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="B305" t="s">
+        <v>386</v>
+      </c>
+      <c r="C305" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
         <v>66</v>
       </c>
-      <c r="C65" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="B306" t="s">
+        <v>387</v>
+      </c>
+      <c r="C306" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
         <v>67</v>
       </c>
-      <c r="C66" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="B307" t="s">
+        <v>388</v>
+      </c>
+      <c r="C307" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
         <v>68</v>
       </c>
-      <c r="C67" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="B308" t="s">
+        <v>389</v>
+      </c>
+      <c r="C308" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>68</v>
+      </c>
+      <c r="B309" t="s">
+        <v>390</v>
+      </c>
+      <c r="C309" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
         <v>69</v>
       </c>
-      <c r="C68" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+      <c r="B310" t="s">
+        <v>391</v>
+      </c>
+      <c r="C310" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
         <v>70</v>
       </c>
-      <c r="C69" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+      <c r="B311" t="s">
+        <v>392</v>
+      </c>
+      <c r="C311" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
         <v>71</v>
       </c>
-      <c r="C70" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="B312" t="s">
+        <v>393</v>
+      </c>
+      <c r="C312" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
         <v>72</v>
       </c>
-      <c r="C71" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="B313" t="s">
+        <v>394</v>
+      </c>
+      <c r="C313" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
         <v>73</v>
       </c>
-      <c r="C72" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+      <c r="B314" t="s">
+        <v>395</v>
+      </c>
+      <c r="C314" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
         <v>74</v>
       </c>
-      <c r="C73" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+      <c r="B315" t="s">
+        <v>396</v>
+      </c>
+      <c r="C315" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>74</v>
+      </c>
+      <c r="B316" t="s">
+        <v>397</v>
+      </c>
+      <c r="C316" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
         <v>75</v>
       </c>
-      <c r="C74" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="B317" t="s">
+        <v>398</v>
+      </c>
+      <c r="C317" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>75</v>
+      </c>
+      <c r="B318" t="s">
+        <v>399</v>
+      </c>
+      <c r="C318" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
         <v>76</v>
       </c>
-      <c r="C75" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="B319" t="s">
+        <v>400</v>
+      </c>
+      <c r="C319" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
         <v>77</v>
       </c>
-      <c r="C76" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+      <c r="B320" t="s">
+        <v>401</v>
+      </c>
+      <c r="C320" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>630</v>
+      </c>
+      <c r="B321" t="s">
+        <v>402</v>
+      </c>
+      <c r="C321" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
         <v>78</v>
       </c>
-      <c r="C77" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="B322" t="s">
+        <v>403</v>
+      </c>
+      <c r="C322" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
         <v>79</v>
       </c>
-      <c r="C78" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+      <c r="B323" t="s">
+        <v>404</v>
+      </c>
+      <c r="C323" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>631</v>
+      </c>
+      <c r="B324" t="s">
+        <v>405</v>
+      </c>
+      <c r="C324" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
         <v>80</v>
       </c>
-      <c r="C79" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+      <c r="B325" t="s">
+        <v>406</v>
+      </c>
+      <c r="C325" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>632</v>
+      </c>
+      <c r="B326" t="s">
+        <v>407</v>
+      </c>
+      <c r="C326" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
         <v>81</v>
       </c>
-      <c r="C80" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
+      <c r="B327" t="s">
+        <v>408</v>
+      </c>
+      <c r="C327" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>633</v>
+      </c>
+      <c r="B328" t="s">
+        <v>409</v>
+      </c>
+      <c r="C328" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>634</v>
+      </c>
+      <c r="B329" t="s">
+        <v>410</v>
+      </c>
+      <c r="C329" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>635</v>
+      </c>
+      <c r="B330" t="s">
+        <v>411</v>
+      </c>
+      <c r="C330" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>636</v>
+      </c>
+      <c r="B331" t="s">
+        <v>412</v>
+      </c>
+      <c r="C331" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>637</v>
+      </c>
+      <c r="B332" t="s">
+        <v>413</v>
+      </c>
+      <c r="C332" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>638</v>
+      </c>
+      <c r="B333" t="s">
+        <v>414</v>
+      </c>
+      <c r="C333" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>639</v>
+      </c>
+      <c r="B334" t="s">
+        <v>415</v>
+      </c>
+      <c r="C334" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>639</v>
+      </c>
+      <c r="B335" t="s">
+        <v>416</v>
+      </c>
+      <c r="C335" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>640</v>
+      </c>
+      <c r="B336" t="s">
+        <v>417</v>
+      </c>
+      <c r="C336" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
         <v>82</v>
       </c>
-      <c r="C81" t="s">
-        <v>83</v>
+      <c r="B337" t="s">
+        <v>418</v>
+      </c>
+      <c r="C337" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>641</v>
+      </c>
+      <c r="B338" t="s">
+        <v>419</v>
+      </c>
+      <c r="C338" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>642</v>
+      </c>
+      <c r="B339" t="s">
+        <v>420</v>
+      </c>
+      <c r="C339" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>643</v>
+      </c>
+      <c r="B340" t="s">
+        <v>421</v>
+      </c>
+      <c r="C340" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>644</v>
+      </c>
+      <c r="B341" t="s">
+        <v>422</v>
+      </c>
+      <c r="C341" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>645</v>
+      </c>
+      <c r="B342" t="s">
+        <v>423</v>
+      </c>
+      <c r="C342" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>646</v>
+      </c>
+      <c r="B343" t="s">
+        <v>424</v>
+      </c>
+      <c r="C343" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>647</v>
+      </c>
+      <c r="B344" t="s">
+        <v>425</v>
+      </c>
+      <c r="C344" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>648</v>
+      </c>
+      <c r="B345" t="s">
+        <v>426</v>
+      </c>
+      <c r="C345" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>649</v>
+      </c>
+      <c r="B346" t="s">
+        <v>427</v>
+      </c>
+      <c r="C346" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>650</v>
+      </c>
+      <c r="B347" t="s">
+        <v>428</v>
+      </c>
+      <c r="C347" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>651</v>
+      </c>
+      <c r="B348" t="s">
+        <v>429</v>
+      </c>
+      <c r="C348" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>652</v>
+      </c>
+      <c r="B349" t="s">
+        <v>430</v>
+      </c>
+      <c r="C349" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>653</v>
+      </c>
+      <c r="B350" t="s">
+        <v>431</v>
+      </c>
+      <c r="C350" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>654</v>
+      </c>
+      <c r="B351" t="s">
+        <v>432</v>
+      </c>
+      <c r="C351" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>655</v>
+      </c>
+      <c r="B352" t="s">
+        <v>433</v>
+      </c>
+      <c r="C352" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>656</v>
+      </c>
+      <c r="B353" t="s">
+        <v>434</v>
+      </c>
+      <c r="C353" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>657</v>
+      </c>
+      <c r="B354" t="s">
+        <v>435</v>
+      </c>
+      <c r="C354" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>658</v>
+      </c>
+      <c r="B355" t="s">
+        <v>436</v>
+      </c>
+      <c r="C355" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>659</v>
+      </c>
+      <c r="B356" t="s">
+        <v>437</v>
+      </c>
+      <c r="C356" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>660</v>
+      </c>
+      <c r="B357" t="s">
+        <v>438</v>
+      </c>
+      <c r="C357" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>661</v>
+      </c>
+      <c r="B358" t="s">
+        <v>439</v>
+      </c>
+      <c r="C358" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>662</v>
+      </c>
+      <c r="B359" t="s">
+        <v>440</v>
+      </c>
+      <c r="C359" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>663</v>
+      </c>
+      <c r="B360" t="s">
+        <v>441</v>
+      </c>
+      <c r="C360" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>664</v>
+      </c>
+      <c r="B361" t="s">
+        <v>442</v>
+      </c>
+      <c r="C361" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>664</v>
+      </c>
+      <c r="B362" t="s">
+        <v>443</v>
+      </c>
+      <c r="C362" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>664</v>
+      </c>
+      <c r="B363" t="s">
+        <v>444</v>
+      </c>
+      <c r="C363" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>665</v>
+      </c>
+      <c r="B364" t="s">
+        <v>445</v>
+      </c>
+      <c r="C364" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>666</v>
+      </c>
+      <c r="B365" t="s">
+        <v>446</v>
+      </c>
+      <c r="C365" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>666</v>
+      </c>
+      <c r="B366" t="s">
+        <v>447</v>
+      </c>
+      <c r="C366" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>667</v>
+      </c>
+      <c r="B367" t="s">
+        <v>448</v>
+      </c>
+      <c r="C367" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>668</v>
+      </c>
+      <c r="B368" t="s">
+        <v>449</v>
+      </c>
+      <c r="C368" t="s">
+        <v>676</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E478456F-B97C-425D-B9F1-41AEDCFFE255}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43F1FAD-71C2-460E-BBD1-307990D7051C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="647">
   <si>
     <t>UTK</t>
   </si>
@@ -303,7 +303,1672 @@
     <t>99003458</t>
   </si>
   <si>
-    <t>SZ</t>
+    <t>1-8385/2026</t>
+  </si>
+  <si>
+    <t>1020261009KR</t>
+  </si>
+  <si>
+    <t>1440897168KR</t>
+  </si>
+  <si>
+    <t>260904-F00014277</t>
+  </si>
+  <si>
+    <t>260910-F00005337-1</t>
+  </si>
+  <si>
+    <t>260917-F00005760</t>
+  </si>
+  <si>
+    <t>260922-F00010008</t>
+  </si>
+  <si>
+    <t>260925-W00012500</t>
+  </si>
+  <si>
+    <t>260929-F00003490</t>
+  </si>
+  <si>
+    <t>260929-F00008533</t>
+  </si>
+  <si>
+    <t>260929-F00010236</t>
+  </si>
+  <si>
+    <t>260929-F00011378</t>
+  </si>
+  <si>
+    <t>260930-F00009660-1</t>
+  </si>
+  <si>
+    <t>260930-F00012371</t>
+  </si>
+  <si>
+    <t>261001-F00006535</t>
+  </si>
+  <si>
+    <t>261001-F00007724</t>
+  </si>
+  <si>
+    <t>261001-W00012996</t>
+  </si>
+  <si>
+    <t>261002-W00007466</t>
+  </si>
+  <si>
+    <t>261002-W00012830</t>
+  </si>
+  <si>
+    <t>261003-F00001559</t>
+  </si>
+  <si>
+    <t>261003-F00001575</t>
+  </si>
+  <si>
+    <t>261003-F00007433</t>
+  </si>
+  <si>
+    <t>261003-W00006247</t>
+  </si>
+  <si>
+    <t>261004-W00001838</t>
+  </si>
+  <si>
+    <t>261004-W00005124</t>
+  </si>
+  <si>
+    <t>261005-F00010494</t>
+  </si>
+  <si>
+    <t>261005-F00011958-1</t>
+  </si>
+  <si>
+    <t>261005-W00004206</t>
+  </si>
+  <si>
+    <t>261005-W00014805</t>
+  </si>
+  <si>
+    <t>261006-F00001861</t>
+  </si>
+  <si>
+    <t>261006-F00011736</t>
+  </si>
+  <si>
+    <t>261006-F00012986</t>
+  </si>
+  <si>
+    <t>261006-F00015092</t>
+  </si>
+  <si>
+    <t>261006-F00016222</t>
+  </si>
+  <si>
+    <t>261006-W00003113</t>
+  </si>
+  <si>
+    <t>261006-W00003405</t>
+  </si>
+  <si>
+    <t>261006-W00004402</t>
+  </si>
+  <si>
+    <t>261006-W00007203</t>
+  </si>
+  <si>
+    <t>261006-W00009406</t>
+  </si>
+  <si>
+    <t>261006-W00009537</t>
+  </si>
+  <si>
+    <t>261007-F00000471</t>
+  </si>
+  <si>
+    <t>261007-F00002041</t>
+  </si>
+  <si>
+    <t>261007-F00006777</t>
+  </si>
+  <si>
+    <t>261007-F00007630</t>
+  </si>
+  <si>
+    <t>261007-F00008963</t>
+  </si>
+  <si>
+    <t>261007-F00010341</t>
+  </si>
+  <si>
+    <t>261007-F00010740</t>
+  </si>
+  <si>
+    <t>261007-F00011963</t>
+  </si>
+  <si>
+    <t>261007-F00013772</t>
+  </si>
+  <si>
+    <t>261007-F00013855</t>
+  </si>
+  <si>
+    <t>261007-F00015429</t>
+  </si>
+  <si>
+    <t>261007-W00003134</t>
+  </si>
+  <si>
+    <t>261007-W00006483</t>
+  </si>
+  <si>
+    <t>261007-W00007037</t>
+  </si>
+  <si>
+    <t>261007-W00007555</t>
+  </si>
+  <si>
+    <t>261007-W00008462</t>
+  </si>
+  <si>
+    <t>261007-W00008580</t>
+  </si>
+  <si>
+    <t>261007-W00008593</t>
+  </si>
+  <si>
+    <t>261007-W00009070</t>
+  </si>
+  <si>
+    <t>261007-W00011748</t>
+  </si>
+  <si>
+    <t>261007-W00012936</t>
+  </si>
+  <si>
+    <t>261007-W00014383</t>
+  </si>
+  <si>
+    <t>261008-F00000725</t>
+  </si>
+  <si>
+    <t>261008-F00001151</t>
+  </si>
+  <si>
+    <t>261008-F00001211</t>
+  </si>
+  <si>
+    <t>261008-F00002085</t>
+  </si>
+  <si>
+    <t>261008-F00003190</t>
+  </si>
+  <si>
+    <t>261008-F00004163</t>
+  </si>
+  <si>
+    <t>261008-F00006730</t>
+  </si>
+  <si>
+    <t>261008-F00006945</t>
+  </si>
+  <si>
+    <t>261008-F00007488</t>
+  </si>
+  <si>
+    <t>261008-F00007680</t>
+  </si>
+  <si>
+    <t>261008-F00008826</t>
+  </si>
+  <si>
+    <t>261008-F00011904</t>
+  </si>
+  <si>
+    <t>261008-F00012736</t>
+  </si>
+  <si>
+    <t>261008-F00014692</t>
+  </si>
+  <si>
+    <t>261008-F00015668</t>
+  </si>
+  <si>
+    <t>261008-W00001778</t>
+  </si>
+  <si>
+    <t>261008-W00003691</t>
+  </si>
+  <si>
+    <t>261008-W00004592</t>
+  </si>
+  <si>
+    <t>261008-W00005795</t>
+  </si>
+  <si>
+    <t>261008-W00006047</t>
+  </si>
+  <si>
+    <t>261008-W00007411</t>
+  </si>
+  <si>
+    <t>261008-W00007721</t>
+  </si>
+  <si>
+    <t>261008-W00009336</t>
+  </si>
+  <si>
+    <t>261008-W00010330</t>
+  </si>
+  <si>
+    <t>261008-W00012127</t>
+  </si>
+  <si>
+    <t>261008-W00013413</t>
+  </si>
+  <si>
+    <t>261008-W00013628</t>
+  </si>
+  <si>
+    <t>261008-W00013853</t>
+  </si>
+  <si>
+    <t>261008-W00013952</t>
+  </si>
+  <si>
+    <t>261008-W00015069</t>
+  </si>
+  <si>
+    <t>261008-W00015138</t>
+  </si>
+  <si>
+    <t>261009-F00001009</t>
+  </si>
+  <si>
+    <t>261009-F00002169</t>
+  </si>
+  <si>
+    <t>261009-F00005096</t>
+  </si>
+  <si>
+    <t>261009-F00005275-1</t>
+  </si>
+  <si>
+    <t>261009-F00005658</t>
+  </si>
+  <si>
+    <t>261009-W00000641</t>
+  </si>
+  <si>
+    <t>261009-W00003215</t>
+  </si>
+  <si>
+    <t>261009-W00005491</t>
+  </si>
+  <si>
+    <t>261009-W00005547</t>
+  </si>
+  <si>
+    <t>261009-W00005840</t>
+  </si>
+  <si>
+    <t>261009-W00006116</t>
+  </si>
+  <si>
+    <t>267014374</t>
+  </si>
+  <si>
+    <t>267014418</t>
+  </si>
+  <si>
+    <t>267014427</t>
+  </si>
+  <si>
+    <t>267014439</t>
+  </si>
+  <si>
+    <t>267014449</t>
+  </si>
+  <si>
+    <t>267014512</t>
+  </si>
+  <si>
+    <t>26MPE0010586</t>
+  </si>
+  <si>
+    <t>26MPE0010677</t>
+  </si>
+  <si>
+    <t>330115391</t>
+  </si>
+  <si>
+    <t>330382099</t>
+  </si>
+  <si>
+    <t>330382642</t>
+  </si>
+  <si>
+    <t>330557977</t>
+  </si>
+  <si>
+    <t>331182366</t>
+  </si>
+  <si>
+    <t>331280653</t>
+  </si>
+  <si>
+    <t>331622473</t>
+  </si>
+  <si>
+    <t>331622969</t>
+  </si>
+  <si>
+    <t>331821838</t>
+  </si>
+  <si>
+    <t>331879411</t>
+  </si>
+  <si>
+    <t>331989799</t>
+  </si>
+  <si>
+    <t>331989953</t>
+  </si>
+  <si>
+    <t>331990020</t>
+  </si>
+  <si>
+    <t>331990234</t>
+  </si>
+  <si>
+    <t>331990255</t>
+  </si>
+  <si>
+    <t>332109879</t>
+  </si>
+  <si>
+    <t>332110303</t>
+  </si>
+  <si>
+    <t>332110370</t>
+  </si>
+  <si>
+    <t>332110500</t>
+  </si>
+  <si>
+    <t>332156821</t>
+  </si>
+  <si>
+    <t>332156867</t>
+  </si>
+  <si>
+    <t>332156995</t>
+  </si>
+  <si>
+    <t>332157133</t>
+  </si>
+  <si>
+    <t>332157447</t>
+  </si>
+  <si>
+    <t>332157539</t>
+  </si>
+  <si>
+    <t>332206466</t>
+  </si>
+  <si>
+    <t>332207015</t>
+  </si>
+  <si>
+    <t>332207155</t>
+  </si>
+  <si>
+    <t>332251239</t>
+  </si>
+  <si>
+    <t>332251305</t>
+  </si>
+  <si>
+    <t>332251418</t>
+  </si>
+  <si>
+    <t>332251556</t>
+  </si>
+  <si>
+    <t>332251603</t>
+  </si>
+  <si>
+    <t>332251652</t>
+  </si>
+  <si>
+    <t>332251822</t>
+  </si>
+  <si>
+    <t>332251951</t>
+  </si>
+  <si>
+    <t>332252014</t>
+  </si>
+  <si>
+    <t>332252055</t>
+  </si>
+  <si>
+    <t>332311777</t>
+  </si>
+  <si>
+    <t>332311843</t>
+  </si>
+  <si>
+    <t>332360546</t>
+  </si>
+  <si>
+    <t>332360787</t>
+  </si>
+  <si>
+    <t>332360811</t>
+  </si>
+  <si>
+    <t>332360892</t>
+  </si>
+  <si>
+    <t>332361134</t>
+  </si>
+  <si>
+    <t>332361186</t>
+  </si>
+  <si>
+    <t>332361287</t>
+  </si>
+  <si>
+    <t>332361354</t>
+  </si>
+  <si>
+    <t>332415310</t>
+  </si>
+  <si>
+    <t>332443692</t>
+  </si>
+  <si>
+    <t>441130437</t>
+  </si>
+  <si>
+    <t>99003454</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-A2PD</t>
+  </si>
+  <si>
+    <t>NFD6-10-04-J8RW</t>
+  </si>
+  <si>
+    <t>NFD6-10-06-4ZU7</t>
+  </si>
+  <si>
+    <t>NFD6-10-08-2H93</t>
+  </si>
+  <si>
+    <t>NFD6-10-08-4PKE</t>
+  </si>
+  <si>
+    <t>NFD6-10-08-749Z</t>
+  </si>
+  <si>
+    <t>NFD6-10-08-CCN3</t>
+  </si>
+  <si>
+    <t>NFD6-10-08-H6VQ</t>
+  </si>
+  <si>
+    <t>NFD6-10-08-HSLB</t>
+  </si>
+  <si>
+    <t>NFD6-10-08-T94G</t>
+  </si>
+  <si>
+    <t>NFE6-10-03-FGZK</t>
+  </si>
+  <si>
+    <t>NFE6-10-05-QY5G</t>
+  </si>
+  <si>
+    <t>NFE6-10-08-6SZ5</t>
+  </si>
+  <si>
+    <t>NFE6-10-08-MPCN</t>
+  </si>
+  <si>
+    <t>SA26/H007160</t>
+  </si>
+  <si>
+    <t>SA26/H007193</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>K-963</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-803</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>K-918</t>
+  </si>
+  <si>
+    <t>K-953</t>
+  </si>
+  <si>
+    <t>K-981</t>
+  </si>
+  <si>
+    <t>K-982</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>K-912</t>
+  </si>
+  <si>
+    <t>K-929</t>
+  </si>
+  <si>
+    <t>K-921</t>
+  </si>
+  <si>
+    <t>K-991</t>
+  </si>
+  <si>
+    <t>K-964</t>
+  </si>
+  <si>
+    <t>SZ-809</t>
+  </si>
+  <si>
+    <t>K-902</t>
+  </si>
+  <si>
+    <t>K-983</t>
+  </si>
+  <si>
+    <t>K-961</t>
+  </si>
+  <si>
+    <t>K-942</t>
+  </si>
+  <si>
+    <t>SZ-828</t>
+  </si>
+  <si>
+    <t>K-992</t>
+  </si>
+  <si>
+    <t>SZ-870</t>
+  </si>
+  <si>
+    <t>K-911</t>
+  </si>
+  <si>
+    <t>K-925</t>
+  </si>
+  <si>
+    <t>K-999</t>
+  </si>
+  <si>
+    <t>K-930</t>
+  </si>
+  <si>
+    <t>K-973</t>
+  </si>
+  <si>
+    <t>SZ-827</t>
+  </si>
+  <si>
+    <t>K-931</t>
+  </si>
+  <si>
+    <t>K-943</t>
+  </si>
+  <si>
+    <t>K-962</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>K-952</t>
+  </si>
+  <si>
+    <t>K-915</t>
+  </si>
+  <si>
+    <t>K-9131</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>K-998</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-812</t>
+  </si>
+  <si>
+    <t>K-933</t>
+  </si>
+  <si>
+    <t>K-951</t>
+  </si>
+  <si>
+    <t>K-971</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-807</t>
+  </si>
+  <si>
+    <t>SZ-800</t>
+  </si>
+  <si>
+    <t>K-941</t>
+  </si>
+  <si>
+    <t>159995579544967208</t>
+  </si>
+  <si>
+    <t>159995579544967215</t>
+  </si>
+  <si>
+    <t>1020261009KR/1</t>
+  </si>
+  <si>
+    <t>1040965392/1</t>
+  </si>
+  <si>
+    <t>1040965392/2</t>
+  </si>
+  <si>
+    <t>1040965392/3</t>
+  </si>
+  <si>
+    <t>1440897168KR/1</t>
+  </si>
+  <si>
+    <t>248747565/1</t>
+  </si>
+  <si>
+    <t>6ac797fb7c818f22ee6ef711</t>
+  </si>
+  <si>
+    <t>6ab39704219e3d74bbe3a439</t>
+  </si>
+  <si>
+    <t>6aabbdb9f7fbdc73ea0a9068</t>
+  </si>
+  <si>
+    <t>6aabbdb9f7fbdc73ea0a906a</t>
+  </si>
+  <si>
+    <t>6ac79bdc7c818f22ee6ef7c6</t>
+  </si>
+  <si>
+    <t>6ac6205d219e3d74bbe4e06b</t>
+  </si>
+  <si>
+    <t>6ac66ffa219e3d74bbe4ecf8</t>
+  </si>
+  <si>
+    <t>6ac66ffa219e3d74bbe4ecf9</t>
+  </si>
+  <si>
+    <t>6abe0dfd219e3d74bbe46130</t>
+  </si>
+  <si>
+    <t>6ab92f86219e3d74bbe400c9</t>
+  </si>
+  <si>
+    <t>6ac63524219e3d74bbe4e3f9</t>
+  </si>
+  <si>
+    <t>6ac8b7987c818f22ee6f09dc</t>
+  </si>
+  <si>
+    <t>6ac771ec7c818f22ee6eef55</t>
+  </si>
+  <si>
+    <t>6ac64174219e3d74bbe4e61c</t>
+  </si>
+  <si>
+    <t>6ac4e4e3219e3d74bbe4c8a8</t>
+  </si>
+  <si>
+    <t>6ac776207c818f22ee6ef02c</t>
+  </si>
+  <si>
+    <t>6ac774fa7c818f22ee6eefea</t>
+  </si>
+  <si>
+    <t>6ac7aee47c818f22ee6efb54</t>
+  </si>
+  <si>
+    <t>6ac7a9087c818f22ee6efa8f</t>
+  </si>
+  <si>
+    <t>6ac604a0219e3d74bbe4db65</t>
+  </si>
+  <si>
+    <t>6ac64794219e3d74bbe4e708</t>
+  </si>
+  <si>
+    <t>6abe143e219e3d74bbe46252</t>
+  </si>
+  <si>
+    <t>6abee867219e3d74bbe474d7</t>
+  </si>
+  <si>
+    <t>6ac785b47c818f22ee6ef315</t>
+  </si>
+  <si>
+    <t>6ac7479b7c818f22ee6ee5b0</t>
+  </si>
+  <si>
+    <t>6abfad3e219e3d74bbe4839c</t>
+  </si>
+  <si>
+    <t>6ac009d5219e3d74bbe48a15</t>
+  </si>
+  <si>
+    <t>6ac733cf7c818f22ee6ee2e2</t>
+  </si>
+  <si>
+    <t>6ac0bd1e219e3d74bbe48d2a</t>
+  </si>
+  <si>
+    <t>6ac3ba5f219e3d74bbe4b54c</t>
+  </si>
+  <si>
+    <t>6ac15da2219e3d74bbe496f5</t>
+  </si>
+  <si>
+    <t>6ac0f43a219e3d74bbe4924d</t>
+  </si>
+  <si>
+    <t>6ac0f43a219e3d74bbe4924e</t>
+  </si>
+  <si>
+    <t>6ac10111219e3d74bbe492ec</t>
+  </si>
+  <si>
+    <t>6ac894087c818f22ee6f02fc</t>
+  </si>
+  <si>
+    <t>6ac1f858219e3d74bbe497e1</t>
+  </si>
+  <si>
+    <t>6ac2285f219e3d74bbe49a8f</t>
+  </si>
+  <si>
+    <t>6ac2285f219e3d74bbe49a91</t>
+  </si>
+  <si>
+    <t>6ac8c6cf7c818f22ee6f0cca</t>
+  </si>
+  <si>
+    <t>6ac3afde219e3d74bbe4b373</t>
+  </si>
+  <si>
+    <t>6ac7b2127c818f22ee6efbb1</t>
+  </si>
+  <si>
+    <t>6ac7b2127c818f22ee6efbb2</t>
+  </si>
+  <si>
+    <t>6ac36beb219e3d74bbe4a8e8</t>
+  </si>
+  <si>
+    <t>6ac41369219e3d74bbe4ba33</t>
+  </si>
+  <si>
+    <t>6ac6545c219e3d74bbe4e905</t>
+  </si>
+  <si>
+    <t>6ac7c3c37c818f22ee6efda2</t>
+  </si>
+  <si>
+    <t>6ac4e9dd219e3d74bbe4c99e</t>
+  </si>
+  <si>
+    <t>6ac4f91c219e3d74bbe4cc97</t>
+  </si>
+  <si>
+    <t>6ac50612219e3d74bbe4cf1e</t>
+  </si>
+  <si>
+    <t>6ac525a3219e3d74bbe4d294</t>
+  </si>
+  <si>
+    <t>6ac541be219e3d74bbe4d49a</t>
+  </si>
+  <si>
+    <t>6ac48af3219e3d74bbe4ba8f</t>
+  </si>
+  <si>
+    <t>6ac4aa9a219e3d74bbe4bdfa</t>
+  </si>
+  <si>
+    <t>6ac4af45219e3d74bbe4bee2</t>
+  </si>
+  <si>
+    <t>6ac4cdce219e3d74bbe4c4e2</t>
+  </si>
+  <si>
+    <t>6ac4e8ab219e3d74bbe4c968</t>
+  </si>
+  <si>
+    <t>6ac4ec3e219e3d74bbe4ca07</t>
+  </si>
+  <si>
+    <t>6ac4f592219e3d74bbe4cbe5</t>
+  </si>
+  <si>
+    <t>6ac509b9219e3d74bbe4cf72</t>
+  </si>
+  <si>
+    <t>6ac509b9219e3d74bbe4cf73</t>
+  </si>
+  <si>
+    <t>6ac50e2e219e3d74bbe4d026</t>
+  </si>
+  <si>
+    <t>6ac5e4a0219e3d74bbe4d636</t>
+  </si>
+  <si>
+    <t>6ac8c6ed7c818f22ee6f0ccd</t>
+  </si>
+  <si>
+    <t>6ac61e11219e3d74bbe4e017</t>
+  </si>
+  <si>
+    <t>6ac62afd219e3d74bbe4e22a</t>
+  </si>
+  <si>
+    <t>6ac63206219e3d74bbe4e36c</t>
+  </si>
+  <si>
+    <t>6ac63904219e3d74bbe4e478</t>
+  </si>
+  <si>
+    <t>6ac64035219e3d74bbe4e5d3</t>
+  </si>
+  <si>
+    <t>6ac64263219e3d74bbe4e632</t>
+  </si>
+  <si>
+    <t>6ac64263219e3d74bbe4e633</t>
+  </si>
+  <si>
+    <t>6ac7a1d07c818f22ee6ef8e9</t>
+  </si>
+  <si>
+    <t>6ac7a1d07c818f22ee6ef8ea</t>
+  </si>
+  <si>
+    <t>6ac65c34219e3d74bbe4ea4e</t>
+  </si>
+  <si>
+    <t>6ac65fb1219e3d74bbe4eabc</t>
+  </si>
+  <si>
+    <t>6ac65e87219e3d74bbe4ea8c</t>
+  </si>
+  <si>
+    <t>6ac65e87219e3d74bbe4ea8d</t>
+  </si>
+  <si>
+    <t>6ac6658e219e3d74bbe4eb85</t>
+  </si>
+  <si>
+    <t>6ac6739c219e3d74bbe4ed70</t>
+  </si>
+  <si>
+    <t>6ac8c1b57c818f22ee6f0be5</t>
+  </si>
+  <si>
+    <t>6ac630d8219e3d74bbe4e320</t>
+  </si>
+  <si>
+    <t>6ac64397219e3d74bbe4e667</t>
+  </si>
+  <si>
+    <t>6ac64264219e3d74bbe4e636</t>
+  </si>
+  <si>
+    <t>6ac645eb219e3d74bbe4e6a9</t>
+  </si>
+  <si>
+    <t>6ac64f54219e3d74bbe4e82d</t>
+  </si>
+  <si>
+    <t>6ac64f54219e3d74bbe4e82e</t>
+  </si>
+  <si>
+    <t>6ac6506f219e3d74bbe4e862</t>
+  </si>
+  <si>
+    <t>6ac651a2219e3d74bbe4e8a4</t>
+  </si>
+  <si>
+    <t>6ac66337219e3d74bbe4eb44</t>
+  </si>
+  <si>
+    <t>6ac69ef4219e3d74bbe4f1bb</t>
+  </si>
+  <si>
+    <t>6ac68081219e3d74bbe4eee0</t>
+  </si>
+  <si>
+    <t>6ac6b14b7c818f22ee6ee1c3</t>
+  </si>
+  <si>
+    <t>6ac6b14b7c818f22ee6ee1c4</t>
+  </si>
+  <si>
+    <t>6ac6a27c219e3d74bbe4f1fa</t>
+  </si>
+  <si>
+    <t>6ac73fa07c818f22ee6ee453</t>
+  </si>
+  <si>
+    <t>6ac73fa07c818f22ee6ee454</t>
+  </si>
+  <si>
+    <t>6ac7455e7c818f22ee6ee526</t>
+  </si>
+  <si>
+    <t>6ac744727c818f22ee6ee519</t>
+  </si>
+  <si>
+    <t>6ac74b3f7c818f22ee6ee6a9</t>
+  </si>
+  <si>
+    <t>6ac74ebc7c818f22ee6ee744</t>
+  </si>
+  <si>
+    <t>6ac7549d7c818f22ee6ee8c6</t>
+  </si>
+  <si>
+    <t>6ac762ac7c818f22ee6eec05</t>
+  </si>
+  <si>
+    <t>6ac762ac7c818f22ee6eec08</t>
+  </si>
+  <si>
+    <t>6ac762ac7c818f22ee6eec0a</t>
+  </si>
+  <si>
+    <t>6ac75cd57c818f22ee6eea99</t>
+  </si>
+  <si>
+    <t>6ac75cd57c818f22ee6eea9a</t>
+  </si>
+  <si>
+    <t>6ac76ae17c818f22ee6eedc7</t>
+  </si>
+  <si>
+    <t>6ac76ae17c818f22ee6eedca</t>
+  </si>
+  <si>
+    <t>6ac768907c818f22ee6eed5f</t>
+  </si>
+  <si>
+    <t>6ac76f917c818f22ee6eeeca</t>
+  </si>
+  <si>
+    <t>6ac773247c818f22ee6eef7f</t>
+  </si>
+  <si>
+    <t>6ac7757b7c818f22ee6eeff3</t>
+  </si>
+  <si>
+    <t>6ac77ed07c818f22ee6ef1e3</t>
+  </si>
+  <si>
+    <t>6ac7895e7c818f22ee6ef3ca</t>
+  </si>
+  <si>
+    <t>6ac79af97c818f22ee6ef7b5</t>
+  </si>
+  <si>
+    <t>6ac79c1b7c818f22ee6ef7e1</t>
+  </si>
+  <si>
+    <t>6ac79c1b7c818f22ee6ef7e2</t>
+  </si>
+  <si>
+    <t>6ac7a45c7c818f22ee6ef969</t>
+  </si>
+  <si>
+    <t>6ac7a45c7c818f22ee6ef96c</t>
+  </si>
+  <si>
+    <t>6ac7bcef7c818f22ee6efcf4</t>
+  </si>
+  <si>
+    <t>6ac7bcef7c818f22ee6efcf5</t>
+  </si>
+  <si>
+    <t>6ac7bcef7c818f22ee6efcf6</t>
+  </si>
+  <si>
+    <t>6ac7bcef7c818f22ee6efcf7</t>
+  </si>
+  <si>
+    <t>6ac7c2c37c818f22ee6efd9a</t>
+  </si>
+  <si>
+    <t>6ac7d6b27c818f22ee6eff38</t>
+  </si>
+  <si>
+    <t>6ac7304a7c818f22ee6ee2b3</t>
+  </si>
+  <si>
+    <t>6ac73bff7c818f22ee6ee3b5</t>
+  </si>
+  <si>
+    <t>6ac7549e7c818f22ee6ee8e0</t>
+  </si>
+  <si>
+    <t>6ac760527c818f22ee6eeb7e</t>
+  </si>
+  <si>
+    <t>6ac762ac7c818f22ee6eebff</t>
+  </si>
+  <si>
+    <t>6ac76f987c818f22ee6eeed5</t>
+  </si>
+  <si>
+    <t>6ac774f97c818f22ee6eefe7</t>
+  </si>
+  <si>
+    <t>6ac7882c7c818f22ee6ef388</t>
+  </si>
+  <si>
+    <t>6ac7895e7c818f22ee6ef3c4</t>
+  </si>
+  <si>
+    <t>6ac78cdc7c818f22ee6ef496</t>
+  </si>
+  <si>
+    <t>6ac7a1fd7c818f22ee6ef929</t>
+  </si>
+  <si>
+    <t>6ac7b0077c818f22ee6efb6b</t>
+  </si>
+  <si>
+    <t>6ac7b12e7c818f22ee6efba2</t>
+  </si>
+  <si>
+    <t>6ac7b5dd7c818f22ee6efc2e</t>
+  </si>
+  <si>
+    <t>6ac7ca137c818f22ee6efe3a</t>
+  </si>
+  <si>
+    <t>6ac7ddc17c818f22ee6effca</t>
+  </si>
+  <si>
+    <t>6ac7dc9e7c818f22ee6effc1</t>
+  </si>
+  <si>
+    <t>6ac7def27c818f22ee6effdf</t>
+  </si>
+  <si>
+    <t>6ac7e5ee7c818f22ee6f0032</t>
+  </si>
+  <si>
+    <t>6ac7e5ee7c818f22ee6f0033</t>
+  </si>
+  <si>
+    <t>6ac7e3967c818f22ee6f000a</t>
+  </si>
+  <si>
+    <t>6ac7e3967c818f22ee6f000b</t>
+  </si>
+  <si>
+    <t>6ac7f8c07c818f22ee6f00d7</t>
+  </si>
+  <si>
+    <t>6ac7f8c07c818f22ee6f00d8</t>
+  </si>
+  <si>
+    <t>6ac7f8c07c818f22ee6f00db</t>
+  </si>
+  <si>
+    <t>6ac7f8c07c818f22ee6f00dc</t>
+  </si>
+  <si>
+    <t>6ac896ea7c818f22ee6f0355</t>
+  </si>
+  <si>
+    <t>6ac898107c818f22ee6f0367</t>
+  </si>
+  <si>
+    <t>6ac898107c818f22ee6f0368</t>
+  </si>
+  <si>
+    <t>6ac8a0437c818f22ee6f0567</t>
+  </si>
+  <si>
+    <t>6ac8a0437c818f22ee6f0568</t>
+  </si>
+  <si>
+    <t>6ac8a07f7c818f22ee6f0595</t>
+  </si>
+  <si>
+    <t>6ac8b6827c818f22ee6f09b3</t>
+  </si>
+  <si>
+    <t>6ac8b7b37c818f22ee6f09f0</t>
+  </si>
+  <si>
+    <t>6ac8b7b37c818f22ee6f09f3</t>
+  </si>
+  <si>
+    <t>6ac8ba0b7c818f22ee6f0a8d</t>
+  </si>
+  <si>
+    <t>6ac8ba0b7c818f22ee6f0a8e</t>
+  </si>
+  <si>
+    <t>6ac8634e7c818f22ee6f015d</t>
+  </si>
+  <si>
+    <t>6ac89a7b7c818f22ee6f0441</t>
+  </si>
+  <si>
+    <t>6ac89a7b7c818f22ee6f0443</t>
+  </si>
+  <si>
+    <t>6ac8a03f7c818f22ee6f0564</t>
+  </si>
+  <si>
+    <t>6ac8bcf97c818f22ee6f0b17</t>
+  </si>
+  <si>
+    <t>6ac8beba7c818f22ee6f0b73</t>
+  </si>
+  <si>
+    <t>6ac8bebb7c818f22ee6f0b78</t>
+  </si>
+  <si>
+    <t>6ac8c49b7c818f22ee6f0c79</t>
+  </si>
+  <si>
+    <t>6ac8c49b7c818f22ee6f0c7a</t>
+  </si>
+  <si>
+    <t>6ac8c6f17c818f22ee6f0cd7</t>
+  </si>
+  <si>
+    <t>6ac8c8197c818f22ee6f0d36</t>
+  </si>
+  <si>
+    <t>1449-395482</t>
+  </si>
+  <si>
+    <t>1449-241218</t>
+  </si>
+  <si>
+    <t>1449-595437</t>
+  </si>
+  <si>
+    <t>1449-675375</t>
+  </si>
+  <si>
+    <t>1449-638007</t>
+  </si>
+  <si>
+    <t>1449-131895</t>
+  </si>
+  <si>
+    <t>26MPE0010586/1</t>
+  </si>
+  <si>
+    <t>26MPE0010677/1</t>
+  </si>
+  <si>
+    <t>326667587/1</t>
+  </si>
+  <si>
+    <t>327812873/1</t>
+  </si>
+  <si>
+    <t>328443663/1</t>
+  </si>
+  <si>
+    <t>329583693/1</t>
+  </si>
+  <si>
+    <t>329788785/1</t>
+  </si>
+  <si>
+    <t>329788785/2</t>
+  </si>
+  <si>
+    <t>330052176/1</t>
+  </si>
+  <si>
+    <t>330115391/1</t>
+  </si>
+  <si>
+    <t>330184482/1</t>
+  </si>
+  <si>
+    <t>330277769/1</t>
+  </si>
+  <si>
+    <t>330382099/1</t>
+  </si>
+  <si>
+    <t>330382642/1</t>
+  </si>
+  <si>
+    <t>330557977/1</t>
+  </si>
+  <si>
+    <t>330669867/1</t>
+  </si>
+  <si>
+    <t>330669867/2</t>
+  </si>
+  <si>
+    <t>330670402/1</t>
+  </si>
+  <si>
+    <t>330795579/1</t>
+  </si>
+  <si>
+    <t>331182366/1</t>
+  </si>
+  <si>
+    <t>331182366/2</t>
+  </si>
+  <si>
+    <t>331280653/1</t>
+  </si>
+  <si>
+    <t>331365412/1</t>
+  </si>
+  <si>
+    <t>331547742/1</t>
+  </si>
+  <si>
+    <t>331622473/1</t>
+  </si>
+  <si>
+    <t>331622473/2</t>
+  </si>
+  <si>
+    <t>331622473/3</t>
+  </si>
+  <si>
+    <t>331622969/1</t>
+  </si>
+  <si>
+    <t>331623072/1</t>
+  </si>
+  <si>
+    <t>331623135/1</t>
+  </si>
+  <si>
+    <t>331623135/2</t>
+  </si>
+  <si>
+    <t>331623135/3</t>
+  </si>
+  <si>
+    <t>331720661/1</t>
+  </si>
+  <si>
+    <t>331821359/1</t>
+  </si>
+  <si>
+    <t>331821359/2</t>
+  </si>
+  <si>
+    <t>331821838/1</t>
+  </si>
+  <si>
+    <t>331821838/2</t>
+  </si>
+  <si>
+    <t>331879411/1</t>
+  </si>
+  <si>
+    <t>331879441/1</t>
+  </si>
+  <si>
+    <t>331879441/2</t>
+  </si>
+  <si>
+    <t>331879699/1</t>
+  </si>
+  <si>
+    <t>331879699/2</t>
+  </si>
+  <si>
+    <t>331880257/1</t>
+  </si>
+  <si>
+    <t>331989799/1</t>
+  </si>
+  <si>
+    <t>331989799/2</t>
+  </si>
+  <si>
+    <t>331989953/1</t>
+  </si>
+  <si>
+    <t>331989984/1</t>
+  </si>
+  <si>
+    <t>331989985/1</t>
+  </si>
+  <si>
+    <t>331990020/1</t>
+  </si>
+  <si>
+    <t>331990042/1</t>
+  </si>
+  <si>
+    <t>331990105/1</t>
+  </si>
+  <si>
+    <t>331990163/1</t>
+  </si>
+  <si>
+    <t>331990234/1</t>
+  </si>
+  <si>
+    <t>331990235/1</t>
+  </si>
+  <si>
+    <t>331990255/1</t>
+  </si>
+  <si>
+    <t>331990303/1</t>
+  </si>
+  <si>
+    <t>331990303/2</t>
+  </si>
+  <si>
+    <t>331990303/3</t>
+  </si>
+  <si>
+    <t>332049257/1</t>
+  </si>
+  <si>
+    <t>332049430/1</t>
+  </si>
+  <si>
+    <t>332049470/1</t>
+  </si>
+  <si>
+    <t>332049503/1</t>
+  </si>
+  <si>
+    <t>332049535/1</t>
+  </si>
+  <si>
+    <t>332049646/1</t>
+  </si>
+  <si>
+    <t>332049794/1</t>
+  </si>
+  <si>
+    <t>332049841/1</t>
+  </si>
+  <si>
+    <t>332049884/1</t>
+  </si>
+  <si>
+    <t>332049951/1</t>
+  </si>
+  <si>
+    <t>332109879/1</t>
+  </si>
+  <si>
+    <t>332109936/1</t>
+  </si>
+  <si>
+    <t>332109965/1</t>
+  </si>
+  <si>
+    <t>332109965/2</t>
+  </si>
+  <si>
+    <t>332110094/1</t>
+  </si>
+  <si>
+    <t>332110218/1</t>
+  </si>
+  <si>
+    <t>332110303/1</t>
+  </si>
+  <si>
+    <t>332110370/1</t>
+  </si>
+  <si>
+    <t>332110500/1</t>
+  </si>
+  <si>
+    <t>332110552/1</t>
+  </si>
+  <si>
+    <t>332110572/1</t>
+  </si>
+  <si>
+    <t>332156821/1</t>
+  </si>
+  <si>
+    <t>332156853/1</t>
+  </si>
+  <si>
+    <t>332156867/1</t>
+  </si>
+  <si>
+    <t>332156995/1</t>
+  </si>
+  <si>
+    <t>332157133/1</t>
+  </si>
+  <si>
+    <t>332157447/1</t>
+  </si>
+  <si>
+    <t>332157455/1</t>
+  </si>
+  <si>
+    <t>332157539/1</t>
+  </si>
+  <si>
+    <t>332206466/1</t>
+  </si>
+  <si>
+    <t>332207015/1</t>
+  </si>
+  <si>
+    <t>332207155/1</t>
+  </si>
+  <si>
+    <t>332207155/2</t>
+  </si>
+  <si>
+    <t>332251239/1</t>
+  </si>
+  <si>
+    <t>332251305/1</t>
+  </si>
+  <si>
+    <t>332251418/1</t>
+  </si>
+  <si>
+    <t>332251556/1</t>
+  </si>
+  <si>
+    <t>332251603/1</t>
+  </si>
+  <si>
+    <t>332251603/2</t>
+  </si>
+  <si>
+    <t>332251652/1</t>
+  </si>
+  <si>
+    <t>332251822/1</t>
+  </si>
+  <si>
+    <t>332251951/1</t>
+  </si>
+  <si>
+    <t>332252014/1</t>
+  </si>
+  <si>
+    <t>332252014/2</t>
+  </si>
+  <si>
+    <t>332252055/1</t>
+  </si>
+  <si>
+    <t>332311777/1</t>
+  </si>
+  <si>
+    <t>332311843/1</t>
+  </si>
+  <si>
+    <t>332360546/1</t>
+  </si>
+  <si>
+    <t>332360787/1</t>
+  </si>
+  <si>
+    <t>332360811/1</t>
+  </si>
+  <si>
+    <t>332360892/1</t>
+  </si>
+  <si>
+    <t>332361134/1</t>
+  </si>
+  <si>
+    <t>332361186/1</t>
+  </si>
+  <si>
+    <t>332361287/1</t>
+  </si>
+  <si>
+    <t>332361354/1</t>
+  </si>
+  <si>
+    <t>332415310/1</t>
+  </si>
+  <si>
+    <t>332443692/1</t>
+  </si>
+  <si>
+    <t>441130437/1</t>
+  </si>
+  <si>
+    <t>441130437/2</t>
+  </si>
+  <si>
+    <t>441130437/3</t>
+  </si>
+  <si>
+    <t>441130437/4</t>
+  </si>
+  <si>
+    <t>99003454/1</t>
+  </si>
+  <si>
+    <t>99003458/1</t>
+  </si>
+  <si>
+    <t>202610092602042001</t>
+  </si>
+  <si>
+    <t>202610092602044001</t>
+  </si>
+  <si>
+    <t>202610072602056101</t>
+  </si>
+  <si>
+    <t>202610092602063001</t>
+  </si>
+  <si>
+    <t>202610092602064101</t>
+  </si>
+  <si>
+    <t>202610092602066801</t>
+  </si>
+  <si>
+    <t>202610092602062901</t>
+  </si>
+  <si>
+    <t>202610092602065401</t>
+  </si>
+  <si>
+    <t>202610092602064801</t>
+  </si>
+  <si>
+    <t>202610092602066301</t>
+  </si>
+  <si>
+    <t>202610092602037801</t>
+  </si>
+  <si>
+    <t>202610062602046901</t>
+  </si>
+  <si>
+    <t>202610092602063101</t>
+  </si>
+  <si>
+    <t>202610092602062101</t>
+  </si>
+  <si>
+    <t>159995579544935238</t>
+  </si>
+  <si>
+    <t>159995579544935245</t>
+  </si>
+  <si>
+    <t>159995579544964559</t>
+  </si>
+  <si>
+    <t>159995579544964566</t>
   </si>
 </sst>
 </file>
@@ -346,9 +2011,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -665,7 +2329,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC11F24F-E222-443E-8401-2ECBA69A40D4}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C326"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -685,707 +2349,3578 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>327</v>
+      </c>
+      <c r="C7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C8" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B9" t="s">
+        <v>329</v>
+      </c>
+      <c r="C9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>330</v>
+      </c>
+      <c r="C10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" t="s">
+        <v>331</v>
+      </c>
+      <c r="C11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" t="s">
+        <v>332</v>
+      </c>
+      <c r="C12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" t="s">
+        <v>333</v>
+      </c>
+      <c r="C13" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" t="s">
+        <v>334</v>
+      </c>
+      <c r="C14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B15" t="s">
+        <v>335</v>
+      </c>
+      <c r="C15" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B16" t="s">
+        <v>336</v>
+      </c>
+      <c r="C16" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>337</v>
+      </c>
+      <c r="C17" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B19" t="s">
+        <v>339</v>
+      </c>
+      <c r="C19" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B20" t="s">
+        <v>340</v>
+      </c>
+      <c r="C20" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B22" t="s">
+        <v>342</v>
+      </c>
+      <c r="C22" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" t="s">
+        <v>343</v>
+      </c>
+      <c r="C23" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" t="s">
+        <v>344</v>
+      </c>
+      <c r="C24" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" t="s">
+        <v>345</v>
+      </c>
+      <c r="C25" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B26" t="s">
+        <v>346</v>
+      </c>
+      <c r="C26" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" t="s">
+        <v>347</v>
+      </c>
+      <c r="C27" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" t="s">
+        <v>348</v>
+      </c>
+      <c r="C28" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" t="s">
+        <v>349</v>
+      </c>
+      <c r="C29" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" t="s">
+        <v>350</v>
+      </c>
+      <c r="C30" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B31" t="s">
+        <v>351</v>
+      </c>
+      <c r="C31" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" t="s">
+        <v>352</v>
+      </c>
+      <c r="C32" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>16</v>
       </c>
-      <c r="C11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B33" t="s">
+        <v>353</v>
+      </c>
+      <c r="C33" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B34" t="s">
+        <v>354</v>
+      </c>
+      <c r="C34" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" t="s">
+        <v>355</v>
+      </c>
+      <c r="C35" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" t="s">
+        <v>356</v>
+      </c>
+      <c r="C36" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" t="s">
+        <v>357</v>
+      </c>
+      <c r="C37" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" t="s">
+        <v>358</v>
+      </c>
+      <c r="C38" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>4</v>
       </c>
-      <c r="C13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B39" t="s">
+        <v>359</v>
+      </c>
+      <c r="C39" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" t="s">
+        <v>360</v>
+      </c>
+      <c r="C40" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" t="s">
+        <v>361</v>
+      </c>
+      <c r="C41" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" t="s">
+        <v>362</v>
+      </c>
+      <c r="C42" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>5</v>
       </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B43" t="s">
+        <v>363</v>
+      </c>
+      <c r="C43" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>18</v>
       </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B44" t="s">
+        <v>364</v>
+      </c>
+      <c r="C44" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" t="s">
+        <v>365</v>
+      </c>
+      <c r="C45" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" t="s">
+        <v>366</v>
+      </c>
+      <c r="C46" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" t="s">
+        <v>367</v>
+      </c>
+      <c r="C47" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>19</v>
       </c>
-      <c r="C16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B48" t="s">
+        <v>368</v>
+      </c>
+      <c r="C48" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" t="s">
+        <v>369</v>
+      </c>
+      <c r="C49" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" t="s">
+        <v>370</v>
+      </c>
+      <c r="C50" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51" t="s">
+        <v>371</v>
+      </c>
+      <c r="C51" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" t="s">
+        <v>372</v>
+      </c>
+      <c r="C52" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>119</v>
+      </c>
+      <c r="B53" t="s">
+        <v>373</v>
+      </c>
+      <c r="C53" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>20</v>
       </c>
-      <c r="C17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B54" t="s">
+        <v>374</v>
+      </c>
+      <c r="C54" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" t="s">
+        <v>375</v>
+      </c>
+      <c r="C55" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>21</v>
       </c>
-      <c r="C18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B56" t="s">
+        <v>376</v>
+      </c>
+      <c r="C56" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>121</v>
+      </c>
+      <c r="B57" t="s">
+        <v>377</v>
+      </c>
+      <c r="C57" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" t="s">
+        <v>378</v>
+      </c>
+      <c r="C58" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>123</v>
+      </c>
+      <c r="B59" t="s">
+        <v>379</v>
+      </c>
+      <c r="C59" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>124</v>
+      </c>
+      <c r="B60" t="s">
+        <v>380</v>
+      </c>
+      <c r="C60" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>22</v>
       </c>
-      <c r="C19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B61" t="s">
+        <v>381</v>
+      </c>
+      <c r="C61" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" t="s">
+        <v>382</v>
+      </c>
+      <c r="C62" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" t="s">
+        <v>383</v>
+      </c>
+      <c r="C63" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" t="s">
+        <v>384</v>
+      </c>
+      <c r="C64" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" t="s">
+        <v>385</v>
+      </c>
+      <c r="C65" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>23</v>
       </c>
-      <c r="C20" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B66" t="s">
+        <v>386</v>
+      </c>
+      <c r="C66" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>24</v>
       </c>
-      <c r="C21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B67" t="s">
+        <v>387</v>
+      </c>
+      <c r="C67" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68" t="s">
+        <v>388</v>
+      </c>
+      <c r="C68" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>129</v>
+      </c>
+      <c r="B69" t="s">
+        <v>389</v>
+      </c>
+      <c r="C69" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>130</v>
+      </c>
+      <c r="B70" t="s">
+        <v>390</v>
+      </c>
+      <c r="C70" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" t="s">
+        <v>391</v>
+      </c>
+      <c r="C71" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>132</v>
+      </c>
+      <c r="B72" t="s">
+        <v>392</v>
+      </c>
+      <c r="C72" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>133</v>
+      </c>
+      <c r="B73" t="s">
+        <v>393</v>
+      </c>
+      <c r="C73" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>134</v>
+      </c>
+      <c r="B74" t="s">
+        <v>394</v>
+      </c>
+      <c r="C74" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>135</v>
+      </c>
+      <c r="B75" t="s">
+        <v>395</v>
+      </c>
+      <c r="C75" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>25</v>
       </c>
-      <c r="C22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B76" t="s">
+        <v>396</v>
+      </c>
+      <c r="C76" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>136</v>
+      </c>
+      <c r="B77" t="s">
+        <v>397</v>
+      </c>
+      <c r="C77" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>137</v>
+      </c>
+      <c r="B78" t="s">
+        <v>398</v>
+      </c>
+      <c r="C78" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>137</v>
+      </c>
+      <c r="B79" t="s">
+        <v>399</v>
+      </c>
+      <c r="C79" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>138</v>
+      </c>
+      <c r="B80" t="s">
+        <v>400</v>
+      </c>
+      <c r="C80" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>138</v>
+      </c>
+      <c r="B81" t="s">
+        <v>401</v>
+      </c>
+      <c r="C81" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>139</v>
+      </c>
+      <c r="B82" t="s">
+        <v>402</v>
+      </c>
+      <c r="C82" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>140</v>
+      </c>
+      <c r="B83" t="s">
+        <v>403</v>
+      </c>
+      <c r="C83" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>26</v>
       </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B84" t="s">
+        <v>404</v>
+      </c>
+      <c r="C84" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>26</v>
+      </c>
+      <c r="B85" t="s">
+        <v>405</v>
+      </c>
+      <c r="C85" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>27</v>
       </c>
-      <c r="C24" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B86" t="s">
+        <v>406</v>
+      </c>
+      <c r="C86" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>141</v>
+      </c>
+      <c r="B87" t="s">
+        <v>407</v>
+      </c>
+      <c r="C87" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>142</v>
+      </c>
+      <c r="B88" t="s">
+        <v>408</v>
+      </c>
+      <c r="C88" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>143</v>
+      </c>
+      <c r="B89" t="s">
+        <v>409</v>
+      </c>
+      <c r="C89" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>144</v>
+      </c>
+      <c r="B90" t="s">
+        <v>410</v>
+      </c>
+      <c r="C90" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>145</v>
+      </c>
+      <c r="B91" t="s">
+        <v>411</v>
+      </c>
+      <c r="C91" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>28</v>
       </c>
-      <c r="C25" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="B92" t="s">
+        <v>412</v>
+      </c>
+      <c r="C92" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>146</v>
+      </c>
+      <c r="B93" t="s">
+        <v>413</v>
+      </c>
+      <c r="C93" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>146</v>
+      </c>
+      <c r="B94" t="s">
+        <v>414</v>
+      </c>
+      <c r="C94" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>147</v>
+      </c>
+      <c r="B95" t="s">
+        <v>415</v>
+      </c>
+      <c r="C95" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>148</v>
+      </c>
+      <c r="B96" t="s">
+        <v>416</v>
+      </c>
+      <c r="C96" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>149</v>
+      </c>
+      <c r="B97" t="s">
+        <v>417</v>
+      </c>
+      <c r="C97" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>29</v>
       </c>
-      <c r="C26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B98" t="s">
+        <v>418</v>
+      </c>
+      <c r="C98" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>150</v>
+      </c>
+      <c r="B99" t="s">
+        <v>419</v>
+      </c>
+      <c r="C99" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>151</v>
+      </c>
+      <c r="B100" t="s">
+        <v>420</v>
+      </c>
+      <c r="C100" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>151</v>
+      </c>
+      <c r="B101" t="s">
+        <v>421</v>
+      </c>
+      <c r="C101" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>152</v>
+      </c>
+      <c r="B102" t="s">
+        <v>422</v>
+      </c>
+      <c r="C102" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>153</v>
+      </c>
+      <c r="B103" t="s">
+        <v>423</v>
+      </c>
+      <c r="C103" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>153</v>
+      </c>
+      <c r="B104" t="s">
+        <v>424</v>
+      </c>
+      <c r="C104" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>154</v>
+      </c>
+      <c r="B105" t="s">
+        <v>425</v>
+      </c>
+      <c r="C105" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>155</v>
+      </c>
+      <c r="B106" t="s">
+        <v>426</v>
+      </c>
+      <c r="C106" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>30</v>
       </c>
-      <c r="C27" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B107" t="s">
+        <v>427</v>
+      </c>
+      <c r="C107" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>156</v>
+      </c>
+      <c r="B108" t="s">
+        <v>428</v>
+      </c>
+      <c r="C108" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>157</v>
+      </c>
+      <c r="B109" t="s">
+        <v>429</v>
+      </c>
+      <c r="C109" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>158</v>
+      </c>
+      <c r="B110" t="s">
+        <v>430</v>
+      </c>
+      <c r="C110" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>158</v>
+      </c>
+      <c r="B111" t="s">
+        <v>431</v>
+      </c>
+      <c r="C111" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>158</v>
+      </c>
+      <c r="B112" t="s">
+        <v>432</v>
+      </c>
+      <c r="C112" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>31</v>
       </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B113" t="s">
+        <v>433</v>
+      </c>
+      <c r="C113" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>31</v>
+      </c>
+      <c r="B114" t="s">
+        <v>434</v>
+      </c>
+      <c r="C114" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>32</v>
       </c>
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="B115" t="s">
+        <v>435</v>
+      </c>
+      <c r="C115" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>32</v>
+      </c>
+      <c r="B116" t="s">
+        <v>436</v>
+      </c>
+      <c r="C116" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>33</v>
       </c>
-      <c r="C30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="B117" t="s">
+        <v>437</v>
+      </c>
+      <c r="C117" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>159</v>
+      </c>
+      <c r="B118" t="s">
+        <v>438</v>
+      </c>
+      <c r="C118" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>160</v>
+      </c>
+      <c r="B119" t="s">
+        <v>439</v>
+      </c>
+      <c r="C119" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>161</v>
+      </c>
+      <c r="B120" t="s">
+        <v>440</v>
+      </c>
+      <c r="C120" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>162</v>
+      </c>
+      <c r="B121" t="s">
+        <v>441</v>
+      </c>
+      <c r="C121" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>163</v>
+      </c>
+      <c r="B122" t="s">
+        <v>442</v>
+      </c>
+      <c r="C122" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>34</v>
       </c>
-      <c r="C31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="B123" t="s">
+        <v>443</v>
+      </c>
+      <c r="C123" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>164</v>
+      </c>
+      <c r="B124" t="s">
+        <v>444</v>
+      </c>
+      <c r="C124" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>164</v>
+      </c>
+      <c r="B125" t="s">
+        <v>445</v>
+      </c>
+      <c r="C125" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>165</v>
+      </c>
+      <c r="B126" t="s">
+        <v>446</v>
+      </c>
+      <c r="C126" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>165</v>
+      </c>
+      <c r="B127" t="s">
+        <v>447</v>
+      </c>
+      <c r="C127" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>35</v>
       </c>
-      <c r="C32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="B128" t="s">
+        <v>448</v>
+      </c>
+      <c r="C128" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>35</v>
+      </c>
+      <c r="B129" t="s">
+        <v>449</v>
+      </c>
+      <c r="C129" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>35</v>
+      </c>
+      <c r="B130" t="s">
+        <v>450</v>
+      </c>
+      <c r="C130" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>35</v>
+      </c>
+      <c r="B131" t="s">
+        <v>451</v>
+      </c>
+      <c r="C131" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>166</v>
+      </c>
+      <c r="B132" t="s">
+        <v>452</v>
+      </c>
+      <c r="C132" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>167</v>
+      </c>
+      <c r="B133" t="s">
+        <v>453</v>
+      </c>
+      <c r="C133" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>36</v>
       </c>
-      <c r="C33" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="B134" t="s">
+        <v>454</v>
+      </c>
+      <c r="C134" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>168</v>
+      </c>
+      <c r="B135" t="s">
+        <v>455</v>
+      </c>
+      <c r="C135" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>169</v>
+      </c>
+      <c r="B136" t="s">
+        <v>456</v>
+      </c>
+      <c r="C136" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>37</v>
       </c>
-      <c r="C34" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="B137" t="s">
+        <v>457</v>
+      </c>
+      <c r="C137" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>170</v>
+      </c>
+      <c r="B138" t="s">
+        <v>458</v>
+      </c>
+      <c r="C138" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>171</v>
+      </c>
+      <c r="B139" t="s">
+        <v>459</v>
+      </c>
+      <c r="C139" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>172</v>
+      </c>
+      <c r="B140" t="s">
+        <v>460</v>
+      </c>
+      <c r="C140" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>173</v>
+      </c>
+      <c r="B141" t="s">
+        <v>461</v>
+      </c>
+      <c r="C141" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>38</v>
       </c>
-      <c r="C35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="B142" t="s">
+        <v>462</v>
+      </c>
+      <c r="C142" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>174</v>
+      </c>
+      <c r="B143" t="s">
+        <v>463</v>
+      </c>
+      <c r="C143" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>175</v>
+      </c>
+      <c r="B144" t="s">
+        <v>464</v>
+      </c>
+      <c r="C144" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>39</v>
       </c>
-      <c r="C36" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="B145" t="s">
+        <v>465</v>
+      </c>
+      <c r="C145" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>176</v>
+      </c>
+      <c r="B146" t="s">
+        <v>466</v>
+      </c>
+      <c r="C146" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>40</v>
       </c>
-      <c r="C37" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="B147" t="s">
+        <v>467</v>
+      </c>
+      <c r="C147" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>177</v>
+      </c>
+      <c r="B148" t="s">
+        <v>468</v>
+      </c>
+      <c r="C148" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>41</v>
       </c>
-      <c r="C38" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="B149" t="s">
+        <v>469</v>
+      </c>
+      <c r="C149" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>178</v>
+      </c>
+      <c r="B150" t="s">
+        <v>470</v>
+      </c>
+      <c r="C150" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>179</v>
+      </c>
+      <c r="B151" t="s">
+        <v>471</v>
+      </c>
+      <c r="C151" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>180</v>
+      </c>
+      <c r="B152" t="s">
+        <v>472</v>
+      </c>
+      <c r="C152" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>180</v>
+      </c>
+      <c r="B153" t="s">
+        <v>473</v>
+      </c>
+      <c r="C153" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>181</v>
+      </c>
+      <c r="B154" t="s">
+        <v>474</v>
+      </c>
+      <c r="C154" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>181</v>
+      </c>
+      <c r="B155" t="s">
+        <v>475</v>
+      </c>
+      <c r="C155" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>182</v>
+      </c>
+      <c r="B156" t="s">
+        <v>476</v>
+      </c>
+      <c r="C156" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>182</v>
+      </c>
+      <c r="B157" t="s">
+        <v>477</v>
+      </c>
+      <c r="C157" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>183</v>
+      </c>
+      <c r="B158" t="s">
+        <v>478</v>
+      </c>
+      <c r="C158" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>183</v>
+      </c>
+      <c r="B159" t="s">
+        <v>479</v>
+      </c>
+      <c r="C159" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>184</v>
+      </c>
+      <c r="B160" t="s">
+        <v>480</v>
+      </c>
+      <c r="C160" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
         <v>42</v>
       </c>
-      <c r="C39" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="B161" t="s">
+        <v>481</v>
+      </c>
+      <c r="C161" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>42</v>
+      </c>
+      <c r="B162" t="s">
+        <v>482</v>
+      </c>
+      <c r="C162" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>185</v>
+      </c>
+      <c r="B163" t="s">
+        <v>483</v>
+      </c>
+      <c r="C163" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>185</v>
+      </c>
+      <c r="B164" t="s">
+        <v>484</v>
+      </c>
+      <c r="C164" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
         <v>43</v>
       </c>
-      <c r="C40" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="B165" t="s">
+        <v>485</v>
+      </c>
+      <c r="C165" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>186</v>
+      </c>
+      <c r="B166" t="s">
+        <v>486</v>
+      </c>
+      <c r="C166" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>187</v>
+      </c>
+      <c r="B167" t="s">
+        <v>487</v>
+      </c>
+      <c r="C167" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>187</v>
+      </c>
+      <c r="B168" t="s">
+        <v>488</v>
+      </c>
+      <c r="C168" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>188</v>
+      </c>
+      <c r="B169" t="s">
+        <v>489</v>
+      </c>
+      <c r="C169" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>188</v>
+      </c>
+      <c r="B170" t="s">
+        <v>490</v>
+      </c>
+      <c r="C170" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>189</v>
+      </c>
+      <c r="B171" t="s">
+        <v>491</v>
+      </c>
+      <c r="C171" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
         <v>44</v>
       </c>
-      <c r="C41" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="B172" t="s">
+        <v>492</v>
+      </c>
+      <c r="C172" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>44</v>
+      </c>
+      <c r="B173" t="s">
+        <v>493</v>
+      </c>
+      <c r="C173" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>190</v>
+      </c>
+      <c r="B174" t="s">
+        <v>494</v>
+      </c>
+      <c r="C174" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
         <v>45</v>
       </c>
-      <c r="C42" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="B175" t="s">
+        <v>495</v>
+      </c>
+      <c r="C175" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>191</v>
+      </c>
+      <c r="B176" t="s">
+        <v>496</v>
+      </c>
+      <c r="C176" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>192</v>
+      </c>
+      <c r="B177" t="s">
+        <v>497</v>
+      </c>
+      <c r="C177" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>193</v>
+      </c>
+      <c r="B178" t="s">
+        <v>498</v>
+      </c>
+      <c r="C178" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>193</v>
+      </c>
+      <c r="B179" t="s">
+        <v>499</v>
+      </c>
+      <c r="C179" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
         <v>46</v>
       </c>
-      <c r="C43" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="B180" t="s">
+        <v>500</v>
+      </c>
+      <c r="C180" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>194</v>
+      </c>
+      <c r="B181" t="s">
+        <v>501</v>
+      </c>
+      <c r="C181" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>195</v>
+      </c>
+      <c r="B182" t="s">
+        <v>502</v>
+      </c>
+      <c r="C182" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>196</v>
+      </c>
+      <c r="B183" t="s">
+        <v>503</v>
+      </c>
+      <c r="C183" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>197</v>
+      </c>
+      <c r="B184" t="s">
+        <v>504</v>
+      </c>
+      <c r="C184" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>198</v>
+      </c>
+      <c r="B185" t="s">
+        <v>505</v>
+      </c>
+      <c r="C185" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>199</v>
+      </c>
+      <c r="B186" t="s">
+        <v>506</v>
+      </c>
+      <c r="C186" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>200</v>
+      </c>
+      <c r="B187" t="s">
+        <v>507</v>
+      </c>
+      <c r="C187" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>201</v>
+      </c>
+      <c r="B188" t="s">
+        <v>508</v>
+      </c>
+      <c r="C188" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>202</v>
+      </c>
+      <c r="B189" t="s">
+        <v>509</v>
+      </c>
+      <c r="C189" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
         <v>47</v>
       </c>
-      <c r="C44" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="B190" t="s">
+        <v>510</v>
+      </c>
+      <c r="C190" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
         <v>48</v>
       </c>
-      <c r="C45" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="B191" t="s">
+        <v>511</v>
+      </c>
+      <c r="C191" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
         <v>49</v>
       </c>
-      <c r="C46" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="B192" t="s">
+        <v>512</v>
+      </c>
+      <c r="C192" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
         <v>50</v>
       </c>
-      <c r="C47" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="B193" t="s">
+        <v>513</v>
+      </c>
+      <c r="C193" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
         <v>51</v>
       </c>
-      <c r="C48" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="B194" t="s">
+        <v>514</v>
+      </c>
+      <c r="C194" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>51</v>
+      </c>
+      <c r="B195" t="s">
+        <v>515</v>
+      </c>
+      <c r="C195" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
         <v>52</v>
       </c>
-      <c r="C49" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="B196" t="s">
+        <v>516</v>
+      </c>
+      <c r="C196" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>203</v>
+      </c>
+      <c r="B197" t="s">
+        <v>517</v>
+      </c>
+      <c r="C197" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
         <v>53</v>
       </c>
-      <c r="C50" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="B198" t="s">
+        <v>518</v>
+      </c>
+      <c r="C198" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
         <v>54</v>
       </c>
-      <c r="C51" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="B199" t="s">
+        <v>519</v>
+      </c>
+      <c r="C199" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>204</v>
+      </c>
+      <c r="B200" t="s">
+        <v>520</v>
+      </c>
+      <c r="C200" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>205</v>
+      </c>
+      <c r="B201" t="s">
+        <v>521</v>
+      </c>
+      <c r="C201" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>206</v>
+      </c>
+      <c r="B202" t="s">
+        <v>522</v>
+      </c>
+      <c r="C202" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
         <v>55</v>
       </c>
-      <c r="C52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="B203" t="s">
+        <v>523</v>
+      </c>
+      <c r="C203" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>55</v>
+      </c>
+      <c r="B204" t="s">
+        <v>524</v>
+      </c>
+      <c r="C204" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
         <v>56</v>
       </c>
-      <c r="C53" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="B205" t="s">
+        <v>525</v>
+      </c>
+      <c r="C205" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
         <v>57</v>
       </c>
-      <c r="C54" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="B206" t="s">
+        <v>526</v>
+      </c>
+      <c r="C206" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>207</v>
+      </c>
+      <c r="B207" t="s">
+        <v>527</v>
+      </c>
+      <c r="C207" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>207</v>
+      </c>
+      <c r="B208" t="s">
+        <v>528</v>
+      </c>
+      <c r="C208" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>208</v>
+      </c>
+      <c r="B209" t="s">
+        <v>529</v>
+      </c>
+      <c r="C209" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
         <v>58</v>
       </c>
-      <c r="C55" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="B210" t="s">
+        <v>530</v>
+      </c>
+      <c r="C210" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
         <v>6</v>
       </c>
-      <c r="C56" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="B211" t="s">
+        <v>531</v>
+      </c>
+      <c r="C211" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>209</v>
+      </c>
+      <c r="B212" t="s">
+        <v>532</v>
+      </c>
+      <c r="C212" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>209</v>
+      </c>
+      <c r="B213" t="s">
+        <v>533</v>
+      </c>
+      <c r="C213" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>209</v>
+      </c>
+      <c r="B214" t="s">
+        <v>534</v>
+      </c>
+      <c r="C214" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>210</v>
+      </c>
+      <c r="B215" t="s">
+        <v>535</v>
+      </c>
+      <c r="C215" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
         <v>7</v>
       </c>
-      <c r="C57" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+      <c r="B216" t="s">
+        <v>536</v>
+      </c>
+      <c r="C216" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
         <v>59</v>
       </c>
-      <c r="C58" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="B217" t="s">
+        <v>537</v>
+      </c>
+      <c r="C217" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>59</v>
+      </c>
+      <c r="B218" t="s">
+        <v>538</v>
+      </c>
+      <c r="C218" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>59</v>
+      </c>
+      <c r="B219" t="s">
+        <v>539</v>
+      </c>
+      <c r="C219" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
         <v>60</v>
       </c>
-      <c r="C59" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="B220" t="s">
+        <v>540</v>
+      </c>
+      <c r="C220" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
         <v>61</v>
       </c>
-      <c r="C60" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="B221" t="s">
+        <v>541</v>
+      </c>
+      <c r="C221" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>61</v>
+      </c>
+      <c r="B222" t="s">
+        <v>542</v>
+      </c>
+      <c r="C222" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>211</v>
+      </c>
+      <c r="B223" t="s">
+        <v>543</v>
+      </c>
+      <c r="C223" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>211</v>
+      </c>
+      <c r="B224" t="s">
+        <v>544</v>
+      </c>
+      <c r="C224" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>212</v>
+      </c>
+      <c r="B225" t="s">
+        <v>545</v>
+      </c>
+      <c r="C225" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
         <v>62</v>
       </c>
-      <c r="C61" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="B226" t="s">
+        <v>546</v>
+      </c>
+      <c r="C226" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>62</v>
+      </c>
+      <c r="B227" t="s">
+        <v>547</v>
+      </c>
+      <c r="C227" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
         <v>63</v>
       </c>
-      <c r="C62" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+      <c r="B228" t="s">
+        <v>548</v>
+      </c>
+      <c r="C228" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>63</v>
+      </c>
+      <c r="B229" t="s">
+        <v>549</v>
+      </c>
+      <c r="C229" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
         <v>64</v>
       </c>
-      <c r="C63" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="B230" t="s">
+        <v>550</v>
+      </c>
+      <c r="C230" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>213</v>
+      </c>
+      <c r="B231" t="s">
+        <v>551</v>
+      </c>
+      <c r="C231" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>213</v>
+      </c>
+      <c r="B232" t="s">
+        <v>552</v>
+      </c>
+      <c r="C232" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>214</v>
+      </c>
+      <c r="B233" t="s">
+        <v>553</v>
+      </c>
+      <c r="C233" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
         <v>65</v>
       </c>
-      <c r="C64" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="B234" t="s">
+        <v>554</v>
+      </c>
+      <c r="C234" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
         <v>66</v>
       </c>
-      <c r="C65" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+      <c r="B235" t="s">
+        <v>555</v>
+      </c>
+      <c r="C235" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>215</v>
+      </c>
+      <c r="B236" t="s">
+        <v>556</v>
+      </c>
+      <c r="C236" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
         <v>67</v>
       </c>
-      <c r="C66" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="B237" t="s">
+        <v>557</v>
+      </c>
+      <c r="C237" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
         <v>68</v>
       </c>
-      <c r="C67" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="B238" t="s">
+        <v>558</v>
+      </c>
+      <c r="C238" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
         <v>69</v>
       </c>
-      <c r="C68" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+      <c r="B239" t="s">
+        <v>559</v>
+      </c>
+      <c r="C239" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>216</v>
+      </c>
+      <c r="B240" t="s">
+        <v>560</v>
+      </c>
+      <c r="C240" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
         <v>70</v>
       </c>
-      <c r="C69" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+      <c r="B241" t="s">
+        <v>561</v>
+      </c>
+      <c r="C241" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>217</v>
+      </c>
+      <c r="B242" t="s">
+        <v>562</v>
+      </c>
+      <c r="C242" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
         <v>71</v>
       </c>
-      <c r="C70" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="B243" t="s">
+        <v>563</v>
+      </c>
+      <c r="C243" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>71</v>
+      </c>
+      <c r="B244" t="s">
+        <v>564</v>
+      </c>
+      <c r="C244" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>71</v>
+      </c>
+      <c r="B245" t="s">
+        <v>565</v>
+      </c>
+      <c r="C245" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
         <v>72</v>
       </c>
-      <c r="C71" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
+      <c r="B246" t="s">
+        <v>566</v>
+      </c>
+      <c r="C246" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
         <v>73</v>
       </c>
-      <c r="C72" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
+      <c r="B247" t="s">
+        <v>567</v>
+      </c>
+      <c r="C247" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
         <v>74</v>
       </c>
-      <c r="C73" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+      <c r="B248" t="s">
+        <v>568</v>
+      </c>
+      <c r="C248" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
         <v>75</v>
       </c>
-      <c r="C74" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="B249" t="s">
+        <v>569</v>
+      </c>
+      <c r="C249" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
         <v>76</v>
       </c>
-      <c r="C75" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="B250" t="s">
+        <v>570</v>
+      </c>
+      <c r="C250" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
         <v>77</v>
       </c>
-      <c r="C76" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+      <c r="B251" t="s">
+        <v>571</v>
+      </c>
+      <c r="C251" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
         <v>78</v>
       </c>
-      <c r="C77" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="B252" t="s">
+        <v>572</v>
+      </c>
+      <c r="C252" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
         <v>79</v>
       </c>
-      <c r="C78" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+      <c r="B253" t="s">
+        <v>573</v>
+      </c>
+      <c r="C253" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
         <v>80</v>
       </c>
-      <c r="C79" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+      <c r="B254" t="s">
+        <v>574</v>
+      </c>
+      <c r="C254" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
         <v>81</v>
       </c>
-      <c r="C80" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
+      <c r="B255" t="s">
+        <v>575</v>
+      </c>
+      <c r="C255" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>218</v>
+      </c>
+      <c r="B256" t="s">
+        <v>576</v>
+      </c>
+      <c r="C256" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
         <v>82</v>
       </c>
-      <c r="C81" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
+      <c r="B257" t="s">
+        <v>577</v>
+      </c>
+      <c r="C257" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
         <v>83</v>
       </c>
-      <c r="C82" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
+      <c r="B258" t="s">
+        <v>578</v>
+      </c>
+      <c r="C258" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>83</v>
+      </c>
+      <c r="B259" t="s">
+        <v>579</v>
+      </c>
+      <c r="C259" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
         <v>84</v>
       </c>
-      <c r="C83" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
+      <c r="B260" t="s">
+        <v>580</v>
+      </c>
+      <c r="C260" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
         <v>85</v>
       </c>
-      <c r="C84" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+      <c r="B261" t="s">
+        <v>581</v>
+      </c>
+      <c r="C261" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>219</v>
+      </c>
+      <c r="B262" t="s">
+        <v>582</v>
+      </c>
+      <c r="C262" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>220</v>
+      </c>
+      <c r="B263" t="s">
+        <v>583</v>
+      </c>
+      <c r="C263" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>221</v>
+      </c>
+      <c r="B264" t="s">
+        <v>584</v>
+      </c>
+      <c r="C264" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
         <v>86</v>
       </c>
-      <c r="C85" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
+      <c r="B265" t="s">
+        <v>585</v>
+      </c>
+      <c r="C265" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
         <v>87</v>
       </c>
-      <c r="C86" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
+      <c r="B266" t="s">
+        <v>586</v>
+      </c>
+      <c r="C266" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>222</v>
+      </c>
+      <c r="B267" t="s">
+        <v>587</v>
+      </c>
+      <c r="C267" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
         <v>88</v>
       </c>
-      <c r="C87" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
+      <c r="B268" t="s">
+        <v>588</v>
+      </c>
+      <c r="C268" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>223</v>
+      </c>
+      <c r="B269" t="s">
+        <v>589</v>
+      </c>
+      <c r="C269" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>224</v>
+      </c>
+      <c r="B270" t="s">
+        <v>590</v>
+      </c>
+      <c r="C270" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>225</v>
+      </c>
+      <c r="B271" t="s">
+        <v>591</v>
+      </c>
+      <c r="C271" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>226</v>
+      </c>
+      <c r="B272" t="s">
+        <v>592</v>
+      </c>
+      <c r="C272" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
         <v>89</v>
       </c>
-      <c r="C88" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
+      <c r="B273" t="s">
+        <v>593</v>
+      </c>
+      <c r="C273" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>227</v>
+      </c>
+      <c r="B274" t="s">
+        <v>594</v>
+      </c>
+      <c r="C274" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>228</v>
+      </c>
+      <c r="B275" t="s">
+        <v>595</v>
+      </c>
+      <c r="C275" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>229</v>
+      </c>
+      <c r="B276" t="s">
+        <v>596</v>
+      </c>
+      <c r="C276" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>230</v>
+      </c>
+      <c r="B277" t="s">
+        <v>597</v>
+      </c>
+      <c r="C277" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>230</v>
+      </c>
+      <c r="B278" t="s">
+        <v>598</v>
+      </c>
+      <c r="C278" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>231</v>
+      </c>
+      <c r="B279" t="s">
+        <v>599</v>
+      </c>
+      <c r="C279" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>232</v>
+      </c>
+      <c r="B280" t="s">
+        <v>600</v>
+      </c>
+      <c r="C280" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>233</v>
+      </c>
+      <c r="B281" t="s">
+        <v>601</v>
+      </c>
+      <c r="C281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>234</v>
+      </c>
+      <c r="B282" t="s">
+        <v>602</v>
+      </c>
+      <c r="C282" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>235</v>
+      </c>
+      <c r="B283" t="s">
+        <v>603</v>
+      </c>
+      <c r="C283" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>235</v>
+      </c>
+      <c r="B284" t="s">
+        <v>604</v>
+      </c>
+      <c r="C284" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>236</v>
+      </c>
+      <c r="B285" t="s">
+        <v>605</v>
+      </c>
+      <c r="C285" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>237</v>
+      </c>
+      <c r="B286" t="s">
+        <v>606</v>
+      </c>
+      <c r="C286" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>238</v>
+      </c>
+      <c r="B287" t="s">
+        <v>607</v>
+      </c>
+      <c r="C287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>239</v>
+      </c>
+      <c r="B288" t="s">
+        <v>608</v>
+      </c>
+      <c r="C288" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>239</v>
+      </c>
+      <c r="B289" t="s">
+        <v>609</v>
+      </c>
+      <c r="C289" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>240</v>
+      </c>
+      <c r="B290" t="s">
+        <v>610</v>
+      </c>
+      <c r="C290" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>241</v>
+      </c>
+      <c r="B291" t="s">
+        <v>611</v>
+      </c>
+      <c r="C291" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>242</v>
+      </c>
+      <c r="B292" t="s">
+        <v>612</v>
+      </c>
+      <c r="C292" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>243</v>
+      </c>
+      <c r="B293" t="s">
+        <v>613</v>
+      </c>
+      <c r="C293" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>244</v>
+      </c>
+      <c r="B294" t="s">
+        <v>614</v>
+      </c>
+      <c r="C294" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>245</v>
+      </c>
+      <c r="B295" t="s">
+        <v>615</v>
+      </c>
+      <c r="C295" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>246</v>
+      </c>
+      <c r="B296" t="s">
+        <v>616</v>
+      </c>
+      <c r="C296" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>247</v>
+      </c>
+      <c r="B297" t="s">
+        <v>617</v>
+      </c>
+      <c r="C297" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>248</v>
+      </c>
+      <c r="B298" t="s">
+        <v>618</v>
+      </c>
+      <c r="C298" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>249</v>
+      </c>
+      <c r="B299" t="s">
+        <v>619</v>
+      </c>
+      <c r="C299" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>250</v>
+      </c>
+      <c r="B300" t="s">
+        <v>620</v>
+      </c>
+      <c r="C300" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>251</v>
+      </c>
+      <c r="B301" t="s">
+        <v>621</v>
+      </c>
+      <c r="C301" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>252</v>
+      </c>
+      <c r="B302" t="s">
+        <v>622</v>
+      </c>
+      <c r="C302" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>253</v>
+      </c>
+      <c r="B303" t="s">
+        <v>623</v>
+      </c>
+      <c r="C303" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>253</v>
+      </c>
+      <c r="B304" t="s">
+        <v>624</v>
+      </c>
+      <c r="C304" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>253</v>
+      </c>
+      <c r="B305" t="s">
+        <v>625</v>
+      </c>
+      <c r="C305" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>253</v>
+      </c>
+      <c r="B306" t="s">
+        <v>626</v>
+      </c>
+      <c r="C306" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>254</v>
+      </c>
+      <c r="B307" t="s">
+        <v>627</v>
+      </c>
+      <c r="C307" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
         <v>90</v>
       </c>
-      <c r="C89" t="s">
-        <v>91</v>
+      <c r="B308" t="s">
+        <v>628</v>
+      </c>
+      <c r="C308" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>255</v>
+      </c>
+      <c r="B309" t="s">
+        <v>629</v>
+      </c>
+      <c r="C309" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>256</v>
+      </c>
+      <c r="B310" t="s">
+        <v>630</v>
+      </c>
+      <c r="C310" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>257</v>
+      </c>
+      <c r="B311" t="s">
+        <v>631</v>
+      </c>
+      <c r="C311" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>258</v>
+      </c>
+      <c r="B312" t="s">
+        <v>632</v>
+      </c>
+      <c r="C312" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>259</v>
+      </c>
+      <c r="B313" t="s">
+        <v>633</v>
+      </c>
+      <c r="C313" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>260</v>
+      </c>
+      <c r="B314" t="s">
+        <v>634</v>
+      </c>
+      <c r="C314" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>261</v>
+      </c>
+      <c r="B315" t="s">
+        <v>635</v>
+      </c>
+      <c r="C315" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>262</v>
+      </c>
+      <c r="B316" t="s">
+        <v>636</v>
+      </c>
+      <c r="C316" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>263</v>
+      </c>
+      <c r="B317" t="s">
+        <v>637</v>
+      </c>
+      <c r="C317" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>264</v>
+      </c>
+      <c r="B318" t="s">
+        <v>638</v>
+      </c>
+      <c r="C318" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>265</v>
+      </c>
+      <c r="B319" t="s">
+        <v>639</v>
+      </c>
+      <c r="C319" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>266</v>
+      </c>
+      <c r="B320" t="s">
+        <v>640</v>
+      </c>
+      <c r="C320" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>267</v>
+      </c>
+      <c r="B321" t="s">
+        <v>641</v>
+      </c>
+      <c r="C321" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>268</v>
+      </c>
+      <c r="B322" t="s">
+        <v>642</v>
+      </c>
+      <c r="C322" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>269</v>
+      </c>
+      <c r="B323" t="s">
+        <v>643</v>
+      </c>
+      <c r="C323" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>269</v>
+      </c>
+      <c r="B324" t="s">
+        <v>644</v>
+      </c>
+      <c r="C324" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>270</v>
+      </c>
+      <c r="B325" t="s">
+        <v>645</v>
+      </c>
+      <c r="C325" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>270</v>
+      </c>
+      <c r="B326" t="s">
+        <v>646</v>
+      </c>
+      <c r="C326" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AE53A8-A244-4D15-989E-254722C72A6C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026493E1-1CE1-4AF3-A85B-38D9F48394C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="947">
   <si>
     <t>UTK</t>
   </si>
@@ -2866,6 +2866,9 @@
   </si>
   <si>
     <t>SZL20261013/01</t>
+  </si>
+  <si>
+    <t>332443959/1</t>
   </si>
 </sst>
 </file>
@@ -3226,7 +3229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC11F24F-E222-443E-8401-2ECBA69A40D4}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:C499"/>
+  <dimension ref="A1:C500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -8723,6 +8726,17 @@
         <v>698</v>
       </c>
     </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A500">
+        <v>332443959</v>
+      </c>
+      <c r="B500" t="s">
+        <v>946</v>
+      </c>
+      <c r="C500" t="s">
+        <v>659</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30912FA-633F-4ABD-84B4-16C51C0F3E14}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE4E651-312B-429E-869B-83F3CF98449F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>

--- a/adatok.xlsx
+++ b/adatok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wh.local\fs\UserProfile_TSSWH19\_TSSWH19_redirected_folders\MilakTa1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CE415A-F2B7-4F54-9692-85E9E6F5274C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2B0858-BEF0-49F7-A956-797D745481CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{44A28A39-CCFD-46FF-9CFD-04D3E2713E2E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="750">
   <si>
     <t>UTK</t>
   </si>
@@ -69,9 +69,6 @@
     <t>261026-W00008708</t>
   </si>
   <si>
-    <t>261026-W00012230</t>
-  </si>
-  <si>
     <t>261027-F00006288</t>
   </si>
   <si>
@@ -243,9 +240,6 @@
     <t>99003620</t>
   </si>
   <si>
-    <t>SZ</t>
-  </si>
-  <si>
     <t>261028-W00001468</t>
   </si>
   <si>
@@ -334,6 +328,1956 @@
   </si>
   <si>
     <t>W2</t>
+  </si>
+  <si>
+    <t>1-8877/2026</t>
+  </si>
+  <si>
+    <t>1-8884/2026</t>
+  </si>
+  <si>
+    <t>1340850490</t>
+  </si>
+  <si>
+    <t>1640789215</t>
+  </si>
+  <si>
+    <t>2026/14091</t>
+  </si>
+  <si>
+    <t>2440272791</t>
+  </si>
+  <si>
+    <t>248747843</t>
+  </si>
+  <si>
+    <t>260916-W00003395</t>
+  </si>
+  <si>
+    <t>261009-W00005143</t>
+  </si>
+  <si>
+    <t>261014-F00011248</t>
+  </si>
+  <si>
+    <t>261016-F00010079</t>
+  </si>
+  <si>
+    <t>261017-F00000964</t>
+  </si>
+  <si>
+    <t>261017-F00001126</t>
+  </si>
+  <si>
+    <t>261017-F00002689</t>
+  </si>
+  <si>
+    <t>261018-W00005353</t>
+  </si>
+  <si>
+    <t>261019-F00011125</t>
+  </si>
+  <si>
+    <t>261019-F00013256</t>
+  </si>
+  <si>
+    <t>261019-W00003647</t>
+  </si>
+  <si>
+    <t>261020-F00003452</t>
+  </si>
+  <si>
+    <t>261020-F00012684</t>
+  </si>
+  <si>
+    <t>261020-F00013298</t>
+  </si>
+  <si>
+    <t>261020-W00009527</t>
+  </si>
+  <si>
+    <t>261021-F00000885</t>
+  </si>
+  <si>
+    <t>261021-F00002895</t>
+  </si>
+  <si>
+    <t>261021-F00005445</t>
+  </si>
+  <si>
+    <t>261021-F00009460</t>
+  </si>
+  <si>
+    <t>261021-W00010513</t>
+  </si>
+  <si>
+    <t>261022-F00010477-4</t>
+  </si>
+  <si>
+    <t>261022-F00013891</t>
+  </si>
+  <si>
+    <t>261022-W00002817</t>
+  </si>
+  <si>
+    <t>261022-W00008461</t>
+  </si>
+  <si>
+    <t>261023-W00007893</t>
+  </si>
+  <si>
+    <t>261024-F00005146</t>
+  </si>
+  <si>
+    <t>261024-F00007995</t>
+  </si>
+  <si>
+    <t>261024-W00002480</t>
+  </si>
+  <si>
+    <t>261024-W00005390</t>
+  </si>
+  <si>
+    <t>261024-W00005477</t>
+  </si>
+  <si>
+    <t>261024-W00007753</t>
+  </si>
+  <si>
+    <t>261025-F00004301-1</t>
+  </si>
+  <si>
+    <t>261025-W00008902</t>
+  </si>
+  <si>
+    <t>261026-F00007935</t>
+  </si>
+  <si>
+    <t>261026-W00000563</t>
+  </si>
+  <si>
+    <t>261026-W00004915</t>
+  </si>
+  <si>
+    <t>261026-W00007903</t>
+  </si>
+  <si>
+    <t>261026-W00008408</t>
+  </si>
+  <si>
+    <t>261026-W00008828</t>
+  </si>
+  <si>
+    <t>261026-W00010175</t>
+  </si>
+  <si>
+    <t>261027-F00000311</t>
+  </si>
+  <si>
+    <t>261027-F00001387</t>
+  </si>
+  <si>
+    <t>261027-F00002008</t>
+  </si>
+  <si>
+    <t>261027-F00002783</t>
+  </si>
+  <si>
+    <t>261027-F00002875</t>
+  </si>
+  <si>
+    <t>261027-F00012933</t>
+  </si>
+  <si>
+    <t>261027-F00014311</t>
+  </si>
+  <si>
+    <t>261027-F00014786</t>
+  </si>
+  <si>
+    <t>261027-F00014944</t>
+  </si>
+  <si>
+    <t>261027-F00015725</t>
+  </si>
+  <si>
+    <t>261027-W00007155</t>
+  </si>
+  <si>
+    <t>261027-W00008402</t>
+  </si>
+  <si>
+    <t>261027-W00008577</t>
+  </si>
+  <si>
+    <t>261027-W00008842</t>
+  </si>
+  <si>
+    <t>261027-W00008907</t>
+  </si>
+  <si>
+    <t>261027-W00008963</t>
+  </si>
+  <si>
+    <t>261027-W00009448</t>
+  </si>
+  <si>
+    <t>261027-W00010354</t>
+  </si>
+  <si>
+    <t>261027-W00010555</t>
+  </si>
+  <si>
+    <t>261027-W00010597</t>
+  </si>
+  <si>
+    <t>261027-W00012884</t>
+  </si>
+  <si>
+    <t>261028-F00000224</t>
+  </si>
+  <si>
+    <t>261028-F00000376</t>
+  </si>
+  <si>
+    <t>261028-F00000579-1</t>
+  </si>
+  <si>
+    <t>261028-F00002855</t>
+  </si>
+  <si>
+    <t>261028-F00004390</t>
+  </si>
+  <si>
+    <t>261028-F00004443</t>
+  </si>
+  <si>
+    <t>261028-F00004811</t>
+  </si>
+  <si>
+    <t>261028-F00005118-10</t>
+  </si>
+  <si>
+    <t>261028-F00005733</t>
+  </si>
+  <si>
+    <t>261028-F00007114</t>
+  </si>
+  <si>
+    <t>261028-F00007222</t>
+  </si>
+  <si>
+    <t>261028-F00007945</t>
+  </si>
+  <si>
+    <t>261028-F00010632</t>
+  </si>
+  <si>
+    <t>261028-F00011266</t>
+  </si>
+  <si>
+    <t>261028-F00012230</t>
+  </si>
+  <si>
+    <t>261028-F00013409</t>
+  </si>
+  <si>
+    <t>261028-F00013745</t>
+  </si>
+  <si>
+    <t>261028-F00014656</t>
+  </si>
+  <si>
+    <t>261028-F00014933</t>
+  </si>
+  <si>
+    <t>261028-W00000215</t>
+  </si>
+  <si>
+    <t>261028-W00000696</t>
+  </si>
+  <si>
+    <t>261028-W00002774</t>
+  </si>
+  <si>
+    <t>261028-W00003802</t>
+  </si>
+  <si>
+    <t>261028-W00004464</t>
+  </si>
+  <si>
+    <t>261028-W00005448</t>
+  </si>
+  <si>
+    <t>261028-W00006552</t>
+  </si>
+  <si>
+    <t>261028-W00006689</t>
+  </si>
+  <si>
+    <t>261028-W00006957</t>
+  </si>
+  <si>
+    <t>261028-W00007008</t>
+  </si>
+  <si>
+    <t>261028-W00007171</t>
+  </si>
+  <si>
+    <t>261028-W00008387</t>
+  </si>
+  <si>
+    <t>261028-W00008510</t>
+  </si>
+  <si>
+    <t>261028-W00009127</t>
+  </si>
+  <si>
+    <t>261028-W00009523</t>
+  </si>
+  <si>
+    <t>261028-W00011814</t>
+  </si>
+  <si>
+    <t>261028-W00012876</t>
+  </si>
+  <si>
+    <t>261029-F00000259</t>
+  </si>
+  <si>
+    <t>261029-F00000506</t>
+  </si>
+  <si>
+    <t>261029-F00001478</t>
+  </si>
+  <si>
+    <t>261029-F00002127</t>
+  </si>
+  <si>
+    <t>261029-F00002695</t>
+  </si>
+  <si>
+    <t>261029-F00002930</t>
+  </si>
+  <si>
+    <t>261029-F00003100</t>
+  </si>
+  <si>
+    <t>261029-F00003233</t>
+  </si>
+  <si>
+    <t>261029-F00003575</t>
+  </si>
+  <si>
+    <t>261029-F00004935</t>
+  </si>
+  <si>
+    <t>261029-W00002611</t>
+  </si>
+  <si>
+    <t>261029-W00002623</t>
+  </si>
+  <si>
+    <t>261029-W00003542</t>
+  </si>
+  <si>
+    <t>261029-W00003801</t>
+  </si>
+  <si>
+    <t>261029-W00004298</t>
+  </si>
+  <si>
+    <t>261029-W00004913</t>
+  </si>
+  <si>
+    <t>261029-W00004964</t>
+  </si>
+  <si>
+    <t>267014971</t>
+  </si>
+  <si>
+    <t>267015274</t>
+  </si>
+  <si>
+    <t>267015302</t>
+  </si>
+  <si>
+    <t>267015310</t>
+  </si>
+  <si>
+    <t>267015311</t>
+  </si>
+  <si>
+    <t>267015328</t>
+  </si>
+  <si>
+    <t>267015366</t>
+  </si>
+  <si>
+    <t>267015384</t>
+  </si>
+  <si>
+    <t>267015385</t>
+  </si>
+  <si>
+    <t>267015386</t>
+  </si>
+  <si>
+    <t>267015387</t>
+  </si>
+  <si>
+    <t>267015389</t>
+  </si>
+  <si>
+    <t>267015391</t>
+  </si>
+  <si>
+    <t>267015424</t>
+  </si>
+  <si>
+    <t>267015434</t>
+  </si>
+  <si>
+    <t>267015435</t>
+  </si>
+  <si>
+    <t>267015443</t>
+  </si>
+  <si>
+    <t>267015454</t>
+  </si>
+  <si>
+    <t>267015459</t>
+  </si>
+  <si>
+    <t>26MPE0011711</t>
+  </si>
+  <si>
+    <t>332826195</t>
+  </si>
+  <si>
+    <t>332900460</t>
+  </si>
+  <si>
+    <t>333493039</t>
+  </si>
+  <si>
+    <t>333841877</t>
+  </si>
+  <si>
+    <t>333897188</t>
+  </si>
+  <si>
+    <t>334061053</t>
+  </si>
+  <si>
+    <t>334188241</t>
+  </si>
+  <si>
+    <t>334277883</t>
+  </si>
+  <si>
+    <t>334278155</t>
+  </si>
+  <si>
+    <t>334764493</t>
+  </si>
+  <si>
+    <t>334764673</t>
+  </si>
+  <si>
+    <t>334764829</t>
+  </si>
+  <si>
+    <t>334811470</t>
+  </si>
+  <si>
+    <t>334811813</t>
+  </si>
+  <si>
+    <t>334927275</t>
+  </si>
+  <si>
+    <t>334927300</t>
+  </si>
+  <si>
+    <t>334927499</t>
+  </si>
+  <si>
+    <t>334927529</t>
+  </si>
+  <si>
+    <t>334927720</t>
+  </si>
+  <si>
+    <t>334927757</t>
+  </si>
+  <si>
+    <t>334927827</t>
+  </si>
+  <si>
+    <t>334927929</t>
+  </si>
+  <si>
+    <t>334996372</t>
+  </si>
+  <si>
+    <t>334996671</t>
+  </si>
+  <si>
+    <t>334996713</t>
+  </si>
+  <si>
+    <t>334997053</t>
+  </si>
+  <si>
+    <t>335051652</t>
+  </si>
+  <si>
+    <t>441135352</t>
+  </si>
+  <si>
+    <t>99003611</t>
+  </si>
+  <si>
+    <t>99003613</t>
+  </si>
+  <si>
+    <t>ID5620_XD/2</t>
+  </si>
+  <si>
+    <t>ID5676_XD</t>
+  </si>
+  <si>
+    <t>ID5677_XD</t>
+  </si>
+  <si>
+    <t>NFD6-10-18-FMTF</t>
+  </si>
+  <si>
+    <t>NFD6-10-19-R2FK</t>
+  </si>
+  <si>
+    <t>NFD6-10-20-F23X</t>
+  </si>
+  <si>
+    <t>NFD6-10-20-RQGU</t>
+  </si>
+  <si>
+    <t>NFD6-10-20-UP6S</t>
+  </si>
+  <si>
+    <t>NFD6-10-25-HBBL</t>
+  </si>
+  <si>
+    <t>NFD6-10-26-YCZ7</t>
+  </si>
+  <si>
+    <t>NFD6-10-27-9TJR</t>
+  </si>
+  <si>
+    <t>NFD6-10-27-BL5L</t>
+  </si>
+  <si>
+    <t>NFD6-10-27-BMLC</t>
+  </si>
+  <si>
+    <t>NFD6-10-27-E54F</t>
+  </si>
+  <si>
+    <t>NFD6-10-27-X8WZ</t>
+  </si>
+  <si>
+    <t>NFD6-10-28-6AV8</t>
+  </si>
+  <si>
+    <t>NFD6-10-28-78NL</t>
+  </si>
+  <si>
+    <t>NFD6-10-28-DTCH</t>
+  </si>
+  <si>
+    <t>NFD6-10-28-FALL</t>
+  </si>
+  <si>
+    <t>NFD6-10-28-KSV7</t>
+  </si>
+  <si>
+    <t>NFD6-10-28-QVYS</t>
+  </si>
+  <si>
+    <t>NFD6-10-28-RFSW</t>
+  </si>
+  <si>
+    <t>NFD6-10-28-U25Y</t>
+  </si>
+  <si>
+    <t>NFD6-10-28-XP5D</t>
+  </si>
+  <si>
+    <t>NFE6-10-20-WQPN</t>
+  </si>
+  <si>
+    <t>NFE6-10-27-NHX2</t>
+  </si>
+  <si>
+    <t>NFE6-10-27-Y3F3</t>
+  </si>
+  <si>
+    <t>NFE6-10-28-FRJC</t>
+  </si>
+  <si>
+    <t>NFE6-10-28-SBNK</t>
+  </si>
+  <si>
+    <t>NFE6-10-28-VD6T</t>
+  </si>
+  <si>
+    <t>R440548</t>
+  </si>
+  <si>
+    <t>SA26/H007624</t>
+  </si>
+  <si>
+    <t>SA26/H007629</t>
+  </si>
+  <si>
+    <t>SF26/H000248</t>
+  </si>
+  <si>
+    <t>NFD6-10-28-8AVB</t>
+  </si>
+  <si>
+    <t>26MPE0011687</t>
+  </si>
+  <si>
+    <t>159995579545577673</t>
+  </si>
+  <si>
+    <t>159995579545577659</t>
+  </si>
+  <si>
+    <t>1340850490/1</t>
+  </si>
+  <si>
+    <t>1340850490/2</t>
+  </si>
+  <si>
+    <t>1340850490/3</t>
+  </si>
+  <si>
+    <t>1340850490/4</t>
+  </si>
+  <si>
+    <t>1640789215/1</t>
+  </si>
+  <si>
+    <t>1640789215/2</t>
+  </si>
+  <si>
+    <t>1640789215/3</t>
+  </si>
+  <si>
+    <t>1640789215/4</t>
+  </si>
+  <si>
+    <t>1640789215/5</t>
+  </si>
+  <si>
+    <t>1640789215/6</t>
+  </si>
+  <si>
+    <t>1640789215/7</t>
+  </si>
+  <si>
+    <t>1640789215/8</t>
+  </si>
+  <si>
+    <t>1640789215/9</t>
+  </si>
+  <si>
+    <t>159995579545235665</t>
+  </si>
+  <si>
+    <t>159995579545235672</t>
+  </si>
+  <si>
+    <t>159995579545235689</t>
+  </si>
+  <si>
+    <t>159995579545235696</t>
+  </si>
+  <si>
+    <t>159995579545235702</t>
+  </si>
+  <si>
+    <t>159995579545235719</t>
+  </si>
+  <si>
+    <t>159995579545235726</t>
+  </si>
+  <si>
+    <t>2440272791/1</t>
+  </si>
+  <si>
+    <t>2440272791/2</t>
+  </si>
+  <si>
+    <t>2440272791/3</t>
+  </si>
+  <si>
+    <t>2440272791/4</t>
+  </si>
+  <si>
+    <t>248747810/1</t>
+  </si>
+  <si>
+    <t>248747843/1</t>
+  </si>
+  <si>
+    <t>6ae30b0ece19280a2197ec0a</t>
+  </si>
+  <si>
+    <t>6ad2243c2ed61dd3c9d41d04</t>
+  </si>
+  <si>
+    <t>6ac8ba267c818f22ee6f0aa2</t>
+  </si>
+  <si>
+    <t>6ae2e3cace19280a2197e875</t>
+  </si>
+  <si>
+    <t>6ad895f52ed61dd3c9d485ea</t>
+  </si>
+  <si>
+    <t>6ae30bd6ce19280a2197ec5c</t>
+  </si>
+  <si>
+    <t>6ae20e658db5819914c2c6aa</t>
+  </si>
+  <si>
+    <t>6ae31256ce19280a2197edc2</t>
+  </si>
+  <si>
+    <t>6ad342c92ed61dd3c9d42983</t>
+  </si>
+  <si>
+    <t>6ad4b7372ed61dd3c9d4379d</t>
+  </si>
+  <si>
+    <t>6ad4b7372ed61dd3c9d437a0</t>
+  </si>
+  <si>
+    <t>6ae197cb8db5819914c2b457</t>
+  </si>
+  <si>
+    <t>6ae32e6fce19280a2197f2e6</t>
+  </si>
+  <si>
+    <t>6ae1f5458db5819914c2c2db</t>
+  </si>
+  <si>
+    <t>6ae1e3408db5819914c2bfdc</t>
+  </si>
+  <si>
+    <t>6ae1cbb78db5819914c2bbe2</t>
+  </si>
+  <si>
+    <t>6ad649232ed61dd3c9d45891</t>
+  </si>
+  <si>
+    <t>6ad726f82ed61dd3c9d462c2</t>
+  </si>
+  <si>
+    <t>6ad883cc2ed61dd3c9d48254</t>
+  </si>
+  <si>
+    <t>6ae2eca9ce19280a2197e8ac</t>
+  </si>
+  <si>
+    <t>6ad77ea52ed61dd3c9d473f8</t>
+  </si>
+  <si>
+    <t>6ae2e5d2ce19280a2197e87b</t>
+  </si>
+  <si>
+    <t>6ad78dbe2ed61dd3c9d47604</t>
+  </si>
+  <si>
+    <t>6ae337f4ce19280a2197f433</t>
+  </si>
+  <si>
+    <t>6ad875c52ed61dd3c9d47f67</t>
+  </si>
+  <si>
+    <t>6ae1d0158db5819914c2bcc7</t>
+  </si>
+  <si>
+    <t>6ae30898ce19280a2197eb92</t>
+  </si>
+  <si>
+    <t>6ae30898ce19280a2197eb93</t>
+  </si>
+  <si>
+    <t>6ad8fedf2ed61dd3c9d49590</t>
+  </si>
+  <si>
+    <t>6ae21c188db5819914c2c8d2</t>
+  </si>
+  <si>
+    <t>6ae21c188db5819914c2c8d4</t>
+  </si>
+  <si>
+    <t>6ae31e28ce19280a2197f017</t>
+  </si>
+  <si>
+    <t>6ad9cad02ed61dd3c9d49b7b</t>
+  </si>
+  <si>
+    <t>6ada30bc2ed61dd3c9d4aaff</t>
+  </si>
+  <si>
+    <t>6ae204da8db5819914c2c549</t>
+  </si>
+  <si>
+    <t>6ae204da8db5819914c2c54a</t>
+  </si>
+  <si>
+    <t>6adca60e8db5819914c26b9d</t>
+  </si>
+  <si>
+    <t>6add10af8db5819914c27061</t>
+  </si>
+  <si>
+    <t>6adc67ed8db5819914c26589</t>
+  </si>
+  <si>
+    <t>6adca4db8db5819914c26b69</t>
+  </si>
+  <si>
+    <t>6adcbfda8db5819914c26d58</t>
+  </si>
+  <si>
+    <t>6adcc6d68db5819914c26dc3</t>
+  </si>
+  <si>
+    <t>6adcc6d68db5819914c26dc5</t>
+  </si>
+  <si>
+    <t>6ae0e9578db5819914c2b118</t>
+  </si>
+  <si>
+    <t>6ade3f028db5819914c27998</t>
+  </si>
+  <si>
+    <t>6ade3f028db5819914c27999</t>
+  </si>
+  <si>
+    <t>6ae1d7758db5819914c2be2b</t>
+  </si>
+  <si>
+    <t>6adee1f18db5819914c27b5b</t>
+  </si>
+  <si>
+    <t>6adf1b698db5819914c2806d</t>
+  </si>
+  <si>
+    <t>6ae0b2408db5819914c2aa92</t>
+  </si>
+  <si>
+    <t>6adf5e268db5819914c28ebb</t>
+  </si>
+  <si>
+    <t>6adf652d8db5819914c29013</t>
+  </si>
+  <si>
+    <t>6adf652d8db5819914c29015</t>
+  </si>
+  <si>
+    <t>6adf69da8db5819914c2911c</t>
+  </si>
+  <si>
+    <t>6adf6b3d8db5819914c29162</t>
+  </si>
+  <si>
+    <t>6adf8aad8db5819914c295b0</t>
+  </si>
+  <si>
+    <t>6adf8aad8db5819914c295b1</t>
+  </si>
+  <si>
+    <t>6ae306a1ce19280a2197eb5c</t>
+  </si>
+  <si>
+    <t>6ae247b98db5819914c2cc9c</t>
+  </si>
+  <si>
+    <t>6ae064a58db5819914c29c71</t>
+  </si>
+  <si>
+    <t>6ae064a58db5819914c29c74</t>
+  </si>
+  <si>
+    <t>6ae064a58db5819914c29c75</t>
+  </si>
+  <si>
+    <t>6ae313d5ce19280a2197ee03</t>
+  </si>
+  <si>
+    <t>6ae06bad8db5819914c29dd8</t>
+  </si>
+  <si>
+    <t>6ae088f88db5819914c2a3b8</t>
+  </si>
+  <si>
+    <t>6ae0c70d8db5819914c2add5</t>
+  </si>
+  <si>
+    <t>6ae0d5238db5819914c2af38</t>
+  </si>
+  <si>
+    <t>6ae0dd4f8db5819914c2afea</t>
+  </si>
+  <si>
+    <t>6ae0dd4f8db5819914c2afeb</t>
+  </si>
+  <si>
+    <t>6ae0dd518db5819914c2b000</t>
+  </si>
+  <si>
+    <t>6ae0e2098db5819914c2b078</t>
+  </si>
+  <si>
+    <t>6ae1f9ed8db5819914c2c371</t>
+  </si>
+  <si>
+    <t>6ae0a9078db5819914c2a8ee</t>
+  </si>
+  <si>
+    <t>6ae0bc898db5819914c2ac58</t>
+  </si>
+  <si>
+    <t>6ae0bc888db5819914c2ac4c</t>
+  </si>
+  <si>
+    <t>6ae0c96e8db5819914c2ae25</t>
+  </si>
+  <si>
+    <t>6ae0c2678db5819914c2ad02</t>
+  </si>
+  <si>
+    <t>6ae0c70c8db5819914c2adbe</t>
+  </si>
+  <si>
+    <t>6ae0c38d8db5819914c2ad3a</t>
+  </si>
+  <si>
+    <t>6ae0c38d8db5819914c2ad3b</t>
+  </si>
+  <si>
+    <t>6ae0cbc48db5819914c2ae48</t>
+  </si>
+  <si>
+    <t>6ae12dfc8db5819914c2b38d</t>
+  </si>
+  <si>
+    <t>6ae0d5248db5819914c2af50</t>
+  </si>
+  <si>
+    <t>6ae0d9da8db5819914c2afaf</t>
+  </si>
+  <si>
+    <t>6ae0dfa78db5819914c2b031</t>
+  </si>
+  <si>
+    <t>6ae0dfa78db5819914c2b032</t>
+  </si>
+  <si>
+    <t>6ae0de818db5819914c2b012</t>
+  </si>
+  <si>
+    <t>6ae0de818db5819914c2b013</t>
+  </si>
+  <si>
+    <t>6ae102d38db5819914c2b2a3</t>
+  </si>
+  <si>
+    <t>6ae18c228db5819914c2b3f1</t>
+  </si>
+  <si>
+    <t>6ae19b288db5819914c2b47a</t>
+  </si>
+  <si>
+    <t>6ae229368db5819914c2ca30</t>
+  </si>
+  <si>
+    <t>6ae1aa9c8db5819914c2b59c</t>
+  </si>
+  <si>
+    <t>6ae1bd238db5819914c2b8f9</t>
+  </si>
+  <si>
+    <t>6ae1bd368db5819914c2b925</t>
+  </si>
+  <si>
+    <t>6ae1bd368db5819914c2b926</t>
+  </si>
+  <si>
+    <t>6ae1ceb98db5819914c2bc5e</t>
+  </si>
+  <si>
+    <t>6ae1ceb98db5819914c2bc5f</t>
+  </si>
+  <si>
+    <t>6ae1ceb98db5819914c2bc62</t>
+  </si>
+  <si>
+    <t>6ae1cd948db5819914c2bc3b</t>
+  </si>
+  <si>
+    <t>6ae1cfeb8db5819914c2bcbd</t>
+  </si>
+  <si>
+    <t>6ae32a45ce19280a2197f22c</t>
+  </si>
+  <si>
+    <t>6ae1e1838db5819914c2bf9c</t>
+  </si>
+  <si>
+    <t>6ae1e3d88db5819914c2c002</t>
+  </si>
+  <si>
+    <t>6ae1e9ad8db5819914c2c0fc</t>
+  </si>
+  <si>
+    <t>6ae1ed358db5819914c2c1ab</t>
+  </si>
+  <si>
+    <t>6ae1fecf8db5819914c2c424</t>
+  </si>
+  <si>
+    <t>6ae202498db5819914c2c4af</t>
+  </si>
+  <si>
+    <t>6ae209528db5819914c2c5e4</t>
+  </si>
+  <si>
+    <t>6ae209528db5819914c2c5e5</t>
+  </si>
+  <si>
+    <t>6ae212bc8db5819914c2c74e</t>
+  </si>
+  <si>
+    <t>6ae212bc8db5819914c2c74f</t>
+  </si>
+  <si>
+    <t>6ae216378db5819914c2c7e4</t>
+  </si>
+  <si>
+    <t>6ae216378db5819914c2c7e5</t>
+  </si>
+  <si>
+    <t>6ae221ec8db5819914c2c96d</t>
+  </si>
+  <si>
+    <t>6ae2269b8db5819914c2c9ee</t>
+  </si>
+  <si>
+    <t>6ae2269b8db5819914c2c9ef</t>
+  </si>
+  <si>
+    <t>6ae2312b8db5819914c2caf0</t>
+  </si>
+  <si>
+    <t>6ae243f18db5819914c2cc54</t>
+  </si>
+  <si>
+    <t>6ae25a2a4211d56e4353d063</t>
+  </si>
+  <si>
+    <t>6ae14dd88db5819914c2b3bd</t>
+  </si>
+  <si>
+    <t>6ae14dd88db5819914c2b3be</t>
+  </si>
+  <si>
+    <t>6ae1828f8db5819914c2b3df</t>
+  </si>
+  <si>
+    <t>6ae1b6228db5819914c2b768</t>
+  </si>
+  <si>
+    <t>6ae1b6228db5819914c2b769</t>
+  </si>
+  <si>
+    <t>6ae1b6228db5819914c2b76b</t>
+  </si>
+  <si>
+    <t>6ae1c7b38db5819914c2bb07</t>
+  </si>
+  <si>
+    <t>6ae1c7b38db5819914c2bb09</t>
+  </si>
+  <si>
+    <t>6ae1d3748db5819914c2bd5f</t>
+  </si>
+  <si>
+    <t>6ae1d3748db5819914c2bd60</t>
+  </si>
+  <si>
+    <t>6ae1e1828db5819914c2bf97</t>
+  </si>
+  <si>
+    <t>6ae1eb228db5819914c2c166</t>
+  </si>
+  <si>
+    <t>6ae1eb228db5819914c2c169</t>
+  </si>
+  <si>
+    <t>6ae1f43f8db5819914c2c2c0</t>
+  </si>
+  <si>
+    <t>6ae1f43f8db5819914c2c2c1</t>
+  </si>
+  <si>
+    <t>6ae1f7c48db5819914c2c318</t>
+  </si>
+  <si>
+    <t>6ae1f7c48db5819914c2c319</t>
+  </si>
+  <si>
+    <t>6ae201288db5819914c2c486</t>
+  </si>
+  <si>
+    <t>6ae201288db5819914c2c487</t>
+  </si>
+  <si>
+    <t>6ae1fc748db5819914c2c3cf</t>
+  </si>
+  <si>
+    <t>6ae1fd9e8db5819914c2c3fa</t>
+  </si>
+  <si>
+    <t>6ae1fd9e8db5819914c2c3fb</t>
+  </si>
+  <si>
+    <t>6ae1fff28db5819914c2c436</t>
+  </si>
+  <si>
+    <t>6ae1fff28db5819914c2c438</t>
+  </si>
+  <si>
+    <t>6ae2082a8db5819914c2c5aa</t>
+  </si>
+  <si>
+    <t>6ae213eb8db5819914c2c77b</t>
+  </si>
+  <si>
+    <t>6ae213eb8db5819914c2c77c</t>
+  </si>
+  <si>
+    <t>6ae216368db5819914c2c7c9</t>
+  </si>
+  <si>
+    <t>6ae220c78db5819914c2c95d</t>
+  </si>
+  <si>
+    <t>6ae22b598db5819914c2ca75</t>
+  </si>
+  <si>
+    <t>6ae22a288db5819914c2ca4e</t>
+  </si>
+  <si>
+    <t>6ae2370b8db5819914c2cb57</t>
+  </si>
+  <si>
+    <t>6ae24c1e8db5819914c2ccdc</t>
+  </si>
+  <si>
+    <t>6ae25dd54211d56e4353d082</t>
+  </si>
+  <si>
+    <t>6ae25dd54211d56e4353d083</t>
+  </si>
+  <si>
+    <t>6ae2e92bce19280a2197e895</t>
+  </si>
+  <si>
+    <t>6ae2f738ce19280a2197e935</t>
+  </si>
+  <si>
+    <t>6ae30420ce19280a2197ead4</t>
+  </si>
+  <si>
+    <t>6ae309f8ce19280a2197ebf1</t>
+  </si>
+  <si>
+    <t>6ae309f8ce19280a2197ebf3</t>
+  </si>
+  <si>
+    <t>6ae30ff9ce19280a2197ed55</t>
+  </si>
+  <si>
+    <t>6ae31352ce19280a2197edcd</t>
+  </si>
+  <si>
+    <t>6ae315d5ce19280a2197ee87</t>
+  </si>
+  <si>
+    <t>6ae315d5ce19280a2197ee89</t>
+  </si>
+  <si>
+    <t>6ae315c0ce19280a2197ee7b</t>
+  </si>
+  <si>
+    <t>6ae31a65ce19280a2197ef5c</t>
+  </si>
+  <si>
+    <t>6ae323c4ce19280a2197f119</t>
+  </si>
+  <si>
+    <t>6ae338d9ce19280a2197f451</t>
+  </si>
+  <si>
+    <t>6ae30b29ce19280a2197ec3e</t>
+  </si>
+  <si>
+    <t>6ae3080bce19280a2197eb8e</t>
+  </si>
+  <si>
+    <t>6ae3080bce19280a2197eb8f</t>
+  </si>
+  <si>
+    <t>6ae308cfce19280a2197eba7</t>
+  </si>
+  <si>
+    <t>6ae32bf9ce19280a2197f25a</t>
+  </si>
+  <si>
+    <t>6ae31a65ce19280a2197ef64</t>
+  </si>
+  <si>
+    <t>6ae32292ce19280a2197f0df</t>
+  </si>
+  <si>
+    <t>6ae32e46ce19280a2197f2d6</t>
+  </si>
+  <si>
+    <t>6ae32d2dce19280a2197f2ad</t>
+  </si>
+  <si>
+    <t>6ae33be8ce19280a2197f4e9</t>
+  </si>
+  <si>
+    <t>6ae33be8ce19280a2197f4ea</t>
+  </si>
+  <si>
+    <t>1449-383344</t>
+  </si>
+  <si>
+    <t>1449-762497</t>
+  </si>
+  <si>
+    <t>1449-936938</t>
+  </si>
+  <si>
+    <t>1449-138236</t>
+  </si>
+  <si>
+    <t>1449-744145</t>
+  </si>
+  <si>
+    <t>1449-662663/1</t>
+  </si>
+  <si>
+    <t>1449-662663/2</t>
+  </si>
+  <si>
+    <t>5427-558012</t>
+  </si>
+  <si>
+    <t>1449-881751</t>
+  </si>
+  <si>
+    <t>1449-484103</t>
+  </si>
+  <si>
+    <t>1449-351648</t>
+  </si>
+  <si>
+    <t>1449-491448</t>
+  </si>
+  <si>
+    <t>1449-389266</t>
+  </si>
+  <si>
+    <t>1449-714166</t>
+  </si>
+  <si>
+    <t>1449-838105/1</t>
+  </si>
+  <si>
+    <t>1449-838105/2</t>
+  </si>
+  <si>
+    <t>1449-652422</t>
+  </si>
+  <si>
+    <t>1449-350174</t>
+  </si>
+  <si>
+    <t>1449-137851</t>
+  </si>
+  <si>
+    <t>1449-122341</t>
+  </si>
+  <si>
+    <t>1449-724030</t>
+  </si>
+  <si>
+    <t>26MPE0011711/1</t>
+  </si>
+  <si>
+    <t>332826195/1</t>
+  </si>
+  <si>
+    <t>332826195/2</t>
+  </si>
+  <si>
+    <t>332900460/1</t>
+  </si>
+  <si>
+    <t>332900460/2</t>
+  </si>
+  <si>
+    <t>333446615/1</t>
+  </si>
+  <si>
+    <t>333493039/1</t>
+  </si>
+  <si>
+    <t>333493420/1</t>
+  </si>
+  <si>
+    <t>333493420/2</t>
+  </si>
+  <si>
+    <t>333493420/3</t>
+  </si>
+  <si>
+    <t>333493420/4</t>
+  </si>
+  <si>
+    <t>333533570/1</t>
+  </si>
+  <si>
+    <t>333841877/1</t>
+  </si>
+  <si>
+    <t>333897188/1</t>
+  </si>
+  <si>
+    <t>333951324/1</t>
+  </si>
+  <si>
+    <t>333951324/2</t>
+  </si>
+  <si>
+    <t>334061053/1</t>
+  </si>
+  <si>
+    <t>334188241/1</t>
+  </si>
+  <si>
+    <t>334188241/2</t>
+  </si>
+  <si>
+    <t>334277883/1</t>
+  </si>
+  <si>
+    <t>334277883/2</t>
+  </si>
+  <si>
+    <t>334277883/3</t>
+  </si>
+  <si>
+    <t>334278155/1</t>
+  </si>
+  <si>
+    <t>334374184/1</t>
+  </si>
+  <si>
+    <t>334374242/1</t>
+  </si>
+  <si>
+    <t>334444846/1</t>
+  </si>
+  <si>
+    <t>334498986/1</t>
+  </si>
+  <si>
+    <t>334498986/2</t>
+  </si>
+  <si>
+    <t>334498986/3</t>
+  </si>
+  <si>
+    <t>334498986/4</t>
+  </si>
+  <si>
+    <t>334499022/1</t>
+  </si>
+  <si>
+    <t>334499395/1</t>
+  </si>
+  <si>
+    <t>334499395/2</t>
+  </si>
+  <si>
+    <t>334499395/3</t>
+  </si>
+  <si>
+    <t>334653291/1</t>
+  </si>
+  <si>
+    <t>334653370/1</t>
+  </si>
+  <si>
+    <t>334653515/1</t>
+  </si>
+  <si>
+    <t>334653515/2</t>
+  </si>
+  <si>
+    <t>334653515/3</t>
+  </si>
+  <si>
+    <t>334653963/1</t>
+  </si>
+  <si>
+    <t>334654089/1</t>
+  </si>
+  <si>
+    <t>334712355/1</t>
+  </si>
+  <si>
+    <t>334712799/1</t>
+  </si>
+  <si>
+    <t>334712875/1</t>
+  </si>
+  <si>
+    <t>334764169/1</t>
+  </si>
+  <si>
+    <t>334764466/1</t>
+  </si>
+  <si>
+    <t>334764493/1</t>
+  </si>
+  <si>
+    <t>334764673/1</t>
+  </si>
+  <si>
+    <t>334764718/1</t>
+  </si>
+  <si>
+    <t>334764718/2</t>
+  </si>
+  <si>
+    <t>334764829/1</t>
+  </si>
+  <si>
+    <t>334811262/1</t>
+  </si>
+  <si>
+    <t>334811307/1</t>
+  </si>
+  <si>
+    <t>334811343/1</t>
+  </si>
+  <si>
+    <t>334811470/1</t>
+  </si>
+  <si>
+    <t>334811535/1</t>
+  </si>
+  <si>
+    <t>334811786/1</t>
+  </si>
+  <si>
+    <t>334811813/1</t>
+  </si>
+  <si>
+    <t>334811986/1</t>
+  </si>
+  <si>
+    <t>334873032/1</t>
+  </si>
+  <si>
+    <t>334873042/1</t>
+  </si>
+  <si>
+    <t>334873120/1</t>
+  </si>
+  <si>
+    <t>334873321/1</t>
+  </si>
+  <si>
+    <t>334873321/2</t>
+  </si>
+  <si>
+    <t>334873347/1</t>
+  </si>
+  <si>
+    <t>334873444/1</t>
+  </si>
+  <si>
+    <t>334873565/1</t>
+  </si>
+  <si>
+    <t>334873753/1</t>
+  </si>
+  <si>
+    <t>334927275/1</t>
+  </si>
+  <si>
+    <t>334927300/1</t>
+  </si>
+  <si>
+    <t>334927300/2</t>
+  </si>
+  <si>
+    <t>334927499/1</t>
+  </si>
+  <si>
+    <t>334927529/1</t>
+  </si>
+  <si>
+    <t>334927720/1</t>
+  </si>
+  <si>
+    <t>334927757/1</t>
+  </si>
+  <si>
+    <t>334927827/1</t>
+  </si>
+  <si>
+    <t>334927929/1</t>
+  </si>
+  <si>
+    <t>334927929/2</t>
+  </si>
+  <si>
+    <t>334996372/1</t>
+  </si>
+  <si>
+    <t>334996671/1</t>
+  </si>
+  <si>
+    <t>334996713/1</t>
+  </si>
+  <si>
+    <t>334997053/1</t>
+  </si>
+  <si>
+    <t>335051652/1</t>
+  </si>
+  <si>
+    <t>441135352/1</t>
+  </si>
+  <si>
+    <t>99003611/1</t>
+  </si>
+  <si>
+    <t>99003613/1</t>
+  </si>
+  <si>
+    <t>99003614/1</t>
+  </si>
+  <si>
+    <t>99003619/1</t>
+  </si>
+  <si>
+    <t>99003620/1</t>
+  </si>
+  <si>
+    <t>159995579545579721</t>
+  </si>
+  <si>
+    <t>159995579545579042</t>
+  </si>
+  <si>
+    <t>159995579545578977</t>
+  </si>
+  <si>
+    <t>202610292602139701</t>
+  </si>
+  <si>
+    <t>202610272602144201</t>
+  </si>
+  <si>
+    <t>202610292602150801</t>
+  </si>
+  <si>
+    <t>202610292602150802</t>
+  </si>
+  <si>
+    <t>202610292602192601</t>
+  </si>
+  <si>
+    <t>202610292602192602</t>
+  </si>
+  <si>
+    <t>202610292602150401</t>
+  </si>
+  <si>
+    <t>202610292602203401</t>
+  </si>
+  <si>
+    <t>202610272602194501</t>
+  </si>
+  <si>
+    <t>202610292602203901</t>
+  </si>
+  <si>
+    <t>202610292602203902</t>
+  </si>
+  <si>
+    <t>202610292602205201</t>
+  </si>
+  <si>
+    <t>202610292602204801</t>
+  </si>
+  <si>
+    <t>202610292602204802</t>
+  </si>
+  <si>
+    <t>202610292602204901</t>
+  </si>
+  <si>
+    <t>202610292602204701</t>
+  </si>
+  <si>
+    <t>202610292602211901</t>
+  </si>
+  <si>
+    <t>202610292602214401</t>
+  </si>
+  <si>
+    <t>202610292602210301</t>
+  </si>
+  <si>
+    <t>202610292602210101</t>
+  </si>
+  <si>
+    <t>202610292602213401</t>
+  </si>
+  <si>
+    <t>202610292602211301</t>
+  </si>
+  <si>
+    <t>202610292602215101</t>
+  </si>
+  <si>
+    <t>202610292602209901</t>
+  </si>
+  <si>
+    <t>202610292602210401</t>
+  </si>
+  <si>
+    <t>202610272602152401</t>
+  </si>
+  <si>
+    <t>202610292602204501</t>
+  </si>
+  <si>
+    <t>202610292602205101</t>
+  </si>
+  <si>
+    <t>202610292602208501</t>
+  </si>
+  <si>
+    <t>202610292602215201</t>
+  </si>
+  <si>
+    <t>202610292602214901</t>
+  </si>
+  <si>
+    <t>159995579545520259</t>
+  </si>
+  <si>
+    <t>159995579545520266</t>
+  </si>
+  <si>
+    <t>159995579545520273</t>
+  </si>
+  <si>
+    <t>159995579545574382</t>
+  </si>
+  <si>
+    <t>159995579545574399</t>
+  </si>
+  <si>
+    <t>159995579545578212</t>
+  </si>
+  <si>
+    <t>159995579545578229</t>
+  </si>
+  <si>
+    <t>159995579545578564</t>
+  </si>
+  <si>
+    <t>6ae2f6bece19280a2197e92b</t>
+  </si>
+  <si>
+    <t>6ada030f2ed61dd3c9d4a4e8</t>
+  </si>
+  <si>
+    <t>6ada030f2ed61dd3c9d4a4ea</t>
+  </si>
+  <si>
+    <t>6ae1d98d8db5819914c2be93</t>
+  </si>
+  <si>
+    <t>6ae06cdd8db5819914c29e0d</t>
+  </si>
+  <si>
+    <t>6ae19c5a8db5819914c2b48b</t>
+  </si>
+  <si>
+    <t>6ae19c5a8db5819914c2b48c</t>
+  </si>
+  <si>
+    <t>6ae245188db5819914c2cc6f</t>
+  </si>
+  <si>
+    <t>6ae3193cce19280a2197ef3a</t>
+  </si>
+  <si>
+    <t>6ae3367fce19280a2197f3db</t>
+  </si>
+  <si>
+    <t>334811398/1</t>
+  </si>
+  <si>
+    <t>334811822/1</t>
+  </si>
+  <si>
+    <t>334811942/1</t>
+  </si>
+  <si>
+    <t>334812051/1</t>
+  </si>
+  <si>
+    <t>334873214/1</t>
+  </si>
+  <si>
+    <t>334873380/1</t>
+  </si>
+  <si>
+    <t>334873398/1</t>
+  </si>
+  <si>
+    <t>202610292602212801</t>
+  </si>
+  <si>
+    <t>6ae1ac758db5819914c2b5b1</t>
+  </si>
+  <si>
+    <t>6adf1a2f8db5819914c28005</t>
+  </si>
+  <si>
+    <t>6ae088f78db5819914c2a3a7</t>
+  </si>
+  <si>
+    <t>6ae0a6438db5819914c2a874</t>
+  </si>
+  <si>
+    <t>6ae0a9c78db5819914c2a902</t>
+  </si>
+  <si>
+    <t>6ae0a9c78db5819914c2a905</t>
+  </si>
+  <si>
+    <t>6ae1215a8db5819914c2b359</t>
+  </si>
+  <si>
+    <t>6ae1215a8db5819914c2b35a</t>
+  </si>
+  <si>
+    <t>6ae1bfb78db5819914c2b9a9</t>
+  </si>
+  <si>
+    <t>6ae1bfb78db5819914c2b9aa</t>
+  </si>
+  <si>
+    <t>6ae1e3d98db5819914c2c00e</t>
+  </si>
+  <si>
+    <t>6ae1b74d8db5819914c2b786</t>
+  </si>
+  <si>
+    <t>6ae1b74d8db5819914c2b787</t>
+  </si>
+  <si>
+    <t>26MPE0011687/1</t>
+  </si>
+  <si>
+    <t>334811537/1</t>
+  </si>
+  <si>
+    <t>334872966/1</t>
+  </si>
+  <si>
+    <t>334873079/1</t>
+  </si>
+  <si>
+    <t>334873393/1</t>
+  </si>
+  <si>
+    <t>SZ-815</t>
+  </si>
+  <si>
+    <t>K-991</t>
+  </si>
+  <si>
+    <t>K-951</t>
+  </si>
+  <si>
+    <t>K-931</t>
+  </si>
+  <si>
+    <t>K-942</t>
+  </si>
+  <si>
+    <t>SZ-819</t>
+  </si>
+  <si>
+    <t>SZ-829</t>
+  </si>
+  <si>
+    <t>K-9141</t>
+  </si>
+  <si>
+    <t>SZ-830</t>
+  </si>
+  <si>
+    <t>K-962</t>
+  </si>
+  <si>
+    <t>SZ-870</t>
+  </si>
+  <si>
+    <t>K-921</t>
+  </si>
+  <si>
+    <t>K-973</t>
+  </si>
+  <si>
+    <t>K-952</t>
+  </si>
+  <si>
+    <t>K-983</t>
+  </si>
+  <si>
+    <t>SZ-822</t>
+  </si>
+  <si>
+    <t>K-953</t>
+  </si>
+  <si>
+    <t>K-998</t>
+  </si>
+  <si>
+    <t>K-912</t>
+  </si>
+  <si>
+    <t>K-941</t>
+  </si>
+  <si>
+    <t>K-925</t>
+  </si>
+  <si>
+    <t>SZ-832</t>
+  </si>
+  <si>
+    <t>K-961</t>
+  </si>
+  <si>
+    <t>K-964</t>
+  </si>
+  <si>
+    <t>K-930</t>
+  </si>
+  <si>
+    <t>SZ-833</t>
+  </si>
+  <si>
+    <t>K-981</t>
+  </si>
+  <si>
+    <t>SZ-837</t>
+  </si>
+  <si>
+    <t>K-943</t>
+  </si>
+  <si>
+    <t>K-982</t>
+  </si>
+  <si>
+    <t>K-929</t>
+  </si>
+  <si>
+    <t>SZ-826</t>
+  </si>
+  <si>
+    <t>K-910</t>
+  </si>
+  <si>
+    <t>SZ-834</t>
+  </si>
+  <si>
+    <t>K-971</t>
+  </si>
+  <si>
+    <t>K-911</t>
+  </si>
+  <si>
+    <t>SZ-836</t>
+  </si>
+  <si>
+    <t>SZ-823</t>
+  </si>
+  <si>
+    <t>SZ-805</t>
+  </si>
+  <si>
+    <t>SZ-811</t>
+  </si>
+  <si>
+    <t>SZ-820</t>
+  </si>
+  <si>
+    <t>SZ-821</t>
+  </si>
+  <si>
+    <t>SZ-854</t>
+  </si>
+  <si>
+    <t>SZ-838</t>
+  </si>
+  <si>
+    <t>K-915</t>
+  </si>
+  <si>
+    <t>SZ-800</t>
+  </si>
+  <si>
+    <t>SZ-801</t>
+  </si>
+  <si>
+    <t>K-9121</t>
   </si>
 </sst>
 </file>
@@ -376,9 +2320,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -695,7 +2638,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC11F24F-E222-443E-8401-2ECBA69A40D4}">
   <sheetPr codeName="Munka1"/>
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C396"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -715,771 +2658,4348 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C3" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>310</v>
+      </c>
+      <c r="C5" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>311</v>
+      </c>
+      <c r="C6" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" t="s">
+        <v>313</v>
+      </c>
+      <c r="C8" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" t="s">
+        <v>314</v>
+      </c>
+      <c r="C9" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" t="s">
+        <v>316</v>
+      </c>
+      <c r="C11" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>317</v>
+      </c>
+      <c r="C12" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" t="s">
+        <v>318</v>
+      </c>
+      <c r="C13" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" t="s">
+        <v>319</v>
+      </c>
+      <c r="C14" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" t="s">
+        <v>320</v>
+      </c>
+      <c r="C15" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" t="s">
+        <v>321</v>
+      </c>
+      <c r="C16" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" t="s">
+        <v>322</v>
+      </c>
+      <c r="C17" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C18" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" t="s">
+        <v>324</v>
+      </c>
+      <c r="C19" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" t="s">
+        <v>325</v>
+      </c>
+      <c r="C20" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" t="s">
+        <v>326</v>
+      </c>
+      <c r="C21" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" t="s">
+        <v>327</v>
+      </c>
+      <c r="C22" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" t="s">
+        <v>328</v>
+      </c>
+      <c r="C23" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" t="s">
+        <v>329</v>
+      </c>
+      <c r="C24" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" t="s">
+        <v>330</v>
+      </c>
+      <c r="C25" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" t="s">
+        <v>331</v>
+      </c>
+      <c r="C26" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" t="s">
+        <v>332</v>
+      </c>
+      <c r="C27" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B28" t="s">
+        <v>333</v>
+      </c>
+      <c r="C28" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" t="s">
+        <v>334</v>
+      </c>
+      <c r="C29" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" t="s">
+        <v>335</v>
+      </c>
+      <c r="C30" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B31" t="s">
+        <v>336</v>
+      </c>
+      <c r="C31" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" t="s">
+        <v>337</v>
+      </c>
+      <c r="C32" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B33" t="s">
+        <v>338</v>
+      </c>
+      <c r="C33" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" t="s">
+        <v>339</v>
+      </c>
+      <c r="C34" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" t="s">
+        <v>340</v>
+      </c>
+      <c r="C35" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" t="s">
+        <v>341</v>
+      </c>
+      <c r="C36" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" t="s">
+        <v>343</v>
+      </c>
+      <c r="C38" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" t="s">
+        <v>344</v>
+      </c>
+      <c r="C39" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" t="s">
+        <v>345</v>
+      </c>
+      <c r="C40" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B41" t="s">
+        <v>346</v>
+      </c>
+      <c r="C41" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" t="s">
+        <v>347</v>
+      </c>
+      <c r="C42" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" t="s">
+        <v>348</v>
+      </c>
+      <c r="C43" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B44" t="s">
+        <v>349</v>
+      </c>
+      <c r="C44" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45" t="s">
+        <v>350</v>
+      </c>
+      <c r="C45" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>8</v>
       </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B46" t="s">
+        <v>351</v>
+      </c>
+      <c r="C46" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" t="s">
+        <v>352</v>
+      </c>
+      <c r="C47" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" t="s">
+        <v>353</v>
+      </c>
+      <c r="C48" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>9</v>
       </c>
-      <c r="C8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B49" t="s">
+        <v>354</v>
+      </c>
+      <c r="C49" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" t="s">
+        <v>355</v>
+      </c>
+      <c r="C50" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>52</v>
+      <c r="B51" t="s">
+        <v>356</v>
       </c>
       <c r="C51" t="s">
-        <v>71</v>
+        <v>723</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>53</v>
+      <c r="A52" t="s">
+        <v>121</v>
+      </c>
+      <c r="B52" t="s">
+        <v>357</v>
       </c>
       <c r="C52" t="s">
-        <v>71</v>
+        <v>724</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>54</v>
+      <c r="A53" t="s">
+        <v>122</v>
+      </c>
+      <c r="B53" t="s">
+        <v>358</v>
       </c>
       <c r="C53" t="s">
-        <v>71</v>
+        <v>705</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>55</v>
+      <c r="A54" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" t="s">
+        <v>359</v>
       </c>
       <c r="C54" t="s">
-        <v>71</v>
+        <v>725</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>56</v>
+      <c r="A55" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" t="s">
+        <v>360</v>
       </c>
       <c r="C55" t="s">
-        <v>71</v>
+        <v>715</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>57</v>
+      <c r="A56" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" t="s">
+        <v>361</v>
       </c>
       <c r="C56" t="s">
-        <v>71</v>
+        <v>719</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>58</v>
+      <c r="A57" t="s">
+        <v>125</v>
+      </c>
+      <c r="B57" t="s">
+        <v>362</v>
       </c>
       <c r="C57" t="s">
-        <v>71</v>
+        <v>719</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>59</v>
+      <c r="A58" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" t="s">
+        <v>363</v>
       </c>
       <c r="C58" t="s">
-        <v>71</v>
+        <v>706</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>60</v>
+      <c r="A59" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" t="s">
+        <v>364</v>
       </c>
       <c r="C59" t="s">
-        <v>71</v>
+        <v>706</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>61</v>
+      <c r="A60" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" t="s">
+        <v>365</v>
       </c>
       <c r="C60" t="s">
-        <v>71</v>
+        <v>706</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>62</v>
+      <c r="A61" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" t="s">
+        <v>366</v>
       </c>
       <c r="C61" t="s">
-        <v>71</v>
+        <v>715</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>63</v>
+      <c r="A62" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" t="s">
+        <v>367</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
+        <v>703</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>64</v>
+      <c r="A63" t="s">
+        <v>130</v>
+      </c>
+      <c r="B63" t="s">
+        <v>368</v>
       </c>
       <c r="C63" t="s">
-        <v>71</v>
+        <v>725</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>65</v>
+      <c r="A64" t="s">
+        <v>131</v>
+      </c>
+      <c r="B64" t="s">
+        <v>369</v>
       </c>
       <c r="C64" t="s">
-        <v>71</v>
+        <v>704</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>66</v>
+      <c r="A65" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" t="s">
+        <v>370</v>
       </c>
       <c r="C65" t="s">
-        <v>71</v>
+        <v>704</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>67</v>
+      <c r="A66" t="s">
+        <v>132</v>
+      </c>
+      <c r="B66" t="s">
+        <v>371</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
+        <v>726</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>68</v>
+      <c r="A67" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" t="s">
+        <v>372</v>
       </c>
       <c r="C67" t="s">
-        <v>71</v>
+        <v>724</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>69</v>
+      <c r="A68" t="s">
+        <v>134</v>
+      </c>
+      <c r="B68" t="s">
+        <v>373</v>
       </c>
       <c r="C68" t="s">
-        <v>71</v>
+        <v>703</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>70</v>
+      <c r="A69" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" t="s">
+        <v>374</v>
       </c>
       <c r="C69" t="s">
-        <v>71</v>
+        <v>716</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>136</v>
+      </c>
+      <c r="B70" t="s">
+        <v>375</v>
       </c>
       <c r="C70" t="s">
-        <v>87</v>
+        <v>706</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>137</v>
+      </c>
+      <c r="B71" t="s">
+        <v>376</v>
       </c>
       <c r="C71" t="s">
-        <v>87</v>
+        <v>725</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>137</v>
+      </c>
+      <c r="B72" t="s">
+        <v>377</v>
       </c>
       <c r="C72" t="s">
-        <v>87</v>
+        <v>725</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>138</v>
+      </c>
+      <c r="B73" t="s">
+        <v>378</v>
       </c>
       <c r="C73" t="s">
-        <v>87</v>
+        <v>721</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>139</v>
+      </c>
+      <c r="B74" t="s">
+        <v>379</v>
       </c>
       <c r="C74" t="s">
-        <v>87</v>
+        <v>725</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>139</v>
+      </c>
+      <c r="B75" t="s">
+        <v>380</v>
       </c>
       <c r="C75" t="s">
-        <v>87</v>
+        <v>725</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>140</v>
+      </c>
+      <c r="B76" t="s">
+        <v>381</v>
       </c>
       <c r="C76" t="s">
-        <v>87</v>
+        <v>725</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>141</v>
+      </c>
+      <c r="B77" t="s">
+        <v>382</v>
       </c>
       <c r="C77" t="s">
-        <v>87</v>
+        <v>722</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>11</v>
+      </c>
+      <c r="B78" t="s">
+        <v>383</v>
       </c>
       <c r="C78" t="s">
-        <v>87</v>
+        <v>727</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>142</v>
+      </c>
+      <c r="B79" t="s">
+        <v>384</v>
       </c>
       <c r="C79" t="s">
-        <v>87</v>
+        <v>728</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>143</v>
+      </c>
+      <c r="B80" t="s">
+        <v>385</v>
       </c>
       <c r="C80" t="s">
-        <v>87</v>
+        <v>705</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>144</v>
+      </c>
+      <c r="B81" t="s">
+        <v>386</v>
       </c>
       <c r="C81" t="s">
-        <v>87</v>
+        <v>714</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>144</v>
+      </c>
+      <c r="B82" t="s">
+        <v>387</v>
       </c>
       <c r="C82" t="s">
-        <v>87</v>
+        <v>714</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>12</v>
+      </c>
+      <c r="B83" t="s">
+        <v>388</v>
       </c>
       <c r="C83" t="s">
-        <v>87</v>
+        <v>729</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>145</v>
+      </c>
+      <c r="B84" t="s">
+        <v>389</v>
       </c>
       <c r="C84" t="s">
-        <v>87</v>
+        <v>724</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>146</v>
+      </c>
+      <c r="B85" t="s">
+        <v>390</v>
       </c>
       <c r="C85" t="s">
-        <v>101</v>
+        <v>730</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>146</v>
+      </c>
+      <c r="B86" t="s">
+        <v>391</v>
       </c>
       <c r="C86" t="s">
-        <v>101</v>
+        <v>730</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>147</v>
+      </c>
+      <c r="B87" t="s">
+        <v>392</v>
       </c>
       <c r="C87" t="s">
-        <v>101</v>
+        <v>716</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>148</v>
+      </c>
+      <c r="B88" t="s">
+        <v>393</v>
       </c>
       <c r="C88" t="s">
-        <v>101</v>
+        <v>721</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>149</v>
+      </c>
+      <c r="B89" t="s">
+        <v>394</v>
       </c>
       <c r="C89" t="s">
-        <v>101</v>
+        <v>724</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>149</v>
+      </c>
+      <c r="B90" t="s">
+        <v>395</v>
       </c>
       <c r="C90" t="s">
-        <v>101</v>
+        <v>724</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>149</v>
+      </c>
+      <c r="B91" t="s">
+        <v>396</v>
       </c>
       <c r="C91" t="s">
-        <v>101</v>
+        <v>724</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>150</v>
+      </c>
+      <c r="B92" t="s">
+        <v>397</v>
       </c>
       <c r="C92" t="s">
-        <v>101</v>
+        <v>706</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>151</v>
+      </c>
+      <c r="B93" t="s">
+        <v>398</v>
       </c>
       <c r="C93" t="s">
-        <v>101</v>
+        <v>728</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>13</v>
+      </c>
+      <c r="B94" t="s">
+        <v>399</v>
       </c>
       <c r="C94" t="s">
-        <v>101</v>
+        <v>708</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>152</v>
+      </c>
+      <c r="B95" t="s">
+        <v>400</v>
       </c>
       <c r="C95" t="s">
-        <v>101</v>
+        <v>718</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>99</v>
+        <v>153</v>
+      </c>
+      <c r="B96" t="s">
+        <v>401</v>
       </c>
       <c r="C96" t="s">
-        <v>101</v>
+        <v>731</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>14</v>
+      </c>
+      <c r="B97" t="s">
+        <v>402</v>
       </c>
       <c r="C97" t="s">
-        <v>101</v>
+        <v>712</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>14</v>
+      </c>
+      <c r="B98" t="s">
+        <v>403</v>
+      </c>
+      <c r="C98" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>154</v>
+      </c>
+      <c r="B99" t="s">
+        <v>404</v>
+      </c>
+      <c r="C99" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>155</v>
+      </c>
+      <c r="B100" t="s">
+        <v>405</v>
+      </c>
+      <c r="C100" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>156</v>
+      </c>
+      <c r="B101" t="s">
+        <v>406</v>
+      </c>
+      <c r="C101" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>157</v>
+      </c>
+      <c r="B102" t="s">
+        <v>407</v>
+      </c>
+      <c r="C102" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>158</v>
+      </c>
+      <c r="B103" t="s">
+        <v>408</v>
+      </c>
+      <c r="C103" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>159</v>
+      </c>
+      <c r="B104" t="s">
+        <v>409</v>
+      </c>
+      <c r="C104" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>410</v>
+      </c>
+      <c r="C105" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>160</v>
+      </c>
+      <c r="B106" t="s">
+        <v>411</v>
+      </c>
+      <c r="C106" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>161</v>
+      </c>
+      <c r="B107" t="s">
+        <v>412</v>
+      </c>
+      <c r="C107" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>162</v>
+      </c>
+      <c r="B108" t="s">
+        <v>413</v>
+      </c>
+      <c r="C108" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>162</v>
+      </c>
+      <c r="B109" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>16</v>
+      </c>
+      <c r="B110" t="s">
+        <v>415</v>
+      </c>
+      <c r="C110" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>163</v>
+      </c>
+      <c r="B111" t="s">
+        <v>416</v>
+      </c>
+      <c r="C111" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>17</v>
+      </c>
+      <c r="B112" t="s">
+        <v>417</v>
+      </c>
+      <c r="C112" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>164</v>
+      </c>
+      <c r="B113" t="s">
+        <v>418</v>
+      </c>
+      <c r="C113" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>165</v>
+      </c>
+      <c r="B114" t="s">
+        <v>419</v>
+      </c>
+      <c r="C114" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>165</v>
+      </c>
+      <c r="B115" t="s">
+        <v>420</v>
+      </c>
+      <c r="C115" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>166</v>
+      </c>
+      <c r="B116" t="s">
+        <v>421</v>
+      </c>
+      <c r="C116" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>166</v>
+      </c>
+      <c r="B117" t="s">
+        <v>422</v>
+      </c>
+      <c r="C117" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>167</v>
+      </c>
+      <c r="B118" t="s">
+        <v>423</v>
+      </c>
+      <c r="C118" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>168</v>
+      </c>
+      <c r="B119" t="s">
+        <v>424</v>
+      </c>
+      <c r="C119" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>169</v>
+      </c>
+      <c r="B120" t="s">
+        <v>425</v>
+      </c>
+      <c r="C120" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>170</v>
+      </c>
+      <c r="B121" t="s">
+        <v>426</v>
+      </c>
+      <c r="C121" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>18</v>
+      </c>
+      <c r="B122" t="s">
+        <v>427</v>
+      </c>
+      <c r="C122" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>19</v>
+      </c>
+      <c r="B123" t="s">
+        <v>428</v>
+      </c>
+      <c r="C123" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>171</v>
+      </c>
+      <c r="B124" t="s">
+        <v>429</v>
+      </c>
+      <c r="C124" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>171</v>
+      </c>
+      <c r="B125" t="s">
+        <v>430</v>
+      </c>
+      <c r="C125" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>172</v>
+      </c>
+      <c r="B126" t="s">
+        <v>431</v>
+      </c>
+      <c r="C126" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>172</v>
+      </c>
+      <c r="B127" t="s">
+        <v>432</v>
+      </c>
+      <c r="C127" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>173</v>
+      </c>
+      <c r="B128" t="s">
+        <v>433</v>
+      </c>
+      <c r="C128" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>174</v>
+      </c>
+      <c r="B129" t="s">
+        <v>434</v>
+      </c>
+      <c r="C129" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>175</v>
+      </c>
+      <c r="B130" t="s">
+        <v>435</v>
+      </c>
+      <c r="C130" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>176</v>
+      </c>
+      <c r="B131" t="s">
+        <v>436</v>
+      </c>
+      <c r="C131" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>177</v>
+      </c>
+      <c r="B132" t="s">
+        <v>437</v>
+      </c>
+      <c r="C132" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>178</v>
+      </c>
+      <c r="B133" t="s">
+        <v>438</v>
+      </c>
+      <c r="C133" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>179</v>
+      </c>
+      <c r="B134" t="s">
+        <v>439</v>
+      </c>
+      <c r="C134" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>20</v>
+      </c>
+      <c r="B135" t="s">
+        <v>440</v>
+      </c>
+      <c r="C135" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>21</v>
+      </c>
+      <c r="B136" t="s">
+        <v>441</v>
+      </c>
+      <c r="C136" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>180</v>
+      </c>
+      <c r="B137" t="s">
+        <v>442</v>
+      </c>
+      <c r="C137" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>181</v>
+      </c>
+      <c r="B138" t="s">
+        <v>443</v>
+      </c>
+      <c r="C138" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>181</v>
+      </c>
+      <c r="B139" t="s">
+        <v>444</v>
+      </c>
+      <c r="C139" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>182</v>
+      </c>
+      <c r="B140" t="s">
+        <v>445</v>
+      </c>
+      <c r="C140" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>182</v>
+      </c>
+      <c r="B141" t="s">
+        <v>446</v>
+      </c>
+      <c r="C141" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>22</v>
+      </c>
+      <c r="B142" t="s">
+        <v>447</v>
+      </c>
+      <c r="C142" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>22</v>
+      </c>
+      <c r="B143" t="s">
+        <v>448</v>
+      </c>
+      <c r="C143" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>183</v>
+      </c>
+      <c r="B144" t="s">
+        <v>449</v>
+      </c>
+      <c r="C144" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>184</v>
+      </c>
+      <c r="B145" t="s">
+        <v>450</v>
+      </c>
+      <c r="C145" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>184</v>
+      </c>
+      <c r="B146" t="s">
+        <v>451</v>
+      </c>
+      <c r="C146" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>23</v>
+      </c>
+      <c r="B147" t="s">
+        <v>452</v>
+      </c>
+      <c r="C147" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>185</v>
+      </c>
+      <c r="B148" t="s">
+        <v>453</v>
+      </c>
+      <c r="C148" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>186</v>
+      </c>
+      <c r="B149" t="s">
+        <v>454</v>
+      </c>
+      <c r="C149" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>187</v>
+      </c>
+      <c r="B150" t="s">
+        <v>455</v>
+      </c>
+      <c r="C150" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>187</v>
+      </c>
+      <c r="B151" t="s">
+        <v>456</v>
+      </c>
+      <c r="C151" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>188</v>
+      </c>
+      <c r="B152" t="s">
+        <v>457</v>
+      </c>
+      <c r="C152" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>189</v>
+      </c>
+      <c r="B153" t="s">
+        <v>458</v>
+      </c>
+      <c r="C153" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>189</v>
+      </c>
+      <c r="B154" t="s">
+        <v>459</v>
+      </c>
+      <c r="C154" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>189</v>
+      </c>
+      <c r="B155" t="s">
+        <v>460</v>
+      </c>
+      <c r="C155" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>190</v>
+      </c>
+      <c r="B156" t="s">
+        <v>461</v>
+      </c>
+      <c r="C156" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>190</v>
+      </c>
+      <c r="B157" t="s">
+        <v>462</v>
+      </c>
+      <c r="C157" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>191</v>
+      </c>
+      <c r="B158" t="s">
+        <v>463</v>
+      </c>
+      <c r="C158" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>191</v>
+      </c>
+      <c r="B159" t="s">
+        <v>464</v>
+      </c>
+      <c r="C159" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>192</v>
+      </c>
+      <c r="B160" t="s">
+        <v>465</v>
+      </c>
+      <c r="C160" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>24</v>
+      </c>
+      <c r="B161" t="s">
+        <v>466</v>
+      </c>
+      <c r="C161" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>24</v>
+      </c>
+      <c r="B162" t="s">
+        <v>467</v>
+      </c>
+      <c r="C162" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>193</v>
+      </c>
+      <c r="B163" t="s">
+        <v>468</v>
+      </c>
+      <c r="C163" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>193</v>
+      </c>
+      <c r="B164" t="s">
+        <v>469</v>
+      </c>
+      <c r="C164" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>194</v>
+      </c>
+      <c r="B165" t="s">
+        <v>470</v>
+      </c>
+      <c r="C165" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>194</v>
+      </c>
+      <c r="B166" t="s">
+        <v>471</v>
+      </c>
+      <c r="C166" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>195</v>
+      </c>
+      <c r="B167" t="s">
+        <v>472</v>
+      </c>
+      <c r="C167" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>195</v>
+      </c>
+      <c r="B168" t="s">
+        <v>473</v>
+      </c>
+      <c r="C168" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>196</v>
+      </c>
+      <c r="B169" t="s">
+        <v>474</v>
+      </c>
+      <c r="C169" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>25</v>
+      </c>
+      <c r="B170" t="s">
+        <v>475</v>
+      </c>
+      <c r="C170" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>25</v>
+      </c>
+      <c r="B171" t="s">
+        <v>476</v>
+      </c>
+      <c r="C171" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>197</v>
+      </c>
+      <c r="B172" t="s">
+        <v>477</v>
+      </c>
+      <c r="C172" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>197</v>
+      </c>
+      <c r="B173" t="s">
+        <v>478</v>
+      </c>
+      <c r="C173" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>26</v>
+      </c>
+      <c r="B174" t="s">
+        <v>479</v>
+      </c>
+      <c r="C174" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>198</v>
+      </c>
+      <c r="B175" t="s">
+        <v>480</v>
+      </c>
+      <c r="C175" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>198</v>
+      </c>
+      <c r="B176" t="s">
+        <v>481</v>
+      </c>
+      <c r="C176" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>199</v>
+      </c>
+      <c r="B177" t="s">
+        <v>482</v>
+      </c>
+      <c r="C177" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>200</v>
+      </c>
+      <c r="B178" t="s">
+        <v>483</v>
+      </c>
+      <c r="C178" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>201</v>
+      </c>
+      <c r="B179" t="s">
+        <v>484</v>
+      </c>
+      <c r="C179" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>27</v>
+      </c>
+      <c r="B180" t="s">
+        <v>485</v>
+      </c>
+      <c r="C180" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>28</v>
+      </c>
+      <c r="B181" t="s">
+        <v>486</v>
+      </c>
+      <c r="C181" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>202</v>
+      </c>
+      <c r="B182" t="s">
+        <v>487</v>
+      </c>
+      <c r="C182" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>203</v>
+      </c>
+      <c r="B183" t="s">
+        <v>488</v>
+      </c>
+      <c r="C183" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>203</v>
+      </c>
+      <c r="B184" t="s">
+        <v>489</v>
+      </c>
+      <c r="C184" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>204</v>
+      </c>
+      <c r="B185" t="s">
+        <v>490</v>
+      </c>
+      <c r="C185" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>205</v>
+      </c>
+      <c r="B186" t="s">
+        <v>491</v>
+      </c>
+      <c r="C186" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>206</v>
+      </c>
+      <c r="B187" t="s">
+        <v>492</v>
+      </c>
+      <c r="C187" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>207</v>
+      </c>
+      <c r="B188" t="s">
+        <v>493</v>
+      </c>
+      <c r="C188" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>207</v>
+      </c>
+      <c r="B189" t="s">
+        <v>494</v>
+      </c>
+      <c r="C189" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>208</v>
+      </c>
+      <c r="B190" t="s">
+        <v>495</v>
+      </c>
+      <c r="C190" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>209</v>
+      </c>
+      <c r="B191" t="s">
+        <v>496</v>
+      </c>
+      <c r="C191" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>210</v>
+      </c>
+      <c r="B192" t="s">
+        <v>497</v>
+      </c>
+      <c r="C192" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>210</v>
+      </c>
+      <c r="B193" t="s">
+        <v>498</v>
+      </c>
+      <c r="C193" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>211</v>
+      </c>
+      <c r="B194" t="s">
+        <v>499</v>
+      </c>
+      <c r="C194" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>212</v>
+      </c>
+      <c r="B195" t="s">
+        <v>500</v>
+      </c>
+      <c r="C195" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>213</v>
+      </c>
+      <c r="B196" t="s">
+        <v>501</v>
+      </c>
+      <c r="C196" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>29</v>
+      </c>
+      <c r="B197" t="s">
+        <v>502</v>
+      </c>
+      <c r="C197" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>30</v>
+      </c>
+      <c r="B198" t="s">
+        <v>503</v>
+      </c>
+      <c r="C198" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>214</v>
+      </c>
+      <c r="B199" t="s">
+        <v>504</v>
+      </c>
+      <c r="C199" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>214</v>
+      </c>
+      <c r="B200" t="s">
+        <v>505</v>
+      </c>
+      <c r="C200" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>215</v>
+      </c>
+      <c r="B201" t="s">
+        <v>506</v>
+      </c>
+      <c r="C201" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>216</v>
+      </c>
+      <c r="B202" t="s">
+        <v>507</v>
+      </c>
+      <c r="C202" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>217</v>
+      </c>
+      <c r="B203" t="s">
+        <v>508</v>
+      </c>
+      <c r="C203" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>218</v>
+      </c>
+      <c r="B204" t="s">
+        <v>509</v>
+      </c>
+      <c r="C204" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>219</v>
+      </c>
+      <c r="B205" t="s">
+        <v>510</v>
+      </c>
+      <c r="C205" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>220</v>
+      </c>
+      <c r="B206" t="s">
+        <v>511</v>
+      </c>
+      <c r="C206" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>31</v>
+      </c>
+      <c r="B207" t="s">
+        <v>512</v>
+      </c>
+      <c r="C207" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>31</v>
+      </c>
+      <c r="B208" t="s">
+        <v>513</v>
+      </c>
+      <c r="C208" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>221</v>
+      </c>
+      <c r="B209" t="s">
+        <v>514</v>
+      </c>
+      <c r="C209" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>222</v>
+      </c>
+      <c r="B210" t="s">
+        <v>515</v>
+      </c>
+      <c r="C210" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>223</v>
+      </c>
+      <c r="B211" t="s">
+        <v>516</v>
+      </c>
+      <c r="C211" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>224</v>
+      </c>
+      <c r="B212" t="s">
+        <v>517</v>
+      </c>
+      <c r="C212" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>225</v>
+      </c>
+      <c r="B213" t="s">
+        <v>518</v>
+      </c>
+      <c r="C213" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>226</v>
+      </c>
+      <c r="B214" t="s">
+        <v>519</v>
+      </c>
+      <c r="C214" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>226</v>
+      </c>
+      <c r="B215" t="s">
+        <v>520</v>
+      </c>
+      <c r="C215" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>227</v>
+      </c>
+      <c r="B216" t="s">
+        <v>521</v>
+      </c>
+      <c r="C216" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>228</v>
+      </c>
+      <c r="B217" t="s">
+        <v>522</v>
+      </c>
+      <c r="C217" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>229</v>
+      </c>
+      <c r="B218" t="s">
+        <v>523</v>
+      </c>
+      <c r="C218" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>230</v>
+      </c>
+      <c r="B219" t="s">
+        <v>524</v>
+      </c>
+      <c r="C219" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>231</v>
+      </c>
+      <c r="B220" t="s">
+        <v>525</v>
+      </c>
+      <c r="C220" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>232</v>
+      </c>
+      <c r="B221" t="s">
+        <v>526</v>
+      </c>
+      <c r="C221" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>233</v>
+      </c>
+      <c r="B222" t="s">
+        <v>527</v>
+      </c>
+      <c r="C222" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>234</v>
+      </c>
+      <c r="B223" t="s">
+        <v>528</v>
+      </c>
+      <c r="C223" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>234</v>
+      </c>
+      <c r="B224" t="s">
+        <v>529</v>
+      </c>
+      <c r="C224" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>235</v>
+      </c>
+      <c r="B225" t="s">
+        <v>530</v>
+      </c>
+      <c r="C225" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>236</v>
+      </c>
+      <c r="B226" t="s">
+        <v>531</v>
+      </c>
+      <c r="C226" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>237</v>
+      </c>
+      <c r="B227" t="s">
+        <v>532</v>
+      </c>
+      <c r="C227" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>238</v>
+      </c>
+      <c r="B228" t="s">
+        <v>533</v>
+      </c>
+      <c r="C228" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>239</v>
+      </c>
+      <c r="B229" t="s">
+        <v>534</v>
+      </c>
+      <c r="C229" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>240</v>
+      </c>
+      <c r="B230" t="s">
+        <v>535</v>
+      </c>
+      <c r="C230" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>241</v>
+      </c>
+      <c r="B231" t="s">
+        <v>536</v>
+      </c>
+      <c r="C231" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>241</v>
+      </c>
+      <c r="B232" t="s">
+        <v>537</v>
+      </c>
+      <c r="C232" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>242</v>
+      </c>
+      <c r="B233" t="s">
+        <v>538</v>
+      </c>
+      <c r="C233" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>242</v>
+      </c>
+      <c r="B234" t="s">
+        <v>539</v>
+      </c>
+      <c r="C234" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>32</v>
+      </c>
+      <c r="B235" t="s">
+        <v>540</v>
+      </c>
+      <c r="C235" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>243</v>
+      </c>
+      <c r="B236" t="s">
+        <v>541</v>
+      </c>
+      <c r="C236" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>33</v>
+      </c>
+      <c r="B237" t="s">
+        <v>542</v>
+      </c>
+      <c r="C237" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>33</v>
+      </c>
+      <c r="B238" t="s">
+        <v>543</v>
+      </c>
+      <c r="C238" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>33</v>
+      </c>
+      <c r="B239" t="s">
+        <v>544</v>
+      </c>
+      <c r="C239" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>33</v>
+      </c>
+      <c r="B240" t="s">
+        <v>545</v>
+      </c>
+      <c r="C240" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>34</v>
+      </c>
+      <c r="B241" t="s">
+        <v>546</v>
+      </c>
+      <c r="C241" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>244</v>
+      </c>
+      <c r="B242" t="s">
+        <v>547</v>
+      </c>
+      <c r="C242" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>245</v>
+      </c>
+      <c r="B243" t="s">
+        <v>548</v>
+      </c>
+      <c r="C243" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>35</v>
+      </c>
+      <c r="B244" t="s">
+        <v>549</v>
+      </c>
+      <c r="C244" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>35</v>
+      </c>
+      <c r="B245" t="s">
+        <v>550</v>
+      </c>
+      <c r="C245" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>246</v>
+      </c>
+      <c r="B246" t="s">
+        <v>551</v>
+      </c>
+      <c r="C246" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>247</v>
+      </c>
+      <c r="B247" t="s">
+        <v>552</v>
+      </c>
+      <c r="C247" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>553</v>
+      </c>
+      <c r="C248" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>554</v>
+      </c>
+      <c r="C249" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>248</v>
+      </c>
+      <c r="B250" t="s">
+        <v>555</v>
+      </c>
+      <c r="C250" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>248</v>
+      </c>
+      <c r="B251" t="s">
+        <v>556</v>
+      </c>
+      <c r="C251" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>249</v>
+      </c>
+      <c r="B252" t="s">
+        <v>557</v>
+      </c>
+      <c r="C252" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>36</v>
+      </c>
+      <c r="B253" t="s">
+        <v>558</v>
+      </c>
+      <c r="C253" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>37</v>
+      </c>
+      <c r="B254" t="s">
+        <v>559</v>
+      </c>
+      <c r="C254" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>38</v>
+      </c>
+      <c r="B255" t="s">
+        <v>560</v>
+      </c>
+      <c r="C255" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>39</v>
+      </c>
+      <c r="B256" t="s">
+        <v>561</v>
+      </c>
+      <c r="C256" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>39</v>
+      </c>
+      <c r="B257" t="s">
+        <v>562</v>
+      </c>
+      <c r="C257" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>39</v>
+      </c>
+      <c r="B258" t="s">
+        <v>563</v>
+      </c>
+      <c r="C258" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>39</v>
+      </c>
+      <c r="B259" t="s">
+        <v>564</v>
+      </c>
+      <c r="C259" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>40</v>
+      </c>
+      <c r="B260" t="s">
+        <v>565</v>
+      </c>
+      <c r="C260" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>41</v>
+      </c>
+      <c r="B261" t="s">
+        <v>566</v>
+      </c>
+      <c r="C261" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>41</v>
+      </c>
+      <c r="B262" t="s">
+        <v>567</v>
+      </c>
+      <c r="C262" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>41</v>
+      </c>
+      <c r="B263" t="s">
+        <v>568</v>
+      </c>
+      <c r="C263" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>42</v>
+      </c>
+      <c r="B264" t="s">
+        <v>569</v>
+      </c>
+      <c r="C264" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>43</v>
+      </c>
+      <c r="B265" t="s">
+        <v>570</v>
+      </c>
+      <c r="C265" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>44</v>
+      </c>
+      <c r="B266" t="s">
+        <v>571</v>
+      </c>
+      <c r="C266" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>44</v>
+      </c>
+      <c r="B267" t="s">
+        <v>572</v>
+      </c>
+      <c r="C267" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>44</v>
+      </c>
+      <c r="B268" t="s">
+        <v>573</v>
+      </c>
+      <c r="C268" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>45</v>
+      </c>
+      <c r="B269" t="s">
+        <v>574</v>
+      </c>
+      <c r="C269" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>46</v>
+      </c>
+      <c r="B270" t="s">
+        <v>575</v>
+      </c>
+      <c r="C270" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>47</v>
+      </c>
+      <c r="B271" t="s">
+        <v>576</v>
+      </c>
+      <c r="C271" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>48</v>
+      </c>
+      <c r="B272" t="s">
+        <v>577</v>
+      </c>
+      <c r="C272" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>49</v>
+      </c>
+      <c r="B273" t="s">
+        <v>578</v>
+      </c>
+      <c r="C273" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>50</v>
+      </c>
+      <c r="B274" t="s">
+        <v>579</v>
+      </c>
+      <c r="C274" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>51</v>
+      </c>
+      <c r="B275" t="s">
+        <v>580</v>
+      </c>
+      <c r="C275" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>250</v>
+      </c>
+      <c r="B276" t="s">
+        <v>581</v>
+      </c>
+      <c r="C276" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>251</v>
+      </c>
+      <c r="B277" t="s">
+        <v>582</v>
+      </c>
+      <c r="C277" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>52</v>
+      </c>
+      <c r="B278" t="s">
+        <v>583</v>
+      </c>
+      <c r="C278" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>52</v>
+      </c>
+      <c r="B279" t="s">
+        <v>584</v>
+      </c>
+      <c r="C279" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>252</v>
+      </c>
+      <c r="B280" t="s">
+        <v>585</v>
+      </c>
+      <c r="C280" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>53</v>
+      </c>
+      <c r="B281" t="s">
+        <v>586</v>
+      </c>
+      <c r="C281" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>54</v>
+      </c>
+      <c r="B282" t="s">
+        <v>587</v>
+      </c>
+      <c r="C282" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>55</v>
+      </c>
+      <c r="B283" t="s">
+        <v>588</v>
+      </c>
+      <c r="C283" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>253</v>
+      </c>
+      <c r="B284" t="s">
+        <v>589</v>
+      </c>
+      <c r="C284" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>56</v>
+      </c>
+      <c r="B285" t="s">
+        <v>590</v>
+      </c>
+      <c r="C285" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>57</v>
+      </c>
+      <c r="B286" t="s">
+        <v>591</v>
+      </c>
+      <c r="C286" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>254</v>
+      </c>
+      <c r="B287" t="s">
+        <v>592</v>
+      </c>
+      <c r="C287" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>58</v>
+      </c>
+      <c r="B288" t="s">
+        <v>593</v>
+      </c>
+      <c r="C288" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>59</v>
+      </c>
+      <c r="B289" t="s">
+        <v>594</v>
+      </c>
+      <c r="C289" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>60</v>
+      </c>
+      <c r="B290" t="s">
+        <v>595</v>
+      </c>
+      <c r="C290" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>61</v>
+      </c>
+      <c r="B291" t="s">
+        <v>596</v>
+      </c>
+      <c r="C291" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>62</v>
+      </c>
+      <c r="B292" t="s">
+        <v>597</v>
+      </c>
+      <c r="C292" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>62</v>
+      </c>
+      <c r="B293" t="s">
+        <v>598</v>
+      </c>
+      <c r="C293" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>63</v>
+      </c>
+      <c r="B294" t="s">
+        <v>599</v>
+      </c>
+      <c r="C294" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>64</v>
+      </c>
+      <c r="B295" t="s">
+        <v>600</v>
+      </c>
+      <c r="C295" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>65</v>
+      </c>
+      <c r="B296" t="s">
+        <v>601</v>
+      </c>
+      <c r="C296" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>66</v>
+      </c>
+      <c r="B297" t="s">
+        <v>602</v>
+      </c>
+      <c r="C297" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>255</v>
+      </c>
+      <c r="B298" t="s">
+        <v>603</v>
+      </c>
+      <c r="C298" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>256</v>
+      </c>
+      <c r="B299" t="s">
+        <v>604</v>
+      </c>
+      <c r="C299" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>256</v>
+      </c>
+      <c r="B300" t="s">
+        <v>605</v>
+      </c>
+      <c r="C300" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>257</v>
+      </c>
+      <c r="B301" t="s">
+        <v>606</v>
+      </c>
+      <c r="C301" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>258</v>
+      </c>
+      <c r="B302" t="s">
+        <v>607</v>
+      </c>
+      <c r="C302" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>259</v>
+      </c>
+      <c r="B303" t="s">
+        <v>608</v>
+      </c>
+      <c r="C303" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>260</v>
+      </c>
+      <c r="B304" t="s">
+        <v>609</v>
+      </c>
+      <c r="C304" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>261</v>
+      </c>
+      <c r="B305" t="s">
+        <v>610</v>
+      </c>
+      <c r="C305" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>262</v>
+      </c>
+      <c r="B306" t="s">
+        <v>611</v>
+      </c>
+      <c r="C306" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>262</v>
+      </c>
+      <c r="B307" t="s">
+        <v>612</v>
+      </c>
+      <c r="C307" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>263</v>
+      </c>
+      <c r="B308" t="s">
+        <v>613</v>
+      </c>
+      <c r="C308" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>264</v>
+      </c>
+      <c r="B309" t="s">
+        <v>614</v>
+      </c>
+      <c r="C309" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>265</v>
+      </c>
+      <c r="B310" t="s">
+        <v>615</v>
+      </c>
+      <c r="C310" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>266</v>
+      </c>
+      <c r="B311" t="s">
+        <v>616</v>
+      </c>
+      <c r="C311" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>267</v>
+      </c>
+      <c r="B312" t="s">
+        <v>617</v>
+      </c>
+      <c r="C312" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>268</v>
+      </c>
+      <c r="B313" t="s">
+        <v>618</v>
+      </c>
+      <c r="C313" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>269</v>
+      </c>
+      <c r="B314" t="s">
+        <v>619</v>
+      </c>
+      <c r="C314" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>270</v>
+      </c>
+      <c r="B315" t="s">
+        <v>620</v>
+      </c>
+      <c r="C315" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>67</v>
+      </c>
+      <c r="B316" t="s">
+        <v>621</v>
+      </c>
+      <c r="C316" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>68</v>
+      </c>
+      <c r="B317" t="s">
+        <v>622</v>
+      </c>
+      <c r="C317" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>69</v>
+      </c>
+      <c r="B318" t="s">
+        <v>623</v>
+      </c>
+      <c r="C318" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>271</v>
+      </c>
+      <c r="B319" t="s">
+        <v>624</v>
+      </c>
+      <c r="C319" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>272</v>
+      </c>
+      <c r="B320" t="s">
+        <v>625</v>
+      </c>
+      <c r="C320" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>273</v>
+      </c>
+      <c r="B321" t="s">
+        <v>626</v>
+      </c>
+      <c r="C321" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>274</v>
+      </c>
+      <c r="B322" t="s">
+        <v>627</v>
+      </c>
+      <c r="C322" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>275</v>
+      </c>
+      <c r="B323" t="s">
+        <v>628</v>
+      </c>
+      <c r="C323" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>276</v>
+      </c>
+      <c r="B324" t="s">
+        <v>629</v>
+      </c>
+      <c r="C324" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>276</v>
+      </c>
+      <c r="B325" t="s">
+        <v>630</v>
+      </c>
+      <c r="C325" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>277</v>
+      </c>
+      <c r="B326" t="s">
+        <v>631</v>
+      </c>
+      <c r="C326" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>277</v>
+      </c>
+      <c r="B327" t="s">
+        <v>632</v>
+      </c>
+      <c r="C327" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>278</v>
+      </c>
+      <c r="B328" t="s">
+        <v>633</v>
+      </c>
+      <c r="C328" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>279</v>
+      </c>
+      <c r="B329" t="s">
+        <v>634</v>
+      </c>
+      <c r="C329" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>280</v>
+      </c>
+      <c r="B330" t="s">
+        <v>635</v>
+      </c>
+      <c r="C330" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>281</v>
+      </c>
+      <c r="B331" t="s">
+        <v>636</v>
+      </c>
+      <c r="C331" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>281</v>
+      </c>
+      <c r="B332" t="s">
+        <v>637</v>
+      </c>
+      <c r="C332" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>282</v>
+      </c>
+      <c r="B333" t="s">
+        <v>638</v>
+      </c>
+      <c r="C333" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>283</v>
+      </c>
+      <c r="B334" t="s">
+        <v>639</v>
+      </c>
+      <c r="C334" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>283</v>
+      </c>
+      <c r="B335" t="s">
+        <v>640</v>
+      </c>
+      <c r="C335" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>284</v>
+      </c>
+      <c r="B336" t="s">
+        <v>641</v>
+      </c>
+      <c r="C336" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>285</v>
+      </c>
+      <c r="B337" t="s">
+        <v>642</v>
+      </c>
+      <c r="C337" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>286</v>
+      </c>
+      <c r="B338" t="s">
+        <v>643</v>
+      </c>
+      <c r="C338" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>287</v>
+      </c>
+      <c r="B339" t="s">
+        <v>644</v>
+      </c>
+      <c r="C339" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>288</v>
+      </c>
+      <c r="B340" t="s">
+        <v>645</v>
+      </c>
+      <c r="C340" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>289</v>
+      </c>
+      <c r="B341" t="s">
+        <v>646</v>
+      </c>
+      <c r="C341" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>290</v>
+      </c>
+      <c r="B342" t="s">
+        <v>647</v>
+      </c>
+      <c r="C342" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>291</v>
+      </c>
+      <c r="B343" t="s">
+        <v>648</v>
+      </c>
+      <c r="C343" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>292</v>
+      </c>
+      <c r="B344" t="s">
+        <v>649</v>
+      </c>
+      <c r="C344" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>293</v>
+      </c>
+      <c r="B345" t="s">
+        <v>650</v>
+      </c>
+      <c r="C345" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>294</v>
+      </c>
+      <c r="B346" t="s">
+        <v>651</v>
+      </c>
+      <c r="C346" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>295</v>
+      </c>
+      <c r="B347" t="s">
+        <v>652</v>
+      </c>
+      <c r="C347" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>296</v>
+      </c>
+      <c r="B348" t="s">
+        <v>653</v>
+      </c>
+      <c r="C348" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>297</v>
+      </c>
+      <c r="B349" t="s">
+        <v>654</v>
+      </c>
+      <c r="C349" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>298</v>
+      </c>
+      <c r="B350" t="s">
+        <v>655</v>
+      </c>
+      <c r="C350" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>299</v>
+      </c>
+      <c r="B351" t="s">
+        <v>656</v>
+      </c>
+      <c r="C351" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>300</v>
+      </c>
+      <c r="B352" t="s">
+        <v>657</v>
+      </c>
+      <c r="C352" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>301</v>
+      </c>
+      <c r="B353" t="s">
+        <v>658</v>
+      </c>
+      <c r="C353" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>301</v>
+      </c>
+      <c r="B354" t="s">
+        <v>659</v>
+      </c>
+      <c r="C354" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>301</v>
+      </c>
+      <c r="B355" t="s">
+        <v>660</v>
+      </c>
+      <c r="C355" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>302</v>
+      </c>
+      <c r="B356" t="s">
+        <v>661</v>
+      </c>
+      <c r="C356" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>302</v>
+      </c>
+      <c r="B357" t="s">
+        <v>662</v>
+      </c>
+      <c r="C357" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>303</v>
+      </c>
+      <c r="B358" t="s">
+        <v>663</v>
+      </c>
+      <c r="C358" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>303</v>
+      </c>
+      <c r="B359" t="s">
+        <v>664</v>
+      </c>
+      <c r="C359" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>304</v>
+      </c>
+      <c r="B360" t="s">
+        <v>665</v>
+      </c>
+      <c r="C360" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>75</v>
+      </c>
+      <c r="B361" t="s">
+        <v>666</v>
+      </c>
+      <c r="C361" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>72</v>
+      </c>
+      <c r="B362" t="s">
+        <v>667</v>
+      </c>
+      <c r="C362" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>72</v>
+      </c>
+      <c r="B363" t="s">
+        <v>668</v>
+      </c>
+      <c r="C363" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>71</v>
+      </c>
+      <c r="B364" t="s">
+        <v>669</v>
+      </c>
+      <c r="C364" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>73</v>
+      </c>
+      <c r="B365" t="s">
+        <v>670</v>
+      </c>
+      <c r="C365" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>70</v>
+      </c>
+      <c r="B366" t="s">
+        <v>671</v>
+      </c>
+      <c r="C366" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>70</v>
+      </c>
+      <c r="B367" t="s">
+        <v>672</v>
+      </c>
+      <c r="C367" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>74</v>
+      </c>
+      <c r="B368" t="s">
+        <v>673</v>
+      </c>
+      <c r="C368" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>76</v>
+      </c>
+      <c r="B369" t="s">
+        <v>674</v>
+      </c>
+      <c r="C369" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>84</v>
+      </c>
+      <c r="B370" t="s">
+        <v>675</v>
+      </c>
+      <c r="C370" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>82</v>
+      </c>
+      <c r="B371" t="s">
+        <v>676</v>
+      </c>
+      <c r="C371" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>81</v>
+      </c>
+      <c r="B372" t="s">
+        <v>677</v>
+      </c>
+      <c r="C372" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>77</v>
+      </c>
+      <c r="B373" t="s">
+        <v>678</v>
+      </c>
+      <c r="C373" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>79</v>
+      </c>
+      <c r="B374" t="s">
+        <v>679</v>
+      </c>
+      <c r="C374" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>78</v>
+      </c>
+      <c r="B375" t="s">
+        <v>680</v>
+      </c>
+      <c r="C375" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>83</v>
+      </c>
+      <c r="B376" t="s">
+        <v>681</v>
+      </c>
+      <c r="C376" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>80</v>
+      </c>
+      <c r="B377" t="s">
+        <v>682</v>
+      </c>
+      <c r="C377" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>305</v>
+      </c>
+      <c r="B378" t="s">
+        <v>683</v>
+      </c>
+      <c r="C378" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>91</v>
+      </c>
+      <c r="B379" t="s">
+        <v>684</v>
+      </c>
+      <c r="C379" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>86</v>
+      </c>
+      <c r="B380" t="s">
+        <v>685</v>
+      </c>
+      <c r="C380" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>87</v>
+      </c>
+      <c r="B381" t="s">
+        <v>686</v>
+      </c>
+      <c r="C381" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>88</v>
+      </c>
+      <c r="B382" t="s">
+        <v>687</v>
+      </c>
+      <c r="C382" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>89</v>
+      </c>
+      <c r="B383" t="s">
+        <v>688</v>
+      </c>
+      <c r="C383" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>89</v>
+      </c>
+      <c r="B384" t="s">
+        <v>689</v>
+      </c>
+      <c r="C384" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>90</v>
+      </c>
+      <c r="B385" t="s">
+        <v>690</v>
+      </c>
+      <c r="C385" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>90</v>
+      </c>
+      <c r="B386" t="s">
+        <v>691</v>
+      </c>
+      <c r="C386" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>93</v>
+      </c>
+      <c r="B387" t="s">
+        <v>692</v>
+      </c>
+      <c r="C387" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>93</v>
+      </c>
+      <c r="B388" t="s">
+        <v>693</v>
+      </c>
+      <c r="C388" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>94</v>
+      </c>
+      <c r="B389" t="s">
+        <v>694</v>
+      </c>
+      <c r="C389" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>92</v>
+      </c>
+      <c r="B390" t="s">
+        <v>695</v>
+      </c>
+      <c r="C390" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>92</v>
+      </c>
+      <c r="B391" t="s">
+        <v>696</v>
+      </c>
+      <c r="C391" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>306</v>
+      </c>
+      <c r="B392" t="s">
+        <v>697</v>
+      </c>
+      <c r="C392" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>95</v>
+      </c>
+      <c r="B393" t="s">
+        <v>698</v>
+      </c>
+      <c r="C393" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>97</v>
+      </c>
+      <c r="B394" t="s">
+        <v>699</v>
+      </c>
+      <c r="C394" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>96</v>
+      </c>
+      <c r="B395" t="s">
+        <v>700</v>
+      </c>
+      <c r="C395" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>98</v>
+      </c>
+      <c r="B396" t="s">
+        <v>701</v>
+      </c>
+      <c r="C396" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
